--- a/reports/screener_2026-08-24.xlsx
+++ b/reports/screener_2026-08-24.xlsx
@@ -1174,7 +1174,7 @@
         <v>-26.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>-8.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="BU2" t="n">
         <v>1.38</v>
@@ -1186,10 +1186,10 @@
         <v>10.15999984741211</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.739092621841178</v>
+        <v>5.738884128649667</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.64601681351538</v>
+        <v>10.64563005864513</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.29447790742652</v>
@@ -1198,7 +1198,7 @@
         <v>27.67799880047428</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.39487558802398</v>
+        <v>71.39398021848989</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1504,10 +1504,10 @@
         <v>13.67000007629395</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.08411226503859</v>
+        <v>15.08411221122868</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.98102825164658</v>
+        <v>27.9810281518292</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.78533212224727</v>
@@ -1516,13 +1516,13 @@
         <v>23.4303842936706</v>
       </c>
       <c r="CB3" t="n">
-        <v>73.80863252004175</v>
+        <v>73.80863262284781</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.30691180760066</v>
+        <v>48.30691184730974</v>
       </c>
       <c r="CD3" t="n">
-        <v>25.78976650113605</v>
+        <v>25.78976666715468</v>
       </c>
       <c r="CE3" t="n">
         <v>8.630044464581562</v>
@@ -1822,10 +1822,10 @@
         <v>23.51000022888184</v>
       </c>
       <c r="BX4" t="n">
-        <v>15.55616503941216</v>
+        <v>15.55616502675489</v>
       </c>
       <c r="BY4" t="n">
-        <v>28.85668614810956</v>
+        <v>28.85668612463031</v>
       </c>
       <c r="BZ4" t="n">
         <v>71.12043448234802</v>
@@ -1834,13 +1834,13 @@
         <v>51.51277527306067</v>
       </c>
       <c r="CB4" t="n">
-        <v>127.4881988874577</v>
+        <v>127.4881988902025</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.80183479027916</v>
+        <v>25.80183479209307</v>
       </c>
       <c r="CD4" t="n">
-        <v>63.22015025477451</v>
+        <v>63.22015028192994</v>
       </c>
       <c r="CE4" t="n">
         <v>41.54649601907847</v>
@@ -2128,22 +2128,22 @@
         <v>-60.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>-26.2</v>
+        <v>-25.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW5" t="n">
         <v>6.900000095367432</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.115400812167315</v>
+        <v>3.115400814292661</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.779068506570369</v>
+        <v>5.779068510512887</v>
       </c>
       <c r="BZ5" t="n">
         <v>19.83188747583914</v>
@@ -2152,7 +2152,7 @@
         <v>13.5801516746889</v>
       </c>
       <c r="CB5" t="n">
-        <v>31.91228043402471</v>
+        <v>31.91228044047912</v>
       </c>
       <c r="CC5" t="n">
         <v>10.95072400487419</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="CX5" t="n">
-        <v>7.5</v>
+        <v>7.360000133514404</v>
       </c>
       <c r="CY5" t="n">
-        <v>-7.999998728434243</v>
+        <v>-6.250000404922851</v>
       </c>
       <c r="CZ5" t="n">
         <v>-60.30064258156551</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.3%))</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
         <v>0.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>51.56</v>
+        <v>51.57</v>
       </c>
       <c r="BJ6" t="n">
         <v>-14</v>
@@ -2444,22 +2444,22 @@
         <v>-37.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>-23.8</v>
+        <v>-23.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BW6" t="n">
         <v>4.179999828338623</v>
       </c>
       <c r="BX6" t="n">
-        <v>3.539168753431935</v>
+        <v>3.539319177617177</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.565158037616239</v>
+        <v>6.565437074479863</v>
       </c>
       <c r="BZ6" t="n">
         <v>12.73218338516937</v>
@@ -2468,25 +2468,25 @@
         <v>8.571766632368943</v>
       </c>
       <c r="CB6" t="n">
-        <v>24.5715721600935</v>
+        <v>24.57145988209843</v>
       </c>
       <c r="CC6" t="n">
-        <v>11.28769658477398</v>
+        <v>11.28763497763521</v>
       </c>
       <c r="CD6" t="n">
-        <v>10.85231831601691</v>
+        <v>10.85194343487941</v>
       </c>
       <c r="CE6" t="n">
         <v>5.170088126502553</v>
       </c>
       <c r="CF6" t="n">
-        <v>9.196535180407999</v>
+        <v>9.196508938505891</v>
       </c>
       <c r="CG6" t="n">
-        <v>9.712042474192923</v>
+        <v>9.711855033624179</v>
       </c>
       <c r="CH6" t="n">
-        <v>8.740838226773631</v>
+        <v>8.740669530261762</v>
       </c>
       <c r="CI6" t="n">
         <v>6</v>
@@ -2498,10 +2498,10 @@
         <v>6.9</v>
       </c>
       <c r="CL6" t="n">
-        <v>109.1109709506317</v>
+        <v>109.1069351487465</v>
       </c>
       <c r="CM6" t="n">
-        <v>120.0128123943785</v>
+        <v>120.0121845976516</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         <v>46.56999969482422</v>
       </c>
       <c r="BX7" t="n">
-        <v>17.74536425554052</v>
+        <v>17.74536429240872</v>
       </c>
       <c r="BY7" t="n">
-        <v>32.91765069402766</v>
+        <v>32.91765076241818</v>
       </c>
       <c r="BZ7" t="n">
         <v>75.52662129209557</v>
@@ -2778,23 +2778,23 @@
         <v>56.51525123994185</v>
       </c>
       <c r="CB7" t="n">
-        <v>103.8564309195623</v>
+        <v>103.8564308648494</v>
       </c>
       <c r="CC7" t="n">
-        <v>48.58755191578657</v>
+        <v>48.58755190688473</v>
       </c>
       <c r="CD7" t="n">
-        <v>61.39492104997974</v>
+        <v>61.39492097587762</v>
       </c>
       <c r="CE7" t="inlineStr"/>
       <c r="CF7" t="n">
-        <v>43.69429703936258</v>
+        <v>43.6942970634518</v>
       </c>
       <c r="CG7" t="n">
-        <v>40.75260130490712</v>
+        <v>40.75260133465145</v>
       </c>
       <c r="CH7" t="n">
-        <v>36.67734117441641</v>
+        <v>36.67734120118631</v>
       </c>
       <c r="CI7" t="n">
         <v>4</v>
@@ -2806,10 +2806,10 @@
         <v>4.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>-21.24255654978516</v>
+        <v>-21.24255649230201</v>
       </c>
       <c r="CM7" t="n">
-        <v>-6.175011110814421</v>
+        <v>-6.17501105908752</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>0.98</v>
       </c>
       <c r="BI8" t="n">
-        <v>87.14</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="BJ8" t="n">
         <v>33.5</v>
@@ -3080,10 +3080,10 @@
         <v>-25.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>-4.9</v>
+        <v>-4.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BV8" t="n">
         <v>0.57</v>
@@ -3092,10 +3092,10 @@
         <v>29.89999961853027</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.20916579786056</v>
+        <v>22.20974212418462</v>
       </c>
       <c r="BY8" t="n">
-        <v>41.19800255503134</v>
+        <v>41.19907164036248</v>
       </c>
       <c r="BZ8" t="n">
         <v>47.27625238013437</v>
@@ -3104,25 +3104,25 @@
         <v>20.75930620677502</v>
       </c>
       <c r="CB8" t="n">
-        <v>67.55450306222518</v>
+        <v>67.55010998277137</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.53805619334043</v>
+        <v>53.53731573302993</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.67226417709977</v>
+        <v>28.66889760145738</v>
       </c>
       <c r="CE8" t="n">
         <v>23.7514480389424</v>
       </c>
       <c r="CF8" t="n">
-        <v>38.11987480142614</v>
+        <v>38.1190179634572</v>
       </c>
       <c r="CG8" t="n">
-        <v>34.93513336606556</v>
+        <v>34.93398462090992</v>
       </c>
       <c r="CH8" t="n">
-        <v>31.441620029459</v>
+        <v>31.44058615881893</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -3134,10 +3134,10 @@
         <v>3.3</v>
       </c>
       <c r="CL8" t="n">
-        <v>5.155921172565248</v>
+        <v>5.152463411183117</v>
       </c>
       <c r="CM8" t="n">
-        <v>27.4912216982159</v>
+        <v>27.48835601935344</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3408,22 +3408,22 @@
         <v>-43.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>-22.5</v>
+        <v>-22.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BW9" t="n">
         <v>4.46999979019165</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.025275124261356</v>
+        <v>3.02542178438461</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.611885355504815</v>
+        <v>5.612157410033452</v>
       </c>
       <c r="BZ9" t="n">
         <v>12.73709617635255</v>
@@ -3432,7 +3432,7 @@
         <v>8.558256916730283</v>
       </c>
       <c r="CB9" t="n">
-        <v>23.52770937473844</v>
+        <v>23.52815093209878</v>
       </c>
       <c r="CC9" t="n">
         <v>11.57513776217851</v>
@@ -3444,7 +3444,7 @@
         <v>5.155438154799276</v>
       </c>
       <c r="CF9" t="n">
-        <v>11.25673372822525</v>
+        <v>11.25683567278082</v>
       </c>
       <c r="CG9" t="n">
         <v>11.57513776217851</v>
@@ -3465,7 +3465,7 @@
         <v>133.0564759492753</v>
       </c>
       <c r="CM9" t="n">
-        <v>151.8285068586686</v>
+        <v>151.8307874976027</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         <v>15.64999961853027</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.389485076695794</v>
+        <v>6.389485077899922</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.8524948172707</v>
+        <v>11.85249481950435</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.41207045901055</v>
@@ -3760,19 +3760,19 @@
         <v>18.65776617291419</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.32865343442887</v>
+        <v>35.32865343248093</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.30206848509627</v>
+        <v>12.30206848486783</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.43947277751732</v>
+        <v>20.43947277499434</v>
       </c>
       <c r="CE10" t="n">
         <v>17.94300967523397</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.27650511735313</v>
+        <v>20.27650511700088</v>
       </c>
       <c r="CG10" t="n">
         <v>18.65776617291419</v>
@@ -3793,7 +3793,7 @@
         <v>7.297060478776829</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.56233617632089</v>
+        <v>29.56233617407011</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4076,10 +4076,10 @@
         <v>32.22000122070312</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.99391746462263</v>
+        <v>44.99391743966054</v>
       </c>
       <c r="BY11" t="n">
-        <v>83.46371689687497</v>
+        <v>83.46371685057029</v>
       </c>
       <c r="BZ11" t="n">
         <v>68.08851932604726</v>
@@ -4100,7 +4100,7 @@
         <v>24.86437698596777</v>
       </c>
       <c r="CF11" t="n">
-        <v>77.15449573223235</v>
+        <v>77.15449572205138</v>
       </c>
       <c r="CG11" t="n">
         <v>68.08851932604726</v>
@@ -4121,7 +4121,7 @@
         <v>90.19138755980858</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.4614922691447</v>
+        <v>139.4614922375464</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4390,34 +4390,34 @@
         <v>33.99</v>
       </c>
       <c r="BP12" t="n">
-        <v>26.77</v>
+        <v>26.84</v>
       </c>
       <c r="BQ12" t="n">
         <v>47.05</v>
       </c>
       <c r="BR12" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="BS12" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="BW12" t="n">
         <v>42.95185852050781</v>
       </c>
       <c r="BX12" t="n">
-        <v>123.7530442207145</v>
+        <v>123.7525655898296</v>
       </c>
       <c r="BY12" t="n">
-        <v>229.5618970294254</v>
+        <v>229.5610091691339</v>
       </c>
       <c r="BZ12" t="n">
         <v>132.970122756245</v>
@@ -4438,13 +4438,13 @@
         <v>57.73149631390972</v>
       </c>
       <c r="CF12" t="n">
-        <v>139.1788102228047</v>
+        <v>139.1786394114076</v>
       </c>
       <c r="CG12" t="n">
-        <v>122.5911819349069</v>
+        <v>122.5909426194644</v>
       </c>
       <c r="CH12" t="n">
-        <v>110.3320637414162</v>
+        <v>110.331848357518</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4456,10 +4456,10 @@
         <v>5.3</v>
       </c>
       <c r="CL12" t="n">
-        <v>156.8737827461808</v>
+        <v>156.8732812919815</v>
       </c>
       <c r="CM12" t="n">
-        <v>224.0344306785987</v>
+        <v>224.0340329975601</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>-0.04512344141920366</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-9.882295920693396</v>
+        <v>-9.882288559867835</v>
       </c>
       <c r="DA12" t="b">
         <v>1</v>
@@ -4658,7 +4658,7 @@
         <v>7.41</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AY13" t="n">
         <v>32.79</v>
@@ -4712,22 +4712,22 @@
         <v>-17.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BW13" t="n">
         <v>18.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>12.5468965739691</v>
+        <v>12.54642264821688</v>
       </c>
       <c r="BY13" t="n">
-        <v>23.27449314471269</v>
+        <v>23.27361401244231</v>
       </c>
       <c r="BZ13" t="n">
         <v>19.9845041322314</v>
@@ -4736,7 +4736,7 @@
         <v>12.4901078746637</v>
       </c>
       <c r="CB13" t="n">
-        <v>33.82285554012955</v>
+        <v>33.82230719628399</v>
       </c>
       <c r="CC13" t="n">
         <v>22.8984489302328</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>19.6760856952865</v>
+        <v>19.67574743078085</v>
       </c>
       <c r="CG13" t="n">
         <v>21.4414765312321</v>
@@ -4767,7 +4767,7 @@
         <v>5.738788373199388</v>
       </c>
       <c r="CM13" t="n">
-        <v>7.814168193350657</v>
+        <v>7.812314689210109</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -5040,22 +5040,22 @@
         <v>-8.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="BW14" t="n">
         <v>47.99185562133789</v>
       </c>
       <c r="BX14" t="n">
-        <v>131.1061234270398</v>
+        <v>131.1054577321602</v>
       </c>
       <c r="BY14" t="n">
-        <v>243.2018589571588</v>
+        <v>243.2006240931572</v>
       </c>
       <c r="BZ14" t="n">
         <v>133.3107100592719</v>
@@ -5076,13 +5076,13 @@
         <v>56.36047046127493</v>
       </c>
       <c r="CF14" t="n">
-        <v>141.8581323873512</v>
+        <v>141.8578948174911</v>
       </c>
       <c r="CG14" t="n">
-        <v>126.4232349858667</v>
+        <v>126.4229021384269</v>
       </c>
       <c r="CH14" t="n">
-        <v>113.78091148728</v>
+        <v>113.7806119245842</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -5094,10 +5094,10 @@
         <v>5.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>137.0837926856309</v>
+        <v>137.0831684907714</v>
       </c>
       <c r="CM14" t="n">
-        <v>195.5879295575289</v>
+        <v>195.5874345363277</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>-0.1416741793906717</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-9.654866496095483</v>
+        <v>-9.654873160851507</v>
       </c>
       <c r="DA14" t="b">
         <v>1</v>
@@ -5380,10 +5380,10 @@
         <v>17.32999992370605</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.62120828010145</v>
+        <v>10.62120825073235</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.70234135958819</v>
+        <v>19.70234130510852</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.45880897049025</v>
@@ -5392,25 +5392,25 @@
         <v>36.8907150460014</v>
       </c>
       <c r="CB15" t="n">
-        <v>41.91990552166546</v>
+        <v>41.91990550878272</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.52256326828227</v>
+        <v>34.52256327451072</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.65458541713855</v>
+        <v>18.654585451202</v>
       </c>
       <c r="CE15" t="n">
         <v>31.24600421044032</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.48498911337235</v>
+        <v>31.48498910950513</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.52256326828227</v>
+        <v>34.52256327451072</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.07030694145404</v>
+        <v>31.07030694705965</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5422,10 +5422,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>79.28624973017078</v>
+        <v>79.28624976251702</v>
       </c>
       <c r="CM15" t="n">
-        <v>81.67910705125507</v>
+        <v>81.67910702893994</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>73.87</v>
+        <v>73.89</v>
       </c>
       <c r="BJ16" t="n">
         <v>-30.3</v>
@@ -5696,10 +5696,10 @@
         <v>-48.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>-16.7</v>
+        <v>-16.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BV16" t="n">
         <v>0.71</v>
@@ -5708,10 +5708,10 @@
         <v>9.739999771118164</v>
       </c>
       <c r="BX16" t="n">
-        <v>9.752333606899221</v>
+        <v>9.754236617904695</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.09057884079806</v>
+        <v>18.09410892621321</v>
       </c>
       <c r="BZ16" t="n">
         <v>24.48861422529709</v>
@@ -5720,25 +5720,25 @@
         <v>17.58365889509133</v>
       </c>
       <c r="CB16" t="n">
-        <v>37.93100542536856</v>
+        <v>37.92942696620967</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.34821912835721</v>
+        <v>24.34739855870606</v>
       </c>
       <c r="CD16" t="n">
-        <v>12.49494170068755</v>
+        <v>12.49077182297235</v>
       </c>
       <c r="CE16" t="n">
         <v>9.739999771118164</v>
       </c>
       <c r="CF16" t="n">
-        <v>19.30366894920215</v>
+        <v>19.30352697293907</v>
       </c>
       <c r="CG16" t="n">
-        <v>17.83711886794469</v>
+        <v>17.83888391065227</v>
       </c>
       <c r="CH16" t="n">
-        <v>16.05340698115022</v>
+        <v>16.05499551958705</v>
       </c>
       <c r="CI16" t="n">
         <v>8</v>
@@ -5750,10 +5750,10 @@
         <v>3.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>64.81937739622015</v>
+        <v>64.83568682613954</v>
       </c>
       <c r="CM16" t="n">
-        <v>98.18962425895481</v>
+        <v>98.18816659708196</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -5940,13 +5940,13 @@
         <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AS17" t="b">
         <v>1</v>
       </c>
       <c r="AT17" t="n">
-        <v>5449639424</v>
+        <v>3429433856</v>
       </c>
       <c r="AU17" t="n">
         <v>6.37</v>
@@ -6024,7 +6024,7 @@
         <v>-38.2</v>
       </c>
       <c r="BT17" t="n">
-        <v>-18.5</v>
+        <v>-18.4</v>
       </c>
       <c r="BU17" t="n">
         <v>1.47</v>
@@ -6036,10 +6036,10 @@
         <v>10.47999954223633</v>
       </c>
       <c r="BX17" t="n">
-        <v>9.072864345344986</v>
+        <v>9.072864391128032</v>
       </c>
       <c r="BY17" t="n">
-        <v>16.83016336061495</v>
+        <v>16.8301634455425</v>
       </c>
       <c r="BZ17" t="n">
         <v>21.79905713259518</v>
@@ -6048,25 +6048,25 @@
         <v>12.87581943989401</v>
       </c>
       <c r="CB17" t="n">
-        <v>33.73326028787612</v>
+        <v>33.73326015275214</v>
       </c>
       <c r="CC17" t="n">
-        <v>25.6201369124789</v>
+        <v>25.62013687860695</v>
       </c>
       <c r="CD17" t="n">
-        <v>13.06488825106885</v>
+        <v>13.06488810288561</v>
       </c>
       <c r="CE17" t="n">
         <v>9.30550460634233</v>
       </c>
       <c r="CF17" t="n">
-        <v>17.78771179202691</v>
+        <v>17.78771176871834</v>
       </c>
       <c r="CG17" t="n">
-        <v>14.9475258058419</v>
+        <v>14.94752577421406</v>
       </c>
       <c r="CH17" t="n">
-        <v>13.45277322525771</v>
+        <v>13.45277319679265</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6078,10 +6078,10 @@
         <v>3.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>28.36616233655887</v>
+        <v>28.36616206494569</v>
       </c>
       <c r="CM17" t="n">
-        <v>69.73008176516764</v>
+        <v>69.73008154275759</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>3.46</v>
       </c>
       <c r="BI18" t="n">
-        <v>89.91</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="BJ18" t="n">
         <v>23.5</v>
@@ -6352,49 +6352,49 @@
         <v>-12.2</v>
       </c>
       <c r="BT18" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW18" t="n">
         <v>34.38000106811523</v>
       </c>
       <c r="BX18" t="n">
-        <v>24.72393448319795</v>
+        <v>24.72347832048936</v>
       </c>
       <c r="BY18" t="n">
-        <v>31.08816167921737</v>
+        <v>31.08887020637266</v>
       </c>
       <c r="BZ18" t="n">
-        <v>34.57831681460159</v>
+        <v>34.57974289034262</v>
       </c>
       <c r="CA18" t="n">
         <v>36.14131846677351</v>
       </c>
       <c r="CB18" t="n">
-        <v>48.68948635977289</v>
+        <v>48.69040290507824</v>
       </c>
       <c r="CC18" t="n">
-        <v>48.57168418558451</v>
+        <v>48.57188486807643</v>
       </c>
       <c r="CD18" t="n">
-        <v>16.52565915624632</v>
+        <v>16.52668479248031</v>
       </c>
       <c r="CE18" t="n">
         <v>29.95270377341624</v>
       </c>
       <c r="CF18" t="n">
-        <v>33.7839081148513</v>
+        <v>33.78438577787867</v>
       </c>
       <c r="CG18" t="n">
-        <v>32.83323924690948</v>
+        <v>32.83430654835764</v>
       </c>
       <c r="CH18" t="n">
-        <v>29.54991532221853</v>
+        <v>29.55087589352188</v>
       </c>
       <c r="CI18" t="n">
         <v>8</v>
@@ -6406,10 +6406,10 @@
         <v>2.9</v>
       </c>
       <c r="CL18" t="n">
-        <v>-14.04911458940072</v>
+        <v>-14.04632060663894</v>
       </c>
       <c r="CM18" t="n">
-        <v>-1.733836343061557</v>
+        <v>-1.732446980023372</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="DD18" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.9, +0.9% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x0.8, +0.9% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
         <v>0.76</v>
       </c>
       <c r="BI19" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="BJ19" t="n">
         <v>3.2</v>
@@ -6688,22 +6688,22 @@
         <v>-31.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>-21.4</v>
+        <v>-21.3</v>
       </c>
       <c r="BU19" t="n">
         <v>1.46</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="BW19" t="n">
         <v>10.98999977111816</v>
       </c>
       <c r="BX19" t="n">
-        <v>3.42436230629624</v>
+        <v>3.424809591929229</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.352192078179525</v>
+        <v>6.353021793028721</v>
       </c>
       <c r="BZ19" t="n">
         <v>19.65148407116271</v>
@@ -6712,13 +6712,13 @@
         <v>18.513475240297</v>
       </c>
       <c r="CB19" t="n">
-        <v>20.93338770324559</v>
+        <v>20.93333042328002</v>
       </c>
       <c r="CC19" t="n">
-        <v>15.91678365913704</v>
+        <v>15.9166954243071</v>
       </c>
       <c r="CD19" t="n">
-        <v>13.05348853535147</v>
+        <v>13.05292134138598</v>
       </c>
       <c r="CE19" t="n">
         <v>28.64218279833469</v>
@@ -6774,7 +6774,7 @@
         <v>-20.64982333269847</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-33.44154600225495</v>
+        <v>-33.44156184895316</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -7018,10 +7018,10 @@
         <v>26.86000061035156</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.115263311955315</v>
+        <v>7.115263333060311</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.19881344367711</v>
+        <v>13.19881348282688</v>
       </c>
       <c r="BZ20" t="n">
         <v>35.80432676933181</v>
@@ -7030,19 +7030,19 @@
         <v>28.29365159335656</v>
       </c>
       <c r="CB20" t="n">
-        <v>45.03018693888243</v>
+        <v>45.03018690797735</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.50039357303511</v>
+        <v>26.50039356777111</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.22423178149021</v>
+        <v>29.22423174337965</v>
       </c>
       <c r="CE20" t="n">
         <v>23.5668842743778</v>
       </c>
       <c r="CF20" t="n">
-        <v>28.80264119630729</v>
+        <v>28.80264119128874</v>
       </c>
       <c r="CG20" t="n">
         <v>28.29365159335656</v>
@@ -7063,7 +7063,7 @@
         <v>-5.196255192163946</v>
       </c>
       <c r="CM20" t="n">
-        <v>7.23246664859365</v>
+        <v>7.232466629909529</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>-7.60233611170672</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-23.86224665397592</v>
+        <v>-23.86225492369548</v>
       </c>
       <c r="DA20" t="b">
         <v>1</v>
@@ -7283,7 +7283,7 @@
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="n">
-        <v>100.83</v>
+        <v>100.82</v>
       </c>
       <c r="BJ21" t="n">
         <v>-0.1</v>
@@ -7314,22 +7314,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW21" t="n">
         <v>37.18999862670898</v>
       </c>
       <c r="BX21" t="n">
-        <v>34.07781575837959</v>
+        <v>34.07294329184204</v>
       </c>
       <c r="BY21" t="n">
-        <v>49.61729974420069</v>
+        <v>49.61020543292201</v>
       </c>
       <c r="BZ21" t="n">
         <v>49.2081406765615</v>
@@ -7346,13 +7346,13 @@
       </c>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="n">
-        <v>48.10185529073987</v>
+        <v>48.09886359628581</v>
       </c>
       <c r="CG21" t="n">
-        <v>49.4127202103811</v>
+        <v>49.40917305474176</v>
       </c>
       <c r="CH21" t="n">
-        <v>44.47144818934299</v>
+        <v>44.46825574926758</v>
       </c>
       <c r="CI21" t="n">
         <v>4</v>
@@ -7364,10 +7364,10 @@
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>19.57905305595962</v>
+        <v>19.57046891991958</v>
       </c>
       <c r="CM21" t="n">
-        <v>29.34083642636718</v>
+        <v>29.33279207421733</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -7650,10 +7650,10 @@
         <v>21.52000045776367</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.029635325999941</v>
+        <v>3.029635323010476</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.61997352972989</v>
+        <v>5.619973524184433</v>
       </c>
       <c r="BZ22" t="n">
         <v>32.85023111352173</v>
@@ -7662,7 +7662,7 @@
         <v>27.39136539639765</v>
       </c>
       <c r="CB22" t="n">
-        <v>42.07544947355464</v>
+        <v>42.07544946873292</v>
       </c>
       <c r="CC22" t="n">
         <v>10.85340539909456</v>
@@ -7956,10 +7956,10 @@
         <v>-32.1</v>
       </c>
       <c r="BT23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="BV23" t="n">
         <v>0.44</v>
@@ -7968,10 +7968,10 @@
         <v>32.18000030517578</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.192274477515815</v>
+        <v>3.192481966833107</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.921669155791836</v>
+        <v>5.922054048475414</v>
       </c>
       <c r="BZ23" t="n">
         <v>32.5982418993562</v>
@@ -7980,7 +7980,7 @@
         <v>22.82235087014609</v>
       </c>
       <c r="CB23" t="n">
-        <v>40.32047761948458</v>
+        <v>40.3206997028517</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8040,7 +8040,7 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX23" t="n">
@@ -8250,13 +8250,13 @@
         <v>79.81999999999999</v>
       </c>
       <c r="BP24" t="n">
-        <v>9.449999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BQ24" t="n">
         <v>14.81</v>
       </c>
       <c r="BR24" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="BS24" t="n">
         <v>-15.6</v>
@@ -8265,7 +8265,7 @@
         <v>-6.3</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BV24" t="n">
         <v>0.88</v>
@@ -8274,35 +8274,35 @@
         <v>12.5</v>
       </c>
       <c r="BX24" t="n">
-        <v>8.391835717791732</v>
+        <v>8.391865450100273</v>
       </c>
       <c r="BY24" t="n">
-        <v>14.24205142317515</v>
+        <v>14.24201355997039</v>
       </c>
       <c r="BZ24" t="n">
-        <v>19.62818999580421</v>
+        <v>19.62806827095434</v>
       </c>
       <c r="CA24" t="n">
         <v>17.48233699953358</v>
       </c>
       <c r="CB24" t="n">
-        <v>23.8202736582025</v>
+        <v>23.82024699044768</v>
       </c>
       <c r="CC24" t="n">
-        <v>17.41209079205115</v>
+        <v>17.41208256318266</v>
       </c>
       <c r="CD24" t="n">
-        <v>9.73241997420155</v>
+        <v>9.732369319862141</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>14.91854198220556</v>
+        <v>14.91850746105192</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.82707110761315</v>
+        <v>15.82704806157652</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.24436399685184</v>
+        <v>14.24434325541887</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8314,10 +8314,10 @@
         <v>2.3</v>
       </c>
       <c r="CL24" t="n">
-        <v>13.95491197481471</v>
+        <v>13.95474604335099</v>
       </c>
       <c r="CM24" t="n">
-        <v>19.34833585764451</v>
+        <v>19.34805968841533</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>0.93</v>
       </c>
       <c r="BI25" t="n">
-        <v>53.33</v>
+        <v>53.34</v>
       </c>
       <c r="BJ25" t="n">
         <v>17.8</v>
@@ -8556,22 +8556,22 @@
         <v>7.66</v>
       </c>
       <c r="BP25" t="n">
-        <v>12.38</v>
+        <v>12.4</v>
       </c>
       <c r="BQ25" t="n">
         <v>17.96</v>
       </c>
       <c r="BR25" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="BS25" t="n">
         <v>-20.2</v>
       </c>
       <c r="BT25" t="n">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BV25" t="n">
         <v>0.84</v>
@@ -8580,10 +8580,10 @@
         <v>14.32999992370605</v>
       </c>
       <c r="BX25" t="n">
-        <v>8.905449596806895</v>
+        <v>8.905780260521059</v>
       </c>
       <c r="BY25" t="n">
-        <v>16.51960900207679</v>
+        <v>16.52022238326656</v>
       </c>
       <c r="BZ25" t="n">
         <v>30.97430652350819</v>
@@ -8592,23 +8592,23 @@
         <v>29.43388465049835</v>
       </c>
       <c r="CB25" t="n">
-        <v>35.7534179562529</v>
+        <v>35.75351902359017</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.58451048445651</v>
+        <v>25.58444332373756</v>
       </c>
       <c r="CD25" t="n">
-        <v>15.93419931312169</v>
+        <v>15.93378815263295</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.4959689017121</v>
+        <v>20.49618812275834</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.05205974326665</v>
+        <v>21.05233285350207</v>
       </c>
       <c r="CH25" t="n">
-        <v>18.94685376893998</v>
+        <v>18.94709956815186</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8620,10 +8620,10 @@
         <v>3.5</v>
       </c>
       <c r="CL25" t="n">
-        <v>32.21810097567614</v>
+        <v>32.2198162528093</v>
       </c>
       <c r="CM25" t="n">
-        <v>43.02839505118006</v>
+        <v>43.02992485611665</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>0.15</v>
       </c>
       <c r="BI26" t="n">
-        <v>228.24</v>
+        <v>228.23</v>
       </c>
       <c r="BJ26" t="n">
         <v>90.7</v>
@@ -8894,7 +8894,7 @@
         <v>-5.4</v>
       </c>
       <c r="BT26" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="BU26" t="n">
         <v>1.1</v>
@@ -8906,10 +8906,10 @@
         <v>5.900000095367432</v>
       </c>
       <c r="BX26" t="n">
-        <v>7.000436751513742</v>
+        <v>7.000252746958866</v>
       </c>
       <c r="BY26" t="n">
-        <v>12.98581017405799</v>
+        <v>12.9854688456087</v>
       </c>
       <c r="BZ26" t="n">
         <v>5.689592522825215</v>
@@ -8930,7 +8930,7 @@
         <v>5.412237592239494</v>
       </c>
       <c r="CF26" t="n">
-        <v>7.363870611343367</v>
+        <v>7.363804944717845</v>
       </c>
       <c r="CG26" t="n">
         <v>5.911462928079274</v>
@@ -8951,7 +8951,7 @@
         <v>-9.825143232645727</v>
       </c>
       <c r="CM26" t="n">
-        <v>24.81136427650803</v>
+        <v>24.81025128287313</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
       <c r="CV26" t="inlineStr"/>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX26" t="n">
@@ -9200,13 +9200,13 @@
         <v>6.67</v>
       </c>
       <c r="BP27" t="n">
-        <v>32.61</v>
+        <v>32.63</v>
       </c>
       <c r="BQ27" t="n">
         <v>48.4</v>
       </c>
       <c r="BR27" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="BS27" t="n">
         <v>-20.3</v>
@@ -9215,7 +9215,7 @@
         <v>-7</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BV27" t="n">
         <v>0.85</v>
@@ -9224,10 +9224,10 @@
         <v>38.59999847412109</v>
       </c>
       <c r="BX27" t="n">
-        <v>19.73061806082051</v>
+        <v>19.73089423195889</v>
       </c>
       <c r="BY27" t="n">
-        <v>36.60029650282205</v>
+        <v>36.60080880028374</v>
       </c>
       <c r="BZ27" t="n">
         <v>56.01861771983619</v>
@@ -9236,23 +9236,23 @@
         <v>42.32200432760474</v>
       </c>
       <c r="CB27" t="n">
-        <v>63.15628612000056</v>
+        <v>63.15584159669065</v>
       </c>
       <c r="CC27" t="n">
-        <v>45.3046605503917</v>
+        <v>45.30457425204306</v>
       </c>
       <c r="CD27" t="n">
-        <v>31.97509348978538</v>
+        <v>31.97454788608441</v>
       </c>
       <c r="CE27" t="inlineStr"/>
       <c r="CF27" t="n">
-        <v>39.41354820846762</v>
+        <v>39.41372375103047</v>
       </c>
       <c r="CG27" t="n">
-        <v>40.95247852660688</v>
+        <v>40.9526915261634</v>
       </c>
       <c r="CH27" t="n">
-        <v>36.8572306739462</v>
+        <v>36.85742237354706</v>
       </c>
       <c r="CI27" t="n">
         <v>4</v>
@@ -9264,10 +9264,10 @@
         <v>2.8</v>
       </c>
       <c r="CL27" t="n">
-        <v>-4.514942665977861</v>
+        <v>-4.514446034867914</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.107641882141409</v>
+        <v>2.10809665563827</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>-10.5860548729689</v>
       </c>
       <c r="CZ27" t="n">
-        <v>-20.73761372683879</v>
+        <v>-20.73760748031875</v>
       </c>
       <c r="DA27" t="b">
         <v>1</v>
@@ -9526,13 +9526,13 @@
         <v>44.81</v>
       </c>
       <c r="BP28" t="n">
-        <v>20.47</v>
+        <v>20.58</v>
       </c>
       <c r="BQ28" t="n">
         <v>31.63</v>
       </c>
       <c r="BR28" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="BS28" t="n">
         <v>-17.7</v>
@@ -9544,43 +9544,43 @@
         <v>0.98</v>
       </c>
       <c r="BV28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BW28" t="n">
         <v>26.02000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.63763580878589</v>
+        <v>16.63820050436581</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.24291835350032</v>
+        <v>28.24299340528112</v>
       </c>
       <c r="BZ28" t="n">
-        <v>48.53822209804601</v>
+        <v>48.53670370467485</v>
       </c>
       <c r="CA28" t="n">
         <v>53.13771001269293</v>
       </c>
       <c r="CB28" t="n">
-        <v>57.10900732510467</v>
+        <v>57.10921877319265</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.1192701942657</v>
+        <v>43.1191674216231</v>
       </c>
       <c r="CD28" t="n">
-        <v>24.06622532388929</v>
+        <v>24.06559372317708</v>
       </c>
       <c r="CE28" t="n">
         <v>29.31279211564875</v>
       </c>
       <c r="CF28" t="n">
-        <v>37.5204726539917</v>
+        <v>37.52029745758203</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.21603115495723</v>
+        <v>36.21597976863593</v>
       </c>
       <c r="CH28" t="n">
-        <v>32.5944280394615</v>
+        <v>32.59438179177234</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9592,10 +9592,10 @@
         <v>3.4</v>
       </c>
       <c r="CL28" t="n">
-        <v>25.26682346670059</v>
+        <v>25.26664572769846</v>
       </c>
       <c r="CM28" t="n">
-        <v>44.19858567987301</v>
+        <v>44.19791236547415</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9878,37 +9878,37 @@
         <v>15</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.819252146308642</v>
+        <v>5.819252150976158</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.57533093218367</v>
+        <v>8.575330928179753</v>
       </c>
       <c r="BZ29" t="n">
-        <v>11.041063292106</v>
+        <v>11.04106327809497</v>
       </c>
       <c r="CA29" t="n">
         <v>11.6021005542244</v>
       </c>
       <c r="CB29" t="n">
-        <v>10.00747570525726</v>
+        <v>10.00747569780333</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.94224989979434</v>
+        <v>14.94224989814919</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.511532858762981</v>
+        <v>5.511532851205339</v>
       </c>
       <c r="CE29" t="n">
         <v>10.66215185399864</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.770144655329492</v>
+        <v>9.770144651578974</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.33481377962795</v>
+        <v>10.33481377590099</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.301332401665153</v>
+        <v>9.301332398310889</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9920,10 +9920,10 @@
         <v>2.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>-37.99111732223231</v>
+        <v>-37.99111734459407</v>
       </c>
       <c r="CM29" t="n">
-        <v>-34.86570229780338</v>
+        <v>-34.86570232280683</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>-26.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>-8.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="BU2" t="n">
         <v>1.38</v>
@@ -10762,10 +10762,10 @@
         <v>10.15999984741211</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.739092621841178</v>
+        <v>5.738884128649667</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.64601681351538</v>
+        <v>10.64563005864513</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.29447790742652</v>
@@ -10774,7 +10774,7 @@
         <v>27.67799880047428</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.39487558802398</v>
+        <v>71.39398021848989</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -11080,10 +11080,10 @@
         <v>13.67000007629395</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.08411226503859</v>
+        <v>15.08411221122868</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.98102825164658</v>
+        <v>27.9810281518292</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.78533212224727</v>
@@ -11092,13 +11092,13 @@
         <v>23.4303842936706</v>
       </c>
       <c r="CB3" t="n">
-        <v>73.80863252004175</v>
+        <v>73.80863262284781</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.30691180760066</v>
+        <v>48.30691184730974</v>
       </c>
       <c r="CD3" t="n">
-        <v>25.78976650113605</v>
+        <v>25.78976666715468</v>
       </c>
       <c r="CE3" t="n">
         <v>8.630044464581562</v>
@@ -11398,10 +11398,10 @@
         <v>23.51000022888184</v>
       </c>
       <c r="BX4" t="n">
-        <v>15.55616503941216</v>
+        <v>15.55616502675489</v>
       </c>
       <c r="BY4" t="n">
-        <v>28.85668614810956</v>
+        <v>28.85668612463031</v>
       </c>
       <c r="BZ4" t="n">
         <v>71.12043448234802</v>
@@ -11410,13 +11410,13 @@
         <v>51.51277527306067</v>
       </c>
       <c r="CB4" t="n">
-        <v>127.4881988874577</v>
+        <v>127.4881988902025</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.80183479027916</v>
+        <v>25.80183479209307</v>
       </c>
       <c r="CD4" t="n">
-        <v>63.22015025477451</v>
+        <v>63.22015028192994</v>
       </c>
       <c r="CE4" t="n">
         <v>41.54649601907847</v>
@@ -11704,22 +11704,22 @@
         <v>-60.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>-26.2</v>
+        <v>-25.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW5" t="n">
         <v>6.900000095367432</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.115400812167315</v>
+        <v>3.115400814292661</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.779068506570369</v>
+        <v>5.779068510512887</v>
       </c>
       <c r="BZ5" t="n">
         <v>19.83188747583914</v>
@@ -11728,7 +11728,7 @@
         <v>13.5801516746889</v>
       </c>
       <c r="CB5" t="n">
-        <v>31.91228043402471</v>
+        <v>31.91228044047912</v>
       </c>
       <c r="CC5" t="n">
         <v>10.95072400487419</v>
@@ -11784,10 +11784,10 @@
         </is>
       </c>
       <c r="CX5" t="n">
-        <v>7.5</v>
+        <v>7.360000133514404</v>
       </c>
       <c r="CY5" t="n">
-        <v>-7.999998728434243</v>
+        <v>-6.250000404922851</v>
       </c>
       <c r="CZ5" t="n">
         <v>-60.30064258156551</v>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.3%))</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
         <v>0.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>51.56</v>
+        <v>51.57</v>
       </c>
       <c r="BJ6" t="n">
         <v>-14</v>
@@ -12020,22 +12020,22 @@
         <v>-37.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>-23.8</v>
+        <v>-23.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BW6" t="n">
         <v>4.179999828338623</v>
       </c>
       <c r="BX6" t="n">
-        <v>3.539168753431935</v>
+        <v>3.539319177617177</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.565158037616239</v>
+        <v>6.565437074479863</v>
       </c>
       <c r="BZ6" t="n">
         <v>12.73218338516937</v>
@@ -12044,25 +12044,25 @@
         <v>8.571766632368943</v>
       </c>
       <c r="CB6" t="n">
-        <v>24.5715721600935</v>
+        <v>24.57145988209843</v>
       </c>
       <c r="CC6" t="n">
-        <v>11.28769658477398</v>
+        <v>11.28763497763521</v>
       </c>
       <c r="CD6" t="n">
-        <v>10.85231831601691</v>
+        <v>10.85194343487941</v>
       </c>
       <c r="CE6" t="n">
         <v>5.170088126502553</v>
       </c>
       <c r="CF6" t="n">
-        <v>9.196535180407999</v>
+        <v>9.196508938505891</v>
       </c>
       <c r="CG6" t="n">
-        <v>9.712042474192923</v>
+        <v>9.711855033624179</v>
       </c>
       <c r="CH6" t="n">
-        <v>8.740838226773631</v>
+        <v>8.740669530261762</v>
       </c>
       <c r="CI6" t="n">
         <v>6</v>
@@ -12074,10 +12074,10 @@
         <v>6.9</v>
       </c>
       <c r="CL6" t="n">
-        <v>109.1109709506317</v>
+        <v>109.1069351487465</v>
       </c>
       <c r="CM6" t="n">
-        <v>120.0128123943785</v>
+        <v>120.0121845976516</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -12342,10 +12342,10 @@
         <v>46.56999969482422</v>
       </c>
       <c r="BX7" t="n">
-        <v>17.74536425554052</v>
+        <v>17.74536429240872</v>
       </c>
       <c r="BY7" t="n">
-        <v>32.91765069402766</v>
+        <v>32.91765076241818</v>
       </c>
       <c r="BZ7" t="n">
         <v>75.52662129209557</v>
@@ -12354,23 +12354,23 @@
         <v>56.51525123994185</v>
       </c>
       <c r="CB7" t="n">
-        <v>103.8564309195623</v>
+        <v>103.8564308648494</v>
       </c>
       <c r="CC7" t="n">
-        <v>48.58755191578657</v>
+        <v>48.58755190688473</v>
       </c>
       <c r="CD7" t="n">
-        <v>61.39492104997974</v>
+        <v>61.39492097587762</v>
       </c>
       <c r="CE7" t="inlineStr"/>
       <c r="CF7" t="n">
-        <v>43.69429703936258</v>
+        <v>43.6942970634518</v>
       </c>
       <c r="CG7" t="n">
-        <v>40.75260130490712</v>
+        <v>40.75260133465145</v>
       </c>
       <c r="CH7" t="n">
-        <v>36.67734117441641</v>
+        <v>36.67734120118631</v>
       </c>
       <c r="CI7" t="n">
         <v>4</v>
@@ -12382,10 +12382,10 @@
         <v>4.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>-21.24255654978516</v>
+        <v>-21.24255649230201</v>
       </c>
       <c r="CM7" t="n">
-        <v>-6.175011110814421</v>
+        <v>-6.17501105908752</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>0.98</v>
       </c>
       <c r="BI8" t="n">
-        <v>87.14</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="BJ8" t="n">
         <v>33.5</v>
@@ -12656,10 +12656,10 @@
         <v>-25.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>-4.9</v>
+        <v>-4.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BV8" t="n">
         <v>0.57</v>
@@ -12668,10 +12668,10 @@
         <v>29.89999961853027</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.20916579786056</v>
+        <v>22.20974212418462</v>
       </c>
       <c r="BY8" t="n">
-        <v>41.19800255503134</v>
+        <v>41.19907164036248</v>
       </c>
       <c r="BZ8" t="n">
         <v>47.27625238013437</v>
@@ -12680,25 +12680,25 @@
         <v>20.75930620677502</v>
       </c>
       <c r="CB8" t="n">
-        <v>67.55450306222518</v>
+        <v>67.55010998277137</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.53805619334043</v>
+        <v>53.53731573302993</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.67226417709977</v>
+        <v>28.66889760145738</v>
       </c>
       <c r="CE8" t="n">
         <v>23.7514480389424</v>
       </c>
       <c r="CF8" t="n">
-        <v>38.11987480142614</v>
+        <v>38.1190179634572</v>
       </c>
       <c r="CG8" t="n">
-        <v>34.93513336606556</v>
+        <v>34.93398462090992</v>
       </c>
       <c r="CH8" t="n">
-        <v>31.441620029459</v>
+        <v>31.44058615881893</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -12710,10 +12710,10 @@
         <v>3.3</v>
       </c>
       <c r="CL8" t="n">
-        <v>5.155921172565248</v>
+        <v>5.152463411183117</v>
       </c>
       <c r="CM8" t="n">
-        <v>27.4912216982159</v>
+        <v>27.48835601935344</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -12984,22 +12984,22 @@
         <v>-43.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>-22.5</v>
+        <v>-22.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BW9" t="n">
         <v>4.46999979019165</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.025275124261356</v>
+        <v>3.02542178438461</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.611885355504815</v>
+        <v>5.612157410033452</v>
       </c>
       <c r="BZ9" t="n">
         <v>12.73709617635255</v>
@@ -13008,7 +13008,7 @@
         <v>8.558256916730283</v>
       </c>
       <c r="CB9" t="n">
-        <v>23.52770937473844</v>
+        <v>23.52815093209878</v>
       </c>
       <c r="CC9" t="n">
         <v>11.57513776217851</v>
@@ -13020,7 +13020,7 @@
         <v>5.155438154799276</v>
       </c>
       <c r="CF9" t="n">
-        <v>11.25673372822525</v>
+        <v>11.25683567278082</v>
       </c>
       <c r="CG9" t="n">
         <v>11.57513776217851</v>
@@ -13041,7 +13041,7 @@
         <v>133.0564759492753</v>
       </c>
       <c r="CM9" t="n">
-        <v>151.8285068586686</v>
+        <v>151.8307874976027</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -13324,10 +13324,10 @@
         <v>15.64999961853027</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.389485076695794</v>
+        <v>6.389485077899922</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.8524948172707</v>
+        <v>11.85249481950435</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.41207045901055</v>
@@ -13336,19 +13336,19 @@
         <v>18.65776617291419</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.32865343442887</v>
+        <v>35.32865343248093</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.30206848509627</v>
+        <v>12.30206848486783</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.43947277751732</v>
+        <v>20.43947277499434</v>
       </c>
       <c r="CE10" t="n">
         <v>17.94300967523397</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.27650511735313</v>
+        <v>20.27650511700088</v>
       </c>
       <c r="CG10" t="n">
         <v>18.65776617291419</v>
@@ -13369,7 +13369,7 @@
         <v>7.297060478776829</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.56233617632089</v>
+        <v>29.56233617407011</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -13652,10 +13652,10 @@
         <v>32.22000122070312</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.99391746462263</v>
+        <v>44.99391743966054</v>
       </c>
       <c r="BY11" t="n">
-        <v>83.46371689687497</v>
+        <v>83.46371685057029</v>
       </c>
       <c r="BZ11" t="n">
         <v>68.08851932604726</v>
@@ -13676,7 +13676,7 @@
         <v>24.86437698596777</v>
       </c>
       <c r="CF11" t="n">
-        <v>77.15449573223235</v>
+        <v>77.15449572205138</v>
       </c>
       <c r="CG11" t="n">
         <v>68.08851932604726</v>
@@ -13697,7 +13697,7 @@
         <v>90.19138755980858</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.4614922691447</v>
+        <v>139.4614922375464</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -13988,10 +13988,10 @@
         <v>6.820000171661377</v>
       </c>
       <c r="BX12" t="n">
-        <v>6.397639794737225</v>
+        <v>6.397639781834083</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.86762181923755</v>
+        <v>11.86762179530222</v>
       </c>
       <c r="BZ12" t="n">
         <v>40.34151887255054</v>
@@ -14000,7 +14000,7 @@
         <v>27.23211426856263</v>
       </c>
       <c r="CB12" t="n">
-        <v>85.65489272376865</v>
+        <v>85.65489264312401</v>
       </c>
       <c r="CC12" t="n">
         <v>51.88018214566937</v>
@@ -14594,34 +14594,34 @@
         <v>33.99</v>
       </c>
       <c r="BP14" t="n">
-        <v>26.77</v>
+        <v>26.84</v>
       </c>
       <c r="BQ14" t="n">
         <v>47.05</v>
       </c>
       <c r="BR14" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="BW14" t="n">
         <v>42.95185852050781</v>
       </c>
       <c r="BX14" t="n">
-        <v>123.7530442207145</v>
+        <v>123.7525655898296</v>
       </c>
       <c r="BY14" t="n">
-        <v>229.5618970294254</v>
+        <v>229.5610091691339</v>
       </c>
       <c r="BZ14" t="n">
         <v>132.970122756245</v>
@@ -14642,13 +14642,13 @@
         <v>57.73149631390972</v>
       </c>
       <c r="CF14" t="n">
-        <v>139.1788102228047</v>
+        <v>139.1786394114076</v>
       </c>
       <c r="CG14" t="n">
-        <v>122.5911819349069</v>
+        <v>122.5909426194644</v>
       </c>
       <c r="CH14" t="n">
-        <v>110.3320637414162</v>
+        <v>110.331848357518</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -14660,10 +14660,10 @@
         <v>5.3</v>
       </c>
       <c r="CL14" t="n">
-        <v>156.8737827461808</v>
+        <v>156.8732812919815</v>
       </c>
       <c r="CM14" t="n">
-        <v>224.0344306785987</v>
+        <v>224.0340329975601</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>-0.04512344141920366</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-9.882295920693396</v>
+        <v>-9.882288559867835</v>
       </c>
       <c r="DA14" t="b">
         <v>1</v>
@@ -14916,22 +14916,22 @@
         <v>-28</v>
       </c>
       <c r="BT15" t="n">
-        <v>-9.1</v>
+        <v>-8.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="BW15" t="n">
         <v>13.35999965667725</v>
       </c>
       <c r="BX15" t="n">
-        <v>9.696598480615128</v>
+        <v>9.69707911856962</v>
       </c>
       <c r="BY15" t="n">
-        <v>17.98719018154106</v>
+        <v>17.98808176494665</v>
       </c>
       <c r="BZ15" t="n">
         <v>49.58543289943235</v>
@@ -14940,23 +14940,23 @@
         <v>48.92317894641553</v>
       </c>
       <c r="CB15" t="n">
-        <v>69.64796684281355</v>
+        <v>69.64895944123833</v>
       </c>
       <c r="CC15" t="n">
-        <v>33.99030572767694</v>
+        <v>33.99023100072877</v>
       </c>
       <c r="CD15" t="n">
-        <v>29.87402122212436</v>
+        <v>29.87346037530802</v>
       </c>
       <c r="CE15" t="inlineStr"/>
       <c r="CF15" t="n">
-        <v>33.85430960288345</v>
+        <v>33.85458188836925</v>
       </c>
       <c r="CG15" t="n">
-        <v>33.99030572767694</v>
+        <v>33.99023100072877</v>
       </c>
       <c r="CH15" t="n">
-        <v>30.59127515490925</v>
+        <v>30.59120790065589</v>
       </c>
       <c r="CI15" t="n">
         <v>3</v>
@@ -14968,10 +14968,10 @@
         <v>5.1</v>
       </c>
       <c r="CL15" t="n">
-        <v>128.9766163251353</v>
+        <v>128.9761129250224</v>
       </c>
       <c r="CM15" t="n">
-        <v>153.4005274915054</v>
+        <v>153.4025655565713</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>7.41</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AY16" t="n">
         <v>32.79</v>
@@ -15220,22 +15220,22 @@
         <v>-17.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BW16" t="n">
         <v>18.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>12.5468965739691</v>
+        <v>12.54642264821688</v>
       </c>
       <c r="BY16" t="n">
-        <v>23.27449314471269</v>
+        <v>23.27361401244231</v>
       </c>
       <c r="BZ16" t="n">
         <v>19.9845041322314</v>
@@ -15244,7 +15244,7 @@
         <v>12.4901078746637</v>
       </c>
       <c r="CB16" t="n">
-        <v>33.82285554012955</v>
+        <v>33.82230719628399</v>
       </c>
       <c r="CC16" t="n">
         <v>22.8984489302328</v>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>19.6760856952865</v>
+        <v>19.67574743078085</v>
       </c>
       <c r="CG16" t="n">
         <v>21.4414765312321</v>
@@ -15275,7 +15275,7 @@
         <v>5.738788373199388</v>
       </c>
       <c r="CM16" t="n">
-        <v>7.814168193350657</v>
+        <v>7.812314689210109</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -15758,22 +15758,22 @@
         <v>-8.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="BW18" t="n">
         <v>47.99185562133789</v>
       </c>
       <c r="BX18" t="n">
-        <v>131.1061234270398</v>
+        <v>131.1054577321602</v>
       </c>
       <c r="BY18" t="n">
-        <v>243.2018589571588</v>
+        <v>243.2006240931572</v>
       </c>
       <c r="BZ18" t="n">
         <v>133.3107100592719</v>
@@ -15794,13 +15794,13 @@
         <v>56.36047046127493</v>
       </c>
       <c r="CF18" t="n">
-        <v>141.8581323873512</v>
+        <v>141.8578948174911</v>
       </c>
       <c r="CG18" t="n">
-        <v>126.4232349858667</v>
+        <v>126.4229021384269</v>
       </c>
       <c r="CH18" t="n">
-        <v>113.78091148728</v>
+        <v>113.7806119245842</v>
       </c>
       <c r="CI18" t="n">
         <v>8</v>
@@ -15812,10 +15812,10 @@
         <v>5.4</v>
       </c>
       <c r="CL18" t="n">
-        <v>137.0837926856309</v>
+        <v>137.0831684907714</v>
       </c>
       <c r="CM18" t="n">
-        <v>195.5879295575289</v>
+        <v>195.5874345363277</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>-0.1416741793906717</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-9.654866496095483</v>
+        <v>-9.654873160851507</v>
       </c>
       <c r="DA18" t="b">
         <v>1</v>
@@ -16098,10 +16098,10 @@
         <v>17.32999992370605</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.62120828010145</v>
+        <v>10.62120825073235</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.70234135958819</v>
+        <v>19.70234130510852</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.45880897049025</v>
@@ -16110,25 +16110,25 @@
         <v>36.8907150460014</v>
       </c>
       <c r="CB19" t="n">
-        <v>41.91990552166546</v>
+        <v>41.91990550878272</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.52256326828227</v>
+        <v>34.52256327451072</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.65458541713855</v>
+        <v>18.654585451202</v>
       </c>
       <c r="CE19" t="n">
         <v>31.24600421044032</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.48498911337235</v>
+        <v>31.48498910950513</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.52256326828227</v>
+        <v>34.52256327451072</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.07030694145404</v>
+        <v>31.07030694705965</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -16140,10 +16140,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>79.28624973017078</v>
+        <v>79.28624976251702</v>
       </c>
       <c r="CM19" t="n">
-        <v>81.67910705125507</v>
+        <v>81.67910702893994</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>73.87</v>
+        <v>73.89</v>
       </c>
       <c r="BJ20" t="n">
         <v>-30.3</v>
@@ -16414,10 +16414,10 @@
         <v>-48.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>-16.7</v>
+        <v>-16.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BV20" t="n">
         <v>0.71</v>
@@ -16426,10 +16426,10 @@
         <v>9.739999771118164</v>
       </c>
       <c r="BX20" t="n">
-        <v>9.752333606899221</v>
+        <v>9.754236617904695</v>
       </c>
       <c r="BY20" t="n">
-        <v>18.09057884079806</v>
+        <v>18.09410892621321</v>
       </c>
       <c r="BZ20" t="n">
         <v>24.48861422529709</v>
@@ -16438,25 +16438,25 @@
         <v>17.58365889509133</v>
       </c>
       <c r="CB20" t="n">
-        <v>37.93100542536856</v>
+        <v>37.92942696620967</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.34821912835721</v>
+        <v>24.34739855870606</v>
       </c>
       <c r="CD20" t="n">
-        <v>12.49494170068755</v>
+        <v>12.49077182297235</v>
       </c>
       <c r="CE20" t="n">
         <v>9.739999771118164</v>
       </c>
       <c r="CF20" t="n">
-        <v>19.30366894920215</v>
+        <v>19.30352697293907</v>
       </c>
       <c r="CG20" t="n">
-        <v>17.83711886794469</v>
+        <v>17.83888391065227</v>
       </c>
       <c r="CH20" t="n">
-        <v>16.05340698115022</v>
+        <v>16.05499551958705</v>
       </c>
       <c r="CI20" t="n">
         <v>8</v>
@@ -16468,10 +16468,10 @@
         <v>3.9</v>
       </c>
       <c r="CL20" t="n">
-        <v>64.81937739622015</v>
+        <v>64.83568682613954</v>
       </c>
       <c r="CM20" t="n">
-        <v>98.18962425895481</v>
+        <v>98.18816659708196</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -16658,13 +16658,13 @@
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AS21" t="b">
         <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>5449639424</v>
+        <v>3429433856</v>
       </c>
       <c r="AU21" t="n">
         <v>6.37</v>
@@ -16742,7 +16742,7 @@
         <v>-38.2</v>
       </c>
       <c r="BT21" t="n">
-        <v>-18.5</v>
+        <v>-18.4</v>
       </c>
       <c r="BU21" t="n">
         <v>1.47</v>
@@ -16754,10 +16754,10 @@
         <v>10.47999954223633</v>
       </c>
       <c r="BX21" t="n">
-        <v>9.072864345344986</v>
+        <v>9.072864391128032</v>
       </c>
       <c r="BY21" t="n">
-        <v>16.83016336061495</v>
+        <v>16.8301634455425</v>
       </c>
       <c r="BZ21" t="n">
         <v>21.79905713259518</v>
@@ -16766,25 +16766,25 @@
         <v>12.87581943989401</v>
       </c>
       <c r="CB21" t="n">
-        <v>33.73326028787612</v>
+        <v>33.73326015275214</v>
       </c>
       <c r="CC21" t="n">
-        <v>25.6201369124789</v>
+        <v>25.62013687860695</v>
       </c>
       <c r="CD21" t="n">
-        <v>13.06488825106885</v>
+        <v>13.06488810288561</v>
       </c>
       <c r="CE21" t="n">
         <v>9.30550460634233</v>
       </c>
       <c r="CF21" t="n">
-        <v>17.78771179202691</v>
+        <v>17.78771176871834</v>
       </c>
       <c r="CG21" t="n">
-        <v>14.9475258058419</v>
+        <v>14.94752577421406</v>
       </c>
       <c r="CH21" t="n">
-        <v>13.45277322525771</v>
+        <v>13.45277319679265</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -16796,10 +16796,10 @@
         <v>3.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>28.36616233655887</v>
+        <v>28.36616206494569</v>
       </c>
       <c r="CM21" t="n">
-        <v>69.73008176516764</v>
+        <v>69.73008154275759</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>3.46</v>
       </c>
       <c r="BI22" t="n">
-        <v>89.91</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="BJ22" t="n">
         <v>23.5</v>
@@ -17070,49 +17070,49 @@
         <v>-12.2</v>
       </c>
       <c r="BT22" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW22" t="n">
         <v>34.38000106811523</v>
       </c>
       <c r="BX22" t="n">
-        <v>24.72393448319795</v>
+        <v>24.72347832048936</v>
       </c>
       <c r="BY22" t="n">
-        <v>31.08816167921737</v>
+        <v>31.08887020637266</v>
       </c>
       <c r="BZ22" t="n">
-        <v>34.57831681460159</v>
+        <v>34.57974289034262</v>
       </c>
       <c r="CA22" t="n">
         <v>36.14131846677351</v>
       </c>
       <c r="CB22" t="n">
-        <v>48.68948635977289</v>
+        <v>48.69040290507824</v>
       </c>
       <c r="CC22" t="n">
-        <v>48.57168418558451</v>
+        <v>48.57188486807643</v>
       </c>
       <c r="CD22" t="n">
-        <v>16.52565915624632</v>
+        <v>16.52668479248031</v>
       </c>
       <c r="CE22" t="n">
         <v>29.95270377341624</v>
       </c>
       <c r="CF22" t="n">
-        <v>33.7839081148513</v>
+        <v>33.78438577787867</v>
       </c>
       <c r="CG22" t="n">
-        <v>32.83323924690948</v>
+        <v>32.83430654835764</v>
       </c>
       <c r="CH22" t="n">
-        <v>29.54991532221853</v>
+        <v>29.55087589352188</v>
       </c>
       <c r="CI22" t="n">
         <v>8</v>
@@ -17124,10 +17124,10 @@
         <v>2.9</v>
       </c>
       <c r="CL22" t="n">
-        <v>-14.04911458940072</v>
+        <v>-14.04632060663894</v>
       </c>
       <c r="CM22" t="n">
-        <v>-1.733836343061557</v>
+        <v>-1.732446980023372</v>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="DD22" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.9, +0.9% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x0.8, +0.9% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
         <v>0.76</v>
       </c>
       <c r="BI23" t="n">
-        <v>32.32</v>
+        <v>32.33</v>
       </c>
       <c r="BJ23" t="n">
         <v>3.2</v>
@@ -17406,22 +17406,22 @@
         <v>-31.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>-21.4</v>
+        <v>-21.3</v>
       </c>
       <c r="BU23" t="n">
         <v>1.46</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="BW23" t="n">
         <v>10.98999977111816</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.42436230629624</v>
+        <v>3.424809591929229</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.352192078179525</v>
+        <v>6.353021793028721</v>
       </c>
       <c r="BZ23" t="n">
         <v>19.65148407116271</v>
@@ -17430,13 +17430,13 @@
         <v>18.513475240297</v>
       </c>
       <c r="CB23" t="n">
-        <v>20.93338770324559</v>
+        <v>20.93333042328002</v>
       </c>
       <c r="CC23" t="n">
-        <v>15.91678365913704</v>
+        <v>15.9166954243071</v>
       </c>
       <c r="CD23" t="n">
-        <v>13.05348853535147</v>
+        <v>13.05292134138598</v>
       </c>
       <c r="CE23" t="n">
         <v>28.64218279833469</v>
@@ -17492,7 +17492,7 @@
         <v>-20.64982333269847</v>
       </c>
       <c r="CZ23" t="n">
-        <v>-33.44154600225495</v>
+        <v>-33.44156184895316</v>
       </c>
       <c r="DA23" t="b">
         <v>1</v>
@@ -17722,22 +17722,22 @@
         <v>-27.1</v>
       </c>
       <c r="BT24" t="n">
-        <v>-9.9</v>
+        <v>-9.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BV24" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BW24" t="n">
         <v>3.525049924850464</v>
       </c>
       <c r="BX24" t="n">
-        <v>5.015081650343956</v>
+        <v>5.015290523664889</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.3019588829008</v>
+        <v>7.30226300245608</v>
       </c>
       <c r="BZ24" t="n">
         <v>6.558232418326445</v>
@@ -17756,7 +17756,7 @@
         <v>2.269402021603749</v>
       </c>
       <c r="CF24" t="n">
-        <v>5.5751373139403</v>
+        <v>5.575222812753002</v>
       </c>
       <c r="CG24" t="n">
         <v>5.913671306074423</v>
@@ -17777,7 +17777,7 @@
         <v>50.98521408013133</v>
       </c>
       <c r="CM24" t="n">
-        <v>58.15768380008981</v>
+        <v>58.16010926397046</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -18056,10 +18056,10 @@
         <v>14.0600004196167</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.318536261991897</v>
+        <v>4.318536256933776</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.01088476599497</v>
+        <v>8.010884756612157</v>
       </c>
       <c r="BZ25" t="n">
         <v>24.13147740413487</v>
@@ -18068,25 +18068,25 @@
         <v>20.35919220371624</v>
       </c>
       <c r="CB25" t="n">
-        <v>29.81638085694662</v>
+        <v>29.81638086056989</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.74090519046545</v>
+        <v>16.74090519151497</v>
       </c>
       <c r="CD25" t="n">
-        <v>18.68436341704097</v>
+        <v>18.68436342508419</v>
       </c>
       <c r="CE25" t="n">
         <v>14.0600004196167</v>
       </c>
       <c r="CF25" t="n">
-        <v>18.82902917970226</v>
+        <v>18.82902918017843</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.68436341704097</v>
+        <v>18.68436342508419</v>
       </c>
       <c r="CH25" t="n">
-        <v>16.81592707533688</v>
+        <v>16.81592708257578</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -18098,10 +18098,10 @@
         <v>6.9</v>
       </c>
       <c r="CL25" t="n">
-        <v>19.60118473307491</v>
+        <v>19.60118478456068</v>
       </c>
       <c r="CM25" t="n">
-        <v>33.91912245914121</v>
+        <v>33.91912246252795</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -18370,22 +18370,22 @@
         <v>-57.5</v>
       </c>
       <c r="BT26" t="n">
-        <v>-28.7</v>
+        <v>-28.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BV26" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BW26" t="n">
         <v>7.639999866485596</v>
       </c>
       <c r="BX26" t="n">
-        <v>3.539988484258922</v>
+        <v>3.539988480383161</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.566678638300299</v>
+        <v>6.566678631110765</v>
       </c>
       <c r="BZ26" t="n">
         <v>24.15990411239478</v>
@@ -18394,13 +18394,13 @@
         <v>22.4844233478593</v>
       </c>
       <c r="CB26" t="n">
-        <v>31.46614681464786</v>
+        <v>31.46614680972297</v>
       </c>
       <c r="CC26" t="n">
-        <v>9.614841882991668</v>
+        <v>9.614841883373693</v>
       </c>
       <c r="CD26" t="n">
-        <v>17.21495361567607</v>
+        <v>17.21495362072044</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="inlineStr"/>
@@ -18682,22 +18682,22 @@
         <v>-20</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BV27" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BW27" t="n">
         <v>12.84000015258789</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.050127624319108</v>
+        <v>8.050127599998383</v>
       </c>
       <c r="BY27" t="n">
-        <v>14.93298674311194</v>
+        <v>14.932986697997</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.59952054530692</v>
@@ -18718,7 +18718,7 @@
         <v>6.103131550478226</v>
       </c>
       <c r="CF27" t="n">
-        <v>10.9291765669031</v>
+        <v>10.92917655698372</v>
       </c>
       <c r="CG27" t="n">
         <v>11.06929470524033</v>
@@ -18739,7 +18739,7 @@
         <v>-22.41148663297802</v>
       </c>
       <c r="CM27" t="n">
-        <v>-14.88180344997629</v>
+        <v>-14.88180352723005</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -19022,10 +19022,10 @@
         <v>26.86000061035156</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.115263311955315</v>
+        <v>7.115263333060311</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.19881344367711</v>
+        <v>13.19881348282688</v>
       </c>
       <c r="BZ28" t="n">
         <v>35.80432676933181</v>
@@ -19034,19 +19034,19 @@
         <v>28.29365159335656</v>
       </c>
       <c r="CB28" t="n">
-        <v>45.03018693888243</v>
+        <v>45.03018690797735</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.50039357303511</v>
+        <v>26.50039356777111</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.22423178149021</v>
+        <v>29.22423174337965</v>
       </c>
       <c r="CE28" t="n">
         <v>23.5668842743778</v>
       </c>
       <c r="CF28" t="n">
-        <v>28.80264119630729</v>
+        <v>28.80264119128874</v>
       </c>
       <c r="CG28" t="n">
         <v>28.29365159335656</v>
@@ -19067,7 +19067,7 @@
         <v>-5.196255192163946</v>
       </c>
       <c r="CM28" t="n">
-        <v>7.23246664859365</v>
+        <v>7.232466629909529</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>-7.60233611170672</v>
       </c>
       <c r="CZ28" t="n">
-        <v>-23.86224665397592</v>
+        <v>-23.86225492369548</v>
       </c>
       <c r="DA28" t="b">
         <v>1</v>
@@ -19287,7 +19287,7 @@
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="n">
-        <v>100.83</v>
+        <v>100.82</v>
       </c>
       <c r="BJ29" t="n">
         <v>-0.1</v>
@@ -19318,22 +19318,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="BT29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU29" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BV29" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW29" t="n">
         <v>37.18999862670898</v>
       </c>
       <c r="BX29" t="n">
-        <v>34.07781575837959</v>
+        <v>34.07294329184204</v>
       </c>
       <c r="BY29" t="n">
-        <v>49.61729974420069</v>
+        <v>49.61020543292201</v>
       </c>
       <c r="BZ29" t="n">
         <v>49.2081406765615</v>
@@ -19350,13 +19350,13 @@
       </c>
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="n">
-        <v>48.10185529073987</v>
+        <v>48.09886359628581</v>
       </c>
       <c r="CG29" t="n">
-        <v>49.4127202103811</v>
+        <v>49.40917305474176</v>
       </c>
       <c r="CH29" t="n">
-        <v>44.47144818934299</v>
+        <v>44.46825574926758</v>
       </c>
       <c r="CI29" t="n">
         <v>4</v>
@@ -19368,10 +19368,10 @@
         <v>1.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>19.57905305595962</v>
+        <v>19.57046891991958</v>
       </c>
       <c r="CM29" t="n">
-        <v>29.34083642636718</v>
+        <v>29.33279207421733</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -19654,10 +19654,10 @@
         <v>21.52000045776367</v>
       </c>
       <c r="BX30" t="n">
-        <v>3.029635325999941</v>
+        <v>3.029635323010476</v>
       </c>
       <c r="BY30" t="n">
-        <v>5.61997352972989</v>
+        <v>5.619973524184433</v>
       </c>
       <c r="BZ30" t="n">
         <v>32.85023111352173</v>
@@ -19666,7 +19666,7 @@
         <v>27.39136539639765</v>
       </c>
       <c r="CB30" t="n">
-        <v>42.07544947355464</v>
+        <v>42.07544946873292</v>
       </c>
       <c r="CC30" t="n">
         <v>10.85340539909456</v>
@@ -19876,7 +19876,7 @@
         <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="AS31" t="b">
         <v>1</v>
@@ -19972,10 +19972,10 @@
         <v>11.10000038146973</v>
       </c>
       <c r="BX31" t="n">
-        <v>1.917937789738674</v>
+        <v>1.917937792372778</v>
       </c>
       <c r="BY31" t="n">
-        <v>3.55777459996524</v>
+        <v>3.557774604851503</v>
       </c>
       <c r="BZ31" t="n">
         <v>27.96102757689617</v>
@@ -19984,7 +19984,7 @@
         <v>23.67867811885924</v>
       </c>
       <c r="CB31" t="n">
-        <v>36.75877087041584</v>
+        <v>36.75877087742677</v>
       </c>
       <c r="CC31" t="n">
         <v>9.158754146</v>
@@ -20286,10 +20286,10 @@
         <v>31.13999938964844</v>
       </c>
       <c r="BX32" t="n">
-        <v>7.388909085479433</v>
+        <v>7.388909098999219</v>
       </c>
       <c r="BY32" t="n">
-        <v>13.70642635356435</v>
+        <v>13.70642637864355</v>
       </c>
       <c r="BZ32" t="n">
         <v>62.61077267266187</v>
@@ -20298,7 +20298,7 @@
         <v>36.53770887188449</v>
       </c>
       <c r="CB32" t="n">
-        <v>86.57734719900435</v>
+        <v>86.57734722772622</v>
       </c>
       <c r="CC32" t="n">
         <v>22.51480113099953</v>
@@ -20582,35 +20582,35 @@
         <v>22.73999977111816</v>
       </c>
       <c r="BX33" t="n">
-        <v>16.32028057716677</v>
+        <v>16.32028063783208</v>
       </c>
       <c r="BY33" t="n">
-        <v>29.66719088675526</v>
+        <v>29.66719087753363</v>
       </c>
       <c r="BZ33" t="n">
-        <v>50.82005059162305</v>
+        <v>50.82005038691943</v>
       </c>
       <c r="CA33" t="n">
         <v>49.41817723779874</v>
       </c>
       <c r="CB33" t="n">
-        <v>62.21486264250041</v>
+        <v>62.2148626693532</v>
       </c>
       <c r="CC33" t="n">
-        <v>45.81119023926416</v>
+        <v>45.81119022606887</v>
       </c>
       <c r="CD33" t="n">
-        <v>24.84311435356077</v>
+        <v>24.84311427855419</v>
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>35.65467807370231</v>
+        <v>35.6546780320885</v>
       </c>
       <c r="CG33" t="n">
-        <v>37.73919056300971</v>
+        <v>37.73919055180126</v>
       </c>
       <c r="CH33" t="n">
-        <v>33.96527150670875</v>
+        <v>33.96527149662113</v>
       </c>
       <c r="CI33" t="n">
         <v>4</v>
@@ -20622,10 +20622,10 @@
         <v>3.1</v>
       </c>
       <c r="CL33" t="n">
-        <v>49.36355254430425</v>
+        <v>49.36355249994359</v>
       </c>
       <c r="CM33" t="n">
-        <v>56.79278114587736</v>
+        <v>56.79278096287908</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -20892,10 +20892,10 @@
         <v>-32.1</v>
       </c>
       <c r="BT34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BU34" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="BV34" t="n">
         <v>0.44</v>
@@ -20904,10 +20904,10 @@
         <v>32.18000030517578</v>
       </c>
       <c r="BX34" t="n">
-        <v>3.192274477515815</v>
+        <v>3.192481966833107</v>
       </c>
       <c r="BY34" t="n">
-        <v>5.921669155791836</v>
+        <v>5.922054048475414</v>
       </c>
       <c r="BZ34" t="n">
         <v>32.5982418993562</v>
@@ -20916,7 +20916,7 @@
         <v>22.82235087014609</v>
       </c>
       <c r="CB34" t="n">
-        <v>40.32047761948458</v>
+        <v>40.3206997028517</v>
       </c>
       <c r="CC34" t="n">
         <v>10.59424454785779</v>
@@ -20976,7 +20976,7 @@
       <c r="CV34" t="inlineStr"/>
       <c r="CW34" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX34" t="n">
@@ -21230,10 +21230,10 @@
         <v>33.22999954223633</v>
       </c>
       <c r="BX35" t="n">
-        <v>15.05518490102872</v>
+        <v>15.05518488751047</v>
       </c>
       <c r="BY35" t="n">
-        <v>27.92736799140826</v>
+        <v>27.92736796633193</v>
       </c>
       <c r="BZ35" t="n">
         <v>19.95908857364602</v>
@@ -21242,7 +21242,7 @@
         <v>36.83662170557399</v>
       </c>
       <c r="CB35" t="n">
-        <v>26.8774969786999</v>
+        <v>26.87749697012078</v>
       </c>
       <c r="CC35" t="n">
         <v>15.03391666666667</v>
@@ -21254,7 +21254,7 @@
         <v>76.15609957570291</v>
       </c>
       <c r="CF35" t="n">
-        <v>22.37178646581842</v>
+        <v>22.37178645907932</v>
       </c>
       <c r="CG35" t="n">
         <v>19.95908857364602</v>
@@ -21275,7 +21275,7 @@
         <v>-45.94288304623754</v>
       </c>
       <c r="CM35" t="n">
-        <v>-32.67593507672727</v>
+        <v>-32.67593509700744</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>-34.5</v>
       </c>
       <c r="BT36" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="BU36" t="n">
         <v>1.72</v>
@@ -21554,10 +21554,10 @@
         <v>23.11000061035156</v>
       </c>
       <c r="BX36" t="n">
-        <v>11.99003828103712</v>
+        <v>11.99003827108877</v>
       </c>
       <c r="BY36" t="n">
-        <v>22.24152101132386</v>
+        <v>22.24152099286967</v>
       </c>
       <c r="BZ36" t="n">
         <v>59.57344515314361</v>
@@ -21566,13 +21566,13 @@
         <v>49.87073049461024</v>
       </c>
       <c r="CB36" t="n">
-        <v>84.10530953904527</v>
+        <v>84.10530953738056</v>
       </c>
       <c r="CC36" t="n">
-        <v>30.75887775854143</v>
+        <v>30.75887776010265</v>
       </c>
       <c r="CD36" t="n">
-        <v>44.34953679368359</v>
+        <v>44.3495368096694</v>
       </c>
       <c r="CE36" t="n">
         <v>5.075463930454974</v>
@@ -21828,13 +21828,13 @@
         <v>79.81999999999999</v>
       </c>
       <c r="BP37" t="n">
-        <v>9.449999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BQ37" t="n">
         <v>14.81</v>
       </c>
       <c r="BR37" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="BS37" t="n">
         <v>-15.6</v>
@@ -21843,7 +21843,7 @@
         <v>-6.3</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BV37" t="n">
         <v>0.88</v>
@@ -21852,35 +21852,35 @@
         <v>12.5</v>
       </c>
       <c r="BX37" t="n">
-        <v>8.391835717791732</v>
+        <v>8.391865450100273</v>
       </c>
       <c r="BY37" t="n">
-        <v>14.24205142317515</v>
+        <v>14.24201355997039</v>
       </c>
       <c r="BZ37" t="n">
-        <v>19.62818999580421</v>
+        <v>19.62806827095434</v>
       </c>
       <c r="CA37" t="n">
         <v>17.48233699953358</v>
       </c>
       <c r="CB37" t="n">
-        <v>23.8202736582025</v>
+        <v>23.82024699044768</v>
       </c>
       <c r="CC37" t="n">
-        <v>17.41209079205115</v>
+        <v>17.41208256318266</v>
       </c>
       <c r="CD37" t="n">
-        <v>9.73241997420155</v>
+        <v>9.732369319862141</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>14.91854198220556</v>
+        <v>14.91850746105192</v>
       </c>
       <c r="CG37" t="n">
-        <v>15.82707110761315</v>
+        <v>15.82704806157652</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.24436399685184</v>
+        <v>14.24434325541887</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -21892,10 +21892,10 @@
         <v>2.3</v>
       </c>
       <c r="CL37" t="n">
-        <v>13.95491197481471</v>
+        <v>13.95474604335099</v>
       </c>
       <c r="CM37" t="n">
-        <v>19.34833585764451</v>
+        <v>19.34805968841533</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>0.93</v>
       </c>
       <c r="BI38" t="n">
-        <v>53.33</v>
+        <v>53.34</v>
       </c>
       <c r="BJ38" t="n">
         <v>17.8</v>
@@ -22134,22 +22134,22 @@
         <v>7.66</v>
       </c>
       <c r="BP38" t="n">
-        <v>12.38</v>
+        <v>12.4</v>
       </c>
       <c r="BQ38" t="n">
         <v>17.96</v>
       </c>
       <c r="BR38" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="BS38" t="n">
         <v>-20.2</v>
       </c>
       <c r="BT38" t="n">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BV38" t="n">
         <v>0.84</v>
@@ -22158,10 +22158,10 @@
         <v>14.32999992370605</v>
       </c>
       <c r="BX38" t="n">
-        <v>8.905449596806895</v>
+        <v>8.905780260521059</v>
       </c>
       <c r="BY38" t="n">
-        <v>16.51960900207679</v>
+        <v>16.52022238326656</v>
       </c>
       <c r="BZ38" t="n">
         <v>30.97430652350819</v>
@@ -22170,23 +22170,23 @@
         <v>29.43388465049835</v>
       </c>
       <c r="CB38" t="n">
-        <v>35.7534179562529</v>
+        <v>35.75351902359017</v>
       </c>
       <c r="CC38" t="n">
-        <v>25.58451048445651</v>
+        <v>25.58444332373756</v>
       </c>
       <c r="CD38" t="n">
-        <v>15.93419931312169</v>
+        <v>15.93378815263295</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>20.4959689017121</v>
+        <v>20.49618812275834</v>
       </c>
       <c r="CG38" t="n">
-        <v>21.05205974326665</v>
+        <v>21.05233285350207</v>
       </c>
       <c r="CH38" t="n">
-        <v>18.94685376893998</v>
+        <v>18.94709956815186</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -22198,10 +22198,10 @@
         <v>3.5</v>
       </c>
       <c r="CL38" t="n">
-        <v>32.21810097567614</v>
+        <v>32.2198162528093</v>
       </c>
       <c r="CM38" t="n">
-        <v>43.02839505118006</v>
+        <v>43.02992485611665</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>0.15</v>
       </c>
       <c r="BI39" t="n">
-        <v>228.24</v>
+        <v>228.23</v>
       </c>
       <c r="BJ39" t="n">
         <v>90.7</v>
@@ -22472,7 +22472,7 @@
         <v>-5.4</v>
       </c>
       <c r="BT39" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="BU39" t="n">
         <v>1.1</v>
@@ -22484,10 +22484,10 @@
         <v>5.900000095367432</v>
       </c>
       <c r="BX39" t="n">
-        <v>7.000436751513742</v>
+        <v>7.000252746958866</v>
       </c>
       <c r="BY39" t="n">
-        <v>12.98581017405799</v>
+        <v>12.9854688456087</v>
       </c>
       <c r="BZ39" t="n">
         <v>5.689592522825215</v>
@@ -22508,7 +22508,7 @@
         <v>5.412237592239494</v>
       </c>
       <c r="CF39" t="n">
-        <v>7.363870611343367</v>
+        <v>7.363804944717845</v>
       </c>
       <c r="CG39" t="n">
         <v>5.911462928079274</v>
@@ -22529,7 +22529,7 @@
         <v>-9.825143232645727</v>
       </c>
       <c r="CM39" t="n">
-        <v>24.81136427650803</v>
+        <v>24.81025128287313</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
       <c r="CV39" t="inlineStr"/>
       <c r="CW39" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX39" t="n">
@@ -22778,13 +22778,13 @@
         <v>6.67</v>
       </c>
       <c r="BP40" t="n">
-        <v>32.61</v>
+        <v>32.63</v>
       </c>
       <c r="BQ40" t="n">
         <v>48.4</v>
       </c>
       <c r="BR40" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="BS40" t="n">
         <v>-20.3</v>
@@ -22793,7 +22793,7 @@
         <v>-7</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BV40" t="n">
         <v>0.85</v>
@@ -22802,10 +22802,10 @@
         <v>38.59999847412109</v>
       </c>
       <c r="BX40" t="n">
-        <v>19.73061806082051</v>
+        <v>19.73089423195889</v>
       </c>
       <c r="BY40" t="n">
-        <v>36.60029650282205</v>
+        <v>36.60080880028374</v>
       </c>
       <c r="BZ40" t="n">
         <v>56.01861771983619</v>
@@ -22814,23 +22814,23 @@
         <v>42.32200432760474</v>
       </c>
       <c r="CB40" t="n">
-        <v>63.15628612000056</v>
+        <v>63.15584159669065</v>
       </c>
       <c r="CC40" t="n">
-        <v>45.3046605503917</v>
+        <v>45.30457425204306</v>
       </c>
       <c r="CD40" t="n">
-        <v>31.97509348978538</v>
+        <v>31.97454788608441</v>
       </c>
       <c r="CE40" t="inlineStr"/>
       <c r="CF40" t="n">
-        <v>39.41354820846762</v>
+        <v>39.41372375103047</v>
       </c>
       <c r="CG40" t="n">
-        <v>40.95247852660688</v>
+        <v>40.9526915261634</v>
       </c>
       <c r="CH40" t="n">
-        <v>36.8572306739462</v>
+        <v>36.85742237354706</v>
       </c>
       <c r="CI40" t="n">
         <v>4</v>
@@ -22842,10 +22842,10 @@
         <v>2.8</v>
       </c>
       <c r="CL40" t="n">
-        <v>-4.514942665977861</v>
+        <v>-4.514446034867914</v>
       </c>
       <c r="CM40" t="n">
-        <v>2.107641882141409</v>
+        <v>2.10809665563827</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>-10.5860548729689</v>
       </c>
       <c r="CZ40" t="n">
-        <v>-20.73761372683879</v>
+        <v>-20.73760748031875</v>
       </c>
       <c r="DA40" t="b">
         <v>1</v>
@@ -23104,13 +23104,13 @@
         <v>44.81</v>
       </c>
       <c r="BP41" t="n">
-        <v>20.47</v>
+        <v>20.58</v>
       </c>
       <c r="BQ41" t="n">
         <v>31.63</v>
       </c>
       <c r="BR41" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="BS41" t="n">
         <v>-17.7</v>
@@ -23122,43 +23122,43 @@
         <v>0.98</v>
       </c>
       <c r="BV41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BW41" t="n">
         <v>26.02000045776367</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.63763580878589</v>
+        <v>16.63820050436581</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.24291835350032</v>
+        <v>28.24299340528112</v>
       </c>
       <c r="BZ41" t="n">
-        <v>48.53822209804601</v>
+        <v>48.53670370467485</v>
       </c>
       <c r="CA41" t="n">
         <v>53.13771001269293</v>
       </c>
       <c r="CB41" t="n">
-        <v>57.10900732510467</v>
+        <v>57.10921877319265</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.1192701942657</v>
+        <v>43.1191674216231</v>
       </c>
       <c r="CD41" t="n">
-        <v>24.06622532388929</v>
+        <v>24.06559372317708</v>
       </c>
       <c r="CE41" t="n">
         <v>29.31279211564875</v>
       </c>
       <c r="CF41" t="n">
-        <v>37.5204726539917</v>
+        <v>37.52029745758203</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.21603115495723</v>
+        <v>36.21597976863593</v>
       </c>
       <c r="CH41" t="n">
-        <v>32.5944280394615</v>
+        <v>32.59438179177234</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -23170,10 +23170,10 @@
         <v>3.4</v>
       </c>
       <c r="CL41" t="n">
-        <v>25.26682346670059</v>
+        <v>25.26664572769846</v>
       </c>
       <c r="CM41" t="n">
-        <v>44.19858567987301</v>
+        <v>44.19791236547415</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -23456,37 +23456,37 @@
         <v>15</v>
       </c>
       <c r="BX42" t="n">
-        <v>5.819252146308642</v>
+        <v>5.819252150976158</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.57533093218367</v>
+        <v>8.575330928179753</v>
       </c>
       <c r="BZ42" t="n">
-        <v>11.041063292106</v>
+        <v>11.04106327809497</v>
       </c>
       <c r="CA42" t="n">
         <v>11.6021005542244</v>
       </c>
       <c r="CB42" t="n">
-        <v>10.00747570525726</v>
+        <v>10.00747569780333</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.94224989979434</v>
+        <v>14.94224989814919</v>
       </c>
       <c r="CD42" t="n">
-        <v>5.511532858762981</v>
+        <v>5.511532851205339</v>
       </c>
       <c r="CE42" t="n">
         <v>10.66215185399864</v>
       </c>
       <c r="CF42" t="n">
-        <v>9.770144655329492</v>
+        <v>9.770144651578974</v>
       </c>
       <c r="CG42" t="n">
-        <v>10.33481377962795</v>
+        <v>10.33481377590099</v>
       </c>
       <c r="CH42" t="n">
-        <v>9.301332401665153</v>
+        <v>9.301332398310889</v>
       </c>
       <c r="CI42" t="n">
         <v>8</v>
@@ -23498,10 +23498,10 @@
         <v>2.7</v>
       </c>
       <c r="CL42" t="n">
-        <v>-37.99111732223231</v>
+        <v>-37.99111734459407</v>
       </c>
       <c r="CM42" t="n">
-        <v>-34.86570229780338</v>
+        <v>-34.86570232280683</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -23784,10 +23784,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX43" t="n">
-        <v>2.442398968519651</v>
+        <v>2.442398974625466</v>
       </c>
       <c r="BY43" t="n">
-        <v>4.530650086603952</v>
+        <v>4.53065009793024</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.27964211470329</v>
@@ -23796,19 +23796,19 @@
         <v>14.98336145462187</v>
       </c>
       <c r="CB43" t="n">
-        <v>10.4410047338407</v>
+        <v>10.44100473483714</v>
       </c>
       <c r="CC43" t="n">
-        <v>7.313546441261829</v>
+        <v>7.313546440675511</v>
       </c>
       <c r="CD43" t="n">
-        <v>6.836171084418274</v>
+        <v>6.83617107903441</v>
       </c>
       <c r="CE43" t="n">
         <v>10.0481764999888</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.633221773634101</v>
+        <v>9.633221774541608</v>
       </c>
       <c r="CG43" t="n">
         <v>10.0481764999888</v>
@@ -23829,7 +23829,7 @@
         <v>0.9303438782148454</v>
       </c>
       <c r="CM43" t="n">
-        <v>7.513635408715458</v>
+        <v>7.513635418843867</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -24108,10 +24108,10 @@
         <v>11.27000045776367</v>
       </c>
       <c r="BX44" t="n">
-        <v>4.580215109676797</v>
+        <v>4.58021510402842</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.496299028450458</v>
+        <v>8.496299017972719</v>
       </c>
       <c r="BZ44" t="n">
         <v>25.35271749836479</v>
@@ -24120,25 +24120,25 @@
         <v>28.4368783520919</v>
       </c>
       <c r="CB44" t="n">
-        <v>23.79941181332184</v>
+        <v>23.7994118079225</v>
       </c>
       <c r="CC44" t="n">
-        <v>14.26838383309442</v>
+        <v>14.26838383365511</v>
       </c>
       <c r="CD44" t="n">
-        <v>13.22806971521074</v>
+        <v>13.22806972025587</v>
       </c>
       <c r="CE44" t="n">
         <v>4.74795751088484</v>
       </c>
       <c r="CF44" t="n">
-        <v>18.93029337342236</v>
+        <v>18.93029337171048</v>
       </c>
       <c r="CG44" t="n">
-        <v>19.03389782320813</v>
+        <v>19.03389782078881</v>
       </c>
       <c r="CH44" t="n">
-        <v>17.13050804088732</v>
+        <v>17.13050803870993</v>
       </c>
       <c r="CI44" t="n">
         <v>6</v>
@@ -24150,10 +24150,10 @@
         <v>6.2</v>
       </c>
       <c r="CL44" t="n">
-        <v>52.0009524852012</v>
+        <v>52.00095246588097</v>
       </c>
       <c r="CM44" t="n">
-        <v>67.9706531012753</v>
+        <v>67.97065308608563</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>-0.4259855571381532</v>
       </c>
       <c r="CZ44" t="n">
-        <v>-31.46237539541535</v>
+        <v>-31.4623710348404</v>
       </c>
       <c r="DA44" t="b">
         <v>0</v>
@@ -24430,10 +24430,10 @@
         <v>6.130000114440918</v>
       </c>
       <c r="BX45" t="n">
-        <v>7.268850402313239</v>
+        <v>7.26885037655265</v>
       </c>
       <c r="BY45" t="n">
-        <v>10.58344618576808</v>
+        <v>10.58344614826066</v>
       </c>
       <c r="BZ45" t="n">
         <v>8.090355480988013</v>
@@ -24452,7 +24452,7 @@
         <v>5.265969804073989</v>
       </c>
       <c r="CF45" t="n">
-        <v>8.150445889346333</v>
+        <v>8.150445878801666</v>
       </c>
       <c r="CG45" t="n">
         <v>8.453964503338835</v>
@@ -24473,7 +24473,7 @@
         <v>24.12019430604668</v>
       </c>
       <c r="CM45" t="n">
-        <v>32.95996308622726</v>
+        <v>32.95996291420984</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -24752,37 +24752,37 @@
         <v>37.56999969482422</v>
       </c>
       <c r="BX46" t="n">
-        <v>29.94470177465283</v>
+        <v>29.94470162183505</v>
       </c>
       <c r="BY46" t="n">
-        <v>36.48598297399831</v>
+        <v>36.4859831038838</v>
       </c>
       <c r="BZ46" t="n">
-        <v>41.07770266839308</v>
+        <v>41.07770302425769</v>
       </c>
       <c r="CA46" t="n">
         <v>49.93624997968088</v>
       </c>
       <c r="CB46" t="n">
-        <v>63.29224283333705</v>
+        <v>63.29224299544705</v>
       </c>
       <c r="CC46" t="n">
-        <v>16.18978532231166</v>
+        <v>16.18978533676625</v>
       </c>
       <c r="CD46" t="n">
-        <v>19.2877400927745</v>
+        <v>19.2877403636165</v>
       </c>
       <c r="CE46" t="n">
         <v>26.84451660947666</v>
       </c>
       <c r="CF46" t="n">
-        <v>35.38236528182813</v>
+        <v>35.38236537937048</v>
       </c>
       <c r="CG46" t="n">
-        <v>33.21534237432557</v>
+        <v>33.21534236285943</v>
       </c>
       <c r="CH46" t="n">
-        <v>29.89380813689302</v>
+        <v>29.89380812657349</v>
       </c>
       <c r="CI46" t="n">
         <v>8</v>
@@ -24794,10 +24794,10 @@
         <v>3.9</v>
       </c>
       <c r="CL46" t="n">
-        <v>-20.43170513783289</v>
+        <v>-20.43170516530036</v>
       </c>
       <c r="CM46" t="n">
-        <v>-5.822822546622131</v>
+        <v>-5.822822286993823</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>-4.708094976579402</v>
       </c>
       <c r="CZ46" t="n">
-        <v>-14.24720368446166</v>
+        <v>-14.2471960338154</v>
       </c>
       <c r="DA46" t="b">
         <v>0</v>
@@ -24980,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>176572465152</v>
+        <v>176880795648</v>
       </c>
       <c r="AU47" t="n">
         <v>6.95</v>
@@ -25046,47 +25046,47 @@
         <v>-22.3</v>
       </c>
       <c r="BT47" t="n">
-        <v>-9.9</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="BU47" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BV47" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="BW47" t="n">
         <v>16.23999977111816</v>
       </c>
       <c r="BX47" t="n">
-        <v>9.662594034148871</v>
+        <v>9.663025679786603</v>
       </c>
       <c r="BY47" t="n">
-        <v>17.80395787005187</v>
+        <v>17.80388362077796</v>
       </c>
       <c r="BZ47" t="n">
-        <v>30.75360295127685</v>
+        <v>30.75210094481649</v>
       </c>
       <c r="CA47" t="n">
         <v>29.51697433685933</v>
       </c>
       <c r="CB47" t="n">
-        <v>33.36711306351489</v>
+        <v>33.36712868411839</v>
       </c>
       <c r="CC47" t="n">
-        <v>27.99688530985606</v>
+        <v>27.99678874795141</v>
       </c>
       <c r="CD47" t="n">
-        <v>14.98126455701181</v>
+        <v>14.98072783156003</v>
       </c>
       <c r="CE47" t="inlineStr"/>
       <c r="CF47" t="n">
-        <v>21.55426004133341</v>
+        <v>21.55394974833312</v>
       </c>
       <c r="CG47" t="n">
-        <v>22.90042158995396</v>
+        <v>22.90033618436469</v>
       </c>
       <c r="CH47" t="n">
-        <v>20.61037943095857</v>
+        <v>20.61030256592822</v>
       </c>
       <c r="CI47" t="n">
         <v>4</v>
@@ -25098,10 +25098,10 @@
         <v>3.2</v>
       </c>
       <c r="CL47" t="n">
-        <v>26.91120518125165</v>
+        <v>26.91073187440782</v>
       </c>
       <c r="CM47" t="n">
-        <v>32.72327798714831</v>
+        <v>32.72136731593731</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>-12.211936357436</v>
       </c>
       <c r="CZ47" t="n">
-        <v>-23.53680185030922</v>
+        <v>-23.53680885638445</v>
       </c>
       <c r="DA47" t="b">
         <v>0</v>
@@ -25335,7 +25335,7 @@
         <v>1.75</v>
       </c>
       <c r="BI48" t="n">
-        <v>82.43000000000001</v>
+        <v>82.44</v>
       </c>
       <c r="BJ48" t="n">
         <v>21.5</v>
@@ -25380,37 +25380,37 @@
         <v>42.31999969482422</v>
       </c>
       <c r="BX48" t="n">
-        <v>30.68716207424264</v>
+        <v>30.68855827580621</v>
       </c>
       <c r="BY48" t="n">
-        <v>48.04756010654296</v>
+        <v>48.04420121888238</v>
       </c>
       <c r="BZ48" t="n">
-        <v>58.28760390655141</v>
+        <v>58.28087750463319</v>
       </c>
       <c r="CA48" t="n">
         <v>48.04405664848608</v>
       </c>
       <c r="CB48" t="n">
-        <v>77.10873493397129</v>
+        <v>77.10597595302087</v>
       </c>
       <c r="CC48" t="n">
-        <v>60.56421148544791</v>
+        <v>60.56363778061468</v>
       </c>
       <c r="CD48" t="n">
-        <v>29.13433659818424</v>
+        <v>29.13108925673961</v>
       </c>
       <c r="CE48" t="n">
         <v>74.487863906757</v>
       </c>
       <c r="CF48" t="n">
-        <v>53.29519120752294</v>
+        <v>53.2932825681175</v>
       </c>
       <c r="CG48" t="n">
-        <v>53.16758200654719</v>
+        <v>53.16253936175778</v>
       </c>
       <c r="CH48" t="n">
-        <v>47.85082380589247</v>
+        <v>47.846285425582</v>
       </c>
       <c r="CI48" t="n">
         <v>8</v>
@@ -25422,10 +25422,10 @@
         <v>2.6</v>
       </c>
       <c r="CL48" t="n">
-        <v>13.06905517710737</v>
+        <v>13.05833121599398</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.93381756106439</v>
+        <v>25.9293075435332</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -25704,10 +25704,10 @@
         <v>12.89999961853027</v>
       </c>
       <c r="BX49" t="n">
-        <v>1.587850267769202</v>
+        <v>1.58785026563191</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.94546224671187</v>
+        <v>2.945462242747192</v>
       </c>
       <c r="BZ49" t="n">
         <v>12.70817806286439</v>
@@ -25716,7 +25716,7 @@
         <v>9.283645602580306</v>
       </c>
       <c r="CB49" t="n">
-        <v>16.03939762280468</v>
+        <v>16.03939762057999</v>
       </c>
       <c r="CC49" t="n">
         <v>6.080625000000001</v>
@@ -26018,10 +26018,10 @@
         <v>32.13000106811523</v>
       </c>
       <c r="BX50" t="n">
-        <v>10.91768361836478</v>
+        <v>10.91768365038088</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.25230311206666</v>
+        <v>20.25230317145653</v>
       </c>
       <c r="BZ50" t="n">
         <v>55.7228421665611</v>
@@ -26030,19 +26030,19 @@
         <v>52.57254206560851</v>
       </c>
       <c r="CB50" t="n">
-        <v>58.5018002317337</v>
+        <v>58.50180022594713</v>
       </c>
       <c r="CC50" t="n">
-        <v>27.80644561837231</v>
+        <v>27.80644569601039</v>
       </c>
       <c r="CD50" t="n">
-        <v>35.43190399537107</v>
+        <v>35.43190395485661</v>
       </c>
       <c r="CE50" t="n">
         <v>51.92061598058906</v>
       </c>
       <c r="CF50" t="n">
-        <v>43.17263616718606</v>
+        <v>43.17263618014704</v>
       </c>
       <c r="CG50" t="n">
         <v>51.92061598058906</v>
@@ -26063,7 +26063,7 @@
         <v>45.43589427048617</v>
       </c>
       <c r="CM50" t="n">
-        <v>34.36861105500921</v>
+        <v>34.36861109534839</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>0.76</v>
       </c>
       <c r="BI51" t="n">
-        <v>49.73</v>
+        <v>49.72</v>
       </c>
       <c r="BJ51" t="n">
         <v>677</v>
@@ -26330,10 +26330,10 @@
         <v>-4.2</v>
       </c>
       <c r="BT51" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BV51" t="n">
         <v>0.66</v>
@@ -26342,10 +26342,10 @@
         <v>34.61000061035156</v>
       </c>
       <c r="BX51" t="n">
-        <v>14.99159691240479</v>
+        <v>14.99089211623212</v>
       </c>
       <c r="BY51" t="n">
-        <v>27.80941227251088</v>
+        <v>27.80810487561059</v>
       </c>
       <c r="BZ51" t="n">
         <v>55.92469610819002</v>
@@ -26354,25 +26354,25 @@
         <v>43.21451128531487</v>
       </c>
       <c r="CB51" t="n">
-        <v>71.19521688179286</v>
+        <v>71.19613402101925</v>
       </c>
       <c r="CC51" t="n">
-        <v>38.37351582026254</v>
+        <v>38.37368980746107</v>
       </c>
       <c r="CD51" t="n">
-        <v>39.93811962899871</v>
+        <v>39.93945248313675</v>
       </c>
       <c r="CE51" t="n">
         <v>20.91248002320442</v>
       </c>
       <c r="CF51" t="n">
-        <v>42.48113600289633</v>
+        <v>42.48129551484813</v>
       </c>
       <c r="CG51" t="n">
-        <v>39.93811962899871</v>
+        <v>39.93945248313675</v>
       </c>
       <c r="CH51" t="n">
-        <v>35.94430766609884</v>
+        <v>35.94550723482308</v>
       </c>
       <c r="CI51" t="n">
         <v>7</v>
@@ -26384,10 +26384,10 @@
         <v>4.7</v>
       </c>
       <c r="CL51" t="n">
-        <v>3.85526446754294</v>
+        <v>3.858730427390067</v>
       </c>
       <c r="CM51" t="n">
-        <v>22.74237287990852</v>
+        <v>22.74283376389865</v>
       </c>
       <c r="CN51" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
       <c r="CV51" t="inlineStr"/>
       <c r="CW51" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="CX51" t="n">
@@ -26435,7 +26435,7 @@
       </c>
       <c r="DD51" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral)</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.2%))</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>3079525120</v>
+        <v>3084497152</v>
       </c>
       <c r="AU52" t="n">
         <v>6.18</v>
@@ -26666,37 +26666,37 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.038973483700296</v>
+        <v>8.03897349794782</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.46347159462653</v>
+        <v>11.46347159863025</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.3221493103641</v>
+        <v>17.32214928571386</v>
       </c>
       <c r="CA52" t="n">
         <v>23.9690447919977</v>
       </c>
       <c r="CB52" t="n">
-        <v>24.68791743476308</v>
+        <v>24.68791744457923</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.04946809843237</v>
+        <v>21.04946809575444</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.614195297508775</v>
+        <v>8.61419528339119</v>
       </c>
       <c r="CE52" t="n">
         <v>10.40894108722206</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.69427013732686</v>
+        <v>15.69427013565457</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.39281045249532</v>
+        <v>14.39281044217206</v>
       </c>
       <c r="CH52" t="n">
-        <v>12.95352940724579</v>
+        <v>12.95352939795485</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -26708,10 +26708,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>23.24956351236844</v>
+        <v>23.24956342396756</v>
       </c>
       <c r="CM52" t="n">
-        <v>49.32701993857697</v>
+        <v>49.32701992266551</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -26972,10 +26972,10 @@
         <v>51.84999847412109</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.13692337233099</v>
+        <v>10.13692342351188</v>
       </c>
       <c r="BY53" t="n">
-        <v>18.80399285567399</v>
+        <v>18.80399295061453</v>
       </c>
       <c r="BZ53" t="n">
         <v>62.0047364424282</v>
@@ -26984,7 +26984,7 @@
         <v>46.3610505390373</v>
       </c>
       <c r="CB53" t="n">
-        <v>83.00242818812728</v>
+        <v>83.00242825279628</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>13.56974985377944</v>
+        <v>13.56974990248658</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -27015,7 +27015,7 @@
         <v>-79.57280557050289</v>
       </c>
       <c r="CM53" t="n">
-        <v>-73.82883268443634</v>
+        <v>-73.82883259049777</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -27280,22 +27280,22 @@
         <v>-42</v>
       </c>
       <c r="BT54" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BV54" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="BW54" t="n">
         <v>4.150000095367432</v>
       </c>
       <c r="BX54" t="n">
-        <v>0.960129478758594</v>
+        <v>0.960129475169628</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.781040183097192</v>
+        <v>1.78104017643966</v>
       </c>
       <c r="BZ54" t="n">
         <v>9.335738754434374</v>
@@ -27304,13 +27304,13 @@
         <v>8.797762939487081</v>
       </c>
       <c r="CB54" t="n">
-        <v>10.56095067798283</v>
+        <v>10.56095067674783</v>
       </c>
       <c r="CC54" t="n">
-        <v>4.233767827382088</v>
+        <v>4.233767827774382</v>
       </c>
       <c r="CD54" t="n">
-        <v>7.086068970711729</v>
+        <v>7.086068975297565</v>
       </c>
       <c r="CE54" t="n">
         <v>6.873907403846603</v>
@@ -27366,7 +27366,7 @@
         <v>2.977664499049459</v>
       </c>
       <c r="CZ54" t="n">
-        <v>-42.69404327219031</v>
+        <v>-42.69403944187445</v>
       </c>
       <c r="DA54" t="b">
         <v>0</v>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="DD54" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.4, +3.0% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.3, +3.0% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -27610,37 +27610,37 @@
         <v>22.79999923706055</v>
       </c>
       <c r="BX55" t="n">
-        <v>10.07191713793068</v>
+        <v>10.07191716805011</v>
       </c>
       <c r="BY55" t="n">
-        <v>14.90117516589922</v>
+        <v>14.9011751469824</v>
       </c>
       <c r="BZ55" t="n">
-        <v>19.71714211362529</v>
+        <v>19.7171420296318</v>
       </c>
       <c r="CA55" t="n">
         <v>21.50330999614219</v>
       </c>
       <c r="CB55" t="n">
-        <v>19.27267993342172</v>
+        <v>19.27267989637069</v>
       </c>
       <c r="CC55" t="n">
-        <v>23.40620860350367</v>
+        <v>23.4062085948841</v>
       </c>
       <c r="CD55" t="n">
-        <v>9.84549152088756</v>
+        <v>9.845491475908402</v>
       </c>
       <c r="CE55" t="n">
         <v>18.93959217930996</v>
       </c>
       <c r="CF55" t="n">
-        <v>17.20718958134004</v>
+        <v>17.20718956090995</v>
       </c>
       <c r="CG55" t="n">
-        <v>19.10613605636584</v>
+        <v>19.10613603784032</v>
       </c>
       <c r="CH55" t="n">
-        <v>17.19552245072926</v>
+        <v>17.19552243405629</v>
       </c>
       <c r="CI55" t="n">
         <v>8</v>
@@ -27652,10 +27652,10 @@
         <v>2.4</v>
       </c>
       <c r="CL55" t="n">
-        <v>-24.5810393590778</v>
+        <v>-24.58103943220484</v>
       </c>
       <c r="CM55" t="n">
-        <v>-24.52986773187959</v>
+        <v>-24.52986782148523</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -27916,10 +27916,10 @@
         <v>29.54999923706055</v>
       </c>
       <c r="BX56" t="n">
-        <v>15.44734655441504</v>
+        <v>15.447346554829</v>
       </c>
       <c r="BY56" t="n">
-        <v>28.65482785843991</v>
+        <v>28.6548278592078</v>
       </c>
       <c r="BZ56" t="n">
         <v>54.76048809665065</v>
@@ -27928,23 +27928,23 @@
         <v>49.53209541256255</v>
       </c>
       <c r="CB56" t="n">
-        <v>61.15959489301815</v>
+        <v>61.15959489291939</v>
       </c>
       <c r="CC56" t="n">
-        <v>36.65061373210148</v>
+        <v>36.65061373202645</v>
       </c>
       <c r="CD56" t="n">
-        <v>30.47171415215617</v>
+        <v>30.47171415158461</v>
       </c>
       <c r="CE56" t="inlineStr"/>
       <c r="CF56" t="n">
-        <v>33.87831906040177</v>
+        <v>33.87831906067848</v>
       </c>
       <c r="CG56" t="n">
-        <v>32.6527207952707</v>
+        <v>32.65272079561713</v>
       </c>
       <c r="CH56" t="n">
-        <v>29.38744871574363</v>
+        <v>29.38744871605542</v>
       </c>
       <c r="CI56" t="n">
         <v>4</v>
@@ -27956,10 +27956,10 @@
         <v>3.5</v>
       </c>
       <c r="CL56" t="n">
-        <v>-0.5500863807571754</v>
+        <v>-0.5500863797020528</v>
       </c>
       <c r="CM56" t="n">
-        <v>14.64744478880664</v>
+        <v>14.64744478974302</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -28216,34 +28216,34 @@
         <v>42.63</v>
       </c>
       <c r="BP57" t="n">
-        <v>9.449999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BQ57" t="n">
         <v>13.28</v>
       </c>
       <c r="BR57" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BS57" t="n">
         <v>-24.4</v>
       </c>
       <c r="BT57" t="n">
-        <v>-11</v>
+        <v>-10.9</v>
       </c>
       <c r="BU57" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BV57" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="BW57" t="n">
         <v>10.03999996185303</v>
       </c>
       <c r="BX57" t="n">
-        <v>12.50069639609318</v>
+        <v>12.50093834400256</v>
       </c>
       <c r="BY57" t="n">
-        <v>18.20101395271167</v>
+        <v>18.20136622886773</v>
       </c>
       <c r="BZ57" t="n">
         <v>16.70655993652344</v>
@@ -28262,7 +28262,7 @@
         <v>14.15379224573121</v>
       </c>
       <c r="CF57" t="n">
-        <v>15.82211689521474</v>
+        <v>15.82221593255898</v>
       </c>
       <c r="CG57" t="n">
         <v>15.43017609112732</v>
@@ -28283,7 +28283,7 @@
         <v>38.31831209939083</v>
       </c>
       <c r="CM57" t="n">
-        <v>57.59080632799662</v>
+        <v>57.59179275573183</v>
       </c>
       <c r="CN57" t="inlineStr">
         <is>
@@ -28558,10 +28558,10 @@
         <v>23.57999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.133603322546042</v>
+        <v>4.133603323496711</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.667834163322909</v>
+        <v>7.6678341650864</v>
       </c>
       <c r="BZ58" t="n">
         <v>28.5068429734585</v>
@@ -28570,13 +28570,13 @@
         <v>28.35212462119746</v>
       </c>
       <c r="CB58" t="n">
-        <v>25.61587731745816</v>
+        <v>25.61587731695162</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.973447624014614</v>
+        <v>2.973447623992884</v>
       </c>
       <c r="CD58" t="n">
-        <v>18.52992833239793</v>
+        <v>18.52992833131622</v>
       </c>
       <c r="CE58" t="n">
         <v>17.35772741057706</v>
@@ -28776,7 +28776,7 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AS59" t="b">
         <v>1</v>
@@ -28854,7 +28854,7 @@
         <v>53.79</v>
       </c>
       <c r="BR59" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="BS59" t="n">
         <v>-8.4</v>
@@ -28863,19 +28863,19 @@
         <v>7.1</v>
       </c>
       <c r="BU59" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="BV59" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BW59" t="n">
         <v>49.27000045776367</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.200611470210896</v>
+        <v>8.20058816185707</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.21213427724121</v>
+        <v>15.21209104024486</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.74077732281127</v>
@@ -28884,25 +28884,25 @@
         <v>12.27584654405641</v>
       </c>
       <c r="CB59" t="n">
-        <v>14.80525318134294</v>
+        <v>14.8053515205832</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.72427249111344</v>
+        <v>20.72428647874579</v>
       </c>
       <c r="CD59" t="n">
-        <v>11.10403957797762</v>
+        <v>11.10410759361875</v>
       </c>
       <c r="CE59" t="n">
         <v>12.93086890519374</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.37422547124344</v>
+        <v>14.37423969588889</v>
       </c>
       <c r="CG59" t="n">
-        <v>13.86806104326834</v>
+        <v>13.86811021288847</v>
       </c>
       <c r="CH59" t="n">
-        <v>12.4812549389415</v>
+        <v>12.48129919159962</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -28914,10 +28914,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-74.6676378668984</v>
+        <v>-74.66754805026008</v>
       </c>
       <c r="CM59" t="n">
-        <v>-70.8256031303153</v>
+        <v>-70.82557425951093</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="DD59" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.1, +0.2% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.2, +0.2% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -29122,7 +29122,7 @@
         <v>1</v>
       </c>
       <c r="AT60" t="n">
-        <v>36793753600</v>
+        <v>36849143808</v>
       </c>
       <c r="AU60" t="n">
         <v>11.16</v>
@@ -29188,34 +29188,34 @@
         <v>31.75</v>
       </c>
       <c r="BP60" t="n">
-        <v>16.19</v>
+        <v>16.7</v>
       </c>
       <c r="BQ60" t="n">
         <v>34.58</v>
       </c>
       <c r="BR60" t="n">
-        <v>113.5</v>
+        <v>107.1</v>
       </c>
       <c r="BS60" t="n">
         <v>0</v>
       </c>
       <c r="BT60" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="BU60" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BV60" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BW60" t="n">
         <v>34.58000183105469</v>
       </c>
       <c r="BX60" t="n">
-        <v>12.62461723141928</v>
+        <v>12.62461722312328</v>
       </c>
       <c r="BY60" t="n">
-        <v>23.41866496428276</v>
+        <v>23.41866494889368</v>
       </c>
       <c r="BZ60" t="n">
         <v>41.05600575819664</v>
@@ -29224,25 +29224,25 @@
         <v>33.48612882862086</v>
       </c>
       <c r="CB60" t="n">
-        <v>41.46139459785485</v>
+        <v>41.4613946098054</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.71416875359945</v>
+        <v>23.71416875517985</v>
       </c>
       <c r="CD60" t="n">
-        <v>24.3841517296257</v>
+        <v>24.38415174367913</v>
       </c>
       <c r="CE60" t="n">
         <v>26.42571186985053</v>
       </c>
       <c r="CF60" t="n">
-        <v>28.32135546668126</v>
+        <v>28.32135546716867</v>
       </c>
       <c r="CG60" t="n">
-        <v>25.40493179973812</v>
+        <v>25.40493180676483</v>
       </c>
       <c r="CH60" t="n">
-        <v>22.8644386197643</v>
+        <v>22.86443862608835</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -29254,10 +29254,10 @@
         <v>3.3</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.8795910669073</v>
+        <v>-33.87959104861914</v>
       </c>
       <c r="CM60" t="n">
-        <v>-18.0990342191157</v>
+        <v>-18.09903421770619</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
       </c>
       <c r="DD60" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.3, +0.8% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.2, +0.8% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -29540,10 +29540,10 @@
         <v>4.28000020980835</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.778660805906363</v>
+        <v>2.778660813780003</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.154415794956303</v>
+        <v>5.154415809561905</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.12731545832422</v>
@@ -29552,13 +29552,13 @@
         <v>14.72539108041317</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.19068596062079</v>
+        <v>15.19068597480548</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.474005170369459</v>
+        <v>9.474005169349537</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.53488945168863</v>
+        <v>6.534889444565822</v>
       </c>
       <c r="CE61" t="n">
         <v>0.7861618511746724</v>
@@ -29806,10 +29806,10 @@
         <v>0.3</v>
       </c>
       <c r="BH62" t="n">
-        <v>18.78</v>
+        <v>18.81</v>
       </c>
       <c r="BI62" t="n">
-        <v>92.40000000000001</v>
+        <v>92.41</v>
       </c>
       <c r="BJ62" t="n">
         <v>18.5</v>
@@ -29842,10 +29842,10 @@
         <v>-28.4</v>
       </c>
       <c r="BT62" t="n">
-        <v>-15.3</v>
+        <v>-15.1</v>
       </c>
       <c r="BU62" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BV62" t="n">
         <v>0.55</v>
@@ -29854,37 +29854,37 @@
         <v>29.32999992370605</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.49922394308147</v>
+        <v>13.50117694556878</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.38720731397909</v>
+        <v>14.38763657641599</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.57050055884073</v>
+        <v>15.56871272036214</v>
       </c>
       <c r="CA62" t="n">
         <v>30.61593302727409</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.74129445297603</v>
+        <v>14.74045327546539</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.53679207961267</v>
+        <v>30.53638493092586</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.445860913373785</v>
+        <v>6.444133677974002</v>
       </c>
       <c r="CE62" t="n">
         <v>38.20992116002673</v>
       </c>
       <c r="CF62" t="n">
-        <v>17.97097318416255</v>
+        <v>17.97063302199804</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.74129445297603</v>
+        <v>14.74045327546539</v>
       </c>
       <c r="CH62" t="n">
-        <v>13.26716500767843</v>
+        <v>13.26640794791885</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -29896,10 +29896,10 @@
         <v>5.9</v>
       </c>
       <c r="CL62" t="n">
-        <v>-54.76588802526656</v>
+        <v>-54.76846920413308</v>
       </c>
       <c r="CM62" t="n">
-        <v>-38.72835584415579</v>
+        <v>-38.72951561969414</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>-10.11339575968881</v>
       </c>
       <c r="CZ62" t="n">
-        <v>-28.85714780225045</v>
+        <v>-28.85716105626636</v>
       </c>
       <c r="DA62" t="b">
         <v>0</v>
@@ -30166,47 +30166,47 @@
         <v>-55.3</v>
       </c>
       <c r="BT63" t="n">
-        <v>-21.7</v>
+        <v>-21.2</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BV63" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BW63" t="n">
         <v>3.369999885559082</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.586813036026534</v>
+        <v>2.586813048877818</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.060288326167432</v>
+        <v>3.060288330555824</v>
       </c>
       <c r="BZ63" t="n">
-        <v>3.832748668444044</v>
+        <v>3.832748654899039</v>
       </c>
       <c r="CA63" t="n">
         <v>6.959812888294945</v>
       </c>
       <c r="CB63" t="n">
-        <v>5.752687125528321</v>
+        <v>5.752687132453274</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.494734991591379</v>
+        <v>8.494734988414685</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.763856226658184</v>
+        <v>1.763856215790111</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.635848751815835</v>
+        <v>4.635848751326528</v>
       </c>
       <c r="CG63" t="n">
-        <v>3.832748668444044</v>
+        <v>3.832748654899039</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.44947380159964</v>
+        <v>3.449473789409135</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -30218,10 +30218,10 @@
         <v>4.8</v>
       </c>
       <c r="CL63" t="n">
-        <v>2.358276520456704</v>
+        <v>2.358276158720662</v>
       </c>
       <c r="CM63" t="n">
-        <v>37.56228217339385</v>
+        <v>37.56228215887438</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -30452,10 +30452,10 @@
         <v>0.98</v>
       </c>
       <c r="BH64" t="n">
-        <v>23.89</v>
+        <v>23.85</v>
       </c>
       <c r="BI64" t="n">
-        <v>95.33</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="BJ64" t="n">
         <v>14.4</v>
@@ -30488,49 +30488,49 @@
         <v>0</v>
       </c>
       <c r="BT64" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="BU64" t="n">
         <v>0.96</v>
       </c>
       <c r="BV64" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="BW64" t="n">
         <v>18.68000030517578</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.765946778162812</v>
+        <v>8.765290487644545</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.219208895780836</v>
+        <v>9.219242373821302</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.671108529748095</v>
+        <v>9.671867763965263</v>
       </c>
       <c r="CA64" t="n">
         <v>16.92012354320182</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.23986100306584</v>
+        <v>9.240422228703936</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.54025529210638</v>
+        <v>17.54041704938382</v>
       </c>
       <c r="CD64" t="n">
-        <v>3.930721374930525</v>
+        <v>3.931472171283423</v>
       </c>
       <c r="CE64" t="n">
         <v>16.048074697233</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.41691251427866</v>
+        <v>11.41711378940464</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.455484766406968</v>
+        <v>9.456144996334601</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.509936289766271</v>
+        <v>8.510530496701142</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -30542,10 +30542,10 @@
         <v>4.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>-54.44359662345203</v>
+        <v>-54.44041564419526</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.88162565438872</v>
+        <v>-38.88054816443858</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
       </c>
       <c r="DD64" t="inlineStr">
         <is>
-          <t>Rompimento (vol x2.3, +0.7% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x2.1, +0.7% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -30814,37 +30814,37 @@
         <v>-53.8</v>
       </c>
       <c r="BT65" t="n">
-        <v>-15.9</v>
+        <v>-15.6</v>
       </c>
       <c r="BU65" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BV65" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BW65" t="n">
         <v>2.109999895095825</v>
       </c>
       <c r="BX65" t="n">
-        <v>0.6054130289764672</v>
+        <v>0.6054745296754893</v>
       </c>
       <c r="BY65" t="n">
-        <v>0.8658247507717745</v>
+        <v>0.8659005945458141</v>
       </c>
       <c r="BZ65" t="n">
-        <v>3.470891447776139</v>
+        <v>3.470842903424572</v>
       </c>
       <c r="CA65" t="n">
         <v>7.099910980401375</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.667995710633876</v>
+        <v>2.668090361952686</v>
       </c>
       <c r="CC65" t="n">
-        <v>2.232874172568285</v>
+        <v>2.232871388002991</v>
       </c>
       <c r="CD65" t="n">
-        <v>1.726797107216507</v>
+        <v>1.726769451582171</v>
       </c>
       <c r="CE65" t="n">
         <v>4.899183273787854</v>
@@ -31128,22 +31128,22 @@
         <v>-23.3</v>
       </c>
       <c r="BT66" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="BU66" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BV66" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="BW66" t="n">
         <v>34.25</v>
       </c>
       <c r="BX66" t="n">
-        <v>9.80569926423385</v>
+        <v>9.805953143272031</v>
       </c>
       <c r="BY66" t="n">
-        <v>18.18957213515379</v>
+        <v>18.19004308076962</v>
       </c>
       <c r="BZ66" t="n">
         <v>28.52372721558767</v>
@@ -31152,25 +31152,25 @@
         <v>21.17463256983125</v>
       </c>
       <c r="CB66" t="n">
-        <v>26.76983906172348</v>
+        <v>26.76923573081139</v>
       </c>
       <c r="CC66" t="n">
-        <v>22.98084687848322</v>
+        <v>22.98076548261489</v>
       </c>
       <c r="CD66" t="n">
-        <v>17.15398885696404</v>
+        <v>17.15346919703837</v>
       </c>
       <c r="CE66" t="n">
         <v>26.06463245419628</v>
       </c>
       <c r="CF66" t="n">
-        <v>21.3328673045217</v>
+        <v>21.33280735926519</v>
       </c>
       <c r="CG66" t="n">
-        <v>22.07773972415723</v>
+        <v>22.07769902622307</v>
       </c>
       <c r="CH66" t="n">
-        <v>19.86996575174151</v>
+        <v>19.86992912360077</v>
       </c>
       <c r="CI66" t="n">
         <v>8</v>
@@ -31182,10 +31182,10 @@
         <v>2.9</v>
       </c>
       <c r="CL66" t="n">
-        <v>-41.98550145476931</v>
+        <v>-41.98560839824594</v>
       </c>
       <c r="CM66" t="n">
-        <v>-37.71425604519212</v>
+        <v>-37.71443106783886</v>
       </c>
       <c r="CN66" t="inlineStr">
         <is>
@@ -31452,22 +31452,22 @@
         <v>-19.5</v>
       </c>
       <c r="BT67" t="n">
-        <v>-3.2</v>
+        <v>-3.1</v>
       </c>
       <c r="BU67" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BV67" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BW67" t="n">
         <v>8.399999618530273</v>
       </c>
       <c r="BX67" t="n">
-        <v>0.4994953431229125</v>
+        <v>0.4995474358854777</v>
       </c>
       <c r="BY67" t="n">
-        <v>0.9265638614930028</v>
+        <v>0.926660493567561</v>
       </c>
       <c r="BZ67" t="n">
         <v>9.44020313363241</v>
@@ -31476,13 +31476,13 @@
         <v>8.673354699458621</v>
       </c>
       <c r="CB67" t="n">
-        <v>10.36613958680074</v>
+        <v>10.36609051786619</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.7358242917928981</v>
+        <v>0.7358232843569932</v>
       </c>
       <c r="CD67" t="n">
-        <v>8.046346018841875</v>
+        <v>8.046276293721037</v>
       </c>
       <c r="CE67" t="inlineStr"/>
       <c r="CF67" t="inlineStr"/>
@@ -31731,7 +31731,7 @@
         <v>0.39</v>
       </c>
       <c r="BI68" t="n">
-        <v>12.16</v>
+        <v>12.17</v>
       </c>
       <c r="BJ68" t="n">
         <v>185</v>
@@ -31764,7 +31764,7 @@
         <v>-45.2</v>
       </c>
       <c r="BT68" t="n">
-        <v>-21.9</v>
+        <v>-21.7</v>
       </c>
       <c r="BU68" t="n">
         <v>1.62</v>
@@ -31776,10 +31776,10 @@
         <v>8.199999809265137</v>
       </c>
       <c r="BX68" t="n">
-        <v>1.575867733688149</v>
+        <v>1.576511909479872</v>
       </c>
       <c r="BY68" t="n">
-        <v>2.923234645991517</v>
+        <v>2.924429592085162</v>
       </c>
       <c r="BZ68" t="n">
         <v>24.03761006034581</v>
@@ -31788,13 +31788,13 @@
         <v>23.81825157629451</v>
       </c>
       <c r="CB68" t="n">
-        <v>25.7085448710588</v>
+        <v>25.70936139294823</v>
       </c>
       <c r="CC68" t="n">
-        <v>6.710898893159271</v>
+        <v>6.710859780780995</v>
       </c>
       <c r="CD68" t="n">
-        <v>17.93799255479411</v>
+        <v>17.9372516495655</v>
       </c>
       <c r="CE68" t="n">
         <v>13.41468215105991</v>
@@ -32081,19 +32081,19 @@
         <v>-2.1</v>
       </c>
       <c r="BU69" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BV69" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BW69" t="n">
         <v>21.17000007629395</v>
       </c>
       <c r="BX69" t="n">
-        <v>5.854056750535286</v>
+        <v>5.854145166759947</v>
       </c>
       <c r="BY69" t="n">
-        <v>10.85927527224296</v>
+        <v>10.8594392843397</v>
       </c>
       <c r="BZ69" t="n">
         <v>32.88423224043315</v>
@@ -32102,25 +32102,25 @@
         <v>33.87809571629486</v>
       </c>
       <c r="CB69" t="n">
-        <v>29.72142193618182</v>
+        <v>29.72141727365121</v>
       </c>
       <c r="CC69" t="n">
-        <v>25.31803145210941</v>
+        <v>25.31801731825158</v>
       </c>
       <c r="CD69" t="n">
-        <v>19.27270999334281</v>
+        <v>19.2726158477468</v>
       </c>
       <c r="CE69" t="n">
         <v>13.20520650594855</v>
       </c>
       <c r="CF69" t="n">
-        <v>23.59128187379337</v>
+        <v>23.59128916952369</v>
       </c>
       <c r="CG69" t="n">
-        <v>25.31803145210941</v>
+        <v>25.31801731825158</v>
       </c>
       <c r="CH69" t="n">
-        <v>22.78622830689847</v>
+        <v>22.78621558642642</v>
       </c>
       <c r="CI69" t="n">
         <v>7</v>
@@ -32132,10 +32132,10 @@
         <v>5.8</v>
       </c>
       <c r="CL69" t="n">
-        <v>7.634521609730016</v>
+        <v>7.634461522474445</v>
       </c>
       <c r="CM69" t="n">
-        <v>11.43732540752684</v>
+        <v>11.43735987011685</v>
       </c>
       <c r="CN69" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>-3.067765895663488</v>
       </c>
       <c r="CZ69" t="n">
-        <v>-21.02089962798474</v>
+        <v>-21.02089346708398</v>
       </c>
       <c r="DA69" t="b">
         <v>0</v>
@@ -32322,7 +32322,7 @@
         <v>1</v>
       </c>
       <c r="AR70" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="AS70" t="b">
         <v>1</v>
@@ -32394,22 +32394,22 @@
         <v>40.69</v>
       </c>
       <c r="BP70" t="n">
-        <v>21.8</v>
+        <v>21.86</v>
       </c>
       <c r="BQ70" t="n">
         <v>35.21</v>
       </c>
       <c r="BR70" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BS70" t="n">
         <v>-32.5</v>
       </c>
       <c r="BT70" t="n">
-        <v>-19.2</v>
+        <v>-19.1</v>
       </c>
       <c r="BU70" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BV70" t="n">
         <v>0.71</v>
@@ -32418,10 +32418,10 @@
         <v>23.75</v>
       </c>
       <c r="BX70" t="n">
-        <v>4.355873343514685</v>
+        <v>4.355978618233742</v>
       </c>
       <c r="BY70" t="n">
-        <v>8.080145052219741</v>
+        <v>8.080340336823591</v>
       </c>
       <c r="BZ70" t="n">
         <v>30.22934678194044</v>
@@ -32430,13 +32430,13 @@
         <v>25.67105067776809</v>
       </c>
       <c r="CB70" t="n">
-        <v>35.61319694296674</v>
+        <v>35.61307617820037</v>
       </c>
       <c r="CC70" t="n">
-        <v>11.8093217926881</v>
+        <v>11.80930977990107</v>
       </c>
       <c r="CD70" t="n">
-        <v>24.79799745869554</v>
+        <v>24.79783255637562</v>
       </c>
       <c r="CE70" t="n">
         <v>24.13715468420423</v>
@@ -32732,35 +32732,35 @@
         <v>23.34000015258789</v>
       </c>
       <c r="BX71" t="n">
-        <v>22.42103488584527</v>
+        <v>22.42103484860471</v>
       </c>
       <c r="BY71" t="n">
-        <v>28.79895002935875</v>
+        <v>28.79895001861679</v>
       </c>
       <c r="BZ71" t="n">
-        <v>39.07628426156025</v>
+        <v>39.0762843118892</v>
       </c>
       <c r="CA71" t="n">
         <v>62.09946198672523</v>
       </c>
       <c r="CB71" t="n">
-        <v>69.18752136168854</v>
+        <v>69.18752132196983</v>
       </c>
       <c r="CC71" t="n">
-        <v>41.79258400952772</v>
+        <v>41.79258401481802</v>
       </c>
       <c r="CD71" t="n">
-        <v>18.86266342435764</v>
+        <v>18.86266345919395</v>
       </c>
       <c r="CE71" t="inlineStr"/>
       <c r="CF71" t="n">
-        <v>40.31978570843763</v>
+        <v>40.31978570883111</v>
       </c>
       <c r="CG71" t="n">
-        <v>39.07628426156025</v>
+        <v>39.0762843118892</v>
       </c>
       <c r="CH71" t="n">
-        <v>35.16865583540422</v>
+        <v>35.16865588070029</v>
       </c>
       <c r="CI71" t="n">
         <v>7</v>
@@ -32772,10 +32772,10 @@
         <v>3.7</v>
       </c>
       <c r="CL71" t="n">
-        <v>50.67975837825689</v>
+        <v>50.67975857232743</v>
       </c>
       <c r="CM71" t="n">
-        <v>72.74972341406371</v>
+        <v>72.74972341574954</v>
       </c>
       <c r="CN71" t="inlineStr">
         <is>
@@ -33054,25 +33054,25 @@
         <v>17.27000045776367</v>
       </c>
       <c r="BX72" t="n">
-        <v>3.983351728858139</v>
+        <v>3.98335168570889</v>
       </c>
       <c r="BY72" t="n">
-        <v>6.851351501856511</v>
+        <v>6.851351448503979</v>
       </c>
       <c r="BZ72" t="n">
-        <v>23.49655306110428</v>
+        <v>23.496553132657</v>
       </c>
       <c r="CA72" t="n">
         <v>32.81823251300876</v>
       </c>
       <c r="CB72" t="n">
-        <v>16.54030069771808</v>
+        <v>16.54030067703286</v>
       </c>
       <c r="CC72" t="n">
-        <v>20.3019217884748</v>
+        <v>20.30192179312825</v>
       </c>
       <c r="CD72" t="n">
-        <v>11.62401153906429</v>
+        <v>11.62401156811237</v>
       </c>
       <c r="CE72" t="n">
         <v>21.74081326930276</v>
@@ -33124,7 +33124,7 @@
         <v>-1.592718182806219</v>
       </c>
       <c r="CZ72" t="n">
-        <v>-40.18283425804393</v>
+        <v>-40.1828262350358</v>
       </c>
       <c r="DA72" t="b">
         <v>0</v>
@@ -33368,10 +33368,10 @@
         <v>12.10000038146973</v>
       </c>
       <c r="BX73" t="n">
-        <v>2.000193688136084</v>
+        <v>2.000193692570833</v>
       </c>
       <c r="BY73" t="n">
-        <v>3.710359291492435</v>
+        <v>3.710359299718895</v>
       </c>
       <c r="BZ73" t="n">
         <v>16.12927616242192</v>
@@ -33380,7 +33380,7 @@
         <v>12.80877999251376</v>
       </c>
       <c r="CB73" t="n">
-        <v>21.0767321283653</v>
+        <v>21.07673213461143</v>
       </c>
       <c r="CC73" t="n">
         <v>9.395602678571429</v>
@@ -33666,35 +33666,35 @@
         <v>12.14999961853027</v>
       </c>
       <c r="BX74" t="n">
-        <v>10.27302895510258</v>
+        <v>10.27302894329599</v>
       </c>
       <c r="BY74" t="n">
-        <v>11.21723175685064</v>
+        <v>11.21723176490275</v>
       </c>
       <c r="BZ74" t="n">
-        <v>11.84528248699496</v>
+        <v>11.84528250911144</v>
       </c>
       <c r="CA74" t="n">
         <v>16.21040951658916</v>
       </c>
       <c r="CB74" t="n">
-        <v>19.5641608738874</v>
+        <v>19.56416088578844</v>
       </c>
       <c r="CC74" t="n">
-        <v>7.409931249492051</v>
+        <v>7.409931251064345</v>
       </c>
       <c r="CD74" t="n">
-        <v>5.054372714161318</v>
+        <v>5.05437273462921</v>
       </c>
       <c r="CE74" t="inlineStr"/>
       <c r="CF74" t="n">
-        <v>10.18636861211006</v>
+        <v>10.18636861709363</v>
       </c>
       <c r="CG74" t="n">
-        <v>10.74513035597661</v>
+        <v>10.74513035409937</v>
       </c>
       <c r="CH74" t="n">
-        <v>9.670617320378947</v>
+        <v>9.670617318689434</v>
       </c>
       <c r="CI74" t="n">
         <v>4</v>
@@ -33706,10 +33706,10 @@
         <v>1.6</v>
       </c>
       <c r="CL74" t="n">
-        <v>-20.40643930860671</v>
+        <v>-20.40643932251216</v>
       </c>
       <c r="CM74" t="n">
-        <v>-16.161572576722</v>
+        <v>-16.16157253570493</v>
       </c>
       <c r="CN74" t="inlineStr">
         <is>
@@ -33976,10 +33976,10 @@
         <v>-44.4</v>
       </c>
       <c r="BT75" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BU75" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BV75" t="n">
         <v>0.35</v>
@@ -33988,10 +33988,10 @@
         <v>3.990000009536743</v>
       </c>
       <c r="BX75" t="n">
-        <v>0.9693269118546918</v>
+        <v>0.9693873018669904</v>
       </c>
       <c r="BY75" t="n">
-        <v>1.798101421490453</v>
+        <v>1.798213444963267</v>
       </c>
       <c r="BZ75" t="n">
         <v>6.076724152455384</v>
@@ -34000,7 +34000,7 @@
         <v>4.034077793072167</v>
       </c>
       <c r="CB75" t="n">
-        <v>8.439146771151361</v>
+        <v>8.439243950481496</v>
       </c>
       <c r="CC75" t="n">
         <v>3.760485277130923</v>
@@ -34058,7 +34058,7 @@
         <v>4.450263855099923</v>
       </c>
       <c r="CZ75" t="n">
-        <v>-45.45317723920104</v>
+        <v>-45.45317360673609</v>
       </c>
       <c r="DA75" t="b">
         <v>0</v>
@@ -34276,34 +34276,34 @@
         <v>48.36</v>
       </c>
       <c r="BP76" t="n">
-        <v>24.75</v>
+        <v>25.13</v>
       </c>
       <c r="BQ76" t="n">
         <v>67.45</v>
       </c>
       <c r="BR76" t="n">
-        <v>120.2</v>
+        <v>116.9</v>
       </c>
       <c r="BS76" t="n">
         <v>-19.2</v>
       </c>
       <c r="BT76" t="n">
-        <v>-5.8</v>
+        <v>-5.9</v>
       </c>
       <c r="BU76" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="BV76" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BW76" t="n">
         <v>54.5</v>
       </c>
       <c r="BX76" t="n">
-        <v>39.63603097058764</v>
+        <v>39.63533179641133</v>
       </c>
       <c r="BY76" t="n">
-        <v>57.71006109317561</v>
+        <v>57.70904309557491</v>
       </c>
       <c r="BZ76" t="n">
         <v>35.35870243293824</v>
@@ -34322,13 +34322,13 @@
         <v>46.00869250560613</v>
       </c>
       <c r="CF76" t="n">
-        <v>42.45412222431214</v>
+        <v>42.45383602901597</v>
       </c>
       <c r="CG76" t="n">
-        <v>40.922904652349</v>
+        <v>40.92255506526084</v>
       </c>
       <c r="CH76" t="n">
-        <v>36.83061418711411</v>
+        <v>36.83029955873476</v>
       </c>
       <c r="CI76" t="n">
         <v>6</v>
@@ -34340,10 +34340,10 @@
         <v>6.4</v>
       </c>
       <c r="CL76" t="n">
-        <v>-32.42089139979063</v>
+        <v>-32.42146869956925</v>
       </c>
       <c r="CM76" t="n">
-        <v>-22.10252802878506</v>
+        <v>-22.10305315776886</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>1.06</v>
       </c>
       <c r="BI77" t="n">
-        <v>64.59999999999999</v>
+        <v>64.61</v>
       </c>
       <c r="BJ77" t="n">
         <v>270</v>
@@ -34598,7 +34598,7 @@
         <v>23.06</v>
       </c>
       <c r="BP77" t="n">
-        <v>26.61</v>
+        <v>26.62</v>
       </c>
       <c r="BQ77" t="n">
         <v>37.14</v>
@@ -34613,7 +34613,7 @@
         <v>-13.6</v>
       </c>
       <c r="BU77" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="BV77" t="n">
         <v>0.61</v>
@@ -34622,10 +34622,10 @@
         <v>27.6299991607666</v>
       </c>
       <c r="BX77" t="n">
-        <v>12.90446969867322</v>
+        <v>12.90524673040236</v>
       </c>
       <c r="BY77" t="n">
-        <v>23.93779129103882</v>
+        <v>23.93923268489639</v>
       </c>
       <c r="BZ77" t="n">
         <v>37.05440170851796</v>
@@ -34634,19 +34634,19 @@
         <v>25.80913235694405</v>
       </c>
       <c r="CB77" t="n">
-        <v>44.39021537077427</v>
+        <v>44.38844778214269</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.45397719587856</v>
+        <v>42.45357889242229</v>
       </c>
       <c r="CD77" t="n">
-        <v>23.87936803739682</v>
+        <v>23.87756488864744</v>
       </c>
       <c r="CE77" t="n">
         <v>23.95070880105463</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.29750805753479</v>
+        <v>29.29728923062847</v>
       </c>
       <c r="CG77" t="n">
         <v>24.87992057899934</v>
@@ -34667,7 +34667,7 @@
         <v>-18.95791096188316</v>
       </c>
       <c r="CM77" t="n">
-        <v>6.03513915098477</v>
+        <v>6.03434716070983</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -34930,22 +34930,22 @@
         <v>22.24</v>
       </c>
       <c r="BP78" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="BQ78" t="n">
         <v>17.55</v>
       </c>
       <c r="BR78" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="BS78" t="n">
         <v>-17.4</v>
       </c>
       <c r="BT78" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="BU78" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BV78" t="n">
         <v>0.78</v>
@@ -34954,10 +34954,10 @@
         <v>14.5</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.339767809856903</v>
+        <v>2.33980008012506</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.340269287284554</v>
+        <v>4.340329148631985</v>
       </c>
       <c r="BZ78" t="n">
         <v>25.44701986754966</v>
@@ -34966,7 +34966,7 @@
         <v>19.48694742147536</v>
       </c>
       <c r="CB78" t="n">
-        <v>33.14658931629094</v>
+        <v>33.14664915519879</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -35244,13 +35244,13 @@
         <v>38.29</v>
       </c>
       <c r="BP79" t="n">
-        <v>10.16</v>
+        <v>10.22</v>
       </c>
       <c r="BQ79" t="n">
         <v>16.67</v>
       </c>
       <c r="BR79" t="n">
-        <v>39.3</v>
+        <v>38.5</v>
       </c>
       <c r="BS79" t="n">
         <v>-15.1</v>
@@ -35259,19 +35259,19 @@
         <v>-5.9</v>
       </c>
       <c r="BU79" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BV79" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="BW79" t="n">
         <v>14.14999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.254464993745623</v>
+        <v>9.254605910108262</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.16703256339813</v>
+        <v>17.16729396325083</v>
       </c>
       <c r="BZ79" t="n">
         <v>13.91889346291953</v>
@@ -35292,7 +35292,7 @@
         <v>11.70742099417638</v>
       </c>
       <c r="CF79" t="n">
-        <v>14.83223900702609</v>
+        <v>14.83228929655301</v>
       </c>
       <c r="CG79" t="n">
         <v>13.26759657778993</v>
@@ -35313,7 +35313,7 @@
         <v>-15.61245765424828</v>
       </c>
       <c r="CM79" t="n">
-        <v>4.821479907337856</v>
+        <v>4.821835310364508</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>1.63</v>
       </c>
       <c r="BI80" t="n">
-        <v>40.01</v>
+        <v>40.02</v>
       </c>
       <c r="BJ80" t="n">
         <v>4.4</v>
@@ -35580,47 +35580,47 @@
         <v>-54.2</v>
       </c>
       <c r="BT80" t="n">
-        <v>-23.4</v>
+        <v>-22.9</v>
       </c>
       <c r="BU80" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="BV80" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BW80" t="n">
         <v>2.369999885559082</v>
       </c>
       <c r="BX80" t="n">
-        <v>1.088826615760449</v>
+        <v>1.08914840413498</v>
       </c>
       <c r="BY80" t="n">
-        <v>1.553866781991795</v>
+        <v>1.554199994179975</v>
       </c>
       <c r="BZ80" t="n">
-        <v>3.884051313230152</v>
+        <v>3.883736424501683</v>
       </c>
       <c r="CA80" t="n">
         <v>7.127125333008402</v>
       </c>
       <c r="CB80" t="n">
-        <v>3.904587863770955</v>
+        <v>3.905025625917294</v>
       </c>
       <c r="CC80" t="n">
-        <v>1.345744207300617</v>
+        <v>1.345734459705644</v>
       </c>
       <c r="CD80" t="n">
-        <v>1.931741823261247</v>
+        <v>1.931561724743789</v>
       </c>
       <c r="CE80" t="inlineStr"/>
       <c r="CF80" t="n">
-        <v>2.284803100885869</v>
+        <v>2.284901105530561</v>
       </c>
       <c r="CG80" t="n">
-        <v>1.742804302626521</v>
+        <v>1.742880859461882</v>
       </c>
       <c r="CH80" t="n">
-        <v>1.568523872363869</v>
+        <v>1.568592773515694</v>
       </c>
       <c r="CI80" t="n">
         <v>6</v>
@@ -35632,10 +35632,10 @@
         <v>6.5</v>
       </c>
       <c r="CL80" t="n">
-        <v>-33.81755493233475</v>
+        <v>-33.81464771059836</v>
       </c>
       <c r="CM80" t="n">
-        <v>-3.594801214647103</v>
+        <v>-3.590665997371811</v>
       </c>
       <c r="CN80" t="inlineStr">
         <is>
@@ -35914,25 +35914,25 @@
         <v>25.78806304931641</v>
       </c>
       <c r="BX81" t="n">
-        <v>11.35620445547206</v>
+        <v>11.35620447532557</v>
       </c>
       <c r="BY81" t="n">
-        <v>12.3132902925093</v>
+        <v>12.31329030227797</v>
       </c>
       <c r="BZ81" t="n">
-        <v>14.19506892653237</v>
+        <v>14.19506891297737</v>
       </c>
       <c r="CA81" t="n">
         <v>32.28961358718046</v>
       </c>
       <c r="CB81" t="n">
-        <v>13.06611002669453</v>
+        <v>13.06611002624236</v>
       </c>
       <c r="CC81" t="n">
-        <v>24.87657762654112</v>
+        <v>24.87657762382468</v>
       </c>
       <c r="CD81" t="n">
-        <v>6.00661309876884</v>
+        <v>6.006613086067356</v>
       </c>
       <c r="CE81" t="n">
         <v>61.44795953901004</v>
@@ -35984,7 +35984,7 @@
         <v>-5.404421354056477</v>
       </c>
       <c r="CZ81" t="n">
-        <v>-20.47333298656073</v>
+        <v>-20.47332352864949</v>
       </c>
       <c r="DA81" t="b">
         <v>0</v>
@@ -36183,7 +36183,7 @@
         <v>0.22</v>
       </c>
       <c r="BI82" t="n">
-        <v>140.75</v>
+        <v>140.74</v>
       </c>
       <c r="BJ82" t="n">
         <v>73.2</v>
@@ -36216,10 +36216,10 @@
         <v>-13.7</v>
       </c>
       <c r="BT82" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="BU82" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BV82" t="n">
         <v>0.5600000000000001</v>
@@ -36228,10 +36228,10 @@
         <v>9.850000381469727</v>
       </c>
       <c r="BX82" t="n">
-        <v>6.038291421997257</v>
+        <v>6.037965018214039</v>
       </c>
       <c r="BY82" t="n">
-        <v>11.20103058780491</v>
+        <v>11.20042510878704</v>
       </c>
       <c r="BZ82" t="n">
         <v>7.958079576492308</v>
@@ -36252,7 +36252,7 @@
         <v>39.30366688938892</v>
       </c>
       <c r="CF82" t="n">
-        <v>10.08363226294837</v>
+        <v>10.08349913683393</v>
       </c>
       <c r="CG82" t="n">
         <v>7.958079576492308</v>
@@ -36273,7 +36273,7 @@
         <v>-27.28658536585368</v>
       </c>
       <c r="CM82" t="n">
-        <v>2.37189718203632</v>
+        <v>2.37054564793191</v>
       </c>
       <c r="CN82" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>0.82</v>
       </c>
       <c r="BI83" t="n">
-        <v>21.48</v>
+        <v>21.49</v>
       </c>
       <c r="BJ83" t="n">
         <v>-89.7</v>
@@ -36540,22 +36540,22 @@
         <v>-43</v>
       </c>
       <c r="BT83" t="n">
-        <v>-12.6</v>
+        <v>-12.4</v>
       </c>
       <c r="BU83" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BV83" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="BW83" t="n">
         <v>6.690000057220459</v>
       </c>
       <c r="BX83" t="n">
-        <v>1.20351248632404</v>
+        <v>1.204080092358347</v>
       </c>
       <c r="BY83" t="n">
-        <v>2.232515662131094</v>
+        <v>2.233568571324733</v>
       </c>
       <c r="BZ83" t="n">
         <v>10.39185237493213</v>
@@ -36564,13 +36564,13 @@
         <v>10.22124134966257</v>
       </c>
       <c r="CB83" t="n">
-        <v>10.15309495100949</v>
+        <v>10.15297125042389</v>
       </c>
       <c r="CC83" t="n">
-        <v>1.875400555711294</v>
+        <v>1.875377704210118</v>
       </c>
       <c r="CD83" t="n">
-        <v>7.23551484866438</v>
+        <v>7.234851521548447</v>
       </c>
       <c r="CE83" t="n">
         <v>10.26177038220516</v>
@@ -36854,7 +36854,7 @@
         <v>-12.8</v>
       </c>
       <c r="BT84" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="BU84" t="n">
         <v>0.61</v>
@@ -36866,10 +36866,10 @@
         <v>18.40999984741211</v>
       </c>
       <c r="BX84" t="n">
-        <v>4.472894335045885</v>
+        <v>4.473085397440171</v>
       </c>
       <c r="BY84" t="n">
-        <v>8.297218991510118</v>
+        <v>8.297573412251516</v>
       </c>
       <c r="BZ84" t="n">
         <v>32.35179018278652</v>
@@ -36878,13 +36878,13 @@
         <v>34.90762684757382</v>
       </c>
       <c r="CB84" t="n">
-        <v>28.27494153201019</v>
+        <v>28.27500205368425</v>
       </c>
       <c r="CC84" t="n">
-        <v>11.13392030370456</v>
+        <v>11.13390790091814</v>
       </c>
       <c r="CD84" t="n">
-        <v>19.07514525149204</v>
+        <v>19.07496030309437</v>
       </c>
       <c r="CE84" t="n">
         <v>41.8667053195644</v>
@@ -37151,19 +37151,19 @@
         <v>-6</v>
       </c>
       <c r="BU85" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BV85" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="BW85" t="n">
         <v>50</v>
       </c>
       <c r="BX85" t="n">
-        <v>10.49147067217292</v>
+        <v>10.49472705518709</v>
       </c>
       <c r="BY85" t="n">
-        <v>15.27558129868377</v>
+        <v>15.28032259235241</v>
       </c>
       <c r="BZ85" t="inlineStr"/>
       <c r="CA85" t="inlineStr"/>
@@ -37174,13 +37174,13 @@
       <c r="CD85" t="inlineStr"/>
       <c r="CE85" t="inlineStr"/>
       <c r="CF85" t="n">
-        <v>17.36491732361889</v>
+        <v>17.3675832158465</v>
       </c>
       <c r="CG85" t="n">
-        <v>15.27558129868377</v>
+        <v>15.28032259235241</v>
       </c>
       <c r="CH85" t="n">
-        <v>13.74802316881539</v>
+        <v>13.75229033311717</v>
       </c>
       <c r="CI85" t="n">
         <v>3</v>
@@ -37192,10 +37192,10 @@
         <v>2.5</v>
       </c>
       <c r="CL85" t="n">
-        <v>-72.50395366236921</v>
+        <v>-72.49541933376567</v>
       </c>
       <c r="CM85" t="n">
-        <v>-65.27016535276221</v>
+        <v>-65.26483356830698</v>
       </c>
       <c r="CN85" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>0.27</v>
       </c>
       <c r="BI86" t="n">
-        <v>138.16</v>
+        <v>138.15</v>
       </c>
       <c r="BJ86" t="n">
         <v>73.5</v>
@@ -37474,10 +37474,10 @@
         <v>-15</v>
       </c>
       <c r="BT86" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="BU86" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BV86" t="n">
         <v>0.52</v>
@@ -37486,10 +37486,10 @@
         <v>22.14999961853027</v>
       </c>
       <c r="BX86" t="n">
-        <v>11.1637503128907</v>
+        <v>11.16306742940736</v>
       </c>
       <c r="BY86" t="n">
-        <v>20.70875683041224</v>
+        <v>20.70749008155064</v>
       </c>
       <c r="BZ86" t="n">
         <v>14.98914683072146</v>
@@ -37510,13 +37510,13 @@
         <v>22.63811085331503</v>
       </c>
       <c r="CF86" t="n">
-        <v>19.40426749218722</v>
+        <v>19.40402378814409</v>
       </c>
       <c r="CG86" t="n">
-        <v>17.84895183056685</v>
+        <v>17.84831845613605</v>
       </c>
       <c r="CH86" t="n">
-        <v>16.06405664751017</v>
+        <v>16.06348661052245</v>
       </c>
       <c r="CI86" t="n">
         <v>8</v>
@@ -37528,10 +37528,10 @@
         <v>3</v>
       </c>
       <c r="CL86" t="n">
-        <v>-27.47604097441483</v>
+        <v>-27.47861450487775</v>
       </c>
       <c r="CM86" t="n">
-        <v>-12.39608204799259</v>
+        <v>-12.39718229199854</v>
       </c>
       <c r="CN86" t="inlineStr">
         <is>
@@ -37796,13 +37796,13 @@
         <v>-12.8</v>
       </c>
       <c r="BT87" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BU87" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="BV87" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BW87" t="n">
         <v>62.84999847412109</v>
@@ -38124,10 +38124,10 @@
         <v>13.92000007629395</v>
       </c>
       <c r="BX88" t="n">
-        <v>6.009189133148966</v>
+        <v>6.009189176339434</v>
       </c>
       <c r="BY88" t="n">
-        <v>8.749379377864894</v>
+        <v>8.749379440750218</v>
       </c>
       <c r="BZ88" t="n">
         <v>3.748524101332394</v>
@@ -38340,13 +38340,13 @@
         <v>0</v>
       </c>
       <c r="AR89" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="AS89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="n">
-        <v>2855378432</v>
+        <v>2877639936</v>
       </c>
       <c r="AU89" t="n">
         <v>6.62</v>
@@ -38424,10 +38424,10 @@
         <v>-52</v>
       </c>
       <c r="BT89" t="n">
-        <v>-27.9</v>
+        <v>-27.5</v>
       </c>
       <c r="BU89" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="BV89" t="n">
         <v>0.66</v>
@@ -38436,10 +38436,10 @@
         <v>7.119999885559082</v>
       </c>
       <c r="BX89" t="n">
-        <v>2.962332531320235</v>
+        <v>2.962332531430638</v>
       </c>
       <c r="BY89" t="n">
-        <v>5.495126845599036</v>
+        <v>5.495126845803833</v>
       </c>
       <c r="BZ89" t="n">
         <v>14.25075505795435</v>
@@ -38448,23 +38448,23 @@
         <v>15.36316945870801</v>
       </c>
       <c r="CB89" t="n">
-        <v>13.58643916872692</v>
+        <v>13.58643916878914</v>
       </c>
       <c r="CC89" t="n">
-        <v>14.99149110012425</v>
+        <v>14.9914911001019</v>
       </c>
       <c r="CD89" t="n">
-        <v>7.475401684016097</v>
+        <v>7.47540168390845</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="n">
-        <v>11.86039721918811</v>
+        <v>11.86039721921095</v>
       </c>
       <c r="CG89" t="n">
-        <v>13.91859711334063</v>
+        <v>13.91859711337175</v>
       </c>
       <c r="CH89" t="n">
-        <v>12.52673740200657</v>
+        <v>12.52673740203457</v>
       </c>
       <c r="CI89" t="n">
         <v>6</v>
@@ -38476,10 +38476,10 @@
         <v>5.2</v>
       </c>
       <c r="CL89" t="n">
-        <v>75.93732588975929</v>
+        <v>75.93732589015256</v>
       </c>
       <c r="CM89" t="n">
-        <v>66.57861530649166</v>
+        <v>66.5786153068124</v>
       </c>
       <c r="CN89" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>-40.5</v>
       </c>
       <c r="BT90" t="n">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="BU90" t="n">
         <v>1.96</v>
@@ -38752,25 +38752,25 @@
         <v>1.610000014305115</v>
       </c>
       <c r="BX90" t="n">
-        <v>0.1435169041583464</v>
+        <v>0.1435318111612521</v>
       </c>
       <c r="BY90" t="n">
-        <v>0.1636087024819044</v>
+        <v>0.163625040168066</v>
       </c>
       <c r="BZ90" t="n">
-        <v>0.7478582191648242</v>
+        <v>0.7478552198004993</v>
       </c>
       <c r="CA90" t="n">
         <v>3.128143894509729</v>
       </c>
       <c r="CB90" t="n">
-        <v>0.2552474090890737</v>
+        <v>0.255255223800898</v>
       </c>
       <c r="CC90" t="n">
-        <v>1.083017860013447</v>
+        <v>1.083017384933685</v>
       </c>
       <c r="CD90" t="n">
-        <v>0.3337470632320914</v>
+        <v>0.3337444920722303</v>
       </c>
       <c r="CE90" t="inlineStr"/>
       <c r="CF90" t="inlineStr"/>
@@ -39034,47 +39034,47 @@
         <v>-32.5</v>
       </c>
       <c r="BT91" t="n">
-        <v>-11.6</v>
+        <v>-11.5</v>
       </c>
       <c r="BU91" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BV91" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="BW91" t="n">
         <v>18.43000030517578</v>
       </c>
       <c r="BX91" t="n">
-        <v>10.98605247096141</v>
+        <v>10.98633928570238</v>
       </c>
       <c r="BY91" t="n">
-        <v>14.59097963710706</v>
+        <v>14.59117227661442</v>
       </c>
       <c r="BZ91" t="n">
-        <v>23.98349995941849</v>
+        <v>23.98319047179236</v>
       </c>
       <c r="CA91" t="n">
         <v>42.51467275133047</v>
       </c>
       <c r="CB91" t="n">
-        <v>29.00872969388575</v>
+        <v>29.00895967311865</v>
       </c>
       <c r="CC91" t="n">
-        <v>15.83208811610292</v>
+        <v>15.83206863401346</v>
       </c>
       <c r="CD91" t="n">
-        <v>11.72612555666556</v>
+        <v>11.72592389148489</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>16.34815504589747</v>
+        <v>16.34819266703066</v>
       </c>
       <c r="CG91" t="n">
-        <v>15.21153387660499</v>
+        <v>15.21162045531394</v>
       </c>
       <c r="CH91" t="n">
-        <v>13.69038048894449</v>
+        <v>13.69045840978255</v>
       </c>
       <c r="CI91" t="n">
         <v>4</v>
@@ -39086,10 +39086,10 @@
         <v>2.2</v>
       </c>
       <c r="CL91" t="n">
-        <v>-25.71687323792523</v>
+        <v>-25.7164504444539</v>
       </c>
       <c r="CM91" t="n">
-        <v>-11.29595889748117</v>
+        <v>-11.2957547676246</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -39370,22 +39370,22 @@
         <v>-29.2</v>
       </c>
       <c r="BT92" t="n">
-        <v>-8</v>
+        <v>-8.1</v>
       </c>
       <c r="BU92" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="BV92" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BW92" t="n">
         <v>3.619999885559082</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.24704449429824</v>
+        <v>33.24704450488574</v>
       </c>
       <c r="BY92" t="n">
-        <v>61.67326753692323</v>
+        <v>61.67326755656305</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.72561561415348</v>
@@ -39649,7 +39649,7 @@
       </c>
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="n">
-        <v>336.19</v>
+        <v>336.2</v>
       </c>
       <c r="BJ93" t="n">
         <v>-43.5</v>
@@ -39685,19 +39685,19 @@
         <v>-3.1</v>
       </c>
       <c r="BU93" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="BV93" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BW93" t="n">
         <v>75.02999877929688</v>
       </c>
       <c r="BX93" t="n">
-        <v>56.09450003537534</v>
+        <v>56.09548785913903</v>
       </c>
       <c r="BY93" t="n">
-        <v>81.6735920515065</v>
+        <v>81.67503032290642</v>
       </c>
       <c r="BZ93" t="n">
         <v>24.29364842169015</v>
@@ -40008,10 +40008,10 @@
         <v>7.739999771118164</v>
       </c>
       <c r="BX94" t="n">
-        <v>4.981494656414204</v>
+        <v>4.981494650184922</v>
       </c>
       <c r="BY94" t="n">
-        <v>7.253056219739082</v>
+        <v>7.253056210669246</v>
       </c>
       <c r="BZ94" t="n">
         <v>5.841509261221256</v>
@@ -40030,13 +40030,13 @@
         <v>7.485306000698566</v>
       </c>
       <c r="CF94" t="n">
-        <v>6.559492388063326</v>
+        <v>6.559492385513473</v>
       </c>
       <c r="CG94" t="n">
-        <v>6.547282740480169</v>
+        <v>6.547282735945251</v>
       </c>
       <c r="CH94" t="n">
-        <v>5.892554466432152</v>
+        <v>5.892554462350725</v>
       </c>
       <c r="CI94" t="n">
         <v>6</v>
@@ -40048,10 +40048,10 @@
         <v>5.9</v>
       </c>
       <c r="CL94" t="n">
-        <v>-23.86880309195564</v>
+        <v>-23.86880314468726</v>
       </c>
       <c r="CM94" t="n">
-        <v>-15.25203382382394</v>
+        <v>-15.25203385676778</v>
       </c>
       <c r="CN94" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>1.44</v>
       </c>
       <c r="BI95" t="n">
-        <v>38.58</v>
+        <v>38.59</v>
       </c>
       <c r="BJ95" t="n">
         <v>24.5</v>
@@ -40318,10 +40318,10 @@
         <v>-34.2</v>
       </c>
       <c r="BT95" t="n">
-        <v>-18.8</v>
+        <v>-18.7</v>
       </c>
       <c r="BU95" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BV95" t="n">
         <v>0.79</v>
@@ -40330,10 +40330,10 @@
         <v>33.91999816894531</v>
       </c>
       <c r="BX95" t="n">
-        <v>8.391158608675051</v>
+        <v>8.392352297610165</v>
       </c>
       <c r="BY95" t="n">
-        <v>15.56559921909222</v>
+        <v>15.56781351206685</v>
       </c>
       <c r="BZ95" t="n">
         <v>40.34470159232723</v>
@@ -40342,19 +40342,19 @@
         <v>40.59709214923609</v>
       </c>
       <c r="CB95" t="n">
-        <v>34.16506909277543</v>
+        <v>34.16445855967465</v>
       </c>
       <c r="CC95" t="n">
-        <v>50.12681064636324</v>
+        <v>50.12648818633644</v>
       </c>
       <c r="CD95" t="n">
-        <v>22.98081074783758</v>
+        <v>22.97948403420753</v>
       </c>
       <c r="CE95" t="n">
         <v>52.55911136579431</v>
       </c>
       <c r="CF95" t="n">
-        <v>36.61988497334658</v>
+        <v>36.61987848566331</v>
       </c>
       <c r="CG95" t="n">
         <v>40.34470159232723</v>
@@ -40375,7 +40375,7 @@
         <v>7.046678635547576</v>
       </c>
       <c r="CM95" t="n">
-        <v>7.959572376607871</v>
+        <v>7.959553250182094</v>
       </c>
       <c r="CN95" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>1</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AS96" t="b">
         <v>1</v>
@@ -40650,10 +40650,10 @@
         <v>-31</v>
       </c>
       <c r="BT96" t="n">
-        <v>-4.3</v>
+        <v>-4.1</v>
       </c>
       <c r="BU96" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BV96" t="n">
         <v>0.57</v>
@@ -40662,10 +40662,10 @@
         <v>18.43000030517578</v>
       </c>
       <c r="BX96" t="n">
-        <v>1.901393171313892</v>
+        <v>1.901526403205117</v>
       </c>
       <c r="BY96" t="n">
-        <v>3.527084332787269</v>
+        <v>3.527331477945492</v>
       </c>
       <c r="BZ96" t="n">
         <v>10.14952219632498</v>
@@ -40674,19 +40674,19 @@
         <v>8.46772853950336</v>
       </c>
       <c r="CB96" t="n">
-        <v>10.30782014701703</v>
+        <v>10.30755427993182</v>
       </c>
       <c r="CC96" t="n">
-        <v>7.564753329683775</v>
+        <v>7.564723054320488</v>
       </c>
       <c r="CD96" t="n">
-        <v>7.830081097242979</v>
+        <v>7.829865250920641</v>
       </c>
       <c r="CE96" t="n">
         <v>13.31345732107621</v>
       </c>
       <c r="CF96" t="n">
-        <v>8.737206709090803</v>
+        <v>8.737168874289001</v>
       </c>
       <c r="CG96" t="n">
         <v>8.46772853950336</v>
@@ -40707,7 +40707,7 @@
         <v>-58.64918307455048</v>
       </c>
       <c r="CM96" t="n">
-        <v>-52.59247659026304</v>
+        <v>-52.59268187947179</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>0.12</v>
       </c>
       <c r="BH97" t="n">
-        <v>836.36</v>
+        <v>836.37</v>
       </c>
       <c r="BI97" t="n">
         <v>99.68000000000001</v>
@@ -40974,7 +40974,7 @@
         <v>-42.1</v>
       </c>
       <c r="BT97" t="n">
-        <v>-22.7</v>
+        <v>-22.4</v>
       </c>
       <c r="BU97" t="n">
         <v>1.13</v>
@@ -40986,25 +40986,25 @@
         <v>5.03000020980835</v>
       </c>
       <c r="BX97" t="n">
-        <v>2.974533253003265</v>
+        <v>2.974533277112433</v>
       </c>
       <c r="BY97" t="n">
-        <v>2.978023637320871</v>
+        <v>2.978023652653838</v>
       </c>
       <c r="BZ97" t="n">
-        <v>2.987602352486064</v>
+        <v>2.987602343653252</v>
       </c>
       <c r="CA97" t="n">
         <v>9.357269522030355</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.464773719760586</v>
+        <v>3.46477373263948</v>
       </c>
       <c r="CC97" t="n">
-        <v>5.22619299842263</v>
+        <v>5.226192996527068</v>
       </c>
       <c r="CD97" t="n">
-        <v>1.119833983346605</v>
+        <v>1.11983397382059</v>
       </c>
       <c r="CE97" t="n">
         <v>6.1778101886163</v>
@@ -41291,7 +41291,7 @@
         <v>-22.5</v>
       </c>
       <c r="BU98" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="BV98" t="n">
         <v>0.35</v>
@@ -41300,10 +41300,10 @@
         <v>6.550000190734863</v>
       </c>
       <c r="BX98" t="n">
-        <v>2.928359214988435</v>
+        <v>2.92835922824577</v>
       </c>
       <c r="BY98" t="n">
-        <v>5.432106343803546</v>
+        <v>5.432106368395903</v>
       </c>
       <c r="BZ98" t="inlineStr"/>
       <c r="CA98" t="inlineStr"/>
@@ -41314,13 +41314,13 @@
         <v>9.705704701814605</v>
       </c>
       <c r="CF98" t="n">
-        <v>6.022056753535527</v>
+        <v>6.022056766152093</v>
       </c>
       <c r="CG98" t="n">
-        <v>5.432106343803546</v>
+        <v>5.432106368395903</v>
       </c>
       <c r="CH98" t="n">
-        <v>4.888895709423191</v>
+        <v>4.888895731556313</v>
       </c>
       <c r="CI98" t="n">
         <v>3</v>
@@ -41332,10 +41332,10 @@
         <v>3.3</v>
       </c>
       <c r="CL98" t="n">
-        <v>-25.36037302199389</v>
+        <v>-25.36037268408363</v>
       </c>
       <c r="CM98" t="n">
-        <v>-8.060204913369695</v>
+        <v>-8.060204720750374</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -41614,37 +41614,37 @@
         <v>23.29999923706055</v>
       </c>
       <c r="BX99" t="n">
-        <v>5.103749852481744</v>
+        <v>5.103749849943674</v>
       </c>
       <c r="BY99" t="n">
-        <v>7.173562615767842</v>
+        <v>7.173562615219081</v>
       </c>
       <c r="BZ99" t="n">
-        <v>10.48983171927599</v>
+        <v>10.48983172369009</v>
       </c>
       <c r="CA99" t="n">
         <v>14.5426935407471</v>
       </c>
       <c r="CB99" t="n">
-        <v>7.042443465067359</v>
+        <v>7.042443467602885</v>
       </c>
       <c r="CC99" t="n">
-        <v>8.428083065910368</v>
+        <v>8.428083066231622</v>
       </c>
       <c r="CD99" t="n">
-        <v>5.203866416480245</v>
+        <v>5.203866419075574</v>
       </c>
       <c r="CE99" t="n">
         <v>11.10595965229168</v>
       </c>
       <c r="CF99" t="n">
-        <v>8.636273791002791</v>
+        <v>8.636273791850215</v>
       </c>
       <c r="CG99" t="n">
-        <v>7.800822840839105</v>
+        <v>7.800822840725351</v>
       </c>
       <c r="CH99" t="n">
-        <v>7.020740556755195</v>
+        <v>7.020740556652816</v>
       </c>
       <c r="CI99" t="n">
         <v>8</v>
@@ -41656,10 +41656,10 @@
         <v>2.8</v>
       </c>
       <c r="CL99" t="n">
-        <v>-69.86806529337505</v>
+        <v>-69.86806529381444</v>
       </c>
       <c r="CM99" t="n">
-        <v>-62.93444603523379</v>
+        <v>-62.93444603159679</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>1</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AS100" t="b">
         <v>1</v>
@@ -41930,22 +41930,22 @@
         <v>-17.8</v>
       </c>
       <c r="BT100" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BU100" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BV100" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="BW100" t="n">
         <v>15.89000034332275</v>
       </c>
       <c r="BX100" t="n">
-        <v>8.001188571767592</v>
+        <v>8.00118854926402</v>
       </c>
       <c r="BY100" t="n">
-        <v>14.84220480062888</v>
+        <v>14.84220475888475</v>
       </c>
       <c r="BZ100" t="n">
         <v>10.31565431401403</v>
@@ -41966,7 +41966,7 @@
         <v>8.797113764315322</v>
       </c>
       <c r="CF100" t="n">
-        <v>12.19659642346885</v>
+        <v>12.19659641543789</v>
       </c>
       <c r="CG100" t="n">
         <v>9.867993843783237</v>
@@ -41987,7 +41987,7 @@
         <v>-44.10828025477708</v>
       </c>
       <c r="CM100" t="n">
-        <v>-23.24357356861816</v>
+        <v>-23.24357361915914</v>
       </c>
       <c r="CN100" t="inlineStr">
         <is>
@@ -42266,25 +42266,25 @@
         <v>44.7599983215332</v>
       </c>
       <c r="BX101" t="n">
-        <v>17.20270106350647</v>
+        <v>17.20270116944813</v>
       </c>
       <c r="BY101" t="n">
-        <v>19.66088481511733</v>
+        <v>19.66088486823818</v>
       </c>
       <c r="BZ101" t="n">
-        <v>24.58949631085723</v>
+        <v>24.58949622586175</v>
       </c>
       <c r="CA101" t="n">
         <v>51.1379037367685</v>
       </c>
       <c r="CB101" t="n">
-        <v>20.90417747879019</v>
+        <v>20.90417746320898</v>
       </c>
       <c r="CC101" t="n">
-        <v>23.35865953897489</v>
+        <v>23.35865953016378</v>
       </c>
       <c r="CD101" t="n">
-        <v>10.99908020932407</v>
+        <v>10.99908013679218</v>
       </c>
       <c r="CE101" t="n">
         <v>115.6180112331857</v>
@@ -42568,7 +42568,7 @@
         <v>-23.7</v>
       </c>
       <c r="BT102" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BU102" t="n">
         <v>0.43</v>
@@ -42580,10 +42580,10 @@
         <v>44.97000122070312</v>
       </c>
       <c r="BX102" t="n">
-        <v>9.838905037218675</v>
+        <v>9.838909709843135</v>
       </c>
       <c r="BY102" t="n">
-        <v>18.25116884404064</v>
+        <v>18.25117751175901</v>
       </c>
       <c r="BZ102" t="n">
         <v>85.61099370320636</v>
@@ -42592,13 +42592,13 @@
         <v>75.72810912354937</v>
       </c>
       <c r="CB102" t="n">
-        <v>103.367921365967</v>
+        <v>103.3679200104117</v>
       </c>
       <c r="CC102" t="n">
-        <v>16.01313589757714</v>
+        <v>16.01313566157055</v>
       </c>
       <c r="CD102" t="n">
-        <v>69.79478030471778</v>
+        <v>69.7947735447385</v>
       </c>
       <c r="CE102" t="n">
         <v>21.24156204581304</v>
@@ -42886,22 +42886,22 @@
         <v>-43.2</v>
       </c>
       <c r="BT103" t="n">
-        <v>-17</v>
+        <v>-16.8</v>
       </c>
       <c r="BU103" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="BV103" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BW103" t="n">
         <v>2.740000009536743</v>
       </c>
       <c r="BX103" t="n">
-        <v>0.5730592403664033</v>
+        <v>0.573059239797577</v>
       </c>
       <c r="BY103" t="n">
-        <v>1.063024890879678</v>
+        <v>1.063024889824505</v>
       </c>
       <c r="BZ103" t="n">
         <v>3.425000011920929</v>
@@ -42910,13 +42910,13 @@
         <v>3.972173446398807</v>
       </c>
       <c r="CB103" t="n">
-        <v>2.462840650171836</v>
+        <v>2.46284065018267</v>
       </c>
       <c r="CC103" t="n">
-        <v>2.642774521603005</v>
+        <v>2.642774521676099</v>
       </c>
       <c r="CD103" t="n">
-        <v>1.762863057894624</v>
+        <v>1.762863058373667</v>
       </c>
       <c r="CE103" t="n">
         <v>8.739324130946441</v>
@@ -42962,10 +42962,10 @@
         </is>
       </c>
       <c r="CX103" t="n">
-        <v>3.420000076293945</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="CY103" t="n">
-        <v>-19.88304244408318</v>
+        <v>-17.96406946261236</v>
       </c>
       <c r="CZ103" t="n">
         <v>-44.53441340487693</v>
@@ -42981,7 +42981,7 @@
       </c>
       <c r="DD103" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-19.9%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-18.0%))</t>
         </is>
       </c>
     </row>
@@ -43200,7 +43200,7 @@
         <v>-28.4</v>
       </c>
       <c r="BT104" t="n">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="BU104" t="n">
         <v>1.38</v>
@@ -43212,10 +43212,10 @@
         <v>11.51000022888184</v>
       </c>
       <c r="BX104" t="n">
-        <v>2.04690381647155</v>
+        <v>2.047077728146336</v>
       </c>
       <c r="BY104" t="n">
-        <v>3.797006579554726</v>
+        <v>3.797329185711454</v>
       </c>
       <c r="BZ104" t="n">
         <v>12.13265736139095</v>
@@ -43224,25 +43224,25 @@
         <v>13.45436807571135</v>
       </c>
       <c r="CB104" t="n">
-        <v>8.853920354721444</v>
+        <v>8.853859618317287</v>
       </c>
       <c r="CC104" t="n">
-        <v>5.744254369015995</v>
+        <v>5.744239476963251</v>
       </c>
       <c r="CD104" t="n">
-        <v>6.578478874467286</v>
+        <v>6.578318945291152</v>
       </c>
       <c r="CE104" t="n">
         <v>11.51000022888184</v>
       </c>
       <c r="CF104" t="n">
-        <v>8.867240834820514</v>
+        <v>8.867253270323898</v>
       </c>
       <c r="CG104" t="n">
-        <v>8.853920354721444</v>
+        <v>8.853859618317287</v>
       </c>
       <c r="CH104" t="n">
-        <v>7.9685283192493</v>
+        <v>7.968473656485559</v>
       </c>
       <c r="CI104" t="n">
         <v>7</v>
@@ -43254,10 +43254,10 @@
         <v>6.6</v>
       </c>
       <c r="CL104" t="n">
-        <v>-30.76865194794684</v>
+        <v>-30.76912686334783</v>
       </c>
       <c r="CM104" t="n">
-        <v>-22.96055031719194</v>
+        <v>-22.96044227633063</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -43512,61 +43512,61 @@
         <v>42.34</v>
       </c>
       <c r="BP105" t="n">
-        <v>40.32</v>
+        <v>40.85</v>
       </c>
       <c r="BQ105" t="n">
         <v>67.15000000000001</v>
       </c>
       <c r="BR105" t="n">
-        <v>28.6</v>
+        <v>26.9</v>
       </c>
       <c r="BS105" t="n">
         <v>-22.8</v>
       </c>
       <c r="BT105" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="BU105" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BV105" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="BW105" t="n">
         <v>51.84999847412109</v>
       </c>
       <c r="BX105" t="n">
-        <v>15.83854320097515</v>
+        <v>15.83854317843969</v>
       </c>
       <c r="BY105" t="n">
-        <v>24.45220078111907</v>
+        <v>24.45220076769969</v>
       </c>
       <c r="BZ105" t="n">
-        <v>45.16372208109831</v>
+        <v>45.16372212057247</v>
       </c>
       <c r="CA105" t="n">
         <v>61.8255726523502</v>
       </c>
       <c r="CB105" t="n">
-        <v>36.03383592654973</v>
+        <v>36.03383593273696</v>
       </c>
       <c r="CC105" t="n">
-        <v>26.79540344857871</v>
+        <v>26.79540345052591</v>
       </c>
       <c r="CD105" t="n">
-        <v>22.58146588511083</v>
+        <v>22.58146590466439</v>
       </c>
       <c r="CE105" t="n">
         <v>20.62544462503444</v>
       </c>
       <c r="CF105" t="n">
-        <v>31.66452357510206</v>
+        <v>31.66452357900297</v>
       </c>
       <c r="CG105" t="n">
-        <v>25.62380211484889</v>
+        <v>25.6238021091128</v>
       </c>
       <c r="CH105" t="n">
-        <v>23.061421903364</v>
+        <v>23.06142189820152</v>
       </c>
       <c r="CI105" t="n">
         <v>8</v>
@@ -43578,10 +43578,10 @@
         <v>3.9</v>
       </c>
       <c r="CL105" t="n">
-        <v>-55.52281083503945</v>
+        <v>-55.52281084499601</v>
       </c>
       <c r="CM105" t="n">
-        <v>-38.93052168380262</v>
+        <v>-38.93052167627915</v>
       </c>
       <c r="CN105" t="inlineStr">
         <is>
@@ -43603,11 +43603,7 @@
           <t>A análise fundamentalista da AXIA3 revela uma empresa de serviços públicos que apresenta desafios em sua eficiência operacional, uma vez que seu ROE de 9,9% e seu ROIC de 3,2% situam-se abaixo das médias setoriais de 12,1% e 9,6%, respectivamente. Essa rentabilidade pressionada convive com múltiplos de valuation que não parecem descontados, dado que o P/L de 12,66 e o P/VP de 1,25 não configuram uma clara assimetria de preço favorável para compensar o retorno sobre o capital investido mais baixo. Por outro lado, a saúde financeira mostra-se controlada, com a relação dívida líquida sobre EBITDA em 2,95 vezes, posicionando-se abaixo do limite prudencial e da média do setor de 3,4 vezes, o que confere segurança ao balanço diante de uma liquidez corrente confortável de 2,05. Esse endividamento sob controle, contudo, não se traduz em proventos robustos, visto que o dividend yield de 2,86% é modesto e reflete a necessidade de retenção de caixa frente a um crescimento histórico tímido, evidenciado pelo CAGR de receita de 9,7% nos últimos cinco anos, patamar muito abaixo dos 37,6% apresentados pelos seus pares. No checklist de critérios de qualidade e valor, o papel atende a apenas 3 dos 8 requisitos avaliados, penalizado principalmente pelas taxas de retorno inferiores à taxa Selic e à média setorial, além de registrar vendas recentes por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de cálculo, variando desde os conservadores R$ 15,84 por Bazin e R$ 24,45 por Gordon até os R$ 61,83 pela fórmula de Graham. Tomando como referência a média ponderada de R$ 31,66 e o preço-teto ajustado com margem de segurança de R$ 23,06, o preço atual de R$ 51,85 indica um expressivo prêmio de mercado, resultando em um upside negativo de 55,5% em relação ao valor justo estimado. Em balanço final, a AXIA3 destaca-se positivamente por sua excelente margem líquida de 27,05%, robusto valor de mercado e endividamento inferior à média de seus pares, mas traz como contrapartidas o fraco crescimento histórico, a baixa rentabilidade sobre o capital e um preço de tela desalinhado com as principais métricas de fluxo de caixa descontado e dividendos.</t>
         </is>
       </c>
-      <c r="CR105" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR105" t="inlineStr"/>
       <c r="CS105" t="b">
         <v>0</v>
       </c>
@@ -43622,7 +43618,7 @@
       </c>
       <c r="CW105" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Baixa</t>
         </is>
       </c>
       <c r="CX105" t="n">
@@ -43638,14 +43634,14 @@
         <v>0</v>
       </c>
       <c r="DB105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC105" t="b">
         <v>0</v>
       </c>
       <c r="DD105" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.5%))</t>
         </is>
       </c>
     </row>
@@ -43864,37 +43860,37 @@
         <v>-52.4</v>
       </c>
       <c r="BT106" t="n">
-        <v>-20.7</v>
+        <v>-20.3</v>
       </c>
       <c r="BU106" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BV106" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW106" t="n">
         <v>15.14000034332275</v>
       </c>
       <c r="BX106" t="n">
-        <v>3.820728849354571</v>
+        <v>3.820728862955463</v>
       </c>
       <c r="BY106" t="n">
-        <v>4.841207724318205</v>
+        <v>4.841207739235919</v>
       </c>
       <c r="BZ106" t="n">
-        <v>14.21439289135326</v>
+        <v>14.21439288455366</v>
       </c>
       <c r="CA106" t="n">
         <v>37.03789734077716</v>
       </c>
       <c r="CB106" t="n">
-        <v>9.722395122878247</v>
+        <v>9.722395134956958</v>
       </c>
       <c r="CC106" t="n">
-        <v>48.39119061173403</v>
+        <v>48.39119060943085</v>
       </c>
       <c r="CD106" t="n">
-        <v>6.819001494248632</v>
+        <v>6.819001489425211</v>
       </c>
       <c r="CE106" t="n">
         <v>20.9161030224964</v>
@@ -44462,13 +44458,13 @@
         <v>24.93</v>
       </c>
       <c r="BP108" t="n">
-        <v>52.32</v>
+        <v>53.05</v>
       </c>
       <c r="BQ108" t="n">
         <v>71.62</v>
       </c>
       <c r="BR108" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
       <c r="BS108" t="n">
         <v>-17.5</v>
@@ -44480,16 +44476,16 @@
         <v>0.73</v>
       </c>
       <c r="BV108" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BW108" t="n">
         <v>59.08000183105469</v>
       </c>
       <c r="BX108" t="n">
-        <v>66.83145657012213</v>
+        <v>66.83145639530029</v>
       </c>
       <c r="BY108" t="n">
-        <v>97.30660076609783</v>
+        <v>97.30660051155725</v>
       </c>
       <c r="BZ108" t="n">
         <v>24.49888433185681</v>
@@ -44782,13 +44778,13 @@
         <v>-23.1</v>
       </c>
       <c r="BT109" t="n">
-        <v>-10</v>
+        <v>-9.9</v>
       </c>
       <c r="BU109" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BV109" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BW109" t="n">
         <v>8.229999542236328</v>
@@ -45093,10 +45089,10 @@
         <v>-40.9</v>
       </c>
       <c r="BU110" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BV110" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BW110" t="n">
         <v>6.539999961853027</v>
@@ -45392,22 +45388,22 @@
         <v>-6.1</v>
       </c>
       <c r="BT111" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="BU111" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BV111" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="BW111" t="n">
         <v>97.26999664306641</v>
       </c>
       <c r="BX111" t="n">
-        <v>4.970373434840474</v>
+        <v>4.969483348297951</v>
       </c>
       <c r="BY111" t="n">
-        <v>9.220042721629079</v>
+        <v>9.218391611092699</v>
       </c>
       <c r="BZ111" t="n">
         <v>41.68264733249126</v>
@@ -45416,13 +45412,13 @@
         <v>41.38446934269194</v>
       </c>
       <c r="CB111" t="n">
-        <v>34.12509521562828</v>
+        <v>34.12631340465155</v>
       </c>
       <c r="CC111" t="n">
-        <v>17.80324331323966</v>
+        <v>17.80332662049297</v>
       </c>
       <c r="CD111" t="n">
-        <v>28.43940532034266</v>
+        <v>28.44042436262346</v>
       </c>
       <c r="CE111" t="n">
         <v>42.08352793520866</v>
@@ -45709,19 +45705,19 @@
         <v>-8.5</v>
       </c>
       <c r="BU112" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BV112" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BW112" t="n">
         <v>17.30999946594238</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.249424040087078</v>
+        <v>3.249533332872448</v>
       </c>
       <c r="BY112" t="n">
-        <v>6.02768159436153</v>
+        <v>6.027884332478391</v>
       </c>
       <c r="BZ112" t="n">
         <v>14.75916942881188</v>
@@ -45730,23 +45726,23 @@
         <v>15.70024654832573</v>
       </c>
       <c r="CB112" t="n">
-        <v>10.37388546242832</v>
+        <v>10.37381102321067</v>
       </c>
       <c r="CC112" t="n">
-        <v>13.01542669537969</v>
+        <v>13.01540775857188</v>
       </c>
       <c r="CD112" t="n">
-        <v>7.656345481915403</v>
+        <v>7.656236801169629</v>
       </c>
       <c r="CE112" t="inlineStr"/>
       <c r="CF112" t="n">
-        <v>11.25545920187042</v>
+        <v>11.25545931542803</v>
       </c>
       <c r="CG112" t="n">
-        <v>11.694656078904</v>
+        <v>11.69460939089127</v>
       </c>
       <c r="CH112" t="n">
-        <v>10.5251904710136</v>
+        <v>10.52514845180215</v>
       </c>
       <c r="CI112" t="n">
         <v>6</v>
@@ -45758,10 +45754,10 @@
         <v>4.8</v>
       </c>
       <c r="CL112" t="n">
-        <v>-39.19589372765705</v>
+        <v>-39.1961364729647</v>
       </c>
       <c r="CM112" t="n">
-        <v>-34.97712565493912</v>
+        <v>-34.97712499891597</v>
       </c>
       <c r="CN112" t="inlineStr">
         <is>
@@ -45950,7 +45946,7 @@
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>26444003328</v>
+        <v>26446039040</v>
       </c>
       <c r="AU113" t="n">
         <v>21.59</v>
@@ -46040,10 +46036,10 @@
         <v>14.25</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.333549790960755</v>
+        <v>1.333549791278858</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.473734862232201</v>
+        <v>2.473734862822282</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.745368226030568</v>
@@ -46052,13 +46048,13 @@
         <v>10.75360939215812</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.87858352205053</v>
+        <v>4.87858352187915</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.696526410480179</v>
+        <v>7.696526410438667</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.286205605356511</v>
+        <v>4.286205605119131</v>
       </c>
       <c r="CE113" t="n">
         <v>11.16944225998353</v>
@@ -46313,7 +46309,7 @@
         <v>1289.96</v>
       </c>
       <c r="BI114" t="n">
-        <v>28865.77</v>
+        <v>28866.92</v>
       </c>
       <c r="BJ114" t="n">
         <v>2.5</v>
@@ -46346,10 +46342,10 @@
         <v>-34.2</v>
       </c>
       <c r="BT114" t="n">
-        <v>-18.7</v>
+        <v>-18.4</v>
       </c>
       <c r="BU114" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BV114" t="n">
         <v>0.49</v>
@@ -46358,10 +46354,10 @@
         <v>18.40999984741211</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.77047441647493</v>
+        <v>11.77094235496264</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.68750503273176</v>
+        <v>14.68808893858382</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -46652,37 +46648,37 @@
         <v>-46.7</v>
       </c>
       <c r="BT115" t="n">
-        <v>-15.6</v>
+        <v>-15.2</v>
       </c>
       <c r="BU115" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="BV115" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BW115" t="n">
         <v>7.869999885559082</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.023899903511879</v>
+        <v>2.023899907414319</v>
       </c>
       <c r="BY115" t="n">
-        <v>2.245933797583305</v>
+        <v>2.245933800897701</v>
       </c>
       <c r="BZ115" t="n">
-        <v>3.283227754020261</v>
+        <v>3.283227752534775</v>
       </c>
       <c r="CA115" t="n">
         <v>9.955734923002648</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.000357702231175</v>
+        <v>2.000357702981388</v>
       </c>
       <c r="CC115" t="n">
-        <v>5.925849691549432</v>
+        <v>5.925849691249074</v>
       </c>
       <c r="CD115" t="n">
-        <v>1.426516298572551</v>
+        <v>1.426516297236668</v>
       </c>
       <c r="CE115" t="n">
         <v>14.66556730038189</v>
@@ -46966,22 +46962,22 @@
         <v>0</v>
       </c>
       <c r="BT116" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BU116" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="BV116" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BW116" t="n">
         <v>11.18000030517578</v>
       </c>
       <c r="BX116" t="n">
-        <v>2.429769114108134</v>
+        <v>2.429719281699719</v>
       </c>
       <c r="BY116" t="n">
-        <v>4.507221706670588</v>
+        <v>4.507129267552978</v>
       </c>
       <c r="BZ116" t="n">
         <v>12.17214495017084</v>
@@ -46990,13 +46986,13 @@
         <v>12.66795579710097</v>
       </c>
       <c r="CB116" t="n">
-        <v>9.627038087049129</v>
+        <v>9.62706315425741</v>
       </c>
       <c r="CC116" t="n">
-        <v>0.7923827793706386</v>
+        <v>0.7923834408559832</v>
       </c>
       <c r="CD116" t="n">
-        <v>6.748454792382121</v>
+        <v>6.748506582207539</v>
       </c>
       <c r="CE116" t="n">
         <v>7.239159730295168</v>
@@ -47296,10 +47292,10 @@
         <v>3.400000095367432</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.674174179285858</v>
+        <v>1.674174181344084</v>
       </c>
       <c r="BY117" t="n">
-        <v>3.105593102575267</v>
+        <v>3.105593106393275</v>
       </c>
       <c r="BZ117" t="n">
         <v>1.164684624188688</v>
@@ -47308,7 +47304,7 @@
         <v>4.65742755893486</v>
       </c>
       <c r="CB117" t="n">
-        <v>1.616815915375581</v>
+        <v>1.616815916120544</v>
       </c>
       <c r="CC117" t="n">
         <v>0.7445919647652398</v>
@@ -47598,22 +47594,22 @@
         <v>-31.7</v>
       </c>
       <c r="BT118" t="n">
-        <v>-5.5</v>
+        <v>-5.4</v>
       </c>
       <c r="BU118" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BV118" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BW118" t="n">
         <v>4.710000038146973</v>
       </c>
       <c r="BX118" t="n">
-        <v>1.448542800121124</v>
+        <v>1.448542797629799</v>
       </c>
       <c r="BY118" t="n">
-        <v>1.509703496126238</v>
+        <v>1.509703493529724</v>
       </c>
       <c r="BZ118" t="inlineStr"/>
       <c r="CA118" t="inlineStr"/>
@@ -47902,10 +47898,10 @@
         <v>-57.3</v>
       </c>
       <c r="BT119" t="n">
-        <v>-30.5</v>
+        <v>-30.2</v>
       </c>
       <c r="BU119" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BV119" t="n">
         <v>0.6899999999999999</v>
@@ -47914,10 +47910,10 @@
         <v>6.110000133514404</v>
       </c>
       <c r="BX119" t="n">
-        <v>0.9798900275486497</v>
+        <v>0.9801914038873228</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.817696001102745</v>
+        <v>1.818255054210984</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -47968,10 +47964,10 @@
         </is>
       </c>
       <c r="CX119" t="n">
-        <v>7.730000019073486</v>
+        <v>7.710000038146973</v>
       </c>
       <c r="CY119" t="n">
-        <v>-20.95730765280457</v>
+        <v>-20.75226843989891</v>
       </c>
       <c r="CZ119" t="n">
         <v>-58.17730263024769</v>
@@ -47987,7 +47983,7 @@
       </c>
       <c r="DD119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-21.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-20.8%))</t>
         </is>
       </c>
     </row>
@@ -48170,10 +48166,10 @@
         <v>2.12</v>
       </c>
       <c r="BH120" t="n">
-        <v>35.1</v>
+        <v>35.23</v>
       </c>
       <c r="BI120" t="n">
-        <v>88.34</v>
+        <v>88.39</v>
       </c>
       <c r="BJ120" t="n">
         <v>20.9</v>
@@ -48206,10 +48202,10 @@
         <v>-46.5</v>
       </c>
       <c r="BT120" t="n">
-        <v>-12.6</v>
+        <v>-12.3</v>
       </c>
       <c r="BU120" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BV120" t="n">
         <v>0.55</v>
@@ -48218,25 +48214,25 @@
         <v>3.299999952316284</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.128667182923974</v>
+        <v>1.129231943796697</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.17886624212474</v>
+        <v>1.179258246745238</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.33440653815281</v>
+        <v>1.334182667672991</v>
       </c>
       <c r="CA120" t="n">
         <v>4.000073406115944</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.9504674185273897</v>
+        <v>0.950539373348023</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.177339858138429</v>
+        <v>2.177296676335917</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.5369186657084881</v>
+        <v>0.5366945234133217</v>
       </c>
       <c r="CE120" t="n">
         <v>4.93751177672036</v>
@@ -48532,10 +48528,10 @@
         <v>5.239999771118164</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.191433403804608</v>
+        <v>5.191433399592619</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.55872703593951</v>
+        <v>7.558727029806853</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -48544,13 +48540,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.375080219872059</v>
+        <v>6.375080214699736</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.375080219872059</v>
+        <v>6.375080214699736</v>
       </c>
       <c r="CH121" t="n">
-        <v>5.737572197884854</v>
+        <v>5.737572193229762</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -48562,10 +48558,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.495657414132141</v>
+        <v>9.495657325294516</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.66184157125792</v>
+        <v>21.66184147254948</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -48832,22 +48828,22 @@
         <v>-56</v>
       </c>
       <c r="BT122" t="n">
-        <v>-16.3</v>
+        <v>-16</v>
       </c>
       <c r="BU122" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BV122" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BW122" t="n">
         <v>4.789999961853027</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.272756696327944</v>
+        <v>5.272756686097852</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.400753444850711</v>
+        <v>9.400753426611566</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -48856,13 +48852,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.336755070589327</v>
+        <v>7.336755056354709</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.336755070589327</v>
+        <v>7.336755056354709</v>
       </c>
       <c r="CH122" t="n">
-        <v>6.603079563530395</v>
+        <v>6.603079550719237</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -48874,10 +48870,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134897946787</v>
+        <v>37.85134871201157</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816553274209</v>
+        <v>53.1681652355684</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -48906,10 +48902,10 @@
         </is>
       </c>
       <c r="CX122" t="n">
-        <v>4.949999809265137</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="CY122" t="n">
-        <v>-3.232320274288303</v>
+        <v>-2.044987880632343</v>
       </c>
       <c r="CZ122" t="n">
         <v>-57.68551156372263</v>
@@ -48925,7 +48921,7 @@
       </c>
       <c r="DD122" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
         </is>
       </c>
     </row>
@@ -49130,22 +49126,22 @@
         <v>-17.5</v>
       </c>
       <c r="BT123" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="BU123" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BV123" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BW123" t="n">
         <v>21.03000068664551</v>
       </c>
       <c r="BX123" t="n">
-        <v>36.4274170897653</v>
+        <v>36.42741699332814</v>
       </c>
       <c r="BY123" t="n">
-        <v>67.57285870151462</v>
+        <v>67.57285852262369</v>
       </c>
       <c r="BZ123" t="n">
         <v>19.70633020495424</v>
@@ -49164,7 +49160,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>25.49883429995774</v>
+        <v>25.49883428388488</v>
       </c>
       <c r="CG123" t="n">
         <v>22.92261274222209</v>
@@ -49185,7 +49181,7 @@
         <v>-1.90037663146353</v>
       </c>
       <c r="CM123" t="n">
-        <v>21.24980250785264</v>
+        <v>21.2498024314244</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -49452,37 +49448,37 @@
         <v>-34.3</v>
       </c>
       <c r="BT124" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="BU124" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BV124" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BW124" t="n">
         <v>9.090000152587891</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.518187442501676</v>
+        <v>3.518187436274411</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.631196083624279</v>
+        <v>3.631196078186726</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.385743493866426</v>
+        <v>4.385743495061829</v>
       </c>
       <c r="CA124" t="n">
         <v>18.9170762302566</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.451708564697996</v>
+        <v>3.451708560936539</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.742135616288168</v>
+        <v>7.742135616540219</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.732684429852898</v>
+        <v>1.732684431074937</v>
       </c>
       <c r="CE124" t="n">
         <v>20.26176339670673</v>
@@ -49766,22 +49762,22 @@
         <v>-36.4</v>
       </c>
       <c r="BT125" t="n">
-        <v>-23.6</v>
+        <v>-23.4</v>
       </c>
       <c r="BU125" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="BV125" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BW125" t="n">
         <v>11.28999996185303</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7667711041936762</v>
+        <v>0.7670876391874237</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.422360398279269</v>
+        <v>1.422947570692671</v>
       </c>
       <c r="BZ125" t="n">
         <v>15.56633709620735</v>
@@ -49790,13 +49786,13 @@
         <v>16.25115692351487</v>
       </c>
       <c r="CB125" t="n">
-        <v>13.67049076062193</v>
+        <v>13.6704307505937</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.678304309403704</v>
+        <v>1.678297583250632</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.02917988093443</v>
+        <v>11.0288523052001</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -49840,10 +49836,10 @@
         </is>
       </c>
       <c r="CX125" t="n">
-        <v>12.06999969482422</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="CY125" t="n">
-        <v>-6.462301182208529</v>
+        <v>-4.322035768120402</v>
       </c>
       <c r="CZ125" t="n">
         <v>-36.92737317063685</v>
@@ -49859,7 +49855,7 @@
       </c>
       <c r="DD125" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
         </is>
       </c>
     </row>
@@ -50076,10 +50072,10 @@
         <v>0</v>
       </c>
       <c r="BT126" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="BU126" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="BV126" t="n">
         <v>0.33</v>
@@ -50384,25 +50380,25 @@
         <v>18.89999961853027</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5886462649336317</v>
+        <v>0.588646264889812</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7906544490453721</v>
+        <v>0.7906544489905655</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.609265560797217</v>
+        <v>4.609265560820834</v>
       </c>
       <c r="CA127" t="n">
         <v>11.51795868166206</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.76572740411077</v>
+        <v>1.765727404119163</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6741747290838402</v>
+        <v>0.6741747290841664</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.261637496145553</v>
+        <v>2.26163749616063</v>
       </c>
       <c r="CE127" t="n">
         <v>18.89999961853027</v>
@@ -50698,10 +50694,10 @@
         <v>4.989999771118164</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.22681410775884</v>
+        <v>1.226814118379893</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.053240702167295</v>
+        <v>2.053240719943075</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -50712,13 +50708,13 @@
         <v>5.871634259790683</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.640027404963067</v>
+        <v>1.640027419161484</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.640027404963067</v>
+        <v>1.640027419161484</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.476024664466761</v>
+        <v>1.476024677245336</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -50730,10 +50726,10 @@
         <v>4.8</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.42034604871311</v>
+        <v>-70.42034579262943</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.13371783190345</v>
+        <v>-67.13371754736603</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -51012,37 +51008,37 @@
         <v>16.76000022888184</v>
       </c>
       <c r="BX129" t="n">
-        <v>2.018107866283926</v>
+        <v>2.018107859704232</v>
       </c>
       <c r="BY129" t="n">
-        <v>3.646153666924492</v>
+        <v>3.646153660299482</v>
       </c>
       <c r="BZ129" t="n">
-        <v>9.926116020421139</v>
+        <v>9.926116034747922</v>
       </c>
       <c r="CA129" t="n">
         <v>12.04263895963171</v>
       </c>
       <c r="CB129" t="n">
-        <v>5.758979290462557</v>
+        <v>5.758979294682138</v>
       </c>
       <c r="CC129" t="n">
-        <v>5.544942947978397</v>
+        <v>5.544942948553958</v>
       </c>
       <c r="CD129" t="n">
-        <v>4.85966339847498</v>
+        <v>4.85966340378453</v>
       </c>
       <c r="CE129" t="n">
         <v>15.42017902790524</v>
       </c>
       <c r="CF129" t="n">
-        <v>6.963082380648879</v>
+        <v>6.963082383616623</v>
       </c>
       <c r="CG129" t="n">
-        <v>5.651961119220477</v>
+        <v>5.651961121618048</v>
       </c>
       <c r="CH129" t="n">
-        <v>5.086765007298429</v>
+        <v>5.086765009456244</v>
       </c>
       <c r="CI129" t="n">
         <v>6</v>
@@ -51054,10 +51050,10 @@
         <v>7.6</v>
       </c>
       <c r="CL129" t="n">
-        <v>-69.64937387928784</v>
+        <v>-69.64937386641306</v>
       </c>
       <c r="CM129" t="n">
-        <v>-58.45416297399759</v>
+        <v>-58.45416295629029</v>
       </c>
       <c r="CN129" t="inlineStr">
         <is>
@@ -51287,7 +51283,7 @@
       </c>
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="n">
-        <v>172.9</v>
+        <v>172.91</v>
       </c>
       <c r="BJ130" t="n">
         <v>-17.3</v>
@@ -51320,22 +51316,22 @@
         <v>-13.1</v>
       </c>
       <c r="BT130" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="BU130" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="BV130" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BW130" t="n">
         <v>18.79999923706055</v>
       </c>
       <c r="BX130" t="n">
-        <v>1.447712586742458</v>
+        <v>1.447783520302165</v>
       </c>
       <c r="BY130" t="n">
-        <v>2.107869526297018</v>
+        <v>2.107972805559953</v>
       </c>
       <c r="BZ130" t="inlineStr"/>
       <c r="CA130" t="inlineStr"/>
@@ -51388,10 +51384,10 @@
         </is>
       </c>
       <c r="CX130" t="n">
-        <v>20.38999938964844</v>
+        <v>19.86000061035156</v>
       </c>
       <c r="CY130" t="n">
-        <v>-7.79794114851764</v>
+        <v>-5.337368281542321</v>
       </c>
       <c r="CZ130" t="n">
         <v>-15.10502492905792</v>
@@ -51407,7 +51403,7 @@
       </c>
       <c r="DD130" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
         </is>
       </c>
     </row>
@@ -51922,7 +51918,7 @@
         <v>-13</v>
       </c>
       <c r="BT132" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="BU132" t="n">
         <v>1.36</v>
@@ -51934,10 +51930,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.8550990101520491</v>
+        <v>0.8551117973919462</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.9464877168620494</v>
+        <v>0.9465018707382106</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -51946,13 +51942,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.9007933635070493</v>
+        <v>0.9008068340650783</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.9007933635070493</v>
+        <v>0.9008068340650783</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.8107140271563444</v>
+        <v>0.8107261506585706</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -51964,10 +51960,10 @@
         <v>1.1</v>
       </c>
       <c r="CL132" t="n">
-        <v>-80.03167392654403</v>
+        <v>-80.03137531811061</v>
       </c>
       <c r="CM132" t="n">
-        <v>-77.81297102949337</v>
+        <v>-77.81263924234513</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -52248,10 +52244,10 @@
         <v>1.039999961853027</v>
       </c>
       <c r="BX133" t="n">
-        <v>0.3048180258761597</v>
+        <v>0.3048180261667492</v>
       </c>
       <c r="BY133" t="n">
-        <v>0.5654374380002762</v>
+        <v>0.5654374385393198</v>
       </c>
       <c r="BZ133" t="inlineStr"/>
       <c r="CA133" t="inlineStr"/>
@@ -52260,13 +52256,13 @@
       <c r="CD133" t="inlineStr"/>
       <c r="CE133" t="inlineStr"/>
       <c r="CF133" t="n">
-        <v>0.435127731938218</v>
+        <v>0.4351277323530345</v>
       </c>
       <c r="CG133" t="n">
-        <v>0.435127731938218</v>
+        <v>0.4351277323530345</v>
       </c>
       <c r="CH133" t="n">
-        <v>0.3916149587443962</v>
+        <v>0.3916149591177311</v>
       </c>
       <c r="CI133" t="n">
         <v>2</v>
@@ -52278,10 +52274,10 @@
         <v>1.9</v>
       </c>
       <c r="CL133" t="n">
-        <v>-62.34471412415887</v>
+        <v>-62.34471408826128</v>
       </c>
       <c r="CM133" t="n">
-        <v>-58.16079347128763</v>
+        <v>-58.16079343140142</v>
       </c>
       <c r="CN133" t="inlineStr">
         <is>
@@ -52546,10 +52542,10 @@
         <v>-21.1</v>
       </c>
       <c r="BT134" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="BU134" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BV134" t="n">
         <v>0.82</v>
@@ -52558,10 +52554,10 @@
         <v>35.77000045776367</v>
       </c>
       <c r="BX134" t="n">
-        <v>8.056625193313568</v>
+        <v>8.056625183516472</v>
       </c>
       <c r="BY134" t="n">
-        <v>11.73044628146456</v>
+        <v>11.73044626719999</v>
       </c>
       <c r="BZ134" t="n">
         <v>7.91506393107962</v>
@@ -52859,10 +52855,10 @@
         <v>-10.8</v>
       </c>
       <c r="BU135" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="BV135" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BW135" t="n">
         <v>2.579999923706055</v>
@@ -53166,22 +53162,22 @@
         <v>-51.2</v>
       </c>
       <c r="BT136" t="n">
-        <v>-12.3</v>
+        <v>-11.8</v>
       </c>
       <c r="BU136" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BV136" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BW136" t="n">
         <v>5.090000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>0.9696997101857272</v>
+        <v>0.9696997099488727</v>
       </c>
       <c r="BY136" t="n">
-        <v>1.798792962394524</v>
+        <v>1.798792961955159</v>
       </c>
       <c r="BZ136" t="inlineStr"/>
       <c r="CA136" t="inlineStr"/>
@@ -53192,13 +53188,13 @@
         <v>2.687155457559689</v>
       </c>
       <c r="CF136" t="n">
-        <v>1.818549376713313</v>
+        <v>1.818549376487907</v>
       </c>
       <c r="CG136" t="n">
-        <v>1.798792962394524</v>
+        <v>1.798792961955159</v>
       </c>
       <c r="CH136" t="n">
-        <v>1.618913666155071</v>
+        <v>1.618913665759643</v>
       </c>
       <c r="CI136" t="n">
         <v>3</v>
@@ -53210,10 +53206,10 @@
         <v>2.8</v>
       </c>
       <c r="CL136" t="n">
-        <v>-68.1942314808778</v>
+        <v>-68.19423148864654</v>
       </c>
       <c r="CM136" t="n">
-        <v>-64.27211547746782</v>
+        <v>-64.27211548189624</v>
       </c>
       <c r="CN136" t="inlineStr">
         <is>
@@ -53265,7 +53261,7 @@
       </c>
       <c r="DD136" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.1, +3.7% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.0, +3.7% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -53418,7 +53414,7 @@
         <v>5.97</v>
       </c>
       <c r="AX137" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="AY137" t="n">
         <v>3.69</v>
@@ -53451,7 +53447,7 @@
         <v>13.07</v>
       </c>
       <c r="BI137" t="n">
-        <v>67.69</v>
+        <v>67.7</v>
       </c>
       <c r="BJ137" t="n">
         <v>-58.5</v>
@@ -53484,37 +53480,37 @@
         <v>-32</v>
       </c>
       <c r="BT137" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="BU137" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BV137" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BW137" t="n">
         <v>4.909999847412109</v>
       </c>
       <c r="BX137" t="n">
-        <v>1.523642876566413</v>
+        <v>1.523881198784834</v>
       </c>
       <c r="BY137" t="n">
-        <v>1.685354300067705</v>
+        <v>1.685559995038767</v>
       </c>
       <c r="BZ137" t="n">
-        <v>2.489969443266916</v>
+        <v>2.48988388248115</v>
       </c>
       <c r="CA137" t="n">
         <v>7.747739573095417</v>
       </c>
       <c r="CB137" t="n">
-        <v>1.744907894130134</v>
+        <v>1.744998930341796</v>
       </c>
       <c r="CC137" t="n">
-        <v>1.782263260447801</v>
+        <v>1.782256379807031</v>
       </c>
       <c r="CD137" t="n">
-        <v>1.0780994123283</v>
+        <v>1.078022024337534</v>
       </c>
       <c r="CE137" t="n">
         <v>0.03462128620209939</v>
@@ -53560,7 +53556,7 @@
       <c r="CV137" t="inlineStr"/>
       <c r="CW137" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CX137" t="n">
@@ -53812,10 +53808,10 @@
         <v>6.380000114440918</v>
       </c>
       <c r="BX138" t="n">
-        <v>1.750831184159987</v>
+        <v>1.750831185064184</v>
       </c>
       <c r="BY138" t="n">
-        <v>2.549210204136942</v>
+        <v>2.549210205453452</v>
       </c>
       <c r="BZ138" t="n">
         <v>1.700461332398399</v>
@@ -54122,10 +54118,10 @@
         <v>1.830000042915344</v>
       </c>
       <c r="BX139" t="n">
-        <v>0.5136933434025496</v>
+        <v>0.5136933449409921</v>
       </c>
       <c r="BY139" t="n">
-        <v>0.7479375079941122</v>
+        <v>0.7479375102340846</v>
       </c>
       <c r="BZ139" t="n">
         <v>0.3540837292338526</v>
@@ -54680,10 +54676,10 @@
         <v>-74.09999999999999</v>
       </c>
       <c r="BT141" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="BU141" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BV141" t="n">
         <v>0.03</v>
@@ -55244,10 +55240,10 @@
         <v>0.76</v>
       </c>
       <c r="BH143" t="n">
-        <v>314.75</v>
+        <v>315.87</v>
       </c>
       <c r="BI143" t="n">
-        <v>85.33</v>
+        <v>85.38</v>
       </c>
       <c r="BJ143" t="n">
         <v>-2.6</v>
@@ -55280,10 +55276,10 @@
         <v>-62.2</v>
       </c>
       <c r="BT143" t="n">
-        <v>-31.6</v>
+        <v>-31.2</v>
       </c>
       <c r="BU143" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BV143" t="n">
         <v>0.59</v>
@@ -55292,25 +55288,25 @@
         <v>4.159999847412109</v>
       </c>
       <c r="BX143" t="n">
-        <v>0.6952579219727789</v>
+        <v>0.6956808240881132</v>
       </c>
       <c r="BY143" t="n">
-        <v>0.7018725269324378</v>
+        <v>0.7022758351932048</v>
       </c>
       <c r="BZ143" t="n">
-        <v>0.8225111860650789</v>
+        <v>0.8224835262240521</v>
       </c>
       <c r="CA143" t="n">
         <v>6.067610485147757</v>
       </c>
       <c r="CB143" t="n">
-        <v>0.2801105277665936</v>
+        <v>0.2802260972553379</v>
       </c>
       <c r="CC143" t="n">
-        <v>0.4177501727682303</v>
+        <v>0.4177484617637583</v>
       </c>
       <c r="CD143" t="n">
-        <v>0.3130278715293705</v>
+        <v>0.3129984713743125</v>
       </c>
       <c r="CE143" t="inlineStr"/>
       <c r="CF143" t="inlineStr"/>
@@ -55594,10 +55590,10 @@
         <v>-29</v>
       </c>
       <c r="BT144" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="BU144" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BV144" t="n">
         <v>0.31</v>
@@ -55606,10 +55602,10 @@
         <v>19.54000091552734</v>
       </c>
       <c r="BX144" t="n">
-        <v>29.75287272689911</v>
+        <v>29.75287272692384</v>
       </c>
       <c r="BY144" t="n">
-        <v>39.80273195909615</v>
+        <v>39.80273195912922</v>
       </c>
       <c r="BZ144" t="n">
         <v>2.525572356336101</v>
@@ -55618,7 +55614,7 @@
         <v>7.002148431252935</v>
       </c>
       <c r="CB144" t="n">
-        <v>6.480024632845599</v>
+        <v>6.480024632850281</v>
       </c>
       <c r="CC144" t="n">
         <v>3.046690502845772</v>
@@ -55908,22 +55904,22 @@
         <v>-54.5</v>
       </c>
       <c r="BT145" t="n">
-        <v>-13.5</v>
+        <v>-13.2</v>
       </c>
       <c r="BU145" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="BV145" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="BW145" t="n">
         <v>3.640000104904175</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.6583625626958485</v>
+        <v>0.6583625636119577</v>
       </c>
       <c r="BY145" t="n">
-        <v>1.221262553800799</v>
+        <v>1.221262555500181</v>
       </c>
       <c r="BZ145" t="inlineStr"/>
       <c r="CA145" t="inlineStr"/>
@@ -55934,13 +55930,13 @@
         <v>3.264431296215689</v>
       </c>
       <c r="CF145" t="n">
-        <v>0.9398125582483237</v>
+        <v>0.9398125595560696</v>
       </c>
       <c r="CG145" t="n">
-        <v>0.9398125582483237</v>
+        <v>0.9398125595560696</v>
       </c>
       <c r="CH145" t="n">
-        <v>0.8458313024234914</v>
+        <v>0.8458313036004627</v>
       </c>
       <c r="CI145" t="n">
         <v>2</v>
@@ -55952,10 +55948,10 @@
         <v>5</v>
       </c>
       <c r="CL145" t="n">
-        <v>-76.76287697673683</v>
+        <v>-76.76287694440246</v>
       </c>
       <c r="CM145" t="n">
-        <v>-74.18097441859648</v>
+        <v>-74.18097438266939</v>
       </c>
       <c r="CN145" t="inlineStr">
         <is>
@@ -56220,13 +56216,13 @@
         <v>-42.6</v>
       </c>
       <c r="BT146" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="BU146" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BV146" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="BW146" t="n">
         <v>1.559999942779541</v>
@@ -56544,10 +56540,10 @@
         <v>18.48999977111816</v>
       </c>
       <c r="BX147" t="n">
-        <v>9.370797992568059</v>
+        <v>9.370797943144415</v>
       </c>
       <c r="BY147" t="n">
-        <v>13.6438818771791</v>
+        <v>13.64388180521827</v>
       </c>
       <c r="BZ147" t="n">
         <v>4.677596633899998</v>
@@ -57163,19 +57159,19 @@
         <v>-15.8</v>
       </c>
       <c r="BU149" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BV149" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BW149" t="n">
         <v>10.22999954223633</v>
       </c>
       <c r="BX149" t="n">
-        <v>5.465905823613741</v>
+        <v>5.465905843783379</v>
       </c>
       <c r="BY149" t="n">
-        <v>10.00463206677745</v>
+        <v>10.00463210369535</v>
       </c>
       <c r="BZ149" t="inlineStr"/>
       <c r="CA149" t="inlineStr"/>
@@ -57186,13 +57182,13 @@
         <v>2.757870606147196</v>
       </c>
       <c r="CF149" t="n">
-        <v>6.076136165512795</v>
+        <v>6.076136184541976</v>
       </c>
       <c r="CG149" t="n">
-        <v>5.465905823613741</v>
+        <v>5.465905843783379</v>
       </c>
       <c r="CH149" t="n">
-        <v>4.919315241252367</v>
+        <v>4.919315259405041</v>
       </c>
       <c r="CI149" t="n">
         <v>3</v>
@@ -57204,10 +57200,10 @@
         <v>3.6</v>
       </c>
       <c r="CL149" t="n">
-        <v>-51.91284983990351</v>
+        <v>-51.91284966245802</v>
       </c>
       <c r="CM149" t="n">
-        <v>-40.60472690710871</v>
+        <v>-40.6047267210952</v>
       </c>
       <c r="CN149" t="inlineStr">
         <is>
@@ -57388,13 +57384,13 @@
         <v>1</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS150" t="b">
         <v>1</v>
       </c>
       <c r="AT150" t="n">
-        <v>48513810432</v>
+        <v>48699994112</v>
       </c>
       <c r="AU150" t="n">
         <v>51.22</v>
@@ -57458,13 +57454,13 @@
         <v>34.87</v>
       </c>
       <c r="BP150" t="n">
-        <v>13.71</v>
+        <v>14</v>
       </c>
       <c r="BQ150" t="n">
         <v>27.59</v>
       </c>
       <c r="BR150" t="n">
-        <v>85</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="BS150" t="n">
         <v>-8.1</v>
@@ -57473,10 +57469,10 @@
         <v>-1.6</v>
       </c>
       <c r="BU150" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BV150" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BW150" t="n">
         <v>25.36000061035156</v>
@@ -57788,22 +57784,22 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="BT151" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BU151" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BV151" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="BW151" t="n">
         <v>14.77999973297119</v>
       </c>
       <c r="BX151" t="n">
-        <v>3.780435860499745</v>
+        <v>3.780435849624868</v>
       </c>
       <c r="BY151" t="n">
-        <v>5.504314612887629</v>
+        <v>5.504314597053808</v>
       </c>
       <c r="BZ151" t="inlineStr"/>
       <c r="CA151" t="inlineStr"/>
@@ -57814,7 +57810,7 @@
         <v>5.063572783384453</v>
       </c>
       <c r="CF151" t="n">
-        <v>4.782774418923943</v>
+        <v>4.782774410021043</v>
       </c>
       <c r="CG151" t="n">
         <v>5.063572783384453</v>
@@ -57835,7 +57831,7 @@
         <v>-69.16633567401371</v>
       </c>
       <c r="CM151" t="n">
-        <v>-67.6402266215571</v>
+        <v>-67.64022668179324</v>
       </c>
       <c r="CN151" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-24.xlsx
+++ b/reports/screener_2026-08-24.xlsx
@@ -1174,7 +1174,7 @@
         <v>-26.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="BU2" t="n">
         <v>1.38</v>
@@ -1186,10 +1186,10 @@
         <v>10.15999984741211</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.738884128649667</v>
+        <v>5.739092644462467</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.64563005864513</v>
+        <v>10.64601685547787</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.29447790742652</v>
@@ -1198,7 +1198,7 @@
         <v>27.67799880047428</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.39398021848989</v>
+        <v>71.39487568517062</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1260,7 +1260,7 @@
         <v>-8.878922017834656</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-28.21663909745649</v>
+        <v>-28.21664403987539</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -1504,10 +1504,10 @@
         <v>13.67000007629395</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.08411221122868</v>
+        <v>15.08411215817256</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.9810281518292</v>
+        <v>27.9810280534101</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.78533212224727</v>
@@ -1516,13 +1516,13 @@
         <v>23.4303842936706</v>
       </c>
       <c r="CB3" t="n">
-        <v>73.80863262284781</v>
+        <v>73.80863272421371</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.30691184730974</v>
+        <v>48.30691188646256</v>
       </c>
       <c r="CD3" t="n">
-        <v>25.78976666715468</v>
+        <v>25.78976683084767</v>
       </c>
       <c r="CE3" t="n">
         <v>8.630044464581562</v>
@@ -1822,10 +1822,10 @@
         <v>23.51000022888184</v>
       </c>
       <c r="BX4" t="n">
-        <v>15.55616502675489</v>
+        <v>15.55616500524296</v>
       </c>
       <c r="BY4" t="n">
-        <v>28.85668612463031</v>
+        <v>28.85668608472568</v>
       </c>
       <c r="BZ4" t="n">
         <v>71.12043448234802</v>
@@ -1834,13 +1834,13 @@
         <v>51.51277527306067</v>
       </c>
       <c r="CB4" t="n">
-        <v>127.4881988902025</v>
+        <v>127.4881988948674</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.80183479209307</v>
+        <v>25.80183479517592</v>
       </c>
       <c r="CD4" t="n">
-        <v>63.22015028192994</v>
+        <v>63.22015032808249</v>
       </c>
       <c r="CE4" t="n">
         <v>41.54649601907847</v>
@@ -2128,22 +2128,22 @@
         <v>-60.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>-25.7</v>
+        <v>-26.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW5" t="n">
         <v>6.900000095367432</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.115400814292661</v>
+        <v>3.115400820686986</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.779068510512887</v>
+        <v>5.779068522374359</v>
       </c>
       <c r="BZ5" t="n">
         <v>19.83188747583914</v>
@@ -2152,7 +2152,7 @@
         <v>13.5801516746889</v>
       </c>
       <c r="CB5" t="n">
-        <v>31.91228044047912</v>
+        <v>31.91228045989789</v>
       </c>
       <c r="CC5" t="n">
         <v>10.95072400487419</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="CX5" t="n">
-        <v>7.360000133514404</v>
+        <v>7.5</v>
       </c>
       <c r="CY5" t="n">
-        <v>-6.250000404922851</v>
+        <v>-7.999998728434243</v>
       </c>
       <c r="CZ5" t="n">
         <v>-60.30064258156551</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
         <v>0.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>51.57</v>
+        <v>51.56</v>
       </c>
       <c r="BJ6" t="n">
         <v>-14</v>
@@ -2444,22 +2444,22 @@
         <v>-37.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>-23.6</v>
+        <v>-23.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="BW6" t="n">
         <v>4.179999828338623</v>
       </c>
       <c r="BX6" t="n">
-        <v>3.539319177617177</v>
+        <v>3.539168768139573</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.565437074479863</v>
+        <v>6.565158064898907</v>
       </c>
       <c r="BZ6" t="n">
         <v>12.73218338516937</v>
@@ -2468,25 +2468,25 @@
         <v>8.571766632368943</v>
       </c>
       <c r="CB6" t="n">
-        <v>24.57145988209843</v>
+        <v>24.57157214911559</v>
       </c>
       <c r="CC6" t="n">
-        <v>11.28763497763521</v>
+        <v>11.28769657875037</v>
       </c>
       <c r="CD6" t="n">
-        <v>10.85194343487941</v>
+        <v>10.85231827936312</v>
       </c>
       <c r="CE6" t="n">
         <v>5.170088126502553</v>
       </c>
       <c r="CF6" t="n">
-        <v>9.196508938505891</v>
+        <v>9.196535177842211</v>
       </c>
       <c r="CG6" t="n">
-        <v>9.711855033624179</v>
+        <v>9.71204245586603</v>
       </c>
       <c r="CH6" t="n">
-        <v>8.740669530261762</v>
+        <v>8.740838210279428</v>
       </c>
       <c r="CI6" t="n">
         <v>6</v>
@@ -2498,10 +2498,10 @@
         <v>6.9</v>
       </c>
       <c r="CL6" t="n">
-        <v>109.1069351487465</v>
+        <v>109.1109705560335</v>
       </c>
       <c r="CM6" t="n">
-        <v>120.0121845976516</v>
+        <v>120.012812332996</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         <v>46.56999969482422</v>
       </c>
       <c r="BX7" t="n">
-        <v>17.74536429240872</v>
+        <v>17.74536425519681</v>
       </c>
       <c r="BY7" t="n">
-        <v>32.91765076241818</v>
+        <v>32.91765069339008</v>
       </c>
       <c r="BZ7" t="n">
         <v>75.52662129209557</v>
@@ -2778,23 +2778,23 @@
         <v>56.51525123994185</v>
       </c>
       <c r="CB7" t="n">
-        <v>103.8564308648494</v>
+        <v>103.8564309200723</v>
       </c>
       <c r="CC7" t="n">
-        <v>48.58755190688473</v>
+        <v>48.58755191586955</v>
       </c>
       <c r="CD7" t="n">
-        <v>61.39492097587762</v>
+        <v>61.39492105067058</v>
       </c>
       <c r="CE7" t="inlineStr"/>
       <c r="CF7" t="n">
-        <v>43.6942970634518</v>
+        <v>43.694297039138</v>
       </c>
       <c r="CG7" t="n">
-        <v>40.75260133465145</v>
+        <v>40.75260130462981</v>
       </c>
       <c r="CH7" t="n">
-        <v>36.67734120118631</v>
+        <v>36.67734117416683</v>
       </c>
       <c r="CI7" t="n">
         <v>4</v>
@@ -2806,10 +2806,10 @@
         <v>4.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>-21.24255649230201</v>
+        <v>-21.24255655032107</v>
       </c>
       <c r="CM7" t="n">
-        <v>-6.17501105908752</v>
+        <v>-6.175011111296669</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>0.98</v>
       </c>
       <c r="BI8" t="n">
-        <v>87.15000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="BJ8" t="n">
         <v>33.5</v>
@@ -3080,10 +3080,10 @@
         <v>-25.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BV8" t="n">
         <v>0.57</v>
@@ -3092,10 +3092,10 @@
         <v>29.89999961853027</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.20974212418462</v>
+        <v>22.20916577175993</v>
       </c>
       <c r="BY8" t="n">
-        <v>41.19907164036248</v>
+        <v>41.19800250661468</v>
       </c>
       <c r="BZ8" t="n">
         <v>47.27625238013437</v>
@@ -3104,25 +3104,25 @@
         <v>20.75930620677502</v>
       </c>
       <c r="CB8" t="n">
-        <v>67.55010998277137</v>
+        <v>67.55450326117871</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.53731573302993</v>
+        <v>53.53805622687435</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.66889760145738</v>
+        <v>28.67226432956505</v>
       </c>
       <c r="CE8" t="n">
         <v>23.7514480389424</v>
       </c>
       <c r="CF8" t="n">
-        <v>38.1190179634572</v>
+        <v>38.11987484023057</v>
       </c>
       <c r="CG8" t="n">
-        <v>34.93398462090992</v>
+        <v>34.93513341808986</v>
       </c>
       <c r="CH8" t="n">
-        <v>31.44058615881893</v>
+        <v>31.44162007628088</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -3134,10 +3134,10 @@
         <v>3.3</v>
       </c>
       <c r="CL8" t="n">
-        <v>5.152463411183117</v>
+        <v>5.15592132916014</v>
       </c>
       <c r="CM8" t="n">
-        <v>27.48835601935344</v>
+        <v>27.49122182799659</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3408,22 +3408,22 @@
         <v>-43.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>-22.3</v>
+        <v>-22.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="BW9" t="n">
         <v>4.46999979019165</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.02542178438461</v>
+        <v>3.025275119143402</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.612157410033452</v>
+        <v>5.61188534601101</v>
       </c>
       <c r="BZ9" t="n">
         <v>12.73709617635255</v>
@@ -3432,7 +3432,7 @@
         <v>8.558256916730283</v>
       </c>
       <c r="CB9" t="n">
-        <v>23.52815093209878</v>
+        <v>23.52770935932955</v>
       </c>
       <c r="CC9" t="n">
         <v>11.57513776217851</v>
@@ -3444,7 +3444,7 @@
         <v>5.155438154799276</v>
       </c>
       <c r="CF9" t="n">
-        <v>11.25683567278082</v>
+        <v>11.25673372466772</v>
       </c>
       <c r="CG9" t="n">
         <v>11.57513776217851</v>
@@ -3465,7 +3465,7 @@
         <v>133.0564759492753</v>
       </c>
       <c r="CM9" t="n">
-        <v>151.8307874976027</v>
+        <v>151.8285067790818</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>-16.75977866941296</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-43.78031520539255</v>
+        <v>-43.78031869667932</v>
       </c>
       <c r="DA9" t="b">
         <v>1</v>
@@ -3748,10 +3748,10 @@
         <v>15.64999961853027</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.389485077899922</v>
+        <v>6.38948506165804</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.85249481950435</v>
+        <v>11.85249478937566</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.41207045901055</v>
@@ -3760,19 +3760,19 @@
         <v>18.65776617291419</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.32865343248093</v>
+        <v>35.32865345875565</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.30206848486783</v>
+        <v>12.30206848794914</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.43947277499434</v>
+        <v>20.43947280902563</v>
       </c>
       <c r="CE10" t="n">
         <v>17.94300967523397</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.27650511700088</v>
+        <v>20.27650512175211</v>
       </c>
       <c r="CG10" t="n">
         <v>18.65776617291419</v>
@@ -3793,7 +3793,7 @@
         <v>7.297060478776829</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.56233617407011</v>
+        <v>29.56233620442941</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4076,10 +4076,10 @@
         <v>32.22000122070312</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.99391743966054</v>
+        <v>44.99391766859999</v>
       </c>
       <c r="BY11" t="n">
-        <v>83.46371685057029</v>
+        <v>83.46371727525298</v>
       </c>
       <c r="BZ11" t="n">
         <v>68.08851932604726</v>
@@ -4100,7 +4100,7 @@
         <v>24.86437698596777</v>
       </c>
       <c r="CF11" t="n">
-        <v>77.15449572205138</v>
+        <v>77.15449581542597</v>
       </c>
       <c r="CG11" t="n">
         <v>68.08851932604726</v>
@@ -4121,7 +4121,7 @@
         <v>90.19138755980858</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.4614922375464</v>
+        <v>139.4614925273496</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4390,34 +4390,34 @@
         <v>33.99</v>
       </c>
       <c r="BP12" t="n">
-        <v>26.84</v>
+        <v>26.77</v>
       </c>
       <c r="BQ12" t="n">
         <v>47.05</v>
       </c>
       <c r="BR12" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="BS12" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BW12" t="n">
         <v>42.95185852050781</v>
       </c>
       <c r="BX12" t="n">
-        <v>123.7525655898296</v>
+        <v>123.7530441509836</v>
       </c>
       <c r="BY12" t="n">
-        <v>229.5610091691339</v>
+        <v>229.5618969000746</v>
       </c>
       <c r="BZ12" t="n">
         <v>132.970122756245</v>
@@ -4438,13 +4438,13 @@
         <v>57.73149631390972</v>
       </c>
       <c r="CF12" t="n">
-        <v>139.1786394114076</v>
+        <v>139.1788101979195</v>
       </c>
       <c r="CG12" t="n">
-        <v>122.5909426194644</v>
+        <v>122.5911819000414</v>
       </c>
       <c r="CH12" t="n">
-        <v>110.331848357518</v>
+        <v>110.3320637100373</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4456,10 +4456,10 @@
         <v>5.3</v>
       </c>
       <c r="CL12" t="n">
-        <v>156.8732812919815</v>
+        <v>156.8737826731248</v>
       </c>
       <c r="CM12" t="n">
-        <v>224.0340329975601</v>
+        <v>224.0344306206612</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>7.41</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AY13" t="n">
         <v>32.79</v>
@@ -4712,22 +4712,22 @@
         <v>-17.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BW13" t="n">
         <v>18.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>12.54642264821688</v>
+        <v>12.54689652838352</v>
       </c>
       <c r="BY13" t="n">
-        <v>23.27361401244231</v>
+        <v>23.27449306015142</v>
       </c>
       <c r="BZ13" t="n">
         <v>19.9845041322314</v>
@@ -4736,7 +4736,7 @@
         <v>12.4901078746637</v>
       </c>
       <c r="CB13" t="n">
-        <v>33.82230719628399</v>
+        <v>33.82285548738589</v>
       </c>
       <c r="CC13" t="n">
         <v>22.8984489302328</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>19.67574743078085</v>
+        <v>19.67608566274978</v>
       </c>
       <c r="CG13" t="n">
         <v>21.4414765312321</v>
@@ -4767,7 +4767,7 @@
         <v>5.738788373199388</v>
       </c>
       <c r="CM13" t="n">
-        <v>7.812314689210109</v>
+        <v>7.814168015067313</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -5040,22 +5040,22 @@
         <v>-8.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BW14" t="n">
         <v>47.99185562133789</v>
       </c>
       <c r="BX14" t="n">
-        <v>131.1054577321602</v>
+        <v>131.1061229136058</v>
       </c>
       <c r="BY14" t="n">
-        <v>243.2006240931572</v>
+        <v>243.2018580047387</v>
       </c>
       <c r="BZ14" t="n">
         <v>133.3107100592719</v>
@@ -5076,13 +5076,13 @@
         <v>56.36047046127493</v>
       </c>
       <c r="CF14" t="n">
-        <v>141.8578948174911</v>
+        <v>141.8581322041194</v>
       </c>
       <c r="CG14" t="n">
-        <v>126.4229021384269</v>
+        <v>126.4232347291497</v>
       </c>
       <c r="CH14" t="n">
-        <v>113.7806119245842</v>
+        <v>113.7809112562347</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -5094,10 +5094,10 @@
         <v>5.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>137.0831684907714</v>
+        <v>137.0837922042048</v>
       </c>
       <c r="CM14" t="n">
-        <v>195.5874345363277</v>
+        <v>195.5879291757311</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         <v>17.32999992370605</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.62120825073235</v>
+        <v>10.62120827830933</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.70234130510852</v>
+        <v>19.7023413562638</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.45880897049025</v>
@@ -5392,25 +5392,25 @@
         <v>36.8907150460014</v>
       </c>
       <c r="CB15" t="n">
-        <v>41.91990550878272</v>
+        <v>41.91990552087936</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.52256327451072</v>
+        <v>34.52256326866235</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.654585451202</v>
+        <v>18.65458541921712</v>
       </c>
       <c r="CE15" t="n">
         <v>31.24600421044032</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.48498910950513</v>
+        <v>31.48498911313637</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.52256327451072</v>
+        <v>34.52256326866235</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.07030694705965</v>
+        <v>31.07030694179611</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5422,10 +5422,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>79.28624976251702</v>
+        <v>79.28624973214464</v>
       </c>
       <c r="CM15" t="n">
-        <v>81.67910702893994</v>
+        <v>81.67910704989343</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>-6.124074482380681</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-24.09722456771111</v>
+        <v>-24.09721816922623</v>
       </c>
       <c r="DA15" t="b">
         <v>1</v>
@@ -5663,7 +5663,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>73.89</v>
+        <v>73.87</v>
       </c>
       <c r="BJ16" t="n">
         <v>-30.3</v>
@@ -5696,10 +5696,10 @@
         <v>-48.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>-16.4</v>
+        <v>-16.7</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BV16" t="n">
         <v>0.71</v>
@@ -5708,10 +5708,10 @@
         <v>9.739999771118164</v>
       </c>
       <c r="BX16" t="n">
-        <v>9.754236617904695</v>
+        <v>9.752333580856762</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.09410892621321</v>
+        <v>18.09057879248929</v>
       </c>
       <c r="BZ16" t="n">
         <v>24.48861422529709</v>
@@ -5720,25 +5720,25 @@
         <v>17.58365889509133</v>
       </c>
       <c r="CB16" t="n">
-        <v>37.92942696620967</v>
+        <v>37.93100544696957</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.34739855870606</v>
+        <v>24.3482191395866</v>
       </c>
       <c r="CD16" t="n">
-        <v>12.49077182297235</v>
+        <v>12.49494175775179</v>
       </c>
       <c r="CE16" t="n">
         <v>9.739999771118164</v>
       </c>
       <c r="CF16" t="n">
-        <v>19.30352697293907</v>
+        <v>19.30366895114507</v>
       </c>
       <c r="CG16" t="n">
-        <v>17.83888391065227</v>
+        <v>17.83711884379031</v>
       </c>
       <c r="CH16" t="n">
-        <v>16.05499551958705</v>
+        <v>16.05340695941128</v>
       </c>
       <c r="CI16" t="n">
         <v>8</v>
@@ -5750,10 +5750,10 @@
         <v>3.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>64.83568682613954</v>
+        <v>64.81937717302768</v>
       </c>
       <c r="CM16" t="n">
-        <v>98.18816659708196</v>
+        <v>98.18962427890273</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -5940,13 +5940,13 @@
         <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AS17" t="b">
         <v>1</v>
       </c>
       <c r="AT17" t="n">
-        <v>3429433856</v>
+        <v>5449639424</v>
       </c>
       <c r="AU17" t="n">
         <v>6.37</v>
@@ -6024,7 +6024,7 @@
         <v>-38.2</v>
       </c>
       <c r="BT17" t="n">
-        <v>-18.4</v>
+        <v>-18.5</v>
       </c>
       <c r="BU17" t="n">
         <v>1.47</v>
@@ -6036,10 +6036,10 @@
         <v>10.47999954223633</v>
       </c>
       <c r="BX17" t="n">
-        <v>9.072864391128032</v>
+        <v>9.072864347902492</v>
       </c>
       <c r="BY17" t="n">
-        <v>16.8301634455425</v>
+        <v>16.83016336535912</v>
       </c>
       <c r="BZ17" t="n">
         <v>21.79905713259518</v>
@@ -6048,25 +6048,25 @@
         <v>12.87581943989401</v>
       </c>
       <c r="CB17" t="n">
-        <v>33.73326015275214</v>
+        <v>33.7332602803279</v>
       </c>
       <c r="CC17" t="n">
-        <v>25.62013687860695</v>
+        <v>25.62013691058676</v>
       </c>
       <c r="CD17" t="n">
-        <v>13.06488810288561</v>
+        <v>13.06488824279113</v>
       </c>
       <c r="CE17" t="n">
         <v>9.30550460634233</v>
       </c>
       <c r="CF17" t="n">
-        <v>17.78771176871834</v>
+        <v>17.78771179072487</v>
       </c>
       <c r="CG17" t="n">
-        <v>14.94752577421406</v>
+        <v>14.94752580407512</v>
       </c>
       <c r="CH17" t="n">
-        <v>13.45277319679265</v>
+        <v>13.45277322366761</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6078,10 +6078,10 @@
         <v>3.7</v>
       </c>
       <c r="CL17" t="n">
-        <v>28.36616206494569</v>
+        <v>28.36616232138616</v>
       </c>
       <c r="CM17" t="n">
-        <v>69.73008154275759</v>
+        <v>69.73008175274353</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>3.46</v>
       </c>
       <c r="BI18" t="n">
-        <v>89.90000000000001</v>
+        <v>89.91</v>
       </c>
       <c r="BJ18" t="n">
         <v>23.5</v>
@@ -6352,49 +6352,49 @@
         <v>-12.2</v>
       </c>
       <c r="BT18" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW18" t="n">
         <v>34.38000106811523</v>
       </c>
       <c r="BX18" t="n">
-        <v>24.72347832048936</v>
+        <v>24.72393461563617</v>
       </c>
       <c r="BY18" t="n">
-        <v>31.08887020637266</v>
+        <v>31.08816147351682</v>
       </c>
       <c r="BZ18" t="n">
-        <v>34.57974289034262</v>
+        <v>34.57831640058278</v>
       </c>
       <c r="CA18" t="n">
         <v>36.14131846677351</v>
       </c>
       <c r="CB18" t="n">
-        <v>48.69040290507824</v>
+        <v>48.68948609367126</v>
       </c>
       <c r="CC18" t="n">
-        <v>48.57188486807643</v>
+        <v>48.57168412732013</v>
       </c>
       <c r="CD18" t="n">
-        <v>16.52668479248031</v>
+        <v>16.5256588584722</v>
       </c>
       <c r="CE18" t="n">
         <v>29.95270377341624</v>
       </c>
       <c r="CF18" t="n">
-        <v>33.78438577787867</v>
+        <v>33.78390797617364</v>
       </c>
       <c r="CG18" t="n">
-        <v>32.83430654835764</v>
+        <v>32.8332389370498</v>
       </c>
       <c r="CH18" t="n">
-        <v>29.55087589352188</v>
+        <v>29.54991504334482</v>
       </c>
       <c r="CI18" t="n">
         <v>8</v>
@@ -6406,10 +6406,10 @@
         <v>2.9</v>
       </c>
       <c r="CL18" t="n">
-        <v>-14.04632060663894</v>
+        <v>-14.04911540055169</v>
       </c>
       <c r="CM18" t="n">
-        <v>-1.732446980023372</v>
+        <v>-1.733836746428807</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="DD18" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.8, +0.9% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x0.9, +0.9% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
         <v>0.76</v>
       </c>
       <c r="BI19" t="n">
-        <v>32.33</v>
+        <v>32.32</v>
       </c>
       <c r="BJ19" t="n">
         <v>3.2</v>
@@ -6688,22 +6688,22 @@
         <v>-31.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>-21.3</v>
+        <v>-21.4</v>
       </c>
       <c r="BU19" t="n">
         <v>1.46</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BW19" t="n">
         <v>10.98999977111816</v>
       </c>
       <c r="BX19" t="n">
-        <v>3.424809591929229</v>
+        <v>3.424362293534259</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.353021793028721</v>
+        <v>6.352192054506049</v>
       </c>
       <c r="BZ19" t="n">
         <v>19.65148407116271</v>
@@ -6712,13 +6712,13 @@
         <v>18.513475240297</v>
       </c>
       <c r="CB19" t="n">
-        <v>20.93333042328002</v>
+        <v>20.93338770487991</v>
       </c>
       <c r="CC19" t="n">
-        <v>15.9166954243071</v>
+        <v>15.91678366165456</v>
       </c>
       <c r="CD19" t="n">
-        <v>13.05292134138598</v>
+        <v>13.05348855153468</v>
       </c>
       <c r="CE19" t="n">
         <v>28.64218279833469</v>
@@ -7018,10 +7018,10 @@
         <v>26.86000061035156</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.115263333060311</v>
+        <v>7.115263290125771</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.19881348282688</v>
+        <v>13.1988134031833</v>
       </c>
       <c r="BZ20" t="n">
         <v>35.80432676933181</v>
@@ -7030,19 +7030,19 @@
         <v>28.29365159335656</v>
       </c>
       <c r="CB20" t="n">
-        <v>45.03018690797735</v>
+        <v>45.0301869708485</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.50039356777111</v>
+        <v>26.50039357847983</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.22423174337965</v>
+        <v>29.22423182090912</v>
       </c>
       <c r="CE20" t="n">
         <v>23.5668842743778</v>
       </c>
       <c r="CF20" t="n">
-        <v>28.80264119128874</v>
+        <v>28.80264120149813</v>
       </c>
       <c r="CG20" t="n">
         <v>28.29365159335656</v>
@@ -7063,7 +7063,7 @@
         <v>-5.196255192163946</v>
       </c>
       <c r="CM20" t="n">
-        <v>7.232466629909529</v>
+        <v>7.232466667919191</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>-7.60233611170672</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-23.86225492369548</v>
+        <v>-23.86224665397592</v>
       </c>
       <c r="DA20" t="b">
         <v>1</v>
@@ -7283,7 +7283,7 @@
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="n">
-        <v>100.82</v>
+        <v>100.83</v>
       </c>
       <c r="BJ21" t="n">
         <v>-0.1</v>
@@ -7314,22 +7314,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW21" t="n">
         <v>37.18999862670898</v>
       </c>
       <c r="BX21" t="n">
-        <v>34.07294329184204</v>
+        <v>34.07781570272913</v>
       </c>
       <c r="BY21" t="n">
-        <v>49.61020543292201</v>
+        <v>49.61729966317361</v>
       </c>
       <c r="BZ21" t="n">
         <v>49.2081406765615</v>
@@ -7346,13 +7346,13 @@
       </c>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="n">
-        <v>48.09886359628581</v>
+        <v>48.10185525657049</v>
       </c>
       <c r="CG21" t="n">
-        <v>49.40917305474176</v>
+        <v>49.41272016986755</v>
       </c>
       <c r="CH21" t="n">
-        <v>44.46825574926758</v>
+        <v>44.4714481528808</v>
       </c>
       <c r="CI21" t="n">
         <v>4</v>
@@ -7364,10 +7364,10 @@
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>19.57046891991958</v>
+        <v>19.57905295791662</v>
       </c>
       <c r="CM21" t="n">
-        <v>29.33279207421733</v>
+        <v>29.3408363344893</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -7650,10 +7650,10 @@
         <v>21.52000045776367</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.029635323010476</v>
+        <v>3.029635331043024</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.619973524184433</v>
+        <v>5.61997353908481</v>
       </c>
       <c r="BZ22" t="n">
         <v>32.85023111352173</v>
@@ -7662,7 +7662,7 @@
         <v>27.39136539639765</v>
       </c>
       <c r="CB22" t="n">
-        <v>42.07544946873292</v>
+        <v>42.07544948168865</v>
       </c>
       <c r="CC22" t="n">
         <v>10.85340539909456</v>
@@ -7956,10 +7956,10 @@
         <v>-32.1</v>
       </c>
       <c r="BT23" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BV23" t="n">
         <v>0.44</v>
@@ -7968,10 +7968,10 @@
         <v>32.18000030517578</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.192481966833107</v>
+        <v>3.192274472260646</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.922054048475414</v>
+        <v>5.921669146043498</v>
       </c>
       <c r="BZ23" t="n">
         <v>32.5982418993562</v>
@@ -7980,7 +7980,7 @@
         <v>22.82235087014609</v>
       </c>
       <c r="CB23" t="n">
-        <v>40.3206997028517</v>
+        <v>40.32047761385977</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8040,7 +8040,7 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CX23" t="n">
@@ -8250,13 +8250,13 @@
         <v>79.81999999999999</v>
       </c>
       <c r="BP24" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BQ24" t="n">
         <v>14.81</v>
       </c>
       <c r="BR24" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="BS24" t="n">
         <v>-15.6</v>
@@ -8265,7 +8265,7 @@
         <v>-6.3</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BV24" t="n">
         <v>0.88</v>
@@ -8274,35 +8274,35 @@
         <v>12.5</v>
       </c>
       <c r="BX24" t="n">
-        <v>8.391865450100273</v>
+        <v>8.391835611596907</v>
       </c>
       <c r="BY24" t="n">
-        <v>14.24201355997039</v>
+        <v>14.24205155841178</v>
       </c>
       <c r="BZ24" t="n">
-        <v>19.62806827095434</v>
+        <v>19.62819043057112</v>
       </c>
       <c r="CA24" t="n">
         <v>17.48233699953358</v>
       </c>
       <c r="CB24" t="n">
-        <v>23.82024699044768</v>
+        <v>23.82027375345167</v>
       </c>
       <c r="CC24" t="n">
-        <v>17.41208256318266</v>
+        <v>17.41209082144219</v>
       </c>
       <c r="CD24" t="n">
-        <v>9.732369319862141</v>
+        <v>9.732420155123551</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>14.91850746105192</v>
+        <v>14.9185421055055</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.82704806157652</v>
+        <v>15.82707118992699</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.24434325541887</v>
+        <v>14.24436407093429</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8314,10 +8314,10 @@
         <v>2.3</v>
       </c>
       <c r="CL24" t="n">
-        <v>13.95474604335099</v>
+        <v>13.95491256747432</v>
       </c>
       <c r="CM24" t="n">
-        <v>19.34805968841533</v>
+        <v>19.34833684404398</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>0.93</v>
       </c>
       <c r="BI25" t="n">
-        <v>53.34</v>
+        <v>53.33</v>
       </c>
       <c r="BJ25" t="n">
         <v>17.8</v>
@@ -8556,22 +8556,22 @@
         <v>7.66</v>
       </c>
       <c r="BP25" t="n">
-        <v>12.4</v>
+        <v>12.38</v>
       </c>
       <c r="BQ25" t="n">
         <v>17.96</v>
       </c>
       <c r="BR25" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="BS25" t="n">
         <v>-20.2</v>
       </c>
       <c r="BT25" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BV25" t="n">
         <v>0.84</v>
@@ -8580,10 +8580,10 @@
         <v>14.32999992370605</v>
       </c>
       <c r="BX25" t="n">
-        <v>8.905780260521059</v>
+        <v>8.905449517252643</v>
       </c>
       <c r="BY25" t="n">
-        <v>16.52022238326656</v>
+        <v>16.51960885450365</v>
       </c>
       <c r="BZ25" t="n">
         <v>30.97430652350819</v>
@@ -8592,23 +8592,23 @@
         <v>29.43388465049835</v>
       </c>
       <c r="CB25" t="n">
-        <v>35.75351902359017</v>
+        <v>35.75341793193715</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.58444332373756</v>
+        <v>25.58451050061468</v>
       </c>
       <c r="CD25" t="n">
-        <v>15.93378815263295</v>
+        <v>15.93419941204263</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.49618812275834</v>
+        <v>20.49596884896979</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.05233285350207</v>
+        <v>21.05205967755916</v>
       </c>
       <c r="CH25" t="n">
-        <v>18.94709956815186</v>
+        <v>18.94685370980325</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8620,10 +8620,10 @@
         <v>3.5</v>
       </c>
       <c r="CL25" t="n">
-        <v>32.2198162528093</v>
+        <v>32.21810056299829</v>
       </c>
       <c r="CM25" t="n">
-        <v>43.02992485611665</v>
+        <v>43.02839468312487</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>-11.18262088953247</v>
       </c>
       <c r="CZ25" t="n">
-        <v>-21.22131924064164</v>
+        <v>-21.22135337943183</v>
       </c>
       <c r="DA25" t="b">
         <v>1</v>
@@ -8861,7 +8861,7 @@
         <v>0.15</v>
       </c>
       <c r="BI26" t="n">
-        <v>228.23</v>
+        <v>228.24</v>
       </c>
       <c r="BJ26" t="n">
         <v>90.7</v>
@@ -8894,7 +8894,7 @@
         <v>-5.4</v>
       </c>
       <c r="BT26" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="BU26" t="n">
         <v>1.1</v>
@@ -8906,10 +8906,10 @@
         <v>5.900000095367432</v>
       </c>
       <c r="BX26" t="n">
-        <v>7.000252746958866</v>
+        <v>7.000436734462028</v>
       </c>
       <c r="BY26" t="n">
-        <v>12.9854688456087</v>
+        <v>12.98581014242706</v>
       </c>
       <c r="BZ26" t="n">
         <v>5.689592522825215</v>
@@ -8930,7 +8930,7 @@
         <v>5.412237592239494</v>
       </c>
       <c r="CF26" t="n">
-        <v>7.363804944717845</v>
+        <v>7.363870605258036</v>
       </c>
       <c r="CG26" t="n">
         <v>5.911462928079274</v>
@@ -8951,7 +8951,7 @@
         <v>-9.825143232645727</v>
       </c>
       <c r="CM26" t="n">
-        <v>24.81025128287313</v>
+        <v>24.81136417336685</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
       <c r="CV26" t="inlineStr"/>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CX26" t="n">
@@ -9200,13 +9200,13 @@
         <v>6.67</v>
       </c>
       <c r="BP27" t="n">
-        <v>32.63</v>
+        <v>32.61</v>
       </c>
       <c r="BQ27" t="n">
         <v>48.4</v>
       </c>
       <c r="BR27" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="BS27" t="n">
         <v>-20.3</v>
@@ -9215,7 +9215,7 @@
         <v>-7</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BV27" t="n">
         <v>0.85</v>
@@ -9224,10 +9224,10 @@
         <v>38.59999847412109</v>
       </c>
       <c r="BX27" t="n">
-        <v>19.73089423195889</v>
+        <v>19.73061786521055</v>
       </c>
       <c r="BY27" t="n">
-        <v>36.60080880028374</v>
+        <v>36.60029613996557</v>
       </c>
       <c r="BZ27" t="n">
         <v>56.01861771983619</v>
@@ -9236,23 +9236,23 @@
         <v>42.32200432760474</v>
       </c>
       <c r="CB27" t="n">
-        <v>63.15584159669065</v>
+        <v>63.15628643485311</v>
       </c>
       <c r="CC27" t="n">
-        <v>45.30457425204306</v>
+        <v>45.30466061151618</v>
       </c>
       <c r="CD27" t="n">
-        <v>31.97454788608441</v>
+        <v>31.97509387623241</v>
       </c>
       <c r="CE27" t="inlineStr"/>
       <c r="CF27" t="n">
-        <v>39.41372375103047</v>
+        <v>39.41354808413212</v>
       </c>
       <c r="CG27" t="n">
-        <v>40.9526915261634</v>
+        <v>40.95247837574088</v>
       </c>
       <c r="CH27" t="n">
-        <v>36.85742237354706</v>
+        <v>36.8572305381668</v>
       </c>
       <c r="CI27" t="n">
         <v>4</v>
@@ -9264,10 +9264,10 @@
         <v>2.8</v>
       </c>
       <c r="CL27" t="n">
-        <v>-4.514446034867914</v>
+        <v>-4.514943017737982</v>
       </c>
       <c r="CM27" t="n">
-        <v>2.10809665563827</v>
+        <v>2.107641560028717</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>-10.5860548729689</v>
       </c>
       <c r="CZ27" t="n">
-        <v>-20.73760748031875</v>
+        <v>-20.73761372683879</v>
       </c>
       <c r="DA27" t="b">
         <v>1</v>
@@ -9526,13 +9526,13 @@
         <v>44.81</v>
       </c>
       <c r="BP28" t="n">
-        <v>20.58</v>
+        <v>20.47</v>
       </c>
       <c r="BQ28" t="n">
         <v>31.63</v>
       </c>
       <c r="BR28" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="BS28" t="n">
         <v>-17.7</v>
@@ -9544,43 +9544,43 @@
         <v>0.98</v>
       </c>
       <c r="BV28" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BW28" t="n">
         <v>26.02000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.63820050436581</v>
+        <v>16.63763597848288</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.24299340528112</v>
+        <v>28.24291837605552</v>
       </c>
       <c r="BZ28" t="n">
-        <v>48.53670370467485</v>
+        <v>48.53822164173958</v>
       </c>
       <c r="CA28" t="n">
         <v>53.13771001269293</v>
       </c>
       <c r="CB28" t="n">
-        <v>57.10921877319265</v>
+        <v>57.10900738864706</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.1191674216231</v>
+        <v>43.11927016338144</v>
       </c>
       <c r="CD28" t="n">
-        <v>24.06559372317708</v>
+        <v>24.06622513408661</v>
       </c>
       <c r="CE28" t="n">
         <v>29.31279211564875</v>
       </c>
       <c r="CF28" t="n">
-        <v>37.52029745758203</v>
+        <v>37.52047260134185</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.21597976863593</v>
+        <v>36.2160311395151</v>
       </c>
       <c r="CH28" t="n">
-        <v>32.59438179177234</v>
+        <v>32.59442802556359</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9592,10 +9592,10 @@
         <v>3.4</v>
       </c>
       <c r="CL28" t="n">
-        <v>25.26664572769846</v>
+        <v>25.26682341328814</v>
       </c>
       <c r="CM28" t="n">
-        <v>44.19791236547415</v>
+        <v>44.19858547752926</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9878,37 +9878,37 @@
         <v>15</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.819252150976158</v>
+        <v>5.819252139010201</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.575330928179753</v>
+        <v>8.575330938444459</v>
       </c>
       <c r="BZ29" t="n">
-        <v>11.04106327809497</v>
+        <v>11.04106331401458</v>
       </c>
       <c r="CA29" t="n">
         <v>11.6021005542244</v>
       </c>
       <c r="CB29" t="n">
-        <v>10.00747569780333</v>
+        <v>10.00747571691271</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.94224989814919</v>
+        <v>14.94224990236679</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.511532851205339</v>
+        <v>5.511532870580615</v>
       </c>
       <c r="CE29" t="n">
         <v>10.66215185399864</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.770144651578974</v>
+        <v>9.770144661194051</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.33481377590099</v>
+        <v>10.33481378545568</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.301332398310889</v>
+        <v>9.30133240691011</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9920,10 +9920,10 @@
         <v>2.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>-37.99111734459407</v>
+        <v>-37.99111728726594</v>
       </c>
       <c r="CM29" t="n">
-        <v>-34.86570232280683</v>
+        <v>-34.86570225870634</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>-26.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="BU2" t="n">
         <v>1.38</v>
@@ -10762,10 +10762,10 @@
         <v>10.15999984741211</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.738884128649667</v>
+        <v>5.739092644462467</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.64563005864513</v>
+        <v>10.64601685547787</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.29447790742652</v>
@@ -10774,7 +10774,7 @@
         <v>27.67799880047428</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.39398021848989</v>
+        <v>71.39487568517062</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -10836,7 +10836,7 @@
         <v>-8.878922017834656</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-28.21663909745649</v>
+        <v>-28.21664403987539</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -11080,10 +11080,10 @@
         <v>13.67000007629395</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.08411221122868</v>
+        <v>15.08411215817256</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.9810281518292</v>
+        <v>27.9810280534101</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.78533212224727</v>
@@ -11092,13 +11092,13 @@
         <v>23.4303842936706</v>
       </c>
       <c r="CB3" t="n">
-        <v>73.80863262284781</v>
+        <v>73.80863272421371</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.30691184730974</v>
+        <v>48.30691188646256</v>
       </c>
       <c r="CD3" t="n">
-        <v>25.78976666715468</v>
+        <v>25.78976683084767</v>
       </c>
       <c r="CE3" t="n">
         <v>8.630044464581562</v>
@@ -11398,10 +11398,10 @@
         <v>23.51000022888184</v>
       </c>
       <c r="BX4" t="n">
-        <v>15.55616502675489</v>
+        <v>15.55616500524296</v>
       </c>
       <c r="BY4" t="n">
-        <v>28.85668612463031</v>
+        <v>28.85668608472568</v>
       </c>
       <c r="BZ4" t="n">
         <v>71.12043448234802</v>
@@ -11410,13 +11410,13 @@
         <v>51.51277527306067</v>
       </c>
       <c r="CB4" t="n">
-        <v>127.4881988902025</v>
+        <v>127.4881988948674</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.80183479209307</v>
+        <v>25.80183479517592</v>
       </c>
       <c r="CD4" t="n">
-        <v>63.22015028192994</v>
+        <v>63.22015032808249</v>
       </c>
       <c r="CE4" t="n">
         <v>41.54649601907847</v>
@@ -11704,22 +11704,22 @@
         <v>-60.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>-25.7</v>
+        <v>-26.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW5" t="n">
         <v>6.900000095367432</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.115400814292661</v>
+        <v>3.115400820686986</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.779068510512887</v>
+        <v>5.779068522374359</v>
       </c>
       <c r="BZ5" t="n">
         <v>19.83188747583914</v>
@@ -11728,7 +11728,7 @@
         <v>13.5801516746889</v>
       </c>
       <c r="CB5" t="n">
-        <v>31.91228044047912</v>
+        <v>31.91228045989789</v>
       </c>
       <c r="CC5" t="n">
         <v>10.95072400487419</v>
@@ -11784,10 +11784,10 @@
         </is>
       </c>
       <c r="CX5" t="n">
-        <v>7.360000133514404</v>
+        <v>7.5</v>
       </c>
       <c r="CY5" t="n">
-        <v>-6.250000404922851</v>
+        <v>-7.999998728434243</v>
       </c>
       <c r="CZ5" t="n">
         <v>-60.30064258156551</v>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-6.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-8.0%))</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
         <v>0.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>51.57</v>
+        <v>51.56</v>
       </c>
       <c r="BJ6" t="n">
         <v>-14</v>
@@ -12020,22 +12020,22 @@
         <v>-37.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>-23.6</v>
+        <v>-23.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="BW6" t="n">
         <v>4.179999828338623</v>
       </c>
       <c r="BX6" t="n">
-        <v>3.539319177617177</v>
+        <v>3.539168768139573</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.565437074479863</v>
+        <v>6.565158064898907</v>
       </c>
       <c r="BZ6" t="n">
         <v>12.73218338516937</v>
@@ -12044,25 +12044,25 @@
         <v>8.571766632368943</v>
       </c>
       <c r="CB6" t="n">
-        <v>24.57145988209843</v>
+        <v>24.57157214911559</v>
       </c>
       <c r="CC6" t="n">
-        <v>11.28763497763521</v>
+        <v>11.28769657875037</v>
       </c>
       <c r="CD6" t="n">
-        <v>10.85194343487941</v>
+        <v>10.85231827936312</v>
       </c>
       <c r="CE6" t="n">
         <v>5.170088126502553</v>
       </c>
       <c r="CF6" t="n">
-        <v>9.196508938505891</v>
+        <v>9.196535177842211</v>
       </c>
       <c r="CG6" t="n">
-        <v>9.711855033624179</v>
+        <v>9.71204245586603</v>
       </c>
       <c r="CH6" t="n">
-        <v>8.740669530261762</v>
+        <v>8.740838210279428</v>
       </c>
       <c r="CI6" t="n">
         <v>6</v>
@@ -12074,10 +12074,10 @@
         <v>6.9</v>
       </c>
       <c r="CL6" t="n">
-        <v>109.1069351487465</v>
+        <v>109.1109705560335</v>
       </c>
       <c r="CM6" t="n">
-        <v>120.0121845976516</v>
+        <v>120.012812332996</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -12342,10 +12342,10 @@
         <v>46.56999969482422</v>
       </c>
       <c r="BX7" t="n">
-        <v>17.74536429240872</v>
+        <v>17.74536425519681</v>
       </c>
       <c r="BY7" t="n">
-        <v>32.91765076241818</v>
+        <v>32.91765069339008</v>
       </c>
       <c r="BZ7" t="n">
         <v>75.52662129209557</v>
@@ -12354,23 +12354,23 @@
         <v>56.51525123994185</v>
       </c>
       <c r="CB7" t="n">
-        <v>103.8564308648494</v>
+        <v>103.8564309200723</v>
       </c>
       <c r="CC7" t="n">
-        <v>48.58755190688473</v>
+        <v>48.58755191586955</v>
       </c>
       <c r="CD7" t="n">
-        <v>61.39492097587762</v>
+        <v>61.39492105067058</v>
       </c>
       <c r="CE7" t="inlineStr"/>
       <c r="CF7" t="n">
-        <v>43.6942970634518</v>
+        <v>43.694297039138</v>
       </c>
       <c r="CG7" t="n">
-        <v>40.75260133465145</v>
+        <v>40.75260130462981</v>
       </c>
       <c r="CH7" t="n">
-        <v>36.67734120118631</v>
+        <v>36.67734117416683</v>
       </c>
       <c r="CI7" t="n">
         <v>4</v>
@@ -12382,10 +12382,10 @@
         <v>4.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>-21.24255649230201</v>
+        <v>-21.24255655032107</v>
       </c>
       <c r="CM7" t="n">
-        <v>-6.17501105908752</v>
+        <v>-6.175011111296669</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>0.98</v>
       </c>
       <c r="BI8" t="n">
-        <v>87.15000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="BJ8" t="n">
         <v>33.5</v>
@@ -12656,10 +12656,10 @@
         <v>-25.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BV8" t="n">
         <v>0.57</v>
@@ -12668,10 +12668,10 @@
         <v>29.89999961853027</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.20974212418462</v>
+        <v>22.20916577175993</v>
       </c>
       <c r="BY8" t="n">
-        <v>41.19907164036248</v>
+        <v>41.19800250661468</v>
       </c>
       <c r="BZ8" t="n">
         <v>47.27625238013437</v>
@@ -12680,25 +12680,25 @@
         <v>20.75930620677502</v>
       </c>
       <c r="CB8" t="n">
-        <v>67.55010998277137</v>
+        <v>67.55450326117871</v>
       </c>
       <c r="CC8" t="n">
-        <v>53.53731573302993</v>
+        <v>53.53805622687435</v>
       </c>
       <c r="CD8" t="n">
-        <v>28.66889760145738</v>
+        <v>28.67226432956505</v>
       </c>
       <c r="CE8" t="n">
         <v>23.7514480389424</v>
       </c>
       <c r="CF8" t="n">
-        <v>38.1190179634572</v>
+        <v>38.11987484023057</v>
       </c>
       <c r="CG8" t="n">
-        <v>34.93398462090992</v>
+        <v>34.93513341808986</v>
       </c>
       <c r="CH8" t="n">
-        <v>31.44058615881893</v>
+        <v>31.44162007628088</v>
       </c>
       <c r="CI8" t="n">
         <v>8</v>
@@ -12710,10 +12710,10 @@
         <v>3.3</v>
       </c>
       <c r="CL8" t="n">
-        <v>5.152463411183117</v>
+        <v>5.15592132916014</v>
       </c>
       <c r="CM8" t="n">
-        <v>27.48835601935344</v>
+        <v>27.49122182799659</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -12984,22 +12984,22 @@
         <v>-43.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>-22.3</v>
+        <v>-22.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="BW9" t="n">
         <v>4.46999979019165</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.02542178438461</v>
+        <v>3.025275119143402</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.612157410033452</v>
+        <v>5.61188534601101</v>
       </c>
       <c r="BZ9" t="n">
         <v>12.73709617635255</v>
@@ -13008,7 +13008,7 @@
         <v>8.558256916730283</v>
       </c>
       <c r="CB9" t="n">
-        <v>23.52815093209878</v>
+        <v>23.52770935932955</v>
       </c>
       <c r="CC9" t="n">
         <v>11.57513776217851</v>
@@ -13020,7 +13020,7 @@
         <v>5.155438154799276</v>
       </c>
       <c r="CF9" t="n">
-        <v>11.25683567278082</v>
+        <v>11.25673372466772</v>
       </c>
       <c r="CG9" t="n">
         <v>11.57513776217851</v>
@@ -13041,7 +13041,7 @@
         <v>133.0564759492753</v>
       </c>
       <c r="CM9" t="n">
-        <v>151.8307874976027</v>
+        <v>151.8285067790818</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>-16.75977866941296</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-43.78031520539255</v>
+        <v>-43.78031869667932</v>
       </c>
       <c r="DA9" t="b">
         <v>1</v>
@@ -13324,10 +13324,10 @@
         <v>15.64999961853027</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.389485077899922</v>
+        <v>6.38948506165804</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.85249481950435</v>
+        <v>11.85249478937566</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.41207045901055</v>
@@ -13336,19 +13336,19 @@
         <v>18.65776617291419</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.32865343248093</v>
+        <v>35.32865345875565</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.30206848486783</v>
+        <v>12.30206848794914</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.43947277499434</v>
+        <v>20.43947280902563</v>
       </c>
       <c r="CE10" t="n">
         <v>17.94300967523397</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.27650511700088</v>
+        <v>20.27650512175211</v>
       </c>
       <c r="CG10" t="n">
         <v>18.65776617291419</v>
@@ -13369,7 +13369,7 @@
         <v>7.297060478776829</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.56233617407011</v>
+        <v>29.56233620442941</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -13652,10 +13652,10 @@
         <v>32.22000122070312</v>
       </c>
       <c r="BX11" t="n">
-        <v>44.99391743966054</v>
+        <v>44.99391766859999</v>
       </c>
       <c r="BY11" t="n">
-        <v>83.46371685057029</v>
+        <v>83.46371727525298</v>
       </c>
       <c r="BZ11" t="n">
         <v>68.08851932604726</v>
@@ -13676,7 +13676,7 @@
         <v>24.86437698596777</v>
       </c>
       <c r="CF11" t="n">
-        <v>77.15449572205138</v>
+        <v>77.15449581542597</v>
       </c>
       <c r="CG11" t="n">
         <v>68.08851932604726</v>
@@ -13697,7 +13697,7 @@
         <v>90.19138755980858</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.4614922375464</v>
+        <v>139.4614925273496</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -13988,10 +13988,10 @@
         <v>6.820000171661377</v>
       </c>
       <c r="BX12" t="n">
-        <v>6.397639781834083</v>
+        <v>6.397639802179014</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.86762179530222</v>
+        <v>11.86762183304207</v>
       </c>
       <c r="BZ12" t="n">
         <v>40.34151887255054</v>
@@ -14000,7 +14000,7 @@
         <v>27.23211426856263</v>
       </c>
       <c r="CB12" t="n">
-        <v>85.65489264312401</v>
+        <v>85.65489277027983</v>
       </c>
       <c r="CC12" t="n">
         <v>51.88018214566937</v>
@@ -14300,10 +14300,10 @@
         <v>13.52000045776367</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.1990986373195479</v>
+        <v>0.1990986372966361</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.2898876159372617</v>
+        <v>0.2898876159039022</v>
       </c>
       <c r="BZ13" t="n">
         <v>76.00432689769848</v>
@@ -14594,34 +14594,34 @@
         <v>33.99</v>
       </c>
       <c r="BP14" t="n">
-        <v>26.84</v>
+        <v>26.77</v>
       </c>
       <c r="BQ14" t="n">
         <v>47.05</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="BS14" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BW14" t="n">
         <v>42.95185852050781</v>
       </c>
       <c r="BX14" t="n">
-        <v>123.7525655898296</v>
+        <v>123.7530441509836</v>
       </c>
       <c r="BY14" t="n">
-        <v>229.5610091691339</v>
+        <v>229.5618969000746</v>
       </c>
       <c r="BZ14" t="n">
         <v>132.970122756245</v>
@@ -14642,13 +14642,13 @@
         <v>57.73149631390972</v>
       </c>
       <c r="CF14" t="n">
-        <v>139.1786394114076</v>
+        <v>139.1788101979195</v>
       </c>
       <c r="CG14" t="n">
-        <v>122.5909426194644</v>
+        <v>122.5911819000414</v>
       </c>
       <c r="CH14" t="n">
-        <v>110.331848357518</v>
+        <v>110.3320637100373</v>
       </c>
       <c r="CI14" t="n">
         <v>8</v>
@@ -14660,10 +14660,10 @@
         <v>5.3</v>
       </c>
       <c r="CL14" t="n">
-        <v>156.8732812919815</v>
+        <v>156.8737826731248</v>
       </c>
       <c r="CM14" t="n">
-        <v>224.0340329975601</v>
+        <v>224.0344306206612</v>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
@@ -14916,22 +14916,22 @@
         <v>-28</v>
       </c>
       <c r="BT15" t="n">
-        <v>-8.9</v>
+        <v>-9.1</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BW15" t="n">
         <v>13.35999965667725</v>
       </c>
       <c r="BX15" t="n">
-        <v>9.69707911856962</v>
+        <v>9.696598467714521</v>
       </c>
       <c r="BY15" t="n">
-        <v>17.98808176494665</v>
+        <v>17.98719015761043</v>
       </c>
       <c r="BZ15" t="n">
         <v>49.58543289943235</v>
@@ -14940,23 +14940,23 @@
         <v>48.92317894641553</v>
       </c>
       <c r="CB15" t="n">
-        <v>69.64895944123833</v>
+        <v>69.64796681617162</v>
       </c>
       <c r="CC15" t="n">
-        <v>33.99023100072877</v>
+        <v>33.99030572968265</v>
       </c>
       <c r="CD15" t="n">
-        <v>29.87346037530802</v>
+        <v>29.87402123717782</v>
       </c>
       <c r="CE15" t="inlineStr"/>
       <c r="CF15" t="n">
-        <v>33.85458188836925</v>
+        <v>33.85430959557515</v>
       </c>
       <c r="CG15" t="n">
-        <v>33.99023100072877</v>
+        <v>33.99030572968265</v>
       </c>
       <c r="CH15" t="n">
-        <v>30.59120790065589</v>
+        <v>30.59127515671438</v>
       </c>
       <c r="CI15" t="n">
         <v>3</v>
@@ -14968,10 +14968,10 @@
         <v>5.1</v>
       </c>
       <c r="CL15" t="n">
-        <v>128.9761129250224</v>
+        <v>128.9766163386468</v>
       </c>
       <c r="CM15" t="n">
-        <v>153.4025655565713</v>
+        <v>153.4005274368025</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>7.41</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>32.79</v>
@@ -15220,22 +15220,22 @@
         <v>-17.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BW16" t="n">
         <v>18.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>12.54642264821688</v>
+        <v>12.54689652838352</v>
       </c>
       <c r="BY16" t="n">
-        <v>23.27361401244231</v>
+        <v>23.27449306015142</v>
       </c>
       <c r="BZ16" t="n">
         <v>19.9845041322314</v>
@@ -15244,7 +15244,7 @@
         <v>12.4901078746637</v>
       </c>
       <c r="CB16" t="n">
-        <v>33.82230719628399</v>
+        <v>33.82285548738589</v>
       </c>
       <c r="CC16" t="n">
         <v>22.8984489302328</v>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>19.67574743078085</v>
+        <v>19.67608566274978</v>
       </c>
       <c r="CG16" t="n">
         <v>21.4414765312321</v>
@@ -15275,7 +15275,7 @@
         <v>5.738788373199388</v>
       </c>
       <c r="CM16" t="n">
-        <v>7.812314689210109</v>
+        <v>7.814168015067313</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -15758,22 +15758,22 @@
         <v>-8.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BW18" t="n">
         <v>47.99185562133789</v>
       </c>
       <c r="BX18" t="n">
-        <v>131.1054577321602</v>
+        <v>131.1061229136058</v>
       </c>
       <c r="BY18" t="n">
-        <v>243.2006240931572</v>
+        <v>243.2018580047387</v>
       </c>
       <c r="BZ18" t="n">
         <v>133.3107100592719</v>
@@ -15794,13 +15794,13 @@
         <v>56.36047046127493</v>
       </c>
       <c r="CF18" t="n">
-        <v>141.8578948174911</v>
+        <v>141.8581322041194</v>
       </c>
       <c r="CG18" t="n">
-        <v>126.4229021384269</v>
+        <v>126.4232347291497</v>
       </c>
       <c r="CH18" t="n">
-        <v>113.7806119245842</v>
+        <v>113.7809112562347</v>
       </c>
       <c r="CI18" t="n">
         <v>8</v>
@@ -15812,10 +15812,10 @@
         <v>5.4</v>
       </c>
       <c r="CL18" t="n">
-        <v>137.0831684907714</v>
+        <v>137.0837922042048</v>
       </c>
       <c r="CM18" t="n">
-        <v>195.5874345363277</v>
+        <v>195.5879291757311</v>
       </c>
       <c r="CN18" t="inlineStr">
         <is>
@@ -16098,10 +16098,10 @@
         <v>17.32999992370605</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.62120825073235</v>
+        <v>10.62120827830933</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.70234130510852</v>
+        <v>19.7023413562638</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.45880897049025</v>
@@ -16110,25 +16110,25 @@
         <v>36.8907150460014</v>
       </c>
       <c r="CB19" t="n">
-        <v>41.91990550878272</v>
+        <v>41.91990552087936</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.52256327451072</v>
+        <v>34.52256326866235</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.654585451202</v>
+        <v>18.65458541921712</v>
       </c>
       <c r="CE19" t="n">
         <v>31.24600421044032</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.48498910950513</v>
+        <v>31.48498911313637</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.52256327451072</v>
+        <v>34.52256326866235</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.07030694705965</v>
+        <v>31.07030694179611</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -16140,10 +16140,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>79.28624976251702</v>
+        <v>79.28624973214464</v>
       </c>
       <c r="CM19" t="n">
-        <v>81.67910702893994</v>
+        <v>81.67910704989343</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>-6.124074482380681</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-24.09722456771111</v>
+        <v>-24.09721816922623</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -16381,7 +16381,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>73.89</v>
+        <v>73.87</v>
       </c>
       <c r="BJ20" t="n">
         <v>-30.3</v>
@@ -16414,10 +16414,10 @@
         <v>-48.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>-16.4</v>
+        <v>-16.7</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BV20" t="n">
         <v>0.71</v>
@@ -16426,10 +16426,10 @@
         <v>9.739999771118164</v>
       </c>
       <c r="BX20" t="n">
-        <v>9.754236617904695</v>
+        <v>9.752333580856762</v>
       </c>
       <c r="BY20" t="n">
-        <v>18.09410892621321</v>
+        <v>18.09057879248929</v>
       </c>
       <c r="BZ20" t="n">
         <v>24.48861422529709</v>
@@ -16438,25 +16438,25 @@
         <v>17.58365889509133</v>
       </c>
       <c r="CB20" t="n">
-        <v>37.92942696620967</v>
+        <v>37.93100544696957</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.34739855870606</v>
+        <v>24.3482191395866</v>
       </c>
       <c r="CD20" t="n">
-        <v>12.49077182297235</v>
+        <v>12.49494175775179</v>
       </c>
       <c r="CE20" t="n">
         <v>9.739999771118164</v>
       </c>
       <c r="CF20" t="n">
-        <v>19.30352697293907</v>
+        <v>19.30366895114507</v>
       </c>
       <c r="CG20" t="n">
-        <v>17.83888391065227</v>
+        <v>17.83711884379031</v>
       </c>
       <c r="CH20" t="n">
-        <v>16.05499551958705</v>
+        <v>16.05340695941128</v>
       </c>
       <c r="CI20" t="n">
         <v>8</v>
@@ -16468,10 +16468,10 @@
         <v>3.9</v>
       </c>
       <c r="CL20" t="n">
-        <v>64.83568682613954</v>
+        <v>64.81937717302768</v>
       </c>
       <c r="CM20" t="n">
-        <v>98.18816659708196</v>
+        <v>98.18962427890273</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -16658,13 +16658,13 @@
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AS21" t="b">
         <v>1</v>
       </c>
       <c r="AT21" t="n">
-        <v>3429433856</v>
+        <v>5449639424</v>
       </c>
       <c r="AU21" t="n">
         <v>6.37</v>
@@ -16742,7 +16742,7 @@
         <v>-38.2</v>
       </c>
       <c r="BT21" t="n">
-        <v>-18.4</v>
+        <v>-18.5</v>
       </c>
       <c r="BU21" t="n">
         <v>1.47</v>
@@ -16754,10 +16754,10 @@
         <v>10.47999954223633</v>
       </c>
       <c r="BX21" t="n">
-        <v>9.072864391128032</v>
+        <v>9.072864347902492</v>
       </c>
       <c r="BY21" t="n">
-        <v>16.8301634455425</v>
+        <v>16.83016336535912</v>
       </c>
       <c r="BZ21" t="n">
         <v>21.79905713259518</v>
@@ -16766,25 +16766,25 @@
         <v>12.87581943989401</v>
       </c>
       <c r="CB21" t="n">
-        <v>33.73326015275214</v>
+        <v>33.7332602803279</v>
       </c>
       <c r="CC21" t="n">
-        <v>25.62013687860695</v>
+        <v>25.62013691058676</v>
       </c>
       <c r="CD21" t="n">
-        <v>13.06488810288561</v>
+        <v>13.06488824279113</v>
       </c>
       <c r="CE21" t="n">
         <v>9.30550460634233</v>
       </c>
       <c r="CF21" t="n">
-        <v>17.78771176871834</v>
+        <v>17.78771179072487</v>
       </c>
       <c r="CG21" t="n">
-        <v>14.94752577421406</v>
+        <v>14.94752580407512</v>
       </c>
       <c r="CH21" t="n">
-        <v>13.45277319679265</v>
+        <v>13.45277322366761</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -16796,10 +16796,10 @@
         <v>3.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>28.36616206494569</v>
+        <v>28.36616232138616</v>
       </c>
       <c r="CM21" t="n">
-        <v>69.73008154275759</v>
+        <v>69.73008175274353</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>3.46</v>
       </c>
       <c r="BI22" t="n">
-        <v>89.90000000000001</v>
+        <v>89.91</v>
       </c>
       <c r="BJ22" t="n">
         <v>23.5</v>
@@ -17070,49 +17070,49 @@
         <v>-12.2</v>
       </c>
       <c r="BT22" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BW22" t="n">
         <v>34.38000106811523</v>
       </c>
       <c r="BX22" t="n">
-        <v>24.72347832048936</v>
+        <v>24.72393461563617</v>
       </c>
       <c r="BY22" t="n">
-        <v>31.08887020637266</v>
+        <v>31.08816147351682</v>
       </c>
       <c r="BZ22" t="n">
-        <v>34.57974289034262</v>
+        <v>34.57831640058278</v>
       </c>
       <c r="CA22" t="n">
         <v>36.14131846677351</v>
       </c>
       <c r="CB22" t="n">
-        <v>48.69040290507824</v>
+        <v>48.68948609367126</v>
       </c>
       <c r="CC22" t="n">
-        <v>48.57188486807643</v>
+        <v>48.57168412732013</v>
       </c>
       <c r="CD22" t="n">
-        <v>16.52668479248031</v>
+        <v>16.5256588584722</v>
       </c>
       <c r="CE22" t="n">
         <v>29.95270377341624</v>
       </c>
       <c r="CF22" t="n">
-        <v>33.78438577787867</v>
+        <v>33.78390797617364</v>
       </c>
       <c r="CG22" t="n">
-        <v>32.83430654835764</v>
+        <v>32.8332389370498</v>
       </c>
       <c r="CH22" t="n">
-        <v>29.55087589352188</v>
+        <v>29.54991504334482</v>
       </c>
       <c r="CI22" t="n">
         <v>8</v>
@@ -17124,10 +17124,10 @@
         <v>2.9</v>
       </c>
       <c r="CL22" t="n">
-        <v>-14.04632060663894</v>
+        <v>-14.04911540055169</v>
       </c>
       <c r="CM22" t="n">
-        <v>-1.732446980023372</v>
+        <v>-1.733836746428807</v>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="DD22" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.8, +0.9% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x0.9, +0.9% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
         <v>0.76</v>
       </c>
       <c r="BI23" t="n">
-        <v>32.33</v>
+        <v>32.32</v>
       </c>
       <c r="BJ23" t="n">
         <v>3.2</v>
@@ -17406,22 +17406,22 @@
         <v>-31.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>-21.3</v>
+        <v>-21.4</v>
       </c>
       <c r="BU23" t="n">
         <v>1.46</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BW23" t="n">
         <v>10.98999977111816</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.424809591929229</v>
+        <v>3.424362293534259</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.353021793028721</v>
+        <v>6.352192054506049</v>
       </c>
       <c r="BZ23" t="n">
         <v>19.65148407116271</v>
@@ -17430,13 +17430,13 @@
         <v>18.513475240297</v>
       </c>
       <c r="CB23" t="n">
-        <v>20.93333042328002</v>
+        <v>20.93338770487991</v>
       </c>
       <c r="CC23" t="n">
-        <v>15.9166954243071</v>
+        <v>15.91678366165456</v>
       </c>
       <c r="CD23" t="n">
-        <v>13.05292134138598</v>
+        <v>13.05348855153468</v>
       </c>
       <c r="CE23" t="n">
         <v>28.64218279833469</v>
@@ -17722,22 +17722,22 @@
         <v>-27.1</v>
       </c>
       <c r="BT24" t="n">
-        <v>-9.6</v>
+        <v>-9.9</v>
       </c>
       <c r="BU24" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="BV24" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="BW24" t="n">
         <v>3.525049924850464</v>
       </c>
       <c r="BX24" t="n">
-        <v>5.015290523664889</v>
+        <v>5.015081573902594</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.30226300245608</v>
+        <v>7.301958771602177</v>
       </c>
       <c r="BZ24" t="n">
         <v>6.558232418326445</v>
@@ -17756,7 +17756,7 @@
         <v>2.269402021603749</v>
       </c>
       <c r="CF24" t="n">
-        <v>5.575222812753002</v>
+        <v>5.575137282650303</v>
       </c>
       <c r="CG24" t="n">
         <v>5.913671306074423</v>
@@ -17777,7 +17777,7 @@
         <v>50.98521408013133</v>
       </c>
       <c r="CM24" t="n">
-        <v>58.16010926397046</v>
+        <v>58.1576829124429</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -18056,10 +18056,10 @@
         <v>14.0600004196167</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.318536256933776</v>
+        <v>4.318536269126794</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.010884756612157</v>
+        <v>8.010884779230203</v>
       </c>
       <c r="BZ25" t="n">
         <v>24.13147740413487</v>
@@ -18068,25 +18068,25 @@
         <v>20.35919220371624</v>
       </c>
       <c r="CB25" t="n">
-        <v>29.81638086056989</v>
+        <v>29.81638085183569</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.74090519151497</v>
+        <v>16.74090518898501</v>
       </c>
       <c r="CD25" t="n">
-        <v>18.68436342508419</v>
+        <v>18.68436340569534</v>
       </c>
       <c r="CE25" t="n">
         <v>14.0600004196167</v>
       </c>
       <c r="CF25" t="n">
-        <v>18.82902918017843</v>
+        <v>18.82902917903058</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.68436342508419</v>
+        <v>18.68436340569534</v>
       </c>
       <c r="CH25" t="n">
-        <v>16.81592708257578</v>
+        <v>16.81592706512581</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -18098,10 +18098,10 @@
         <v>6.9</v>
       </c>
       <c r="CL25" t="n">
-        <v>19.60118478456068</v>
+        <v>19.60118466044998</v>
       </c>
       <c r="CM25" t="n">
-        <v>33.91912246252795</v>
+        <v>33.91912245436401</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -18370,13 +18370,13 @@
         <v>-57.5</v>
       </c>
       <c r="BT26" t="n">
-        <v>-28.5</v>
+        <v>-28.7</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BV26" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BW26" t="n">
         <v>7.639999866485596</v>
@@ -18682,22 +18682,22 @@
         <v>-20</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BV27" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="BW27" t="n">
         <v>12.84000015258789</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.050127599998383</v>
+        <v>8.050127617909942</v>
       </c>
       <c r="BY27" t="n">
-        <v>14.932986697997</v>
+        <v>14.93298673122294</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.59952054530692</v>
@@ -18718,7 +18718,7 @@
         <v>6.103131550478226</v>
       </c>
       <c r="CF27" t="n">
-        <v>10.92917655698372</v>
+        <v>10.92917656428908</v>
       </c>
       <c r="CG27" t="n">
         <v>11.06929470524033</v>
@@ -18739,7 +18739,7 @@
         <v>-22.41148663297802</v>
       </c>
       <c r="CM27" t="n">
-        <v>-14.88180352723005</v>
+        <v>-14.88180347033475</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -19022,10 +19022,10 @@
         <v>26.86000061035156</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.115263333060311</v>
+        <v>7.115263290125771</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.19881348282688</v>
+        <v>13.1988134031833</v>
       </c>
       <c r="BZ28" t="n">
         <v>35.80432676933181</v>
@@ -19034,19 +19034,19 @@
         <v>28.29365159335656</v>
       </c>
       <c r="CB28" t="n">
-        <v>45.03018690797735</v>
+        <v>45.0301869708485</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.50039356777111</v>
+        <v>26.50039357847983</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.22423174337965</v>
+        <v>29.22423182090912</v>
       </c>
       <c r="CE28" t="n">
         <v>23.5668842743778</v>
       </c>
       <c r="CF28" t="n">
-        <v>28.80264119128874</v>
+        <v>28.80264120149813</v>
       </c>
       <c r="CG28" t="n">
         <v>28.29365159335656</v>
@@ -19067,7 +19067,7 @@
         <v>-5.196255192163946</v>
       </c>
       <c r="CM28" t="n">
-        <v>7.232466629909529</v>
+        <v>7.232466667919191</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>-7.60233611170672</v>
       </c>
       <c r="CZ28" t="n">
-        <v>-23.86225492369548</v>
+        <v>-23.86224665397592</v>
       </c>
       <c r="DA28" t="b">
         <v>1</v>
@@ -19287,7 +19287,7 @@
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="n">
-        <v>100.82</v>
+        <v>100.83</v>
       </c>
       <c r="BJ29" t="n">
         <v>-0.1</v>
@@ -19318,22 +19318,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="BT29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BV29" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW29" t="n">
         <v>37.18999862670898</v>
       </c>
       <c r="BX29" t="n">
-        <v>34.07294329184204</v>
+        <v>34.07781570272913</v>
       </c>
       <c r="BY29" t="n">
-        <v>49.61020543292201</v>
+        <v>49.61729966317361</v>
       </c>
       <c r="BZ29" t="n">
         <v>49.2081406765615</v>
@@ -19350,13 +19350,13 @@
       </c>
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="n">
-        <v>48.09886359628581</v>
+        <v>48.10185525657049</v>
       </c>
       <c r="CG29" t="n">
-        <v>49.40917305474176</v>
+        <v>49.41272016986755</v>
       </c>
       <c r="CH29" t="n">
-        <v>44.46825574926758</v>
+        <v>44.4714481528808</v>
       </c>
       <c r="CI29" t="n">
         <v>4</v>
@@ -19368,10 +19368,10 @@
         <v>1.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>19.57046891991958</v>
+        <v>19.57905295791662</v>
       </c>
       <c r="CM29" t="n">
-        <v>29.33279207421733</v>
+        <v>29.3408363344893</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -19654,10 +19654,10 @@
         <v>21.52000045776367</v>
       </c>
       <c r="BX30" t="n">
-        <v>3.029635323010476</v>
+        <v>3.029635331043024</v>
       </c>
       <c r="BY30" t="n">
-        <v>5.619973524184433</v>
+        <v>5.61997353908481</v>
       </c>
       <c r="BZ30" t="n">
         <v>32.85023111352173</v>
@@ -19666,7 +19666,7 @@
         <v>27.39136539639765</v>
       </c>
       <c r="CB30" t="n">
-        <v>42.07544946873292</v>
+        <v>42.07544948168865</v>
       </c>
       <c r="CC30" t="n">
         <v>10.85340539909456</v>
@@ -19876,7 +19876,7 @@
         <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="AS31" t="b">
         <v>1</v>
@@ -19972,10 +19972,10 @@
         <v>11.10000038146973</v>
       </c>
       <c r="BX31" t="n">
-        <v>1.917937792372778</v>
+        <v>1.917937790757718</v>
       </c>
       <c r="BY31" t="n">
-        <v>3.557774604851503</v>
+        <v>3.557774601855566</v>
       </c>
       <c r="BZ31" t="n">
         <v>27.96102757689617</v>
@@ -19984,7 +19984,7 @@
         <v>23.67867811885924</v>
       </c>
       <c r="CB31" t="n">
-        <v>36.75877087742677</v>
+        <v>36.75877087312813</v>
       </c>
       <c r="CC31" t="n">
         <v>9.158754146</v>
@@ -20286,10 +20286,10 @@
         <v>31.13999938964844</v>
       </c>
       <c r="BX32" t="n">
-        <v>7.388909098999219</v>
+        <v>7.388909089439232</v>
       </c>
       <c r="BY32" t="n">
-        <v>13.70642637864355</v>
+        <v>13.70642636090977</v>
       </c>
       <c r="BZ32" t="n">
         <v>62.61077267266187</v>
@@ -20298,7 +20298,7 @@
         <v>36.53770887188449</v>
       </c>
       <c r="CB32" t="n">
-        <v>86.57734722772622</v>
+        <v>86.57734720741668</v>
       </c>
       <c r="CC32" t="n">
         <v>22.51480113099953</v>
@@ -20582,35 +20582,35 @@
         <v>22.73999977111816</v>
       </c>
       <c r="BX33" t="n">
-        <v>16.32028063783208</v>
+        <v>16.32028061879938</v>
       </c>
       <c r="BY33" t="n">
-        <v>29.66719087753363</v>
+        <v>29.66719088042677</v>
       </c>
       <c r="BZ33" t="n">
-        <v>50.82005038691943</v>
+        <v>50.82005045114169</v>
       </c>
       <c r="CA33" t="n">
         <v>49.41817723779874</v>
       </c>
       <c r="CB33" t="n">
-        <v>62.2148626693532</v>
+        <v>62.2148626609286</v>
       </c>
       <c r="CC33" t="n">
-        <v>45.81119022606887</v>
+        <v>45.81119023020867</v>
       </c>
       <c r="CD33" t="n">
-        <v>24.84311427855419</v>
+        <v>24.84311430208622</v>
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>35.6546780320885</v>
+        <v>35.65467804514412</v>
       </c>
       <c r="CG33" t="n">
-        <v>37.73919055180126</v>
+        <v>37.73919055531772</v>
       </c>
       <c r="CH33" t="n">
-        <v>33.96527149662113</v>
+        <v>33.96527149978595</v>
       </c>
       <c r="CI33" t="n">
         <v>4</v>
@@ -20622,10 +20622,10 @@
         <v>3.1</v>
       </c>
       <c r="CL33" t="n">
-        <v>49.36355249994359</v>
+        <v>49.36355251386099</v>
       </c>
       <c r="CM33" t="n">
-        <v>56.79278096287908</v>
+        <v>56.79278102029164</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -20892,10 +20892,10 @@
         <v>-32.1</v>
       </c>
       <c r="BT34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BU34" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BV34" t="n">
         <v>0.44</v>
@@ -20904,10 +20904,10 @@
         <v>32.18000030517578</v>
       </c>
       <c r="BX34" t="n">
-        <v>3.192481966833107</v>
+        <v>3.192274472260646</v>
       </c>
       <c r="BY34" t="n">
-        <v>5.922054048475414</v>
+        <v>5.921669146043498</v>
       </c>
       <c r="BZ34" t="n">
         <v>32.5982418993562</v>
@@ -20916,7 +20916,7 @@
         <v>22.82235087014609</v>
       </c>
       <c r="CB34" t="n">
-        <v>40.3206997028517</v>
+        <v>40.32047761385977</v>
       </c>
       <c r="CC34" t="n">
         <v>10.59424454785779</v>
@@ -20976,7 +20976,7 @@
       <c r="CV34" t="inlineStr"/>
       <c r="CW34" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CX34" t="n">
@@ -21230,10 +21230,10 @@
         <v>33.22999954223633</v>
       </c>
       <c r="BX35" t="n">
-        <v>15.05518488751047</v>
+        <v>15.05518488409303</v>
       </c>
       <c r="BY35" t="n">
-        <v>27.92736796633193</v>
+        <v>27.92736795999258</v>
       </c>
       <c r="BZ35" t="n">
         <v>19.95908857364602</v>
@@ -21242,7 +21242,7 @@
         <v>36.83662170557399</v>
       </c>
       <c r="CB35" t="n">
-        <v>26.87749697012078</v>
+        <v>26.87749696795196</v>
       </c>
       <c r="CC35" t="n">
         <v>15.03391666666667</v>
@@ -21254,7 +21254,7 @@
         <v>76.15609957570291</v>
       </c>
       <c r="CF35" t="n">
-        <v>22.37178645907932</v>
+        <v>22.37178645737566</v>
       </c>
       <c r="CG35" t="n">
         <v>19.95908857364602</v>
@@ -21275,7 +21275,7 @@
         <v>-45.94288304623754</v>
       </c>
       <c r="CM35" t="n">
-        <v>-32.67593509700744</v>
+        <v>-32.67593510213431</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>-34.5</v>
       </c>
       <c r="BT36" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="BU36" t="n">
         <v>1.72</v>
@@ -21554,10 +21554,10 @@
         <v>23.11000061035156</v>
       </c>
       <c r="BX36" t="n">
-        <v>11.99003827108877</v>
+        <v>11.99003828575855</v>
       </c>
       <c r="BY36" t="n">
-        <v>22.24152099286967</v>
+        <v>22.24152102008211</v>
       </c>
       <c r="BZ36" t="n">
         <v>59.57344515314361</v>
@@ -21566,13 +21566,13 @@
         <v>49.87073049461024</v>
       </c>
       <c r="CB36" t="n">
-        <v>84.10530953738056</v>
+        <v>84.10530953983535</v>
       </c>
       <c r="CC36" t="n">
-        <v>30.75887776010265</v>
+        <v>30.75887775780049</v>
       </c>
       <c r="CD36" t="n">
-        <v>44.3495368096694</v>
+        <v>44.34953678609681</v>
       </c>
       <c r="CE36" t="n">
         <v>5.075463930454974</v>
@@ -21828,13 +21828,13 @@
         <v>79.81999999999999</v>
       </c>
       <c r="BP37" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BQ37" t="n">
         <v>14.81</v>
       </c>
       <c r="BR37" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="BS37" t="n">
         <v>-15.6</v>
@@ -21843,7 +21843,7 @@
         <v>-6.3</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BV37" t="n">
         <v>0.88</v>
@@ -21852,35 +21852,35 @@
         <v>12.5</v>
       </c>
       <c r="BX37" t="n">
-        <v>8.391865450100273</v>
+        <v>8.391835611596907</v>
       </c>
       <c r="BY37" t="n">
-        <v>14.24201355997039</v>
+        <v>14.24205155841178</v>
       </c>
       <c r="BZ37" t="n">
-        <v>19.62806827095434</v>
+        <v>19.62819043057112</v>
       </c>
       <c r="CA37" t="n">
         <v>17.48233699953358</v>
       </c>
       <c r="CB37" t="n">
-        <v>23.82024699044768</v>
+        <v>23.82027375345167</v>
       </c>
       <c r="CC37" t="n">
-        <v>17.41208256318266</v>
+        <v>17.41209082144219</v>
       </c>
       <c r="CD37" t="n">
-        <v>9.732369319862141</v>
+        <v>9.732420155123551</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>14.91850746105192</v>
+        <v>14.9185421055055</v>
       </c>
       <c r="CG37" t="n">
-        <v>15.82704806157652</v>
+        <v>15.82707118992699</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.24434325541887</v>
+        <v>14.24436407093429</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -21892,10 +21892,10 @@
         <v>2.3</v>
       </c>
       <c r="CL37" t="n">
-        <v>13.95474604335099</v>
+        <v>13.95491256747432</v>
       </c>
       <c r="CM37" t="n">
-        <v>19.34805968841533</v>
+        <v>19.34833684404398</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>0.93</v>
       </c>
       <c r="BI38" t="n">
-        <v>53.34</v>
+        <v>53.33</v>
       </c>
       <c r="BJ38" t="n">
         <v>17.8</v>
@@ -22134,22 +22134,22 @@
         <v>7.66</v>
       </c>
       <c r="BP38" t="n">
-        <v>12.4</v>
+        <v>12.38</v>
       </c>
       <c r="BQ38" t="n">
         <v>17.96</v>
       </c>
       <c r="BR38" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="BS38" t="n">
         <v>-20.2</v>
       </c>
       <c r="BT38" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BV38" t="n">
         <v>0.84</v>
@@ -22158,10 +22158,10 @@
         <v>14.32999992370605</v>
       </c>
       <c r="BX38" t="n">
-        <v>8.905780260521059</v>
+        <v>8.905449517252643</v>
       </c>
       <c r="BY38" t="n">
-        <v>16.52022238326656</v>
+        <v>16.51960885450365</v>
       </c>
       <c r="BZ38" t="n">
         <v>30.97430652350819</v>
@@ -22170,23 +22170,23 @@
         <v>29.43388465049835</v>
       </c>
       <c r="CB38" t="n">
-        <v>35.75351902359017</v>
+        <v>35.75341793193715</v>
       </c>
       <c r="CC38" t="n">
-        <v>25.58444332373756</v>
+        <v>25.58451050061468</v>
       </c>
       <c r="CD38" t="n">
-        <v>15.93378815263295</v>
+        <v>15.93419941204263</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>20.49618812275834</v>
+        <v>20.49596884896979</v>
       </c>
       <c r="CG38" t="n">
-        <v>21.05233285350207</v>
+        <v>21.05205967755916</v>
       </c>
       <c r="CH38" t="n">
-        <v>18.94709956815186</v>
+        <v>18.94685370980325</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -22198,10 +22198,10 @@
         <v>3.5</v>
       </c>
       <c r="CL38" t="n">
-        <v>32.2198162528093</v>
+        <v>32.21810056299829</v>
       </c>
       <c r="CM38" t="n">
-        <v>43.02992485611665</v>
+        <v>43.02839468312487</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>-11.18262088953247</v>
       </c>
       <c r="CZ38" t="n">
-        <v>-21.22131924064164</v>
+        <v>-21.22135337943183</v>
       </c>
       <c r="DA38" t="b">
         <v>1</v>
@@ -22439,7 +22439,7 @@
         <v>0.15</v>
       </c>
       <c r="BI39" t="n">
-        <v>228.23</v>
+        <v>228.24</v>
       </c>
       <c r="BJ39" t="n">
         <v>90.7</v>
@@ -22472,7 +22472,7 @@
         <v>-5.4</v>
       </c>
       <c r="BT39" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="BU39" t="n">
         <v>1.1</v>
@@ -22484,10 +22484,10 @@
         <v>5.900000095367432</v>
       </c>
       <c r="BX39" t="n">
-        <v>7.000252746958866</v>
+        <v>7.000436734462028</v>
       </c>
       <c r="BY39" t="n">
-        <v>12.9854688456087</v>
+        <v>12.98581014242706</v>
       </c>
       <c r="BZ39" t="n">
         <v>5.689592522825215</v>
@@ -22508,7 +22508,7 @@
         <v>5.412237592239494</v>
       </c>
       <c r="CF39" t="n">
-        <v>7.363804944717845</v>
+        <v>7.363870605258036</v>
       </c>
       <c r="CG39" t="n">
         <v>5.911462928079274</v>
@@ -22529,7 +22529,7 @@
         <v>-9.825143232645727</v>
       </c>
       <c r="CM39" t="n">
-        <v>24.81025128287313</v>
+        <v>24.81136417336685</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
       <c r="CV39" t="inlineStr"/>
       <c r="CW39" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CX39" t="n">
@@ -22778,13 +22778,13 @@
         <v>6.67</v>
       </c>
       <c r="BP40" t="n">
-        <v>32.63</v>
+        <v>32.61</v>
       </c>
       <c r="BQ40" t="n">
         <v>48.4</v>
       </c>
       <c r="BR40" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="BS40" t="n">
         <v>-20.3</v>
@@ -22793,7 +22793,7 @@
         <v>-7</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BV40" t="n">
         <v>0.85</v>
@@ -22802,10 +22802,10 @@
         <v>38.59999847412109</v>
       </c>
       <c r="BX40" t="n">
-        <v>19.73089423195889</v>
+        <v>19.73061786521055</v>
       </c>
       <c r="BY40" t="n">
-        <v>36.60080880028374</v>
+        <v>36.60029613996557</v>
       </c>
       <c r="BZ40" t="n">
         <v>56.01861771983619</v>
@@ -22814,23 +22814,23 @@
         <v>42.32200432760474</v>
       </c>
       <c r="CB40" t="n">
-        <v>63.15584159669065</v>
+        <v>63.15628643485311</v>
       </c>
       <c r="CC40" t="n">
-        <v>45.30457425204306</v>
+        <v>45.30466061151618</v>
       </c>
       <c r="CD40" t="n">
-        <v>31.97454788608441</v>
+        <v>31.97509387623241</v>
       </c>
       <c r="CE40" t="inlineStr"/>
       <c r="CF40" t="n">
-        <v>39.41372375103047</v>
+        <v>39.41354808413212</v>
       </c>
       <c r="CG40" t="n">
-        <v>40.9526915261634</v>
+        <v>40.95247837574088</v>
       </c>
       <c r="CH40" t="n">
-        <v>36.85742237354706</v>
+        <v>36.8572305381668</v>
       </c>
       <c r="CI40" t="n">
         <v>4</v>
@@ -22842,10 +22842,10 @@
         <v>2.8</v>
       </c>
       <c r="CL40" t="n">
-        <v>-4.514446034867914</v>
+        <v>-4.514943017737982</v>
       </c>
       <c r="CM40" t="n">
-        <v>2.10809665563827</v>
+        <v>2.107641560028717</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>-10.5860548729689</v>
       </c>
       <c r="CZ40" t="n">
-        <v>-20.73760748031875</v>
+        <v>-20.73761372683879</v>
       </c>
       <c r="DA40" t="b">
         <v>1</v>
@@ -23104,13 +23104,13 @@
         <v>44.81</v>
       </c>
       <c r="BP41" t="n">
-        <v>20.58</v>
+        <v>20.47</v>
       </c>
       <c r="BQ41" t="n">
         <v>31.63</v>
       </c>
       <c r="BR41" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="BS41" t="n">
         <v>-17.7</v>
@@ -23122,43 +23122,43 @@
         <v>0.98</v>
       </c>
       <c r="BV41" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BW41" t="n">
         <v>26.02000045776367</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.63820050436581</v>
+        <v>16.63763597848288</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.24299340528112</v>
+        <v>28.24291837605552</v>
       </c>
       <c r="BZ41" t="n">
-        <v>48.53670370467485</v>
+        <v>48.53822164173958</v>
       </c>
       <c r="CA41" t="n">
         <v>53.13771001269293</v>
       </c>
       <c r="CB41" t="n">
-        <v>57.10921877319265</v>
+        <v>57.10900738864706</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.1191674216231</v>
+        <v>43.11927016338144</v>
       </c>
       <c r="CD41" t="n">
-        <v>24.06559372317708</v>
+        <v>24.06622513408661</v>
       </c>
       <c r="CE41" t="n">
         <v>29.31279211564875</v>
       </c>
       <c r="CF41" t="n">
-        <v>37.52029745758203</v>
+        <v>37.52047260134185</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.21597976863593</v>
+        <v>36.2160311395151</v>
       </c>
       <c r="CH41" t="n">
-        <v>32.59438179177234</v>
+        <v>32.59442802556359</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -23170,10 +23170,10 @@
         <v>3.4</v>
       </c>
       <c r="CL41" t="n">
-        <v>25.26664572769846</v>
+        <v>25.26682341328814</v>
       </c>
       <c r="CM41" t="n">
-        <v>44.19791236547415</v>
+        <v>44.19858547752926</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -23456,37 +23456,37 @@
         <v>15</v>
       </c>
       <c r="BX42" t="n">
-        <v>5.819252150976158</v>
+        <v>5.819252139010201</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.575330928179753</v>
+        <v>8.575330938444459</v>
       </c>
       <c r="BZ42" t="n">
-        <v>11.04106327809497</v>
+        <v>11.04106331401458</v>
       </c>
       <c r="CA42" t="n">
         <v>11.6021005542244</v>
       </c>
       <c r="CB42" t="n">
-        <v>10.00747569780333</v>
+        <v>10.00747571691271</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.94224989814919</v>
+        <v>14.94224990236679</v>
       </c>
       <c r="CD42" t="n">
-        <v>5.511532851205339</v>
+        <v>5.511532870580615</v>
       </c>
       <c r="CE42" t="n">
         <v>10.66215185399864</v>
       </c>
       <c r="CF42" t="n">
-        <v>9.770144651578974</v>
+        <v>9.770144661194051</v>
       </c>
       <c r="CG42" t="n">
-        <v>10.33481377590099</v>
+        <v>10.33481378545568</v>
       </c>
       <c r="CH42" t="n">
-        <v>9.301332398310889</v>
+        <v>9.30133240691011</v>
       </c>
       <c r="CI42" t="n">
         <v>8</v>
@@ -23498,10 +23498,10 @@
         <v>2.7</v>
       </c>
       <c r="CL42" t="n">
-        <v>-37.99111734459407</v>
+        <v>-37.99111728726594</v>
       </c>
       <c r="CM42" t="n">
-        <v>-34.86570232280683</v>
+        <v>-34.86570225870634</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -23784,10 +23784,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX43" t="n">
-        <v>2.442398974625466</v>
+        <v>2.442398973185681</v>
       </c>
       <c r="BY43" t="n">
-        <v>4.53065009793024</v>
+        <v>4.530650095259437</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.27964211470329</v>
@@ -23796,19 +23796,19 @@
         <v>14.98336145462187</v>
       </c>
       <c r="CB43" t="n">
-        <v>10.44100473483714</v>
+        <v>10.44100473460217</v>
       </c>
       <c r="CC43" t="n">
-        <v>7.313546440675511</v>
+        <v>7.313546440813767</v>
       </c>
       <c r="CD43" t="n">
-        <v>6.83617107903441</v>
+        <v>6.836171080303956</v>
       </c>
       <c r="CE43" t="n">
         <v>10.0481764999888</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.633221774541608</v>
+        <v>9.633221774327613</v>
       </c>
       <c r="CG43" t="n">
         <v>10.0481764999888</v>
@@ -23829,7 +23829,7 @@
         <v>0.9303438782148454</v>
       </c>
       <c r="CM43" t="n">
-        <v>7.513635418843867</v>
+        <v>7.513635416455533</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -24108,10 +24108,10 @@
         <v>11.27000045776367</v>
       </c>
       <c r="BX44" t="n">
-        <v>4.58021510402842</v>
+        <v>4.580215098831786</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.496299017972719</v>
+        <v>8.496299008332963</v>
       </c>
       <c r="BZ44" t="n">
         <v>25.35271749836479</v>
@@ -24120,25 +24120,25 @@
         <v>28.4368783520919</v>
       </c>
       <c r="CB44" t="n">
-        <v>23.7994118079225</v>
+        <v>23.79941180295499</v>
       </c>
       <c r="CC44" t="n">
-        <v>14.26838383365511</v>
+        <v>14.26838383417095</v>
       </c>
       <c r="CD44" t="n">
-        <v>13.22806972025587</v>
+        <v>13.22806972489751</v>
       </c>
       <c r="CE44" t="n">
         <v>4.74795751088484</v>
       </c>
       <c r="CF44" t="n">
-        <v>18.93029337171048</v>
+        <v>18.93029337013551</v>
       </c>
       <c r="CG44" t="n">
-        <v>19.03389782078881</v>
+        <v>19.03389781856297</v>
       </c>
       <c r="CH44" t="n">
-        <v>17.13050803870993</v>
+        <v>17.13050803670667</v>
       </c>
       <c r="CI44" t="n">
         <v>6</v>
@@ -24150,10 +24150,10 @@
         <v>6.2</v>
       </c>
       <c r="CL44" t="n">
-        <v>52.00095246588097</v>
+        <v>52.00095244810588</v>
       </c>
       <c r="CM44" t="n">
-        <v>67.97065308608563</v>
+        <v>67.97065307211076</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -24430,10 +24430,10 @@
         <v>6.130000114440918</v>
       </c>
       <c r="BX45" t="n">
-        <v>7.26885037655265</v>
+        <v>7.268850430540041</v>
       </c>
       <c r="BY45" t="n">
-        <v>10.58344614826066</v>
+        <v>10.5834462268663</v>
       </c>
       <c r="BZ45" t="n">
         <v>8.090355480988013</v>
@@ -24452,7 +24452,7 @@
         <v>5.265969804073989</v>
       </c>
       <c r="CF45" t="n">
-        <v>8.150445878801666</v>
+        <v>8.150445900900504</v>
       </c>
       <c r="CG45" t="n">
         <v>8.453964503338835</v>
@@ -24473,7 +24473,7 @@
         <v>24.12019430604668</v>
       </c>
       <c r="CM45" t="n">
-        <v>32.95996291420984</v>
+        <v>32.95996327471291</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -24752,37 +24752,37 @@
         <v>37.56999969482422</v>
       </c>
       <c r="BX46" t="n">
-        <v>29.94470162183505</v>
+        <v>29.9447017237676</v>
       </c>
       <c r="BY46" t="n">
-        <v>36.4859831038838</v>
+        <v>36.48598301724755</v>
       </c>
       <c r="BZ46" t="n">
-        <v>41.07770302425769</v>
+        <v>41.07770278688879</v>
       </c>
       <c r="CA46" t="n">
         <v>49.93624997968088</v>
       </c>
       <c r="CB46" t="n">
-        <v>63.29224299544705</v>
+        <v>63.2922428873164</v>
       </c>
       <c r="CC46" t="n">
-        <v>16.18978533676625</v>
+        <v>16.18978532712475</v>
       </c>
       <c r="CD46" t="n">
-        <v>19.2877403636165</v>
+        <v>19.28774018295941</v>
       </c>
       <c r="CE46" t="n">
         <v>26.84451660947666</v>
       </c>
       <c r="CF46" t="n">
-        <v>35.38236537937048</v>
+        <v>35.38236531430775</v>
       </c>
       <c r="CG46" t="n">
-        <v>33.21534236285943</v>
+        <v>33.21534237050757</v>
       </c>
       <c r="CH46" t="n">
-        <v>29.89380812657349</v>
+        <v>29.89380813345682</v>
       </c>
       <c r="CI46" t="n">
         <v>8</v>
@@ -24794,10 +24794,10 @@
         <v>3.9</v>
       </c>
       <c r="CL46" t="n">
-        <v>-20.43170516530036</v>
+        <v>-20.43170514697903</v>
       </c>
       <c r="CM46" t="n">
-        <v>-5.822822286993823</v>
+        <v>-5.822822460171173</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>-4.708094976579402</v>
       </c>
       <c r="CZ46" t="n">
-        <v>-14.2471960338154</v>
+        <v>-14.24720368446166</v>
       </c>
       <c r="DA46" t="b">
         <v>0</v>
@@ -24980,7 +24980,7 @@
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>176880795648</v>
+        <v>176572465152</v>
       </c>
       <c r="AU47" t="n">
         <v>6.95</v>
@@ -25046,47 +25046,47 @@
         <v>-22.3</v>
       </c>
       <c r="BT47" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="BU47" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BV47" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BW47" t="n">
         <v>16.23999977111816</v>
       </c>
       <c r="BX47" t="n">
-        <v>9.663025679786603</v>
+        <v>9.662593998446887</v>
       </c>
       <c r="BY47" t="n">
-        <v>17.80388362077796</v>
+        <v>17.80395787619318</v>
       </c>
       <c r="BZ47" t="n">
-        <v>30.75210094481649</v>
+        <v>30.75360307551544</v>
       </c>
       <c r="CA47" t="n">
         <v>29.51697433685933</v>
       </c>
       <c r="CB47" t="n">
-        <v>33.36712868411839</v>
+        <v>33.36711306222288</v>
       </c>
       <c r="CC47" t="n">
-        <v>27.99678874795141</v>
+        <v>27.99688531784282</v>
       </c>
       <c r="CD47" t="n">
-        <v>14.98072783156003</v>
+        <v>14.98126460140508</v>
       </c>
       <c r="CE47" t="inlineStr"/>
       <c r="CF47" t="n">
-        <v>21.55394974833312</v>
+        <v>21.55426006699958</v>
       </c>
       <c r="CG47" t="n">
-        <v>22.90033618436469</v>
+        <v>22.900421597018</v>
       </c>
       <c r="CH47" t="n">
-        <v>20.61030256592822</v>
+        <v>20.6103794373162</v>
       </c>
       <c r="CI47" t="n">
         <v>4</v>
@@ -25098,10 +25098,10 @@
         <v>3.2</v>
       </c>
       <c r="CL47" t="n">
-        <v>26.91073187440782</v>
+        <v>26.91120522039965</v>
       </c>
       <c r="CM47" t="n">
-        <v>32.72136731593731</v>
+        <v>32.72327814519124</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>-12.211936357436</v>
       </c>
       <c r="CZ47" t="n">
-        <v>-23.53680885638445</v>
+        <v>-23.53680185030922</v>
       </c>
       <c r="DA47" t="b">
         <v>0</v>
@@ -25335,7 +25335,7 @@
         <v>1.75</v>
       </c>
       <c r="BI48" t="n">
-        <v>82.44</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="BJ48" t="n">
         <v>21.5</v>
@@ -25380,37 +25380,37 @@
         <v>42.31999969482422</v>
       </c>
       <c r="BX48" t="n">
-        <v>30.68855827580621</v>
+        <v>30.68716221319767</v>
       </c>
       <c r="BY48" t="n">
-        <v>48.04420121888238</v>
+        <v>48.04755977222096</v>
       </c>
       <c r="BZ48" t="n">
-        <v>58.28087750463319</v>
+        <v>58.28760323704462</v>
       </c>
       <c r="CA48" t="n">
         <v>48.04405664848608</v>
       </c>
       <c r="CB48" t="n">
-        <v>77.10597595302087</v>
+        <v>77.10873465938751</v>
       </c>
       <c r="CC48" t="n">
-        <v>60.56363778061468</v>
+        <v>60.56421142835072</v>
       </c>
       <c r="CD48" t="n">
-        <v>29.13108925673961</v>
+        <v>29.13433627499707</v>
       </c>
       <c r="CE48" t="n">
         <v>74.487863906757</v>
       </c>
       <c r="CF48" t="n">
-        <v>53.2932825681175</v>
+        <v>53.2951910175552</v>
       </c>
       <c r="CG48" t="n">
-        <v>53.16253936175778</v>
+        <v>53.16758150463279</v>
       </c>
       <c r="CH48" t="n">
-        <v>47.846285425582</v>
+        <v>47.85082335416951</v>
       </c>
       <c r="CI48" t="n">
         <v>8</v>
@@ -25422,10 +25422,10 @@
         <v>2.6</v>
       </c>
       <c r="CL48" t="n">
-        <v>13.05833121599398</v>
+        <v>13.06905410970909</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.9293075435332</v>
+        <v>25.93381711218032</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -25704,10 +25704,10 @@
         <v>12.89999961853027</v>
       </c>
       <c r="BX49" t="n">
-        <v>1.58785026563191</v>
+        <v>1.587850281718146</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.945462242747192</v>
+        <v>2.94546227258716</v>
       </c>
       <c r="BZ49" t="n">
         <v>12.70817806286439</v>
@@ -25716,7 +25716,7 @@
         <v>9.283645602580306</v>
       </c>
       <c r="CB49" t="n">
-        <v>16.03939762057999</v>
+        <v>16.03939763732403</v>
       </c>
       <c r="CC49" t="n">
         <v>6.080625000000001</v>
@@ -26018,10 +26018,10 @@
         <v>32.13000106811523</v>
       </c>
       <c r="BX50" t="n">
-        <v>10.91768365038088</v>
+        <v>10.91768363539309</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.25230317145653</v>
+        <v>20.25230314365418</v>
       </c>
       <c r="BZ50" t="n">
         <v>55.7228421665611</v>
@@ -26030,19 +26030,19 @@
         <v>52.57254206560851</v>
       </c>
       <c r="CB50" t="n">
-        <v>58.50180022594713</v>
+        <v>58.50180022865599</v>
       </c>
       <c r="CC50" t="n">
-        <v>27.80644569601039</v>
+        <v>27.80644565966546</v>
       </c>
       <c r="CD50" t="n">
-        <v>35.43190395485661</v>
+        <v>35.43190397382275</v>
       </c>
       <c r="CE50" t="n">
         <v>51.92061598058906</v>
       </c>
       <c r="CF50" t="n">
-        <v>43.17263618014704</v>
+        <v>43.17263617407958</v>
       </c>
       <c r="CG50" t="n">
         <v>51.92061598058906</v>
@@ -26063,7 +26063,7 @@
         <v>45.43589427048617</v>
       </c>
       <c r="CM50" t="n">
-        <v>34.36861109534839</v>
+        <v>34.36861107646428</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>0.76</v>
       </c>
       <c r="BI51" t="n">
-        <v>49.72</v>
+        <v>49.73</v>
       </c>
       <c r="BJ51" t="n">
         <v>677</v>
@@ -26330,10 +26330,10 @@
         <v>-4.2</v>
       </c>
       <c r="BT51" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BV51" t="n">
         <v>0.66</v>
@@ -26342,10 +26342,10 @@
         <v>34.61000061035156</v>
       </c>
       <c r="BX51" t="n">
-        <v>14.99089211623212</v>
+        <v>14.99159682696495</v>
       </c>
       <c r="BY51" t="n">
-        <v>27.80810487561059</v>
+        <v>27.80941211401997</v>
       </c>
       <c r="BZ51" t="n">
         <v>55.92469610819002</v>
@@ -26354,25 +26354,25 @@
         <v>43.21451128531487</v>
       </c>
       <c r="CB51" t="n">
-        <v>71.19613402101925</v>
+        <v>71.19521699297428</v>
       </c>
       <c r="CC51" t="n">
-        <v>38.37368980746107</v>
+        <v>38.37351584135437</v>
       </c>
       <c r="CD51" t="n">
-        <v>39.93945248313675</v>
+        <v>39.9381197905757</v>
       </c>
       <c r="CE51" t="n">
         <v>20.91248002320442</v>
       </c>
       <c r="CF51" t="n">
-        <v>42.48129551484813</v>
+        <v>42.48113602223338</v>
       </c>
       <c r="CG51" t="n">
-        <v>39.93945248313675</v>
+        <v>39.9381197905757</v>
       </c>
       <c r="CH51" t="n">
-        <v>35.94550723482308</v>
+        <v>35.94430781151814</v>
       </c>
       <c r="CI51" t="n">
         <v>7</v>
@@ -26384,10 +26384,10 @@
         <v>4.7</v>
       </c>
       <c r="CL51" t="n">
-        <v>3.858730427390067</v>
+        <v>3.855264887708487</v>
       </c>
       <c r="CM51" t="n">
-        <v>22.74283376389865</v>
+        <v>22.74237293577979</v>
       </c>
       <c r="CN51" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
       <c r="CV51" t="inlineStr"/>
       <c r="CW51" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX51" t="n">
@@ -26435,7 +26435,7 @@
       </c>
       <c r="DD51" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.2%))</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>3084497152</v>
+        <v>3079525120</v>
       </c>
       <c r="AU52" t="n">
         <v>6.18</v>
@@ -26666,37 +26666,37 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.03897349794782</v>
+        <v>8.0389735068478</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.46347159863025</v>
+        <v>11.46347160113125</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.32214928571386</v>
+        <v>17.32214927031563</v>
       </c>
       <c r="CA52" t="n">
         <v>23.9690447919977</v>
       </c>
       <c r="CB52" t="n">
-        <v>24.68791744457923</v>
+        <v>24.68791745071107</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.04946809575444</v>
+        <v>21.04946809408161</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.61419528339119</v>
+        <v>8.614195274572378</v>
       </c>
       <c r="CE52" t="n">
         <v>10.40894108722206</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.69427013565457</v>
+        <v>15.69427013460994</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.39281044217206</v>
+        <v>14.39281043572344</v>
       </c>
       <c r="CH52" t="n">
-        <v>12.95352939795485</v>
+        <v>12.95352939215109</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -26708,10 +26708,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>23.24956342396756</v>
+        <v>23.24956336874624</v>
       </c>
       <c r="CM52" t="n">
-        <v>49.32701992266551</v>
+        <v>49.3270199127261</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -26972,10 +26972,10 @@
         <v>51.84999847412109</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.13692342351188</v>
+        <v>10.13692339216623</v>
       </c>
       <c r="BY53" t="n">
-        <v>18.80399295061453</v>
+        <v>18.80399289246836</v>
       </c>
       <c r="BZ53" t="n">
         <v>62.0047364424282</v>
@@ -26984,7 +26984,7 @@
         <v>46.3610505390373</v>
       </c>
       <c r="CB53" t="n">
-        <v>83.00242825279628</v>
+        <v>83.00242821318987</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>13.56974990248658</v>
+        <v>13.56974987265597</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -27015,7 +27015,7 @@
         <v>-79.57280557050289</v>
       </c>
       <c r="CM53" t="n">
-        <v>-73.82883259049777</v>
+        <v>-73.82883264803029</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -27280,22 +27280,22 @@
         <v>-42</v>
       </c>
       <c r="BT54" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BV54" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="BW54" t="n">
         <v>4.150000095367432</v>
       </c>
       <c r="BX54" t="n">
-        <v>0.960129475169628</v>
+        <v>0.9601294779982598</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.78104017643966</v>
+        <v>1.781040181686772</v>
       </c>
       <c r="BZ54" t="n">
         <v>9.335738754434374</v>
@@ -27304,13 +27304,13 @@
         <v>8.797762939487081</v>
       </c>
       <c r="CB54" t="n">
-        <v>10.56095067674783</v>
+        <v>10.56095067772119</v>
       </c>
       <c r="CC54" t="n">
-        <v>4.233767827774382</v>
+        <v>4.233767827465197</v>
       </c>
       <c r="CD54" t="n">
-        <v>7.086068975297565</v>
+        <v>7.086068971683254</v>
       </c>
       <c r="CE54" t="n">
         <v>6.873907403846603</v>
@@ -27379,7 +27379,7 @@
       </c>
       <c r="DD54" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.3, +3.0% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.4, +3.0% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -27610,37 +27610,37 @@
         <v>22.79999923706055</v>
       </c>
       <c r="BX55" t="n">
-        <v>10.07191716805011</v>
+        <v>10.07191714797169</v>
       </c>
       <c r="BY55" t="n">
-        <v>14.9011751469824</v>
+        <v>14.90117515959286</v>
       </c>
       <c r="BZ55" t="n">
-        <v>19.7171420296318</v>
+        <v>19.7171420856241</v>
       </c>
       <c r="CA55" t="n">
         <v>21.50330999614219</v>
       </c>
       <c r="CB55" t="n">
-        <v>19.27267989637069</v>
+        <v>19.2726799210699</v>
       </c>
       <c r="CC55" t="n">
-        <v>23.4062085948841</v>
+        <v>23.40620860063014</v>
       </c>
       <c r="CD55" t="n">
-        <v>9.845491475908402</v>
+        <v>9.84549150589271</v>
       </c>
       <c r="CE55" t="n">
         <v>18.93959217930996</v>
       </c>
       <c r="CF55" t="n">
-        <v>17.20718956090995</v>
+        <v>17.20718957452919</v>
       </c>
       <c r="CG55" t="n">
-        <v>19.10613603784032</v>
+        <v>19.10613605018993</v>
       </c>
       <c r="CH55" t="n">
-        <v>17.19552243405629</v>
+        <v>17.19552244517094</v>
       </c>
       <c r="CI55" t="n">
         <v>8</v>
@@ -27652,10 +27652,10 @@
         <v>2.4</v>
       </c>
       <c r="CL55" t="n">
-        <v>-24.58103943220484</v>
+        <v>-24.58103938345639</v>
       </c>
       <c r="CM55" t="n">
-        <v>-24.52986782148523</v>
+        <v>-24.52986776175172</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -27916,10 +27916,10 @@
         <v>29.54999923706055</v>
       </c>
       <c r="BX56" t="n">
-        <v>15.447346554829</v>
+        <v>15.44734650452109</v>
       </c>
       <c r="BY56" t="n">
-        <v>28.6548278592078</v>
+        <v>28.65482776588663</v>
       </c>
       <c r="BZ56" t="n">
         <v>54.76048809665065</v>
@@ -27928,23 +27928,23 @@
         <v>49.53209541256255</v>
       </c>
       <c r="CB56" t="n">
-        <v>61.15959489291939</v>
+        <v>61.15959490492074</v>
       </c>
       <c r="CC56" t="n">
-        <v>36.65061373202645</v>
+        <v>36.65061374114426</v>
       </c>
       <c r="CD56" t="n">
-        <v>30.47171415158461</v>
+        <v>30.47171422104575</v>
       </c>
       <c r="CE56" t="inlineStr"/>
       <c r="CF56" t="n">
-        <v>33.87831906067848</v>
+        <v>33.87831902705065</v>
       </c>
       <c r="CG56" t="n">
-        <v>32.65272079561713</v>
+        <v>32.65272075351544</v>
       </c>
       <c r="CH56" t="n">
-        <v>29.38744871605542</v>
+        <v>29.3874486781639</v>
       </c>
       <c r="CI56" t="n">
         <v>4</v>
@@ -27956,10 +27956,10 @@
         <v>3.5</v>
       </c>
       <c r="CL56" t="n">
-        <v>-0.5500863797020528</v>
+        <v>-0.5500865079305473</v>
       </c>
       <c r="CM56" t="n">
-        <v>14.64744478974302</v>
+        <v>14.64744467594328</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -28216,34 +28216,34 @@
         <v>42.63</v>
       </c>
       <c r="BP57" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BQ57" t="n">
         <v>13.28</v>
       </c>
       <c r="BR57" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BS57" t="n">
         <v>-24.4</v>
       </c>
       <c r="BT57" t="n">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
       <c r="BU57" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="BV57" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BW57" t="n">
         <v>10.03999996185303</v>
       </c>
       <c r="BX57" t="n">
-        <v>12.50093834400256</v>
+        <v>12.50069633136865</v>
       </c>
       <c r="BY57" t="n">
-        <v>18.20136622886773</v>
+        <v>18.20101385847275</v>
       </c>
       <c r="BZ57" t="n">
         <v>16.70655993652344</v>
@@ -28262,7 +28262,7 @@
         <v>14.15379224573121</v>
       </c>
       <c r="CF57" t="n">
-        <v>15.82221593255898</v>
+        <v>15.82211686872083</v>
       </c>
       <c r="CG57" t="n">
         <v>15.43017609112732</v>
@@ -28283,7 +28283,7 @@
         <v>38.31831209939083</v>
       </c>
       <c r="CM57" t="n">
-        <v>57.59179275573183</v>
+        <v>57.59080606411309</v>
       </c>
       <c r="CN57" t="inlineStr">
         <is>
@@ -28558,10 +28558,10 @@
         <v>23.57999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.133603323496711</v>
+        <v>4.133603322079087</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.6678341650864</v>
+        <v>7.667834162456706</v>
       </c>
       <c r="BZ58" t="n">
         <v>28.5068429734585</v>
@@ -28570,13 +28570,13 @@
         <v>28.35212462119746</v>
       </c>
       <c r="CB58" t="n">
-        <v>25.61587731695162</v>
+        <v>25.61587731770697</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.973447623992884</v>
+        <v>2.973447624025288</v>
       </c>
       <c r="CD58" t="n">
-        <v>18.52992833131622</v>
+        <v>18.52992833292925</v>
       </c>
       <c r="CE58" t="n">
         <v>17.35772741057706</v>
@@ -28776,7 +28776,7 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AS59" t="b">
         <v>1</v>
@@ -28854,7 +28854,7 @@
         <v>53.79</v>
       </c>
       <c r="BR59" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="BS59" t="n">
         <v>-8.4</v>
@@ -28863,19 +28863,19 @@
         <v>7.1</v>
       </c>
       <c r="BU59" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BV59" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="BW59" t="n">
         <v>49.27000045776367</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.20058816185707</v>
+        <v>8.200611446205071</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.21209104024486</v>
+        <v>15.21213423271041</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.74077732281127</v>
@@ -28884,25 +28884,25 @@
         <v>12.27584654405641</v>
       </c>
       <c r="CB59" t="n">
-        <v>14.8053515205832</v>
+        <v>14.80525328262485</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.72428647874579</v>
+        <v>20.72427250551963</v>
       </c>
       <c r="CD59" t="n">
-        <v>11.10410759361875</v>
+        <v>11.10403964802854</v>
       </c>
       <c r="CE59" t="n">
         <v>12.93086890519374</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.37423969588889</v>
+        <v>14.37422548589374</v>
       </c>
       <c r="CG59" t="n">
-        <v>13.86811021288847</v>
+        <v>13.86806109390929</v>
       </c>
       <c r="CH59" t="n">
-        <v>12.48129919159962</v>
+        <v>12.48125498451837</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -28914,10 +28914,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-74.66754805026008</v>
+        <v>-74.66763777439412</v>
       </c>
       <c r="CM59" t="n">
-        <v>-70.82557425951093</v>
+        <v>-70.82560310058058</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="DD59" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.2, +0.2% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.1, +0.2% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -29122,7 +29122,7 @@
         <v>1</v>
       </c>
       <c r="AT60" t="n">
-        <v>36849143808</v>
+        <v>36793753600</v>
       </c>
       <c r="AU60" t="n">
         <v>11.16</v>
@@ -29188,34 +29188,34 @@
         <v>31.75</v>
       </c>
       <c r="BP60" t="n">
-        <v>16.7</v>
+        <v>16.19</v>
       </c>
       <c r="BQ60" t="n">
         <v>34.58</v>
       </c>
       <c r="BR60" t="n">
-        <v>107.1</v>
+        <v>113.5</v>
       </c>
       <c r="BS60" t="n">
         <v>0</v>
       </c>
       <c r="BT60" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="BU60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BV60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BW60" t="n">
         <v>34.58000183105469</v>
       </c>
       <c r="BX60" t="n">
-        <v>12.62461722312328</v>
+        <v>12.6246172117681</v>
       </c>
       <c r="BY60" t="n">
-        <v>23.41866494889368</v>
+        <v>23.41866492782983</v>
       </c>
       <c r="BZ60" t="n">
         <v>41.05600575819664</v>
@@ -29224,25 +29224,25 @@
         <v>33.48612882862086</v>
       </c>
       <c r="CB60" t="n">
-        <v>41.4613946098054</v>
+        <v>41.46139462616276</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.71416875517985</v>
+        <v>23.71416875734303</v>
       </c>
       <c r="CD60" t="n">
-        <v>24.38415174367913</v>
+        <v>24.38415176291479</v>
       </c>
       <c r="CE60" t="n">
         <v>26.42571186985053</v>
       </c>
       <c r="CF60" t="n">
-        <v>28.32135546716867</v>
+        <v>28.32135546783582</v>
       </c>
       <c r="CG60" t="n">
-        <v>25.40493180676483</v>
+        <v>25.40493181638266</v>
       </c>
       <c r="CH60" t="n">
-        <v>22.86443862608835</v>
+        <v>22.8644386347444</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -29254,10 +29254,10 @@
         <v>3.3</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.87959104861914</v>
+        <v>-33.8795910235872</v>
       </c>
       <c r="CM60" t="n">
-        <v>-18.09903421770619</v>
+        <v>-18.09903421577691</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
       </c>
       <c r="DD60" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.2, +0.8% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.3, +0.8% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -29540,10 +29540,10 @@
         <v>4.28000020980835</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.778660813780003</v>
+        <v>2.778660808541149</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.154415809561905</v>
+        <v>5.154415799843832</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.12731545832422</v>
@@ -29552,13 +29552,13 @@
         <v>14.72539108041317</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.19068597480548</v>
+        <v>15.19068596536747</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.474005169349537</v>
+        <v>9.474005170028159</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.534889444565822</v>
+        <v>6.534889449305098</v>
       </c>
       <c r="CE61" t="n">
         <v>0.7861618511746724</v>
@@ -29806,10 +29806,10 @@
         <v>0.3</v>
       </c>
       <c r="BH62" t="n">
-        <v>18.81</v>
+        <v>18.78</v>
       </c>
       <c r="BI62" t="n">
-        <v>92.41</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="BJ62" t="n">
         <v>18.5</v>
@@ -29842,10 +29842,10 @@
         <v>-28.4</v>
       </c>
       <c r="BT62" t="n">
-        <v>-15.1</v>
+        <v>-15.3</v>
       </c>
       <c r="BU62" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BV62" t="n">
         <v>0.55</v>
@@ -29854,37 +29854,37 @@
         <v>29.32999992370605</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.50117694556878</v>
+        <v>13.49922386627936</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.38763657641599</v>
+        <v>14.38720729709548</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.56871272036214</v>
+        <v>15.57050062915488</v>
       </c>
       <c r="CA62" t="n">
         <v>30.61593302727409</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.74045327546539</v>
+        <v>14.74129448605546</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.53638493092586</v>
+        <v>30.53679209562385</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.444133677974002</v>
+        <v>6.44586098129757</v>
       </c>
       <c r="CE62" t="n">
         <v>38.20992116002673</v>
       </c>
       <c r="CF62" t="n">
-        <v>17.97063302199804</v>
+        <v>17.9709731975401</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.74045327546539</v>
+        <v>14.74129448605546</v>
       </c>
       <c r="CH62" t="n">
-        <v>13.26640794791885</v>
+        <v>13.26716503744992</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -29896,10 +29896,10 @@
         <v>5.9</v>
       </c>
       <c r="CL62" t="n">
-        <v>-54.76846920413308</v>
+        <v>-54.76588792376131</v>
       </c>
       <c r="CM62" t="n">
-        <v>-38.72951561969414</v>
+        <v>-38.72835579854533</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>-10.11339575968881</v>
       </c>
       <c r="CZ62" t="n">
-        <v>-28.85716105626636</v>
+        <v>-28.85714780225045</v>
       </c>
       <c r="DA62" t="b">
         <v>0</v>
@@ -30166,47 +30166,47 @@
         <v>-55.3</v>
       </c>
       <c r="BT63" t="n">
-        <v>-21.2</v>
+        <v>-21.7</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BV63" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BW63" t="n">
         <v>3.369999885559082</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.586813048877818</v>
+        <v>2.586813036411478</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.060288330555824</v>
+        <v>3.06028832629888</v>
       </c>
       <c r="BZ63" t="n">
-        <v>3.832748654899039</v>
+        <v>3.832748668038321</v>
       </c>
       <c r="CA63" t="n">
         <v>6.959812888294945</v>
       </c>
       <c r="CB63" t="n">
-        <v>5.752687132453274</v>
+        <v>5.752687125735749</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.494734988414685</v>
+        <v>8.494734991496227</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.763856215790111</v>
+        <v>1.763856226332645</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.635848751326528</v>
+        <v>4.635848751801178</v>
       </c>
       <c r="CG63" t="n">
-        <v>3.832748654899039</v>
+        <v>3.832748668038321</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.449473789409135</v>
+        <v>3.449473801234489</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -30218,10 +30218,10 @@
         <v>4.8</v>
       </c>
       <c r="CL63" t="n">
-        <v>2.358276158720662</v>
+        <v>2.358276509621371</v>
       </c>
       <c r="CM63" t="n">
-        <v>37.56228215887438</v>
+        <v>37.56228217295894</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -30452,10 +30452,10 @@
         <v>0.98</v>
       </c>
       <c r="BH64" t="n">
-        <v>23.85</v>
+        <v>23.89</v>
       </c>
       <c r="BI64" t="n">
-        <v>95.31999999999999</v>
+        <v>95.33</v>
       </c>
       <c r="BJ64" t="n">
         <v>14.4</v>
@@ -30488,49 +30488,49 @@
         <v>0</v>
       </c>
       <c r="BT64" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="BU64" t="n">
         <v>0.96</v>
       </c>
       <c r="BV64" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="BW64" t="n">
         <v>18.68000030517578</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.765290487644545</v>
+        <v>8.765946794039504</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.219242373821302</v>
+        <v>9.219208894970851</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.671867763965263</v>
+        <v>9.671108511382304</v>
       </c>
       <c r="CA64" t="n">
         <v>16.92012354320182</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.240422228703936</v>
+        <v>9.239860989488916</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.54041704938382</v>
+        <v>17.54025528819322</v>
       </c>
       <c r="CD64" t="n">
-        <v>3.931472171283423</v>
+        <v>3.930721356767589</v>
       </c>
       <c r="CE64" t="n">
         <v>16.048074697233</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.41711378940464</v>
+        <v>11.41691250940965</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.456144996334601</v>
+        <v>9.455484750435609</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.510530496701142</v>
+        <v>8.509936275392048</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -30542,10 +30542,10 @@
         <v>4.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>-54.44041564419526</v>
+        <v>-54.44359670040182</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.88054816443858</v>
+        <v>-38.8816256804541</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
       </c>
       <c r="DD64" t="inlineStr">
         <is>
-          <t>Rompimento (vol x2.1, +0.7% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x2.3, +0.7% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -30814,37 +30814,37 @@
         <v>-53.8</v>
       </c>
       <c r="BT65" t="n">
-        <v>-15.6</v>
+        <v>-15.9</v>
       </c>
       <c r="BU65" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BV65" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BW65" t="n">
         <v>2.109999895095825</v>
       </c>
       <c r="BX65" t="n">
-        <v>0.6054745296754893</v>
+        <v>0.6054130269382592</v>
       </c>
       <c r="BY65" t="n">
-        <v>0.8659005945458141</v>
+        <v>0.8658247482581838</v>
       </c>
       <c r="BZ65" t="n">
-        <v>3.470842903424572</v>
+        <v>3.470891449384978</v>
       </c>
       <c r="CA65" t="n">
         <v>7.099910980401375</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.668090361952686</v>
+        <v>2.667995707497016</v>
       </c>
       <c r="CC65" t="n">
-        <v>2.232871388002991</v>
+        <v>2.232874172660568</v>
       </c>
       <c r="CD65" t="n">
-        <v>1.726769451582171</v>
+        <v>1.726797108133049</v>
       </c>
       <c r="CE65" t="n">
         <v>4.899183273787854</v>
@@ -31128,22 +31128,22 @@
         <v>-23.3</v>
       </c>
       <c r="BT66" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="BU66" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BV66" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BW66" t="n">
         <v>34.25</v>
       </c>
       <c r="BX66" t="n">
-        <v>9.805953143272031</v>
+        <v>9.805699273181732</v>
       </c>
       <c r="BY66" t="n">
-        <v>18.19004308076962</v>
+        <v>18.18957215175211</v>
       </c>
       <c r="BZ66" t="n">
         <v>28.52372721558767</v>
@@ -31152,25 +31152,25 @@
         <v>21.17463256983125</v>
       </c>
       <c r="CB66" t="n">
-        <v>26.76923573081139</v>
+        <v>26.76983904045929</v>
       </c>
       <c r="CC66" t="n">
-        <v>22.98076548261489</v>
+        <v>22.98084687561445</v>
       </c>
       <c r="CD66" t="n">
-        <v>17.15346919703837</v>
+        <v>17.15398883864881</v>
       </c>
       <c r="CE66" t="n">
         <v>26.06463245419628</v>
       </c>
       <c r="CF66" t="n">
-        <v>21.33280735926519</v>
+        <v>21.33286730240895</v>
       </c>
       <c r="CG66" t="n">
-        <v>22.07769902622307</v>
+        <v>22.07773972272285</v>
       </c>
       <c r="CH66" t="n">
-        <v>19.86992912360077</v>
+        <v>19.86996575045056</v>
       </c>
       <c r="CI66" t="n">
         <v>8</v>
@@ -31182,10 +31182,10 @@
         <v>2.9</v>
       </c>
       <c r="CL66" t="n">
-        <v>-41.98560839824594</v>
+        <v>-41.9855014585385</v>
       </c>
       <c r="CM66" t="n">
-        <v>-37.71443106783886</v>
+        <v>-37.71425605136073</v>
       </c>
       <c r="CN66" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>-1.125864308660995</v>
       </c>
       <c r="CZ66" t="n">
-        <v>-23.80761643582851</v>
+        <v>-23.80760992843718</v>
       </c>
       <c r="DA66" t="b">
         <v>0</v>
@@ -31452,22 +31452,22 @@
         <v>-19.5</v>
       </c>
       <c r="BT67" t="n">
-        <v>-3.1</v>
+        <v>-3.2</v>
       </c>
       <c r="BU67" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BV67" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BW67" t="n">
         <v>8.399999618530273</v>
       </c>
       <c r="BX67" t="n">
-        <v>0.4995474358854777</v>
+        <v>0.4994953422570964</v>
       </c>
       <c r="BY67" t="n">
-        <v>0.926660493567561</v>
+        <v>0.9265638598869136</v>
       </c>
       <c r="BZ67" t="n">
         <v>9.44020313363241</v>
@@ -31476,13 +31476,13 @@
         <v>8.673354699458621</v>
       </c>
       <c r="CB67" t="n">
-        <v>10.36609051786619</v>
+        <v>10.3661395876163</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.7358232843569932</v>
+        <v>0.7358242918096422</v>
       </c>
       <c r="CD67" t="n">
-        <v>8.046276293721037</v>
+        <v>8.046346020000753</v>
       </c>
       <c r="CE67" t="inlineStr"/>
       <c r="CF67" t="inlineStr"/>
@@ -31731,7 +31731,7 @@
         <v>0.39</v>
       </c>
       <c r="BI68" t="n">
-        <v>12.17</v>
+        <v>12.16</v>
       </c>
       <c r="BJ68" t="n">
         <v>185</v>
@@ -31764,7 +31764,7 @@
         <v>-45.2</v>
       </c>
       <c r="BT68" t="n">
-        <v>-21.7</v>
+        <v>-21.9</v>
       </c>
       <c r="BU68" t="n">
         <v>1.62</v>
@@ -31776,10 +31776,10 @@
         <v>8.199999809265137</v>
       </c>
       <c r="BX68" t="n">
-        <v>1.576511909479872</v>
+        <v>1.575867733965469</v>
       </c>
       <c r="BY68" t="n">
-        <v>2.924429592085162</v>
+        <v>2.923234646505944</v>
       </c>
       <c r="BZ68" t="n">
         <v>24.03761006034581</v>
@@ -31788,13 +31788,13 @@
         <v>23.81825157629451</v>
       </c>
       <c r="CB68" t="n">
-        <v>25.70936139294823</v>
+        <v>25.70854487141032</v>
       </c>
       <c r="CC68" t="n">
-        <v>6.710859780780995</v>
+        <v>6.710898893142434</v>
       </c>
       <c r="CD68" t="n">
-        <v>17.9372516495655</v>
+        <v>17.93799255447515</v>
       </c>
       <c r="CE68" t="n">
         <v>13.41468215105991</v>
@@ -32081,19 +32081,19 @@
         <v>-2.1</v>
       </c>
       <c r="BU69" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BV69" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BW69" t="n">
         <v>21.17000007629395</v>
       </c>
       <c r="BX69" t="n">
-        <v>5.854145166759947</v>
+        <v>5.85405671840843</v>
       </c>
       <c r="BY69" t="n">
-        <v>10.8594392843397</v>
+        <v>10.85927521264764</v>
       </c>
       <c r="BZ69" t="n">
         <v>32.88423224043315</v>
@@ -32102,25 +32102,25 @@
         <v>33.87809571629486</v>
       </c>
       <c r="CB69" t="n">
-        <v>29.72141727365121</v>
+        <v>29.72142193787599</v>
       </c>
       <c r="CC69" t="n">
-        <v>25.31801731825158</v>
+        <v>25.31803145724508</v>
       </c>
       <c r="CD69" t="n">
-        <v>19.2726158477468</v>
+        <v>19.27271002755149</v>
       </c>
       <c r="CE69" t="n">
         <v>13.20520650594855</v>
       </c>
       <c r="CF69" t="n">
-        <v>23.59128916952369</v>
+        <v>23.59128187114239</v>
       </c>
       <c r="CG69" t="n">
-        <v>25.31801731825158</v>
+        <v>25.31803145724508</v>
       </c>
       <c r="CH69" t="n">
-        <v>22.78621558642642</v>
+        <v>22.78622831152057</v>
       </c>
       <c r="CI69" t="n">
         <v>7</v>
@@ -32132,10 +32132,10 @@
         <v>5.8</v>
       </c>
       <c r="CL69" t="n">
-        <v>7.634461522474445</v>
+        <v>7.634521631563285</v>
       </c>
       <c r="CM69" t="n">
-        <v>11.43735987011685</v>
+        <v>11.43732539500453</v>
       </c>
       <c r="CN69" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>-3.067765895663488</v>
       </c>
       <c r="CZ69" t="n">
-        <v>-21.02089346708398</v>
+        <v>-21.02089962798474</v>
       </c>
       <c r="DA69" t="b">
         <v>0</v>
@@ -32322,7 +32322,7 @@
         <v>1</v>
       </c>
       <c r="AR70" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AS70" t="b">
         <v>1</v>
@@ -32394,22 +32394,22 @@
         <v>40.69</v>
       </c>
       <c r="BP70" t="n">
-        <v>21.86</v>
+        <v>21.8</v>
       </c>
       <c r="BQ70" t="n">
         <v>35.21</v>
       </c>
       <c r="BR70" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BS70" t="n">
         <v>-32.5</v>
       </c>
       <c r="BT70" t="n">
-        <v>-19.1</v>
+        <v>-19.2</v>
       </c>
       <c r="BU70" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BV70" t="n">
         <v>0.71</v>
@@ -32418,10 +32418,10 @@
         <v>23.75</v>
       </c>
       <c r="BX70" t="n">
-        <v>4.355978618233742</v>
+        <v>4.355873345008507</v>
       </c>
       <c r="BY70" t="n">
-        <v>8.080340336823591</v>
+        <v>8.08014505499078</v>
       </c>
       <c r="BZ70" t="n">
         <v>30.22934678194044</v>
@@ -32430,13 +32430,13 @@
         <v>25.67105067776809</v>
       </c>
       <c r="CB70" t="n">
-        <v>35.61307617820037</v>
+        <v>35.61319694125312</v>
       </c>
       <c r="CC70" t="n">
-        <v>11.80930977990107</v>
+        <v>11.80932179251764</v>
       </c>
       <c r="CD70" t="n">
-        <v>24.79783255637562</v>
+        <v>24.79799745635562</v>
       </c>
       <c r="CE70" t="n">
         <v>24.13715468420423</v>
@@ -32732,35 +32732,35 @@
         <v>23.34000015258789</v>
       </c>
       <c r="BX71" t="n">
-        <v>22.42103484860471</v>
+        <v>22.42103472391846</v>
       </c>
       <c r="BY71" t="n">
-        <v>28.79895001861679</v>
+        <v>28.79894998265126</v>
       </c>
       <c r="BZ71" t="n">
-        <v>39.0762843118892</v>
+        <v>39.07628448039709</v>
       </c>
       <c r="CA71" t="n">
         <v>62.09946198672523</v>
       </c>
       <c r="CB71" t="n">
-        <v>69.18752132196983</v>
+        <v>69.18752118898639</v>
       </c>
       <c r="CC71" t="n">
-        <v>41.79258401481802</v>
+        <v>41.79258403253068</v>
       </c>
       <c r="CD71" t="n">
-        <v>18.86266345919395</v>
+        <v>18.86266357583046</v>
       </c>
       <c r="CE71" t="inlineStr"/>
       <c r="CF71" t="n">
-        <v>40.31978570883111</v>
+        <v>40.31978571014851</v>
       </c>
       <c r="CG71" t="n">
-        <v>39.0762843118892</v>
+        <v>39.07628448039709</v>
       </c>
       <c r="CH71" t="n">
-        <v>35.16865588070029</v>
+        <v>35.16865603235738</v>
       </c>
       <c r="CI71" t="n">
         <v>7</v>
@@ -32772,10 +32772,10 @@
         <v>3.7</v>
       </c>
       <c r="CL71" t="n">
-        <v>50.67975857232743</v>
+        <v>50.67975922210073</v>
       </c>
       <c r="CM71" t="n">
-        <v>72.74972341574954</v>
+        <v>72.74972342139397</v>
       </c>
       <c r="CN71" t="inlineStr">
         <is>
@@ -33054,25 +33054,25 @@
         <v>17.27000045776367</v>
       </c>
       <c r="BX72" t="n">
-        <v>3.98335168570889</v>
+        <v>3.98335166261722</v>
       </c>
       <c r="BY72" t="n">
-        <v>6.851351448503979</v>
+        <v>6.851351419951937</v>
       </c>
       <c r="BZ72" t="n">
-        <v>23.496553132657</v>
+        <v>23.49655317094901</v>
       </c>
       <c r="CA72" t="n">
         <v>32.81823251300876</v>
       </c>
       <c r="CB72" t="n">
-        <v>16.54030067703286</v>
+        <v>16.540300665963</v>
       </c>
       <c r="CC72" t="n">
-        <v>20.30192179312825</v>
+        <v>20.30192179561859</v>
       </c>
       <c r="CD72" t="n">
-        <v>11.62401156811237</v>
+        <v>11.62401158365768</v>
       </c>
       <c r="CE72" t="n">
         <v>21.74081326930276</v>
@@ -33124,7 +33124,7 @@
         <v>-1.592718182806219</v>
       </c>
       <c r="CZ72" t="n">
-        <v>-40.1828262350358</v>
+        <v>-40.18283425804393</v>
       </c>
       <c r="DA72" t="b">
         <v>0</v>
@@ -33368,10 +33368,10 @@
         <v>12.10000038146973</v>
       </c>
       <c r="BX73" t="n">
-        <v>2.000193692570833</v>
+        <v>2.000193689597198</v>
       </c>
       <c r="BY73" t="n">
-        <v>3.710359299718895</v>
+        <v>3.710359294202803</v>
       </c>
       <c r="BZ73" t="n">
         <v>16.12927616242192</v>
@@ -33380,7 +33380,7 @@
         <v>12.80877999251376</v>
       </c>
       <c r="CB73" t="n">
-        <v>21.07673213461143</v>
+        <v>21.07673213042321</v>
       </c>
       <c r="CC73" t="n">
         <v>9.395602678571429</v>
@@ -33666,35 +33666,35 @@
         <v>12.14999961853027</v>
       </c>
       <c r="BX74" t="n">
-        <v>10.27302894329599</v>
+        <v>10.27302895402502</v>
       </c>
       <c r="BY74" t="n">
-        <v>11.21723176490275</v>
+        <v>11.21723175758554</v>
       </c>
       <c r="BZ74" t="n">
-        <v>11.84528250911144</v>
+        <v>11.84528248901348</v>
       </c>
       <c r="CA74" t="n">
         <v>16.21040951658916</v>
       </c>
       <c r="CB74" t="n">
-        <v>19.56416088578844</v>
+        <v>19.56416087497358</v>
       </c>
       <c r="CC74" t="n">
-        <v>7.409931251064345</v>
+        <v>7.409931249635551</v>
       </c>
       <c r="CD74" t="n">
-        <v>5.05437273462921</v>
+        <v>5.054372716029376</v>
       </c>
       <c r="CE74" t="inlineStr"/>
       <c r="CF74" t="n">
-        <v>10.18636861709363</v>
+        <v>10.18636861256489</v>
       </c>
       <c r="CG74" t="n">
-        <v>10.74513035409937</v>
+        <v>10.74513035580528</v>
       </c>
       <c r="CH74" t="n">
-        <v>9.670617318689434</v>
+        <v>9.67061732022475</v>
       </c>
       <c r="CI74" t="n">
         <v>4</v>
@@ -33706,10 +33706,10 @@
         <v>1.6</v>
       </c>
       <c r="CL74" t="n">
-        <v>-20.40643932251216</v>
+        <v>-20.40643930987581</v>
       </c>
       <c r="CM74" t="n">
-        <v>-16.16157253570493</v>
+        <v>-16.16157257297848</v>
       </c>
       <c r="CN74" t="inlineStr">
         <is>
@@ -33976,10 +33976,10 @@
         <v>-44.4</v>
       </c>
       <c r="BT75" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU75" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="BV75" t="n">
         <v>0.35</v>
@@ -33988,10 +33988,10 @@
         <v>3.990000009536743</v>
       </c>
       <c r="BX75" t="n">
-        <v>0.9693873018669904</v>
+        <v>0.96932691697801</v>
       </c>
       <c r="BY75" t="n">
-        <v>1.798213444963267</v>
+        <v>1.798101430994208</v>
       </c>
       <c r="BZ75" t="n">
         <v>6.076724152455384</v>
@@ -34000,7 +34000,7 @@
         <v>4.034077793072167</v>
       </c>
       <c r="CB75" t="n">
-        <v>8.439243950481496</v>
+        <v>8.439146779395781</v>
       </c>
       <c r="CC75" t="n">
         <v>3.760485277130923</v>
@@ -34276,34 +34276,34 @@
         <v>48.36</v>
       </c>
       <c r="BP76" t="n">
-        <v>25.13</v>
+        <v>24.75</v>
       </c>
       <c r="BQ76" t="n">
         <v>67.45</v>
       </c>
       <c r="BR76" t="n">
-        <v>116.9</v>
+        <v>120.2</v>
       </c>
       <c r="BS76" t="n">
         <v>-19.2</v>
       </c>
       <c r="BT76" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="BU76" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="BV76" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="BW76" t="n">
         <v>54.5</v>
       </c>
       <c r="BX76" t="n">
-        <v>39.63533179641133</v>
+        <v>39.63603088489769</v>
       </c>
       <c r="BY76" t="n">
-        <v>57.70904309557491</v>
+        <v>57.71006096841104</v>
       </c>
       <c r="BZ76" t="n">
         <v>35.35870243293824</v>
@@ -34322,13 +34322,13 @@
         <v>46.00869250560613</v>
       </c>
       <c r="CF76" t="n">
-        <v>42.45383602901597</v>
+        <v>42.45412218923639</v>
       </c>
       <c r="CG76" t="n">
-        <v>40.92255506526084</v>
+        <v>40.92290460950403</v>
       </c>
       <c r="CH76" t="n">
-        <v>36.83029955873476</v>
+        <v>36.83061414855363</v>
       </c>
       <c r="CI76" t="n">
         <v>6</v>
@@ -34340,10 +34340,10 @@
         <v>6.4</v>
       </c>
       <c r="CL76" t="n">
-        <v>-32.42146869956925</v>
+        <v>-32.4208914705438</v>
       </c>
       <c r="CM76" t="n">
-        <v>-22.10305315776886</v>
+        <v>-22.10252809314424</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>1.06</v>
       </c>
       <c r="BI77" t="n">
-        <v>64.61</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="BJ77" t="n">
         <v>270</v>
@@ -34598,7 +34598,7 @@
         <v>23.06</v>
       </c>
       <c r="BP77" t="n">
-        <v>26.62</v>
+        <v>26.61</v>
       </c>
       <c r="BQ77" t="n">
         <v>37.14</v>
@@ -34613,7 +34613,7 @@
         <v>-13.6</v>
       </c>
       <c r="BU77" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BV77" t="n">
         <v>0.61</v>
@@ -34622,10 +34622,10 @@
         <v>27.6299991607666</v>
       </c>
       <c r="BX77" t="n">
-        <v>12.90524673040236</v>
+        <v>12.90446972962038</v>
       </c>
       <c r="BY77" t="n">
-        <v>23.93923268489639</v>
+        <v>23.93779134844581</v>
       </c>
       <c r="BZ77" t="n">
         <v>37.05440170851796</v>
@@ -34634,19 +34634,19 @@
         <v>25.80913235694405</v>
       </c>
       <c r="CB77" t="n">
-        <v>44.38844778214269</v>
+        <v>44.39021530037579</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.45357889242229</v>
+        <v>42.45397718001516</v>
       </c>
       <c r="CD77" t="n">
-        <v>23.87756488864744</v>
+        <v>23.87936796558208</v>
       </c>
       <c r="CE77" t="n">
         <v>23.95070880105463</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.29728923062847</v>
+        <v>29.29750804881948</v>
       </c>
       <c r="CG77" t="n">
         <v>24.87992057899934</v>
@@ -34667,7 +34667,7 @@
         <v>-18.95791096188316</v>
       </c>
       <c r="CM77" t="n">
-        <v>6.03434716070983</v>
+        <v>6.035139119441846</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>-6.4677292459832</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-27.40055542927962</v>
+        <v>-27.40056306506667</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -34930,22 +34930,22 @@
         <v>22.24</v>
       </c>
       <c r="BP78" t="n">
-        <v>12.83</v>
+        <v>12.73</v>
       </c>
       <c r="BQ78" t="n">
         <v>17.55</v>
       </c>
       <c r="BR78" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="BS78" t="n">
         <v>-17.4</v>
       </c>
       <c r="BT78" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="BU78" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BV78" t="n">
         <v>0.78</v>
@@ -34954,10 +34954,10 @@
         <v>14.5</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.33980008012506</v>
+        <v>2.339767804465583</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.340329148631985</v>
+        <v>4.340269277283657</v>
       </c>
       <c r="BZ78" t="n">
         <v>25.44701986754966</v>
@@ -34966,7 +34966,7 @@
         <v>19.48694742147536</v>
       </c>
       <c r="CB78" t="n">
-        <v>33.14664915519879</v>
+        <v>33.1465893062938</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -35244,13 +35244,13 @@
         <v>38.29</v>
       </c>
       <c r="BP79" t="n">
-        <v>10.22</v>
+        <v>10.16</v>
       </c>
       <c r="BQ79" t="n">
         <v>16.67</v>
       </c>
       <c r="BR79" t="n">
-        <v>38.5</v>
+        <v>39.3</v>
       </c>
       <c r="BS79" t="n">
         <v>-15.1</v>
@@ -35259,19 +35259,19 @@
         <v>-5.9</v>
       </c>
       <c r="BU79" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BV79" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BW79" t="n">
         <v>14.14999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.254605910108262</v>
+        <v>9.254465001252482</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.16729396325083</v>
+        <v>17.16703257732335</v>
       </c>
       <c r="BZ79" t="n">
         <v>13.91889346291953</v>
@@ -35292,7 +35292,7 @@
         <v>11.70742099417638</v>
       </c>
       <c r="CF79" t="n">
-        <v>14.83228929655301</v>
+        <v>14.8322390097051</v>
       </c>
       <c r="CG79" t="n">
         <v>13.26759657778993</v>
@@ -35313,7 +35313,7 @@
         <v>-15.61245765424828</v>
       </c>
       <c r="CM79" t="n">
-        <v>4.821835310364508</v>
+        <v>4.8214799262708</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>1.63</v>
       </c>
       <c r="BI80" t="n">
-        <v>40.02</v>
+        <v>40.01</v>
       </c>
       <c r="BJ80" t="n">
         <v>4.4</v>
@@ -35580,47 +35580,47 @@
         <v>-54.2</v>
       </c>
       <c r="BT80" t="n">
-        <v>-22.9</v>
+        <v>-23.4</v>
       </c>
       <c r="BU80" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BV80" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="BW80" t="n">
         <v>2.369999885559082</v>
       </c>
       <c r="BX80" t="n">
-        <v>1.08914840413498</v>
+        <v>1.088826618720195</v>
       </c>
       <c r="BY80" t="n">
-        <v>1.554199994179975</v>
+        <v>1.553866785056872</v>
       </c>
       <c r="BZ80" t="n">
-        <v>3.883736424501683</v>
+        <v>3.884051310333654</v>
       </c>
       <c r="CA80" t="n">
         <v>7.127125333008402</v>
       </c>
       <c r="CB80" t="n">
-        <v>3.905025625917294</v>
+        <v>3.904587867797405</v>
       </c>
       <c r="CC80" t="n">
-        <v>1.345734459705644</v>
+        <v>1.34574420721096</v>
       </c>
       <c r="CD80" t="n">
-        <v>1.931561724743789</v>
+        <v>1.931741821604736</v>
       </c>
       <c r="CE80" t="inlineStr"/>
       <c r="CF80" t="n">
-        <v>2.284901105530561</v>
+        <v>2.284803101787304</v>
       </c>
       <c r="CG80" t="n">
-        <v>1.742880859461882</v>
+        <v>1.742804303330804</v>
       </c>
       <c r="CH80" t="n">
-        <v>1.568592773515694</v>
+        <v>1.568523872997724</v>
       </c>
       <c r="CI80" t="n">
         <v>6</v>
@@ -35632,10 +35632,10 @@
         <v>6.5</v>
       </c>
       <c r="CL80" t="n">
-        <v>-33.81464771059836</v>
+        <v>-33.81755490558981</v>
       </c>
       <c r="CM80" t="n">
-        <v>-3.590665997371811</v>
+        <v>-3.594801176611895</v>
       </c>
       <c r="CN80" t="inlineStr">
         <is>
@@ -35914,25 +35914,25 @@
         <v>25.78806304931641</v>
       </c>
       <c r="BX81" t="n">
-        <v>11.35620447532557</v>
+        <v>11.35620450668844</v>
       </c>
       <c r="BY81" t="n">
-        <v>12.31329030227797</v>
+        <v>12.31329031770967</v>
       </c>
       <c r="BZ81" t="n">
-        <v>14.19506891297737</v>
+        <v>14.19506889156436</v>
       </c>
       <c r="CA81" t="n">
         <v>32.28961358718046</v>
       </c>
       <c r="CB81" t="n">
-        <v>13.06611002624236</v>
+        <v>13.06611002552807</v>
       </c>
       <c r="CC81" t="n">
-        <v>24.87657762382468</v>
+        <v>24.87657761953347</v>
       </c>
       <c r="CD81" t="n">
-        <v>6.006613086067356</v>
+        <v>6.006613066002651</v>
       </c>
       <c r="CE81" t="n">
         <v>61.44795953901004</v>
@@ -36183,7 +36183,7 @@
         <v>0.22</v>
       </c>
       <c r="BI82" t="n">
-        <v>140.74</v>
+        <v>140.75</v>
       </c>
       <c r="BJ82" t="n">
         <v>73.2</v>
@@ -36216,10 +36216,10 @@
         <v>-13.7</v>
       </c>
       <c r="BT82" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="BU82" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="BV82" t="n">
         <v>0.5600000000000001</v>
@@ -36228,10 +36228,10 @@
         <v>9.850000381469727</v>
       </c>
       <c r="BX82" t="n">
-        <v>6.037965018214039</v>
+        <v>6.038291427397128</v>
       </c>
       <c r="BY82" t="n">
-        <v>11.20042510878704</v>
+        <v>11.20103059782167</v>
       </c>
       <c r="BZ82" t="n">
         <v>7.958079576492308</v>
@@ -36252,7 +36252,7 @@
         <v>39.30366688938892</v>
       </c>
       <c r="CF82" t="n">
-        <v>10.08349913683393</v>
+        <v>10.08363226515075</v>
       </c>
       <c r="CG82" t="n">
         <v>7.958079576492308</v>
@@ -36273,7 +36273,7 @@
         <v>-27.28658536585368</v>
       </c>
       <c r="CM82" t="n">
-        <v>2.37054564793191</v>
+        <v>2.371897204395479</v>
       </c>
       <c r="CN82" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>0.82</v>
       </c>
       <c r="BI83" t="n">
-        <v>21.49</v>
+        <v>21.48</v>
       </c>
       <c r="BJ83" t="n">
         <v>-89.7</v>
@@ -36540,22 +36540,22 @@
         <v>-43</v>
       </c>
       <c r="BT83" t="n">
-        <v>-12.4</v>
+        <v>-12.6</v>
       </c>
       <c r="BU83" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="BV83" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BW83" t="n">
         <v>6.690000057220459</v>
       </c>
       <c r="BX83" t="n">
-        <v>1.204080092358347</v>
+        <v>1.203512485145762</v>
       </c>
       <c r="BY83" t="n">
-        <v>2.233568571324733</v>
+        <v>2.232515659945388</v>
       </c>
       <c r="BZ83" t="n">
         <v>10.39185237493213</v>
@@ -36564,13 +36564,13 @@
         <v>10.22124134966257</v>
       </c>
       <c r="CB83" t="n">
-        <v>10.15297125042389</v>
+        <v>10.15309495126628</v>
       </c>
       <c r="CC83" t="n">
-        <v>1.875377704210118</v>
+        <v>1.875400555758731</v>
       </c>
       <c r="CD83" t="n">
-        <v>7.234851521548447</v>
+        <v>7.235514850041362</v>
       </c>
       <c r="CE83" t="n">
         <v>10.26177038220516</v>
@@ -36854,7 +36854,7 @@
         <v>-12.8</v>
       </c>
       <c r="BT84" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="BU84" t="n">
         <v>0.61</v>
@@ -36866,10 +36866,10 @@
         <v>18.40999984741211</v>
       </c>
       <c r="BX84" t="n">
-        <v>4.473085397440171</v>
+        <v>4.472894333610699</v>
       </c>
       <c r="BY84" t="n">
-        <v>8.297573412251516</v>
+        <v>8.297218988847847</v>
       </c>
       <c r="BZ84" t="n">
         <v>32.35179018278652</v>
@@ -36878,13 +36878,13 @@
         <v>34.90762684757382</v>
       </c>
       <c r="CB84" t="n">
-        <v>28.27500205368425</v>
+        <v>28.27494153155557</v>
       </c>
       <c r="CC84" t="n">
-        <v>11.13390790091814</v>
+        <v>11.13392030379772</v>
       </c>
       <c r="CD84" t="n">
-        <v>19.07496030309437</v>
+        <v>19.0751452528813</v>
       </c>
       <c r="CE84" t="n">
         <v>41.8667053195644</v>
@@ -37151,19 +37151,19 @@
         <v>-6</v>
       </c>
       <c r="BU85" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BV85" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="BW85" t="n">
         <v>50</v>
       </c>
       <c r="BX85" t="n">
-        <v>10.49472705518709</v>
+        <v>10.49147070962312</v>
       </c>
       <c r="BY85" t="n">
-        <v>15.28032259235241</v>
+        <v>15.27558135321127</v>
       </c>
       <c r="BZ85" t="inlineStr"/>
       <c r="CA85" t="inlineStr"/>
@@ -37174,13 +37174,13 @@
       <c r="CD85" t="inlineStr"/>
       <c r="CE85" t="inlineStr"/>
       <c r="CF85" t="n">
-        <v>17.3675832158465</v>
+        <v>17.36491735427813</v>
       </c>
       <c r="CG85" t="n">
-        <v>15.28032259235241</v>
+        <v>15.27558135321127</v>
       </c>
       <c r="CH85" t="n">
-        <v>13.75229033311717</v>
+        <v>13.74802321789014</v>
       </c>
       <c r="CI85" t="n">
         <v>3</v>
@@ -37192,10 +37192,10 @@
         <v>2.5</v>
       </c>
       <c r="CL85" t="n">
-        <v>-72.49541933376567</v>
+        <v>-72.50395356421973</v>
       </c>
       <c r="CM85" t="n">
-        <v>-65.26483356830698</v>
+        <v>-65.27016529144373</v>
       </c>
       <c r="CN85" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>0.27</v>
       </c>
       <c r="BI86" t="n">
-        <v>138.15</v>
+        <v>138.16</v>
       </c>
       <c r="BJ86" t="n">
         <v>73.5</v>
@@ -37474,10 +37474,10 @@
         <v>-15</v>
       </c>
       <c r="BT86" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="BU86" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="BV86" t="n">
         <v>0.52</v>
@@ -37486,10 +37486,10 @@
         <v>22.14999961853027</v>
       </c>
       <c r="BX86" t="n">
-        <v>11.16306742940736</v>
+        <v>11.16375033702836</v>
       </c>
       <c r="BY86" t="n">
-        <v>20.70749008155064</v>
+        <v>20.7087568751876</v>
       </c>
       <c r="BZ86" t="n">
         <v>14.98914683072146</v>
@@ -37510,13 +37510,13 @@
         <v>22.63811085331503</v>
       </c>
       <c r="CF86" t="n">
-        <v>19.40402378814409</v>
+        <v>19.40426750080134</v>
       </c>
       <c r="CG86" t="n">
-        <v>17.84831845613605</v>
+        <v>17.84895185295453</v>
       </c>
       <c r="CH86" t="n">
-        <v>16.06348661052245</v>
+        <v>16.06405666765908</v>
       </c>
       <c r="CI86" t="n">
         <v>8</v>
@@ -37528,10 +37528,10 @@
         <v>3</v>
       </c>
       <c r="CL86" t="n">
-        <v>-27.47861450487775</v>
+        <v>-27.47604088344909</v>
       </c>
       <c r="CM86" t="n">
-        <v>-12.39718229199854</v>
+        <v>-12.39608200910264</v>
       </c>
       <c r="CN86" t="inlineStr">
         <is>
@@ -37796,13 +37796,13 @@
         <v>-12.8</v>
       </c>
       <c r="BT87" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="BU87" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="BV87" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BW87" t="n">
         <v>62.84999847412109</v>
@@ -38124,10 +38124,10 @@
         <v>13.92000007629395</v>
       </c>
       <c r="BX88" t="n">
-        <v>6.009189176339434</v>
+        <v>6.009189153382634</v>
       </c>
       <c r="BY88" t="n">
-        <v>8.749379440750218</v>
+        <v>8.749379407325115</v>
       </c>
       <c r="BZ88" t="n">
         <v>3.748524101332394</v>
@@ -38340,13 +38340,13 @@
         <v>0</v>
       </c>
       <c r="AR89" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="AS89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="n">
-        <v>2877639936</v>
+        <v>2855378432</v>
       </c>
       <c r="AU89" t="n">
         <v>6.62</v>
@@ -38424,10 +38424,10 @@
         <v>-52</v>
       </c>
       <c r="BT89" t="n">
-        <v>-27.5</v>
+        <v>-27.9</v>
       </c>
       <c r="BU89" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BV89" t="n">
         <v>0.66</v>
@@ -38436,10 +38436,10 @@
         <v>7.119999885559082</v>
       </c>
       <c r="BX89" t="n">
-        <v>2.962332531430638</v>
+        <v>2.962332528713289</v>
       </c>
       <c r="BY89" t="n">
-        <v>5.495126845803833</v>
+        <v>5.495126840763151</v>
       </c>
       <c r="BZ89" t="n">
         <v>14.25075505795435</v>
@@ -38448,23 +38448,23 @@
         <v>15.36316945870801</v>
       </c>
       <c r="CB89" t="n">
-        <v>13.58643916878914</v>
+        <v>13.58643916725763</v>
       </c>
       <c r="CC89" t="n">
-        <v>14.9914911001019</v>
+        <v>14.99149110065199</v>
       </c>
       <c r="CD89" t="n">
-        <v>7.47540168390845</v>
+        <v>7.475401686557974</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="n">
-        <v>11.86039721921095</v>
+        <v>11.86039721864885</v>
       </c>
       <c r="CG89" t="n">
-        <v>13.91859711337175</v>
+        <v>13.91859711260599</v>
       </c>
       <c r="CH89" t="n">
-        <v>12.52673740203457</v>
+        <v>12.52673740134539</v>
       </c>
       <c r="CI89" t="n">
         <v>6</v>
@@ -38476,10 +38476,10 @@
         <v>5.2</v>
       </c>
       <c r="CL89" t="n">
-        <v>75.93732589015256</v>
+        <v>75.93732588047308</v>
       </c>
       <c r="CM89" t="n">
-        <v>66.5786153068124</v>
+        <v>66.5786152989178</v>
       </c>
       <c r="CN89" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>-40.5</v>
       </c>
       <c r="BT90" t="n">
-        <v>-7.6</v>
+        <v>-7.7</v>
       </c>
       <c r="BU90" t="n">
         <v>1.96</v>
@@ -38752,25 +38752,25 @@
         <v>1.610000014305115</v>
       </c>
       <c r="BX90" t="n">
-        <v>0.1435318111612521</v>
+        <v>0.1435169041729764</v>
       </c>
       <c r="BY90" t="n">
-        <v>0.163625040168066</v>
+        <v>0.1636087024979385</v>
       </c>
       <c r="BZ90" t="n">
-        <v>0.7478552198004993</v>
+        <v>0.7478582191618807</v>
       </c>
       <c r="CA90" t="n">
         <v>3.128143894509729</v>
       </c>
       <c r="CB90" t="n">
-        <v>0.255255223800898</v>
+        <v>0.2552474090967433</v>
       </c>
       <c r="CC90" t="n">
-        <v>1.083017384933685</v>
+        <v>1.083017860012981</v>
       </c>
       <c r="CD90" t="n">
-        <v>0.3337444920722303</v>
+        <v>0.333747063229568</v>
       </c>
       <c r="CE90" t="inlineStr"/>
       <c r="CF90" t="inlineStr"/>
@@ -39034,47 +39034,47 @@
         <v>-32.5</v>
       </c>
       <c r="BT91" t="n">
-        <v>-11.5</v>
+        <v>-11.6</v>
       </c>
       <c r="BU91" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BV91" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BW91" t="n">
         <v>18.43000030517578</v>
       </c>
       <c r="BX91" t="n">
-        <v>10.98633928570238</v>
+        <v>10.98605245238198</v>
       </c>
       <c r="BY91" t="n">
-        <v>14.59117227661442</v>
+        <v>14.59097962462799</v>
       </c>
       <c r="BZ91" t="n">
-        <v>23.98319047179236</v>
+        <v>23.98349997946688</v>
       </c>
       <c r="CA91" t="n">
         <v>42.51467275133047</v>
       </c>
       <c r="CB91" t="n">
-        <v>29.00895967311865</v>
+        <v>29.00872967898804</v>
       </c>
       <c r="CC91" t="n">
-        <v>15.83206863401346</v>
+        <v>15.83208811736494</v>
       </c>
       <c r="CD91" t="n">
-        <v>11.72592389148489</v>
+        <v>11.72612556972913</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>16.34819266703066</v>
+        <v>16.34815504346045</v>
       </c>
       <c r="CG91" t="n">
-        <v>15.21162045531394</v>
+        <v>15.21153387099647</v>
       </c>
       <c r="CH91" t="n">
-        <v>13.69045840978255</v>
+        <v>13.69038048389682</v>
       </c>
       <c r="CI91" t="n">
         <v>4</v>
@@ -39086,10 +39086,10 @@
         <v>2.2</v>
       </c>
       <c r="CL91" t="n">
-        <v>-25.7164504444539</v>
+        <v>-25.71687326531359</v>
       </c>
       <c r="CM91" t="n">
-        <v>-11.2957547676246</v>
+        <v>-11.2959589107043</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -39370,22 +39370,22 @@
         <v>-29.2</v>
       </c>
       <c r="BT92" t="n">
-        <v>-8.1</v>
+        <v>-8</v>
       </c>
       <c r="BU92" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="BV92" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="BW92" t="n">
         <v>3.619999885559082</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.24704450488574</v>
+        <v>33.24704447347582</v>
       </c>
       <c r="BY92" t="n">
-        <v>61.67326755656305</v>
+        <v>61.67326749829765</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.72561561415348</v>
@@ -39649,7 +39649,7 @@
       </c>
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="n">
-        <v>336.2</v>
+        <v>336.19</v>
       </c>
       <c r="BJ93" t="n">
         <v>-43.5</v>
@@ -39685,19 +39685,19 @@
         <v>-3.1</v>
       </c>
       <c r="BU93" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="BV93" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BW93" t="n">
         <v>75.02999877929688</v>
       </c>
       <c r="BX93" t="n">
-        <v>56.09548785913903</v>
+        <v>56.09450013181841</v>
       </c>
       <c r="BY93" t="n">
-        <v>81.67503032290642</v>
+        <v>81.67359219192763</v>
       </c>
       <c r="BZ93" t="n">
         <v>24.29364842169015</v>
@@ -40008,10 +40008,10 @@
         <v>7.739999771118164</v>
       </c>
       <c r="BX94" t="n">
-        <v>4.981494650184922</v>
+        <v>4.981494655851651</v>
       </c>
       <c r="BY94" t="n">
-        <v>7.253056210669246</v>
+        <v>7.253056218920004</v>
       </c>
       <c r="BZ94" t="n">
         <v>5.841509261221256</v>
@@ -40030,13 +40030,13 @@
         <v>7.485306000698566</v>
       </c>
       <c r="CF94" t="n">
-        <v>6.559492385513473</v>
+        <v>6.559492387833054</v>
       </c>
       <c r="CG94" t="n">
-        <v>6.547282735945251</v>
+        <v>6.54728274007063</v>
       </c>
       <c r="CH94" t="n">
-        <v>5.892554462350725</v>
+        <v>5.892554466063567</v>
       </c>
       <c r="CI94" t="n">
         <v>6</v>
@@ -40048,10 +40048,10 @@
         <v>5.9</v>
       </c>
       <c r="CL94" t="n">
-        <v>-23.86880314468726</v>
+        <v>-23.86880309671773</v>
       </c>
       <c r="CM94" t="n">
-        <v>-15.25203385676778</v>
+        <v>-15.25203382679903</v>
       </c>
       <c r="CN94" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>-7.691536032472291</v>
       </c>
       <c r="CZ94" t="n">
-        <v>-20.2341272136166</v>
+        <v>-20.23411921596913</v>
       </c>
       <c r="DA94" t="b">
         <v>0</v>
@@ -40285,7 +40285,7 @@
         <v>1.44</v>
       </c>
       <c r="BI95" t="n">
-        <v>38.59</v>
+        <v>38.58</v>
       </c>
       <c r="BJ95" t="n">
         <v>24.5</v>
@@ -40318,10 +40318,10 @@
         <v>-34.2</v>
       </c>
       <c r="BT95" t="n">
-        <v>-18.7</v>
+        <v>-18.8</v>
       </c>
       <c r="BU95" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BV95" t="n">
         <v>0.79</v>
@@ -40330,10 +40330,10 @@
         <v>33.91999816894531</v>
       </c>
       <c r="BX95" t="n">
-        <v>8.392352297610165</v>
+        <v>8.391158559354832</v>
       </c>
       <c r="BY95" t="n">
-        <v>15.56781351206685</v>
+        <v>15.56559912760321</v>
       </c>
       <c r="BZ95" t="n">
         <v>40.34470159232723</v>
@@ -40342,19 +40342,19 @@
         <v>40.59709214923609</v>
       </c>
       <c r="CB95" t="n">
-        <v>34.16445855967465</v>
+        <v>34.16506911800111</v>
       </c>
       <c r="CC95" t="n">
-        <v>50.12648818633644</v>
+        <v>50.12681065968648</v>
       </c>
       <c r="CD95" t="n">
-        <v>22.97948403420753</v>
+        <v>22.98081080265404</v>
       </c>
       <c r="CE95" t="n">
         <v>52.55911136579431</v>
       </c>
       <c r="CF95" t="n">
-        <v>36.61987848566331</v>
+        <v>36.61988497361464</v>
       </c>
       <c r="CG95" t="n">
         <v>40.34470159232723</v>
@@ -40375,7 +40375,7 @@
         <v>7.046678635547576</v>
       </c>
       <c r="CM95" t="n">
-        <v>7.959553250182094</v>
+        <v>7.95957237739815</v>
       </c>
       <c r="CN95" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>1</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS96" t="b">
         <v>1</v>
@@ -40650,10 +40650,10 @@
         <v>-31</v>
       </c>
       <c r="BT96" t="n">
-        <v>-4.1</v>
+        <v>-4.3</v>
       </c>
       <c r="BU96" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BV96" t="n">
         <v>0.57</v>
@@ -40662,10 +40662,10 @@
         <v>18.43000030517578</v>
       </c>
       <c r="BX96" t="n">
-        <v>1.901526403205117</v>
+        <v>1.901393175326287</v>
       </c>
       <c r="BY96" t="n">
-        <v>3.527331477945492</v>
+        <v>3.527084340230262</v>
       </c>
       <c r="BZ96" t="n">
         <v>10.14952219632498</v>
@@ -40674,19 +40674,19 @@
         <v>8.46772853950336</v>
       </c>
       <c r="CB96" t="n">
-        <v>10.30755427993182</v>
+        <v>10.30782013901021</v>
       </c>
       <c r="CC96" t="n">
-        <v>7.564723054320488</v>
+        <v>7.564753328772007</v>
       </c>
       <c r="CD96" t="n">
-        <v>7.829865250920641</v>
+        <v>7.83008109074258</v>
       </c>
       <c r="CE96" t="n">
         <v>13.31345732107621</v>
       </c>
       <c r="CF96" t="n">
-        <v>8.737168874289001</v>
+        <v>8.737206707951374</v>
       </c>
       <c r="CG96" t="n">
         <v>8.46772853950336</v>
@@ -40707,7 +40707,7 @@
         <v>-58.64918307455048</v>
       </c>
       <c r="CM96" t="n">
-        <v>-52.59268187947179</v>
+        <v>-52.5924765964455</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>-42.1</v>
       </c>
       <c r="BT97" t="n">
-        <v>-22.4</v>
+        <v>-22.7</v>
       </c>
       <c r="BU97" t="n">
         <v>1.13</v>
@@ -40986,25 +40986,25 @@
         <v>5.03000020980835</v>
       </c>
       <c r="BX97" t="n">
-        <v>2.974533277112433</v>
+        <v>2.974533263125336</v>
       </c>
       <c r="BY97" t="n">
-        <v>2.978023652653838</v>
+        <v>2.978023643758313</v>
       </c>
       <c r="BZ97" t="n">
-        <v>2.987602343653252</v>
+        <v>2.987602348777667</v>
       </c>
       <c r="CA97" t="n">
         <v>9.357269522030355</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.46477373263948</v>
+        <v>3.464773725167703</v>
       </c>
       <c r="CC97" t="n">
-        <v>5.226192996527068</v>
+        <v>5.22619299762679</v>
       </c>
       <c r="CD97" t="n">
-        <v>1.11983397382059</v>
+        <v>1.119833979347172</v>
       </c>
       <c r="CE97" t="n">
         <v>6.1778101886163</v>
@@ -41291,7 +41291,7 @@
         <v>-22.5</v>
       </c>
       <c r="BU98" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BV98" t="n">
         <v>0.35</v>
@@ -41300,10 +41300,10 @@
         <v>6.550000190734863</v>
       </c>
       <c r="BX98" t="n">
-        <v>2.92835922824577</v>
+        <v>2.928359218006356</v>
       </c>
       <c r="BY98" t="n">
-        <v>5.432106368395903</v>
+        <v>5.432106349401789</v>
       </c>
       <c r="BZ98" t="inlineStr"/>
       <c r="CA98" t="inlineStr"/>
@@ -41314,13 +41314,13 @@
         <v>9.705704701814605</v>
       </c>
       <c r="CF98" t="n">
-        <v>6.022056766152093</v>
+        <v>6.022056756407584</v>
       </c>
       <c r="CG98" t="n">
-        <v>5.432106368395903</v>
+        <v>5.432106349401789</v>
       </c>
       <c r="CH98" t="n">
-        <v>4.888895731556313</v>
+        <v>4.888895714461611</v>
       </c>
       <c r="CI98" t="n">
         <v>3</v>
@@ -41332,10 +41332,10 @@
         <v>3.3</v>
       </c>
       <c r="CL98" t="n">
-        <v>-25.36037268408363</v>
+        <v>-25.36037294507145</v>
       </c>
       <c r="CM98" t="n">
-        <v>-8.060204720750374</v>
+        <v>-8.060204869521503</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -41614,37 +41614,37 @@
         <v>23.29999923706055</v>
       </c>
       <c r="BX99" t="n">
-        <v>5.103749849943674</v>
+        <v>5.103749870689059</v>
       </c>
       <c r="BY99" t="n">
-        <v>7.173562615219081</v>
+        <v>7.173562619704485</v>
       </c>
       <c r="BZ99" t="n">
-        <v>10.48983172369009</v>
+        <v>10.48983168761068</v>
       </c>
       <c r="CA99" t="n">
         <v>14.5426935407471</v>
       </c>
       <c r="CB99" t="n">
-        <v>7.042443467602885</v>
+        <v>7.0424434468783</v>
       </c>
       <c r="CC99" t="n">
-        <v>8.428083066231622</v>
+        <v>8.428083063605797</v>
       </c>
       <c r="CD99" t="n">
-        <v>5.203866419075574</v>
+        <v>5.203866397862172</v>
       </c>
       <c r="CE99" t="n">
         <v>11.10595965229168</v>
       </c>
       <c r="CF99" t="n">
-        <v>8.636273791850215</v>
+        <v>8.636273784923659</v>
       </c>
       <c r="CG99" t="n">
-        <v>7.800822840725351</v>
+        <v>7.80082284165514</v>
       </c>
       <c r="CH99" t="n">
-        <v>7.020740556652816</v>
+        <v>7.020740557489627</v>
       </c>
       <c r="CI99" t="n">
         <v>8</v>
@@ -41656,10 +41656,10 @@
         <v>2.8</v>
       </c>
       <c r="CL99" t="n">
-        <v>-69.86806529381444</v>
+        <v>-69.86806529022299</v>
       </c>
       <c r="CM99" t="n">
-        <v>-62.93444603159679</v>
+        <v>-62.93444606132449</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>1</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AS100" t="b">
         <v>1</v>
@@ -41930,22 +41930,22 @@
         <v>-17.8</v>
       </c>
       <c r="BT100" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BU100" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BV100" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BW100" t="n">
         <v>15.89000034332275</v>
       </c>
       <c r="BX100" t="n">
-        <v>8.00118854926402</v>
+        <v>8.001188555415021</v>
       </c>
       <c r="BY100" t="n">
-        <v>14.84220475888475</v>
+        <v>14.84220477029486</v>
       </c>
       <c r="BZ100" t="n">
         <v>10.31565431401403</v>
@@ -41966,7 +41966,7 @@
         <v>8.797113764315322</v>
       </c>
       <c r="CF100" t="n">
-        <v>12.19659641543789</v>
+        <v>12.19659641763303</v>
       </c>
       <c r="CG100" t="n">
         <v>9.867993843783237</v>
@@ -41987,7 +41987,7 @@
         <v>-44.10828025477708</v>
       </c>
       <c r="CM100" t="n">
-        <v>-23.24357361915914</v>
+        <v>-23.24357360534455</v>
       </c>
       <c r="CN100" t="inlineStr">
         <is>
@@ -42266,25 +42266,25 @@
         <v>44.7599983215332</v>
       </c>
       <c r="BX101" t="n">
-        <v>17.20270116944813</v>
+        <v>17.20270106884731</v>
       </c>
       <c r="BY101" t="n">
-        <v>19.66088486823818</v>
+        <v>19.66088481779531</v>
       </c>
       <c r="BZ101" t="n">
-        <v>24.58949622586175</v>
+        <v>24.58949630657235</v>
       </c>
       <c r="CA101" t="n">
         <v>51.1379037367685</v>
       </c>
       <c r="CB101" t="n">
-        <v>20.90417746320898</v>
+        <v>20.90417747800469</v>
       </c>
       <c r="CC101" t="n">
-        <v>23.35865953016378</v>
+        <v>23.3586595385307</v>
       </c>
       <c r="CD101" t="n">
-        <v>10.99908013679218</v>
+        <v>10.99908020566752</v>
       </c>
       <c r="CE101" t="n">
         <v>115.6180112331857</v>
@@ -42568,7 +42568,7 @@
         <v>-23.7</v>
       </c>
       <c r="BT102" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BU102" t="n">
         <v>0.43</v>
@@ -42580,10 +42580,10 @@
         <v>44.97000122070312</v>
       </c>
       <c r="BX102" t="n">
-        <v>9.838909709843135</v>
+        <v>9.838905051668803</v>
       </c>
       <c r="BY102" t="n">
-        <v>18.25117751175901</v>
+        <v>18.25116887084563</v>
       </c>
       <c r="BZ102" t="n">
         <v>85.61099370320636</v>
@@ -42592,13 +42592,13 @@
         <v>75.72810912354937</v>
       </c>
       <c r="CB102" t="n">
-        <v>103.3679200104117</v>
+        <v>103.3679213617749</v>
       </c>
       <c r="CC102" t="n">
-        <v>16.01313566157055</v>
+        <v>16.01313589684728</v>
       </c>
       <c r="CD102" t="n">
-        <v>69.7947735447385</v>
+        <v>69.79478028381247</v>
       </c>
       <c r="CE102" t="n">
         <v>21.24156204581304</v>
@@ -42886,22 +42886,22 @@
         <v>-43.2</v>
       </c>
       <c r="BT103" t="n">
-        <v>-16.8</v>
+        <v>-17</v>
       </c>
       <c r="BU103" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="BV103" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BW103" t="n">
         <v>2.740000009536743</v>
       </c>
       <c r="BX103" t="n">
-        <v>0.573059239797577</v>
+        <v>0.5730592396982046</v>
       </c>
       <c r="BY103" t="n">
-        <v>1.063024889824505</v>
+        <v>1.06302488964017</v>
       </c>
       <c r="BZ103" t="n">
         <v>3.425000011920929</v>
@@ -42910,13 +42910,13 @@
         <v>3.972173446398807</v>
       </c>
       <c r="CB103" t="n">
-        <v>2.46284065018267</v>
+        <v>2.462840650184562</v>
       </c>
       <c r="CC103" t="n">
-        <v>2.642774521676099</v>
+        <v>2.642774521688868</v>
       </c>
       <c r="CD103" t="n">
-        <v>1.762863058373667</v>
+        <v>1.762863058457354</v>
       </c>
       <c r="CE103" t="n">
         <v>8.739324130946441</v>
@@ -42962,10 +42962,10 @@
         </is>
       </c>
       <c r="CX103" t="n">
-        <v>3.339999914169312</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="CY103" t="n">
-        <v>-17.96406946261236</v>
+        <v>-19.88304244408318</v>
       </c>
       <c r="CZ103" t="n">
         <v>-44.53441340487693</v>
@@ -42981,7 +42981,7 @@
       </c>
       <c r="DD103" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-18.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-19.9%))</t>
         </is>
       </c>
     </row>
@@ -43200,7 +43200,7 @@
         <v>-28.4</v>
       </c>
       <c r="BT104" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="BU104" t="n">
         <v>1.38</v>
@@ -43212,10 +43212,10 @@
         <v>11.51000022888184</v>
       </c>
       <c r="BX104" t="n">
-        <v>2.047077728146336</v>
+        <v>2.046903817929295</v>
       </c>
       <c r="BY104" t="n">
-        <v>3.797329185711454</v>
+        <v>3.797006582258843</v>
       </c>
       <c r="BZ104" t="n">
         <v>12.13265736139095</v>
@@ -43224,25 +43224,25 @@
         <v>13.45436807571135</v>
       </c>
       <c r="CB104" t="n">
-        <v>8.853859618317287</v>
+        <v>8.853920354212345</v>
       </c>
       <c r="CC104" t="n">
-        <v>5.744239476963251</v>
+        <v>5.744254368891167</v>
       </c>
       <c r="CD104" t="n">
-        <v>6.578318945291152</v>
+        <v>6.578478873126744</v>
       </c>
       <c r="CE104" t="n">
         <v>11.51000022888184</v>
       </c>
       <c r="CF104" t="n">
-        <v>8.867253270323898</v>
+        <v>8.867240834924749</v>
       </c>
       <c r="CG104" t="n">
-        <v>8.853859618317287</v>
+        <v>8.853920354212345</v>
       </c>
       <c r="CH104" t="n">
-        <v>7.968473656485559</v>
+        <v>7.968528318791111</v>
       </c>
       <c r="CI104" t="n">
         <v>7</v>
@@ -43254,10 +43254,10 @@
         <v>6.6</v>
       </c>
       <c r="CL104" t="n">
-        <v>-30.76912686334783</v>
+        <v>-30.76865195192763</v>
       </c>
       <c r="CM104" t="n">
-        <v>-22.96044227633063</v>
+        <v>-22.96055031628634</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -43512,61 +43512,61 @@
         <v>42.34</v>
       </c>
       <c r="BP105" t="n">
-        <v>40.85</v>
+        <v>40.32</v>
       </c>
       <c r="BQ105" t="n">
         <v>67.15000000000001</v>
       </c>
       <c r="BR105" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
       <c r="BS105" t="n">
         <v>-22.8</v>
       </c>
       <c r="BT105" t="n">
-        <v>-5.9</v>
+        <v>-6</v>
       </c>
       <c r="BU105" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BV105" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BW105" t="n">
         <v>51.84999847412109</v>
       </c>
       <c r="BX105" t="n">
-        <v>15.83854317843969</v>
+        <v>15.83854321631578</v>
       </c>
       <c r="BY105" t="n">
-        <v>24.45220076769969</v>
+        <v>24.45220079025408</v>
       </c>
       <c r="BZ105" t="n">
-        <v>45.16372212057247</v>
+        <v>45.16372205422694</v>
       </c>
       <c r="CA105" t="n">
         <v>61.8255726523502</v>
       </c>
       <c r="CB105" t="n">
-        <v>36.03383593273696</v>
+        <v>36.03383592233789</v>
       </c>
       <c r="CC105" t="n">
-        <v>26.79540345052591</v>
+        <v>26.79540344725319</v>
       </c>
       <c r="CD105" t="n">
-        <v>22.58146590466439</v>
+        <v>22.58146587180007</v>
       </c>
       <c r="CE105" t="n">
         <v>20.62544462503444</v>
       </c>
       <c r="CF105" t="n">
-        <v>31.66452357900297</v>
+        <v>31.66452357244657</v>
       </c>
       <c r="CG105" t="n">
-        <v>25.6238021091128</v>
+        <v>25.62380211875363</v>
       </c>
       <c r="CH105" t="n">
-        <v>23.06142189820152</v>
+        <v>23.06142190687827</v>
       </c>
       <c r="CI105" t="n">
         <v>8</v>
@@ -43578,10 +43578,10 @@
         <v>3.9</v>
       </c>
       <c r="CL105" t="n">
-        <v>-55.52281084499601</v>
+        <v>-55.52281082826168</v>
       </c>
       <c r="CM105" t="n">
-        <v>-38.93052167627915</v>
+        <v>-38.93052168892409</v>
       </c>
       <c r="CN105" t="inlineStr">
         <is>
@@ -43603,7 +43603,11 @@
           <t>A análise fundamentalista da AXIA3 revela uma empresa de serviços públicos que apresenta desafios em sua eficiência operacional, uma vez que seu ROE de 9,9% e seu ROIC de 3,2% situam-se abaixo das médias setoriais de 12,1% e 9,6%, respectivamente. Essa rentabilidade pressionada convive com múltiplos de valuation que não parecem descontados, dado que o P/L de 12,66 e o P/VP de 1,25 não configuram uma clara assimetria de preço favorável para compensar o retorno sobre o capital investido mais baixo. Por outro lado, a saúde financeira mostra-se controlada, com a relação dívida líquida sobre EBITDA em 2,95 vezes, posicionando-se abaixo do limite prudencial e da média do setor de 3,4 vezes, o que confere segurança ao balanço diante de uma liquidez corrente confortável de 2,05. Esse endividamento sob controle, contudo, não se traduz em proventos robustos, visto que o dividend yield de 2,86% é modesto e reflete a necessidade de retenção de caixa frente a um crescimento histórico tímido, evidenciado pelo CAGR de receita de 9,7% nos últimos cinco anos, patamar muito abaixo dos 37,6% apresentados pelos seus pares. No checklist de critérios de qualidade e valor, o papel atende a apenas 3 dos 8 requisitos avaliados, penalizado principalmente pelas taxas de retorno inferiores à taxa Selic e à média setorial, além de registrar vendas recentes por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de cálculo, variando desde os conservadores R$ 15,84 por Bazin e R$ 24,45 por Gordon até os R$ 61,83 pela fórmula de Graham. Tomando como referência a média ponderada de R$ 31,66 e o preço-teto ajustado com margem de segurança de R$ 23,06, o preço atual de R$ 51,85 indica um expressivo prêmio de mercado, resultando em um upside negativo de 55,5% em relação ao valor justo estimado. Em balanço final, a AXIA3 destaca-se positivamente por sua excelente margem líquida de 27,05%, robusto valor de mercado e endividamento inferior à média de seus pares, mas traz como contrapartidas o fraco crescimento histórico, a baixa rentabilidade sobre o capital e um preço de tela desalinhado com as principais métricas de fluxo de caixa descontado e dividendos.</t>
         </is>
       </c>
-      <c r="CR105" t="inlineStr"/>
+      <c r="CR105" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS105" t="b">
         <v>0</v>
       </c>
@@ -43618,7 +43622,7 @@
       </c>
       <c r="CW105" t="inlineStr">
         <is>
-          <t>Em Baixa</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX105" t="n">
@@ -43634,14 +43638,14 @@
         <v>0</v>
       </c>
       <c r="DB105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC105" t="b">
         <v>0</v>
       </c>
       <c r="DD105" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.5%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -43860,37 +43864,37 @@
         <v>-52.4</v>
       </c>
       <c r="BT106" t="n">
-        <v>-20.3</v>
+        <v>-20.7</v>
       </c>
       <c r="BU106" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BV106" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BW106" t="n">
         <v>15.14000034332275</v>
       </c>
       <c r="BX106" t="n">
-        <v>3.820728862955463</v>
+        <v>3.820728858704681</v>
       </c>
       <c r="BY106" t="n">
-        <v>4.841207739235919</v>
+        <v>4.841207734573582</v>
       </c>
       <c r="BZ106" t="n">
-        <v>14.21439288455366</v>
+        <v>14.21439288667878</v>
       </c>
       <c r="CA106" t="n">
         <v>37.03789734077716</v>
       </c>
       <c r="CB106" t="n">
-        <v>9.722395134956958</v>
+        <v>9.722395131181914</v>
       </c>
       <c r="CC106" t="n">
-        <v>48.39119060943085</v>
+        <v>48.39119061015067</v>
       </c>
       <c r="CD106" t="n">
-        <v>6.819001489425211</v>
+        <v>6.819001490932709</v>
       </c>
       <c r="CE106" t="n">
         <v>20.9161030224964</v>
@@ -44458,13 +44462,13 @@
         <v>24.93</v>
       </c>
       <c r="BP108" t="n">
-        <v>53.05</v>
+        <v>52.32</v>
       </c>
       <c r="BQ108" t="n">
         <v>71.62</v>
       </c>
       <c r="BR108" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="BS108" t="n">
         <v>-17.5</v>
@@ -44476,16 +44480,16 @@
         <v>0.73</v>
       </c>
       <c r="BV108" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="BW108" t="n">
         <v>59.08000183105469</v>
       </c>
       <c r="BX108" t="n">
-        <v>66.83145639530029</v>
+        <v>66.8314564271862</v>
       </c>
       <c r="BY108" t="n">
-        <v>97.30660051155725</v>
+        <v>97.30660055798312</v>
       </c>
       <c r="BZ108" t="n">
         <v>24.49888433185681</v>
@@ -44778,13 +44782,13 @@
         <v>-23.1</v>
       </c>
       <c r="BT109" t="n">
-        <v>-9.9</v>
+        <v>-10</v>
       </c>
       <c r="BU109" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BV109" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="BW109" t="n">
         <v>8.229999542236328</v>
@@ -45089,10 +45093,10 @@
         <v>-40.9</v>
       </c>
       <c r="BU110" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BV110" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="BW110" t="n">
         <v>6.539999961853027</v>
@@ -45388,22 +45392,22 @@
         <v>-6.1</v>
       </c>
       <c r="BT111" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="BU111" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="BV111" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BW111" t="n">
         <v>97.26999664306641</v>
       </c>
       <c r="BX111" t="n">
-        <v>4.969483348297951</v>
+        <v>4.970373447570957</v>
       </c>
       <c r="BY111" t="n">
-        <v>9.218391611092699</v>
+        <v>9.220042745244125</v>
       </c>
       <c r="BZ111" t="n">
         <v>41.68264733249126</v>
@@ -45412,13 +45416,13 @@
         <v>41.38446934269194</v>
       </c>
       <c r="CB111" t="n">
-        <v>34.12631340465155</v>
+        <v>34.1250951982051</v>
       </c>
       <c r="CC111" t="n">
-        <v>17.80332662049297</v>
+        <v>17.80324331204815</v>
       </c>
       <c r="CD111" t="n">
-        <v>28.44042436262346</v>
+        <v>28.43940530576779</v>
       </c>
       <c r="CE111" t="n">
         <v>42.08352793520866</v>
@@ -45705,19 +45709,19 @@
         <v>-8.5</v>
       </c>
       <c r="BU112" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BV112" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BW112" t="n">
         <v>17.30999946594238</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.249533332872448</v>
+        <v>3.249424039637348</v>
       </c>
       <c r="BY112" t="n">
-        <v>6.027884332478391</v>
+        <v>6.02768159352728</v>
       </c>
       <c r="BZ112" t="n">
         <v>14.75916942881188</v>
@@ -45726,23 +45730,23 @@
         <v>15.70024654832573</v>
       </c>
       <c r="CB112" t="n">
-        <v>10.37381102321067</v>
+        <v>10.37388546273463</v>
       </c>
       <c r="CC112" t="n">
-        <v>13.01540775857188</v>
+        <v>13.01542669545761</v>
       </c>
       <c r="CD112" t="n">
-        <v>7.656236801169629</v>
+        <v>7.656345482362615</v>
       </c>
       <c r="CE112" t="inlineStr"/>
       <c r="CF112" t="n">
-        <v>11.25545931542803</v>
+        <v>11.25545920186996</v>
       </c>
       <c r="CG112" t="n">
-        <v>11.69460939089127</v>
+        <v>11.69465607909612</v>
       </c>
       <c r="CH112" t="n">
-        <v>10.52514845180215</v>
+        <v>10.52519047118651</v>
       </c>
       <c r="CI112" t="n">
         <v>6</v>
@@ -45754,10 +45758,10 @@
         <v>4.8</v>
       </c>
       <c r="CL112" t="n">
-        <v>-39.1961364729647</v>
+        <v>-39.19589372665816</v>
       </c>
       <c r="CM112" t="n">
-        <v>-34.97712499891597</v>
+        <v>-34.97712565494181</v>
       </c>
       <c r="CN112" t="inlineStr">
         <is>
@@ -45946,7 +45950,7 @@
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>26446039040</v>
+        <v>26444003328</v>
       </c>
       <c r="AU113" t="n">
         <v>21.59</v>
@@ -46036,10 +46040,10 @@
         <v>14.25</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.333549791278858</v>
+        <v>1.333549786992538</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.473734862822282</v>
+        <v>2.473734854871158</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.745368226030568</v>
@@ -46048,13 +46052,13 @@
         <v>10.75360939215812</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.87858352187915</v>
+        <v>4.878583524188413</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.696526410438667</v>
+        <v>7.696526410998041</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.286205605119131</v>
+        <v>4.286205608317753</v>
       </c>
       <c r="CE113" t="n">
         <v>11.16944225998353</v>
@@ -46309,7 +46313,7 @@
         <v>1289.96</v>
       </c>
       <c r="BI114" t="n">
-        <v>28866.92</v>
+        <v>28865.77</v>
       </c>
       <c r="BJ114" t="n">
         <v>2.5</v>
@@ -46342,10 +46346,10 @@
         <v>-34.2</v>
       </c>
       <c r="BT114" t="n">
-        <v>-18.4</v>
+        <v>-18.7</v>
       </c>
       <c r="BU114" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="BV114" t="n">
         <v>0.49</v>
@@ -46354,10 +46358,10 @@
         <v>18.40999984741211</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.77094235496264</v>
+        <v>11.77047455224335</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.68808893858382</v>
+        <v>14.68750520214714</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -46648,37 +46652,37 @@
         <v>-46.7</v>
       </c>
       <c r="BT115" t="n">
-        <v>-15.2</v>
+        <v>-15.6</v>
       </c>
       <c r="BU115" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BV115" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BW115" t="n">
         <v>7.869999885559082</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.023899907414319</v>
+        <v>2.02389990569688</v>
       </c>
       <c r="BY115" t="n">
-        <v>2.245933800897701</v>
+        <v>2.245933799439057</v>
       </c>
       <c r="BZ115" t="n">
-        <v>3.283227752534775</v>
+        <v>3.283227753188529</v>
       </c>
       <c r="CA115" t="n">
         <v>9.955734923002648</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.000357702981388</v>
+        <v>2.000357702651224</v>
       </c>
       <c r="CC115" t="n">
-        <v>5.925849691249074</v>
+        <v>5.925849691381261</v>
       </c>
       <c r="CD115" t="n">
-        <v>1.426516297236668</v>
+        <v>1.426516297824582</v>
       </c>
       <c r="CE115" t="n">
         <v>14.66556730038189</v>
@@ -46962,22 +46966,22 @@
         <v>0</v>
       </c>
       <c r="BT116" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BU116" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="BV116" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="BW116" t="n">
         <v>11.18000030517578</v>
       </c>
       <c r="BX116" t="n">
-        <v>2.429719281699719</v>
+        <v>2.429769114798179</v>
       </c>
       <c r="BY116" t="n">
-        <v>4.507129267552978</v>
+        <v>4.507221707950622</v>
       </c>
       <c r="BZ116" t="n">
         <v>12.17214495017084</v>
@@ -46986,13 +46990,13 @@
         <v>12.66795579710097</v>
       </c>
       <c r="CB116" t="n">
-        <v>9.62706315425741</v>
+        <v>9.627038086702017</v>
       </c>
       <c r="CC116" t="n">
-        <v>0.7923834408559832</v>
+        <v>0.7923827793614787</v>
       </c>
       <c r="CD116" t="n">
-        <v>6.748506582207539</v>
+        <v>6.748454791664971</v>
       </c>
       <c r="CE116" t="n">
         <v>7.239159730295168</v>
@@ -47292,10 +47296,10 @@
         <v>3.400000095367432</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.674174181344084</v>
+        <v>1.674174180078823</v>
       </c>
       <c r="BY117" t="n">
-        <v>3.105593106393275</v>
+        <v>3.105593104046216</v>
       </c>
       <c r="BZ117" t="n">
         <v>1.164684624188688</v>
@@ -47304,7 +47308,7 @@
         <v>4.65742755893486</v>
       </c>
       <c r="CB117" t="n">
-        <v>1.616815916120544</v>
+        <v>1.61681591566259</v>
       </c>
       <c r="CC117" t="n">
         <v>0.7445919647652398</v>
@@ -47594,22 +47598,22 @@
         <v>-31.7</v>
       </c>
       <c r="BT118" t="n">
-        <v>-5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="BU118" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BV118" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BW118" t="n">
         <v>4.710000038146973</v>
       </c>
       <c r="BX118" t="n">
-        <v>1.448542797629799</v>
+        <v>1.448542792820495</v>
       </c>
       <c r="BY118" t="n">
-        <v>1.509703493529724</v>
+        <v>1.50970348851736</v>
       </c>
       <c r="BZ118" t="inlineStr"/>
       <c r="CA118" t="inlineStr"/>
@@ -47898,10 +47902,10 @@
         <v>-57.3</v>
       </c>
       <c r="BT119" t="n">
-        <v>-30.2</v>
+        <v>-30.5</v>
       </c>
       <c r="BU119" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BV119" t="n">
         <v>0.6899999999999999</v>
@@ -47910,10 +47914,10 @@
         <v>6.110000133514404</v>
       </c>
       <c r="BX119" t="n">
-        <v>0.9801914038873228</v>
+        <v>0.9798900292763161</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.818255054210984</v>
+        <v>1.817696004307566</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -47964,10 +47968,10 @@
         </is>
       </c>
       <c r="CX119" t="n">
-        <v>7.710000038146973</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="CY119" t="n">
-        <v>-20.75226843989891</v>
+        <v>-20.95730765280457</v>
       </c>
       <c r="CZ119" t="n">
         <v>-58.17730263024769</v>
@@ -47983,7 +47987,7 @@
       </c>
       <c r="DD119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-20.8%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-21.0%))</t>
         </is>
       </c>
     </row>
@@ -48166,10 +48170,10 @@
         <v>2.12</v>
       </c>
       <c r="BH120" t="n">
-        <v>35.23</v>
+        <v>35.1</v>
       </c>
       <c r="BI120" t="n">
-        <v>88.39</v>
+        <v>88.34</v>
       </c>
       <c r="BJ120" t="n">
         <v>20.9</v>
@@ -48202,10 +48206,10 @@
         <v>-46.5</v>
       </c>
       <c r="BT120" t="n">
-        <v>-12.3</v>
+        <v>-12.6</v>
       </c>
       <c r="BU120" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BV120" t="n">
         <v>0.55</v>
@@ -48214,25 +48218,25 @@
         <v>3.299999952316284</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.129231943796697</v>
+        <v>1.128667183078744</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.179258246745238</v>
+        <v>1.178866242232186</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.334182667672991</v>
+        <v>1.33440653809145</v>
       </c>
       <c r="CA120" t="n">
         <v>4.000073406115944</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.950539373348023</v>
+        <v>0.9504674185471087</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.177296676335917</v>
+        <v>2.177339858126595</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.5366945234133217</v>
+        <v>0.5369186656470627</v>
       </c>
       <c r="CE120" t="n">
         <v>4.93751177672036</v>
@@ -48528,10 +48532,10 @@
         <v>5.239999771118164</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.191433399592619</v>
+        <v>5.191433405735087</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.558727029806853</v>
+        <v>7.558727038750288</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -48540,13 +48544,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.375080214699736</v>
+        <v>6.375080222242687</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.375080214699736</v>
+        <v>6.375080222242687</v>
       </c>
       <c r="CH121" t="n">
-        <v>5.737572193229762</v>
+        <v>5.737572200018419</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -48558,10 +48562,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.495657325294516</v>
+        <v>9.495657454849038</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.66184147254948</v>
+        <v>21.66184161649893</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -48828,22 +48832,22 @@
         <v>-56</v>
       </c>
       <c r="BT122" t="n">
-        <v>-16</v>
+        <v>-16.3</v>
       </c>
       <c r="BU122" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BV122" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BW122" t="n">
         <v>4.789999961853027</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.272756686097852</v>
+        <v>5.272756699929427</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.400753426611566</v>
+        <v>9.400753451271763</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -48852,13 +48856,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.336755056354709</v>
+        <v>7.336755075600594</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.336755056354709</v>
+        <v>7.336755075600594</v>
       </c>
       <c r="CH122" t="n">
-        <v>6.603079550719237</v>
+        <v>6.603079568040535</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -48870,10 +48874,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134871201157</v>
+        <v>37.85134907362529</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.1681652355684</v>
+        <v>53.16816563736144</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -48902,10 +48906,10 @@
         </is>
       </c>
       <c r="CX122" t="n">
-        <v>4.889999866485596</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="CY122" t="n">
-        <v>-2.044987880632343</v>
+        <v>-3.232320274288303</v>
       </c>
       <c r="CZ122" t="n">
         <v>-57.68551156372263</v>
@@ -48921,7 +48925,7 @@
       </c>
       <c r="DD122" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-2.0%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.2%))</t>
         </is>
       </c>
     </row>
@@ -49126,22 +49130,22 @@
         <v>-17.5</v>
       </c>
       <c r="BT123" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="BU123" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BV123" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BW123" t="n">
         <v>21.03000068664551</v>
       </c>
       <c r="BX123" t="n">
-        <v>36.42741699332814</v>
+        <v>36.42741697234028</v>
       </c>
       <c r="BY123" t="n">
-        <v>67.57285852262369</v>
+        <v>67.57285848369122</v>
       </c>
       <c r="BZ123" t="n">
         <v>19.70633020495424</v>
@@ -49160,7 +49164,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>25.49883428388488</v>
+        <v>25.4988342803869</v>
       </c>
       <c r="CG123" t="n">
         <v>22.92261274222209</v>
@@ -49181,7 +49185,7 @@
         <v>-1.90037663146353</v>
       </c>
       <c r="CM123" t="n">
-        <v>21.2498024314244</v>
+        <v>21.24980241479115</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -49448,37 +49452,37 @@
         <v>-34.3</v>
       </c>
       <c r="BT124" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="BU124" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BV124" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BW124" t="n">
         <v>9.090000152587891</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.518187436274411</v>
+        <v>3.518187440366058</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.631196078186726</v>
+        <v>3.63119608175949</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.385743495061829</v>
+        <v>4.385743494276385</v>
       </c>
       <c r="CA124" t="n">
         <v>18.9170762302566</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.451708560936539</v>
+        <v>3.451708563408018</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.742135616540219</v>
+        <v>7.742135616374609</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.732684431074937</v>
+        <v>1.732684430271992</v>
       </c>
       <c r="CE124" t="n">
         <v>20.26176339670673</v>
@@ -49762,22 +49766,22 @@
         <v>-36.4</v>
       </c>
       <c r="BT125" t="n">
-        <v>-23.4</v>
+        <v>-23.6</v>
       </c>
       <c r="BU125" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BV125" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="BW125" t="n">
         <v>11.28999996185303</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7670876391874237</v>
+        <v>0.7667711032522687</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.422947570692671</v>
+        <v>1.422360396532958</v>
       </c>
       <c r="BZ125" t="n">
         <v>15.56633709620735</v>
@@ -49786,13 +49790,13 @@
         <v>16.25115692351487</v>
       </c>
       <c r="CB125" t="n">
-        <v>13.6704307505937</v>
+        <v>13.67049076080041</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.678297583250632</v>
+        <v>1.678304309423708</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.0288523052001</v>
+        <v>11.02917988190867</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -49836,10 +49840,10 @@
         </is>
       </c>
       <c r="CX125" t="n">
-        <v>11.80000019073486</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="CY125" t="n">
-        <v>-4.322035768120402</v>
+        <v>-6.462301182208529</v>
       </c>
       <c r="CZ125" t="n">
         <v>-36.92737317063685</v>
@@ -49855,7 +49859,7 @@
       </c>
       <c r="DD125" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-4.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.5%))</t>
         </is>
       </c>
     </row>
@@ -50072,10 +50076,10 @@
         <v>0</v>
       </c>
       <c r="BT126" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="BU126" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BV126" t="n">
         <v>0.33</v>
@@ -50380,25 +50384,25 @@
         <v>18.89999961853027</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.588646264889812</v>
+        <v>0.5886462643501161</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7906544489905655</v>
+        <v>0.7906544483155521</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.609265560820834</v>
+        <v>4.609265561111689</v>
       </c>
       <c r="CA127" t="n">
         <v>11.51795868166206</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.765727404119163</v>
+        <v>1.76572740422253</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6741747290841664</v>
+        <v>0.674174729088182</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.26163749616063</v>
+        <v>2.261637496346329</v>
       </c>
       <c r="CE127" t="n">
         <v>18.89999961853027</v>
@@ -50694,10 +50698,10 @@
         <v>4.989999771118164</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.226814118379893</v>
+        <v>1.226814121165864</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.053240719943075</v>
+        <v>2.053240724605778</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -50708,13 +50712,13 @@
         <v>5.871634259790683</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.640027419161484</v>
+        <v>1.640027422885821</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.640027419161484</v>
+        <v>1.640027422885821</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.476024677245336</v>
+        <v>1.476024680597239</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -50726,10 +50730,10 @@
         <v>4.8</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.42034579262943</v>
+        <v>-70.42034572545701</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.13371754736603</v>
+        <v>-67.13371747273001</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -51008,37 +51012,37 @@
         <v>16.76000022888184</v>
       </c>
       <c r="BX129" t="n">
-        <v>2.018107859704232</v>
+        <v>2.018107858334617</v>
       </c>
       <c r="BY129" t="n">
-        <v>3.646153660299482</v>
+        <v>3.646153658920434</v>
       </c>
       <c r="BZ129" t="n">
-        <v>9.926116034747922</v>
+        <v>9.926116037730154</v>
       </c>
       <c r="CA129" t="n">
         <v>12.04263895963171</v>
       </c>
       <c r="CB129" t="n">
-        <v>5.758979294682138</v>
+        <v>5.758979295560477</v>
       </c>
       <c r="CC129" t="n">
-        <v>5.544942948553958</v>
+        <v>5.544942948673764</v>
       </c>
       <c r="CD129" t="n">
-        <v>4.85966340378453</v>
+        <v>4.859663404889753</v>
       </c>
       <c r="CE129" t="n">
         <v>15.42017902790524</v>
       </c>
       <c r="CF129" t="n">
-        <v>6.963082383616623</v>
+        <v>6.963082384234382</v>
       </c>
       <c r="CG129" t="n">
-        <v>5.651961121618048</v>
+        <v>5.65196112211712</v>
       </c>
       <c r="CH129" t="n">
-        <v>5.086765009456244</v>
+        <v>5.086765009905408</v>
       </c>
       <c r="CI129" t="n">
         <v>6</v>
@@ -51050,10 +51054,10 @@
         <v>7.6</v>
       </c>
       <c r="CL129" t="n">
-        <v>-69.64937386641306</v>
+        <v>-69.64937386373306</v>
       </c>
       <c r="CM129" t="n">
-        <v>-58.45416295629029</v>
+        <v>-58.45416295260437</v>
       </c>
       <c r="CN129" t="inlineStr">
         <is>
@@ -51283,7 +51287,7 @@
       </c>
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="n">
-        <v>172.91</v>
+        <v>172.9</v>
       </c>
       <c r="BJ130" t="n">
         <v>-17.3</v>
@@ -51316,22 +51320,22 @@
         <v>-13.1</v>
       </c>
       <c r="BT130" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="BU130" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="BV130" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="BW130" t="n">
         <v>18.79999923706055</v>
       </c>
       <c r="BX130" t="n">
-        <v>1.447783520302165</v>
+        <v>1.447712587042787</v>
       </c>
       <c r="BY130" t="n">
-        <v>2.107972805559953</v>
+        <v>2.107869526734298</v>
       </c>
       <c r="BZ130" t="inlineStr"/>
       <c r="CA130" t="inlineStr"/>
@@ -51384,10 +51388,10 @@
         </is>
       </c>
       <c r="CX130" t="n">
-        <v>19.86000061035156</v>
+        <v>20.38999938964844</v>
       </c>
       <c r="CY130" t="n">
-        <v>-5.337368281542321</v>
+        <v>-7.79794114851764</v>
       </c>
       <c r="CZ130" t="n">
         <v>-15.10502492905792</v>
@@ -51403,7 +51407,7 @@
       </c>
       <c r="DD130" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-5.3%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-7.8%))</t>
         </is>
       </c>
     </row>
@@ -51918,7 +51922,7 @@
         <v>-13</v>
       </c>
       <c r="BT132" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="BU132" t="n">
         <v>1.36</v>
@@ -51930,10 +51934,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.8551117973919462</v>
+        <v>0.8550990086378004</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.9465018707382106</v>
+        <v>0.9464877151859654</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -51942,13 +51946,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.9008068340650783</v>
+        <v>0.9007933619118829</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.9008068340650783</v>
+        <v>0.9007933619118829</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.8107261506585706</v>
+        <v>0.8107140257206946</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -51960,10 +51964,10 @@
         <v>1.1</v>
       </c>
       <c r="CL132" t="n">
-        <v>-80.03137531811061</v>
+        <v>-80.03167396190487</v>
       </c>
       <c r="CM132" t="n">
-        <v>-77.81263924234513</v>
+        <v>-77.81297106878318</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -52244,10 +52248,10 @@
         <v>1.039999961853027</v>
       </c>
       <c r="BX133" t="n">
-        <v>0.3048180261667492</v>
+        <v>0.3048180261958082</v>
       </c>
       <c r="BY133" t="n">
-        <v>0.5654374385393198</v>
+        <v>0.5654374385932242</v>
       </c>
       <c r="BZ133" t="inlineStr"/>
       <c r="CA133" t="inlineStr"/>
@@ -52256,13 +52260,13 @@
       <c r="CD133" t="inlineStr"/>
       <c r="CE133" t="inlineStr"/>
       <c r="CF133" t="n">
-        <v>0.4351277323530345</v>
+        <v>0.4351277323945162</v>
       </c>
       <c r="CG133" t="n">
-        <v>0.4351277323530345</v>
+        <v>0.4351277323945162</v>
       </c>
       <c r="CH133" t="n">
-        <v>0.3916149591177311</v>
+        <v>0.3916149591550646</v>
       </c>
       <c r="CI133" t="n">
         <v>2</v>
@@ -52274,10 +52278,10 @@
         <v>1.9</v>
       </c>
       <c r="CL133" t="n">
-        <v>-62.34471408826128</v>
+        <v>-62.34471408467152</v>
       </c>
       <c r="CM133" t="n">
-        <v>-58.16079343140142</v>
+        <v>-58.16079342741281</v>
       </c>
       <c r="CN133" t="inlineStr">
         <is>
@@ -52542,10 +52546,10 @@
         <v>-21.1</v>
       </c>
       <c r="BT134" t="n">
-        <v>-9.6</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="BU134" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BV134" t="n">
         <v>0.82</v>
@@ -52554,10 +52558,10 @@
         <v>35.77000045776367</v>
       </c>
       <c r="BX134" t="n">
-        <v>8.056625183516472</v>
+        <v>8.056625189205336</v>
       </c>
       <c r="BY134" t="n">
-        <v>11.73044626719999</v>
+        <v>11.73044627548297</v>
       </c>
       <c r="BZ134" t="n">
         <v>7.91506393107962</v>
@@ -52855,10 +52859,10 @@
         <v>-10.8</v>
       </c>
       <c r="BU135" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="BV135" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="BW135" t="n">
         <v>2.579999923706055</v>
@@ -53162,22 +53166,22 @@
         <v>-51.2</v>
       </c>
       <c r="BT136" t="n">
-        <v>-11.8</v>
+        <v>-12.3</v>
       </c>
       <c r="BU136" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BV136" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BW136" t="n">
         <v>5.090000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>0.9696997099488727</v>
+        <v>0.9696997101857272</v>
       </c>
       <c r="BY136" t="n">
-        <v>1.798792961955159</v>
+        <v>1.798792962394524</v>
       </c>
       <c r="BZ136" t="inlineStr"/>
       <c r="CA136" t="inlineStr"/>
@@ -53188,13 +53192,13 @@
         <v>2.687155457559689</v>
       </c>
       <c r="CF136" t="n">
-        <v>1.818549376487907</v>
+        <v>1.818549376713313</v>
       </c>
       <c r="CG136" t="n">
-        <v>1.798792961955159</v>
+        <v>1.798792962394524</v>
       </c>
       <c r="CH136" t="n">
-        <v>1.618913665759643</v>
+        <v>1.618913666155071</v>
       </c>
       <c r="CI136" t="n">
         <v>3</v>
@@ -53206,10 +53210,10 @@
         <v>2.8</v>
       </c>
       <c r="CL136" t="n">
-        <v>-68.19423148864654</v>
+        <v>-68.1942314808778</v>
       </c>
       <c r="CM136" t="n">
-        <v>-64.27211548189624</v>
+        <v>-64.27211547746782</v>
       </c>
       <c r="CN136" t="inlineStr">
         <is>
@@ -53261,7 +53265,7 @@
       </c>
       <c r="DD136" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +3.7% do topo, MM50&gt;MM200)</t>
+          <t>Rompimento (vol x1.1, +3.7% do topo, MM50&gt;MM200)</t>
         </is>
       </c>
     </row>
@@ -53414,7 +53418,7 @@
         <v>5.97</v>
       </c>
       <c r="AX137" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="AY137" t="n">
         <v>3.69</v>
@@ -53447,7 +53451,7 @@
         <v>13.07</v>
       </c>
       <c r="BI137" t="n">
-        <v>67.7</v>
+        <v>67.69</v>
       </c>
       <c r="BJ137" t="n">
         <v>-58.5</v>
@@ -53480,37 +53484,37 @@
         <v>-32</v>
       </c>
       <c r="BT137" t="n">
-        <v>-9.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="BU137" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BV137" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BW137" t="n">
         <v>4.909999847412109</v>
       </c>
       <c r="BX137" t="n">
-        <v>1.523881198784834</v>
+        <v>1.52364286884492</v>
       </c>
       <c r="BY137" t="n">
-        <v>1.685559995038767</v>
+        <v>1.685354293403078</v>
       </c>
       <c r="BZ137" t="n">
-        <v>2.48988388248115</v>
+        <v>2.489969446039118</v>
       </c>
       <c r="CA137" t="n">
         <v>7.747739573095417</v>
       </c>
       <c r="CB137" t="n">
-        <v>1.744998930341796</v>
+        <v>1.744907891180617</v>
       </c>
       <c r="CC137" t="n">
-        <v>1.782256379807031</v>
+        <v>1.78226326067073</v>
       </c>
       <c r="CD137" t="n">
-        <v>1.078022024337534</v>
+        <v>1.078099414835623</v>
       </c>
       <c r="CE137" t="n">
         <v>0.03462128620209939</v>
@@ -53556,7 +53560,7 @@
       <c r="CV137" t="inlineStr"/>
       <c r="CW137" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CX137" t="n">
@@ -53808,10 +53812,10 @@
         <v>6.380000114440918</v>
       </c>
       <c r="BX138" t="n">
-        <v>1.750831185064184</v>
+        <v>1.750831185994548</v>
       </c>
       <c r="BY138" t="n">
-        <v>2.549210205453452</v>
+        <v>2.549210206808061</v>
       </c>
       <c r="BZ138" t="n">
         <v>1.700461332398399</v>
@@ -54118,10 +54122,10 @@
         <v>1.830000042915344</v>
       </c>
       <c r="BX139" t="n">
-        <v>0.5136933449409921</v>
+        <v>0.5136933439391865</v>
       </c>
       <c r="BY139" t="n">
-        <v>0.7479375102340846</v>
+        <v>0.7479375087754556</v>
       </c>
       <c r="BZ139" t="n">
         <v>0.3540837292338526</v>
@@ -54184,7 +54188,7 @@
         <v>-8.955221313529805</v>
       </c>
       <c r="CZ139" t="n">
-        <v>-56.98604440612495</v>
+        <v>-56.98603956253667</v>
       </c>
       <c r="DA139" t="b">
         <v>0</v>
@@ -54676,10 +54680,10 @@
         <v>-74.09999999999999</v>
       </c>
       <c r="BT141" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="BU141" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="BV141" t="n">
         <v>0.03</v>
@@ -55240,10 +55244,10 @@
         <v>0.76</v>
       </c>
       <c r="BH143" t="n">
-        <v>315.87</v>
+        <v>314.75</v>
       </c>
       <c r="BI143" t="n">
-        <v>85.38</v>
+        <v>85.33</v>
       </c>
       <c r="BJ143" t="n">
         <v>-2.6</v>
@@ -55276,10 +55280,10 @@
         <v>-62.2</v>
       </c>
       <c r="BT143" t="n">
-        <v>-31.2</v>
+        <v>-31.6</v>
       </c>
       <c r="BU143" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BV143" t="n">
         <v>0.59</v>
@@ -55288,25 +55292,25 @@
         <v>4.159999847412109</v>
       </c>
       <c r="BX143" t="n">
-        <v>0.6956808240881132</v>
+        <v>0.6952579235814946</v>
       </c>
       <c r="BY143" t="n">
-        <v>0.7022758351932048</v>
+        <v>0.7018725284666706</v>
       </c>
       <c r="BZ143" t="n">
-        <v>0.8224835262240521</v>
+        <v>0.8225111859598578</v>
       </c>
       <c r="CA143" t="n">
         <v>6.067610485147757</v>
       </c>
       <c r="CB143" t="n">
-        <v>0.2802260972553379</v>
+        <v>0.2801105282062188</v>
       </c>
       <c r="CC143" t="n">
-        <v>0.4177484617637583</v>
+        <v>0.4177501727617216</v>
       </c>
       <c r="CD143" t="n">
-        <v>0.3129984713743125</v>
+        <v>0.3130278714175326</v>
       </c>
       <c r="CE143" t="inlineStr"/>
       <c r="CF143" t="inlineStr"/>
@@ -55590,10 +55594,10 @@
         <v>-29</v>
       </c>
       <c r="BT144" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="BU144" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BV144" t="n">
         <v>0.31</v>
@@ -55602,10 +55606,10 @@
         <v>19.54000091552734</v>
       </c>
       <c r="BX144" t="n">
-        <v>29.75287272692384</v>
+        <v>29.75287277305137</v>
       </c>
       <c r="BY144" t="n">
-        <v>39.80273195912922</v>
+        <v>39.80273202083761</v>
       </c>
       <c r="BZ144" t="n">
         <v>2.525572356336101</v>
@@ -55614,7 +55618,7 @@
         <v>7.002148431252935</v>
       </c>
       <c r="CB144" t="n">
-        <v>6.480024632850281</v>
+        <v>6.480024641585374</v>
       </c>
       <c r="CC144" t="n">
         <v>3.046690502845772</v>
@@ -55904,22 +55908,22 @@
         <v>-54.5</v>
       </c>
       <c r="BT145" t="n">
-        <v>-13.2</v>
+        <v>-13.5</v>
       </c>
       <c r="BU145" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BV145" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="BW145" t="n">
         <v>3.640000104904175</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.6583625636119577</v>
+        <v>0.6583625641355085</v>
       </c>
       <c r="BY145" t="n">
-        <v>1.221262555500181</v>
+        <v>1.221262556471368</v>
       </c>
       <c r="BZ145" t="inlineStr"/>
       <c r="CA145" t="inlineStr"/>
@@ -55930,13 +55934,13 @@
         <v>3.264431296215689</v>
       </c>
       <c r="CF145" t="n">
-        <v>0.9398125595560696</v>
+        <v>0.9398125603034384</v>
       </c>
       <c r="CG145" t="n">
-        <v>0.9398125595560696</v>
+        <v>0.9398125603034384</v>
       </c>
       <c r="CH145" t="n">
-        <v>0.8458313036004627</v>
+        <v>0.8458313042730946</v>
       </c>
       <c r="CI145" t="n">
         <v>2</v>
@@ -55948,10 +55952,10 @@
         <v>5</v>
       </c>
       <c r="CL145" t="n">
-        <v>-76.76287694440246</v>
+        <v>-76.76287692592356</v>
       </c>
       <c r="CM145" t="n">
-        <v>-74.18097438266939</v>
+        <v>-74.18097436213729</v>
       </c>
       <c r="CN145" t="inlineStr">
         <is>
@@ -56216,13 +56220,13 @@
         <v>-42.6</v>
       </c>
       <c r="BT146" t="n">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="BU146" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BV146" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="BW146" t="n">
         <v>1.559999942779541</v>
@@ -56540,10 +56544,10 @@
         <v>18.48999977111816</v>
       </c>
       <c r="BX147" t="n">
-        <v>9.370797943144415</v>
+        <v>9.370797965672606</v>
       </c>
       <c r="BY147" t="n">
-        <v>13.64388180521827</v>
+        <v>13.64388183801931</v>
       </c>
       <c r="BZ147" t="n">
         <v>4.677596633899998</v>
@@ -57159,19 +57163,19 @@
         <v>-15.8</v>
       </c>
       <c r="BU149" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BV149" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BW149" t="n">
         <v>10.22999954223633</v>
       </c>
       <c r="BX149" t="n">
-        <v>5.465905843783379</v>
+        <v>5.465905829741256</v>
       </c>
       <c r="BY149" t="n">
-        <v>10.00463210369535</v>
+        <v>10.00463207799307</v>
       </c>
       <c r="BZ149" t="inlineStr"/>
       <c r="CA149" t="inlineStr"/>
@@ -57182,13 +57186,13 @@
         <v>2.757870606147196</v>
       </c>
       <c r="CF149" t="n">
-        <v>6.076136184541976</v>
+        <v>6.07613617129384</v>
       </c>
       <c r="CG149" t="n">
-        <v>5.465905843783379</v>
+        <v>5.465905829741256</v>
       </c>
       <c r="CH149" t="n">
-        <v>4.919315259405041</v>
+        <v>4.919315246767131</v>
       </c>
       <c r="CI149" t="n">
         <v>3</v>
@@ -57200,10 +57204,10 @@
         <v>3.6</v>
       </c>
       <c r="CL149" t="n">
-        <v>-51.91284966245802</v>
+        <v>-51.91284978599574</v>
       </c>
       <c r="CM149" t="n">
-        <v>-40.6047267210952</v>
+        <v>-40.60472685059801</v>
       </c>
       <c r="CN149" t="inlineStr">
         <is>
@@ -57384,13 +57388,13 @@
         <v>1</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS150" t="b">
         <v>1</v>
       </c>
       <c r="AT150" t="n">
-        <v>48699994112</v>
+        <v>48513810432</v>
       </c>
       <c r="AU150" t="n">
         <v>51.22</v>
@@ -57454,13 +57458,13 @@
         <v>34.87</v>
       </c>
       <c r="BP150" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="BQ150" t="n">
         <v>27.59</v>
       </c>
       <c r="BR150" t="n">
-        <v>81.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS150" t="n">
         <v>-8.1</v>
@@ -57469,10 +57473,10 @@
         <v>-1.6</v>
       </c>
       <c r="BU150" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BV150" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BW150" t="n">
         <v>25.36000061035156</v>
@@ -57784,22 +57788,22 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="BT151" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="BU151" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BV151" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BW151" t="n">
         <v>14.77999973297119</v>
       </c>
       <c r="BX151" t="n">
-        <v>3.780435849624868</v>
+        <v>3.780435864612392</v>
       </c>
       <c r="BY151" t="n">
-        <v>5.504314597053808</v>
+        <v>5.504314618875643</v>
       </c>
       <c r="BZ151" t="inlineStr"/>
       <c r="CA151" t="inlineStr"/>
@@ -57810,7 +57814,7 @@
         <v>5.063572783384453</v>
       </c>
       <c r="CF151" t="n">
-        <v>4.782774410021043</v>
+        <v>4.782774422290829</v>
       </c>
       <c r="CG151" t="n">
         <v>5.063572783384453</v>
@@ -57831,7 +57835,7 @@
         <v>-69.16633567401371</v>
       </c>
       <c r="CM151" t="n">
-        <v>-67.64022668179324</v>
+        <v>-67.64022659877709</v>
       </c>
       <c r="CN151" t="inlineStr">
         <is>
